--- a/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN220"/>
+  <dimension ref="A1:BN238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43125,6 +43125,3280 @@
       <c r="BM220" t="inlineStr"/>
       <c r="BN220" t="inlineStr"/>
     </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>M3h3GWnS</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="n">
+        <v>45522.6875</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>26020</v>
+      </c>
+      <c r="F221" t="n">
+        <v>23010</v>
+      </c>
+      <c r="G221" t="n">
+        <v>1</v>
+      </c>
+      <c r="H221" t="n">
+        <v>1</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="K221" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M221" t="n">
+        <v>33</v>
+      </c>
+      <c r="N221" t="n">
+        <v>67</v>
+      </c>
+      <c r="O221" t="n">
+        <v>12</v>
+      </c>
+      <c r="P221" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>5</v>
+      </c>
+      <c r="R221" t="n">
+        <v>4</v>
+      </c>
+      <c r="S221" t="n">
+        <v>11</v>
+      </c>
+      <c r="T221" t="n">
+        <v>6</v>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="W221" t="n">
+        <v>148</v>
+      </c>
+      <c r="X221" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AC221" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>185.1111111111111</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>76.55555555555556</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>12444444.44444444</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>78.44444444444444</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AK221" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AL221" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="AM221" t="n">
+        <v>80850000</v>
+      </c>
+      <c r="AN221" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="AO221" t="n">
+        <v>26.36842105263158</v>
+      </c>
+      <c r="AP221" t="n">
+        <v>182.8947368421053</v>
+      </c>
+      <c r="AQ221" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AR221" t="n">
+        <v>73.73684210526316</v>
+      </c>
+      <c r="AS221" t="n">
+        <v>6868947.368421053</v>
+      </c>
+      <c r="AT221" t="n">
+        <v>76.68421052631579</v>
+      </c>
+      <c r="AU221" t="n">
+        <v>24.52631578947368</v>
+      </c>
+      <c r="AV221" t="n">
+        <v>177.1052631578947</v>
+      </c>
+      <c r="AW221" t="n">
+        <v>2.052631578947369</v>
+      </c>
+      <c r="AX221" t="n">
+        <v>77.89473684210526</v>
+      </c>
+      <c r="AY221" t="n">
+        <v>34988157.89473684</v>
+      </c>
+      <c r="AZ221" t="n">
+        <v>83.36842105263158</v>
+      </c>
+      <c r="BA221" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB221" t="n">
+        <v>172</v>
+      </c>
+      <c r="BC221" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD221" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE221" t="n">
+        <v>69</v>
+      </c>
+      <c r="BF221" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="BG221" t="n">
+        <v>81</v>
+      </c>
+      <c r="BH221" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BI221" t="n">
+        <v>181</v>
+      </c>
+      <c r="BJ221" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BK221" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL221" t="n">
+        <v>168</v>
+      </c>
+      <c r="BM221" t="n">
+        <v>108500000</v>
+      </c>
+      <c r="BN221" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>Eax2EqHs</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="n">
+        <v>45522.58333333334</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F222" t="n">
+        <v>31763</v>
+      </c>
+      <c r="G222" t="n">
+        <v>1</v>
+      </c>
+      <c r="H222" t="n">
+        <v>2</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="K222" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L222" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M222" t="n">
+        <v>66</v>
+      </c>
+      <c r="N222" t="n">
+        <v>34</v>
+      </c>
+      <c r="O222" t="n">
+        <v>11</v>
+      </c>
+      <c r="P222" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>5</v>
+      </c>
+      <c r="R222" t="n">
+        <v>5</v>
+      </c>
+      <c r="S222" t="n">
+        <v>14</v>
+      </c>
+      <c r="T222" t="n">
+        <v>21</v>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="W222" t="n">
+        <v>148</v>
+      </c>
+      <c r="X222" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA222" t="inlineStr"/>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="AC222" t="n">
+        <v>25.88888888888889</v>
+      </c>
+      <c r="AD222" t="n">
+        <v>182</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>1.888888888888889</v>
+      </c>
+      <c r="AF222" t="n">
+        <v>77.66666666666667</v>
+      </c>
+      <c r="AG222" t="n">
+        <v>22555555.55555556</v>
+      </c>
+      <c r="AH222" t="n">
+        <v>81.22222222222223</v>
+      </c>
+      <c r="AI222" t="n">
+        <v>28.125</v>
+      </c>
+      <c r="AJ222" t="n">
+        <v>178.125</v>
+      </c>
+      <c r="AK222" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AL222" t="n">
+        <v>75.125</v>
+      </c>
+      <c r="AM222" t="n">
+        <v>6887500</v>
+      </c>
+      <c r="AN222" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="AO222" t="n">
+        <v>23.125</v>
+      </c>
+      <c r="AP222" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="AQ222" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AR222" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AS222" t="n">
+        <v>17412500</v>
+      </c>
+      <c r="AT222" t="n">
+        <v>81.1875</v>
+      </c>
+      <c r="AU222" t="n">
+        <v>28.06666666666667</v>
+      </c>
+      <c r="AV222" t="n">
+        <v>177.8666666666667</v>
+      </c>
+      <c r="AW222" t="n">
+        <v>1.133333333333333</v>
+      </c>
+      <c r="AX222" t="n">
+        <v>73.86666666666666</v>
+      </c>
+      <c r="AY222" t="n">
+        <v>4980000</v>
+      </c>
+      <c r="AZ222" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="BA222" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB222" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="BC222" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BD222" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE222" t="n">
+        <v>314</v>
+      </c>
+      <c r="BF222" t="n">
+        <v>89000000</v>
+      </c>
+      <c r="BG222" t="n">
+        <v>329</v>
+      </c>
+      <c r="BH222" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BI222" t="n">
+        <v>181</v>
+      </c>
+      <c r="BJ222" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK222" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL222" t="n">
+        <v>137</v>
+      </c>
+      <c r="BM222" t="n">
+        <v>11550000</v>
+      </c>
+      <c r="BN222" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>KbKTWiX8</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="n">
+        <v>45521.6875</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F223" t="n">
+        <v>46673</v>
+      </c>
+      <c r="G223" t="n">
+        <v>1</v>
+      </c>
+      <c r="H223" t="n">
+        <v>2</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="K223" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L223" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M223" t="n">
+        <v>36</v>
+      </c>
+      <c r="N223" t="n">
+        <v>64</v>
+      </c>
+      <c r="O223" t="n">
+        <v>6</v>
+      </c>
+      <c r="P223" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>1</v>
+      </c>
+      <c r="R223" t="n">
+        <v>8</v>
+      </c>
+      <c r="S223" t="n">
+        <v>11</v>
+      </c>
+      <c r="T223" t="n">
+        <v>13</v>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="W223" t="n">
+        <v>148</v>
+      </c>
+      <c r="X223" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="AC223" t="n">
+        <v>22.125</v>
+      </c>
+      <c r="AD223" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF223" t="n">
+        <v>72</v>
+      </c>
+      <c r="AG223" t="n">
+        <v>11602500</v>
+      </c>
+      <c r="AH223" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="AI223" t="inlineStr"/>
+      <c r="AJ223" t="inlineStr"/>
+      <c r="AK223" t="inlineStr"/>
+      <c r="AL223" t="inlineStr"/>
+      <c r="AM223" t="inlineStr"/>
+      <c r="AN223" t="inlineStr"/>
+      <c r="AO223" t="n">
+        <v>23.625</v>
+      </c>
+      <c r="AP223" t="n">
+        <v>178.875</v>
+      </c>
+      <c r="AQ223" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AR223" t="n">
+        <v>69.4375</v>
+      </c>
+      <c r="AS223" t="n">
+        <v>4559062.5</v>
+      </c>
+      <c r="AT223" t="n">
+        <v>76.1875</v>
+      </c>
+      <c r="AU223" t="n">
+        <v>21.3125</v>
+      </c>
+      <c r="AV223" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AW223" t="n">
+        <v>1.6875</v>
+      </c>
+      <c r="AX223" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="AY223" t="n">
+        <v>31759375</v>
+      </c>
+      <c r="AZ223" t="n">
+        <v>82.125</v>
+      </c>
+      <c r="BA223" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="BB223" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="BC223" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BD223" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE223" t="n">
+        <v>376</v>
+      </c>
+      <c r="BF223" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="BG223" t="n">
+        <v>388</v>
+      </c>
+      <c r="BH223" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="BI223" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="BJ223" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK223" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL223" t="n">
+        <v>397</v>
+      </c>
+      <c r="BM223" t="n">
+        <v>257600000</v>
+      </c>
+      <c r="BN223" t="n">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>ruUIA1G6</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F224" t="n">
+        <v>19561</v>
+      </c>
+      <c r="G224" t="n">
+        <v>1</v>
+      </c>
+      <c r="H224" t="n">
+        <v>1</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="K224" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L224" t="n">
+        <v>1</v>
+      </c>
+      <c r="M224" t="n">
+        <v>61</v>
+      </c>
+      <c r="N224" t="n">
+        <v>39</v>
+      </c>
+      <c r="O224" t="n">
+        <v>16</v>
+      </c>
+      <c r="P224" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>5</v>
+      </c>
+      <c r="R224" t="n">
+        <v>4</v>
+      </c>
+      <c r="S224" t="n">
+        <v>14</v>
+      </c>
+      <c r="T224" t="n">
+        <v>12</v>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="W224" t="n">
+        <v>148</v>
+      </c>
+      <c r="X224" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA224" t="inlineStr"/>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr"/>
+      <c r="AD224" t="inlineStr"/>
+      <c r="AE224" t="inlineStr"/>
+      <c r="AF224" t="inlineStr"/>
+      <c r="AG224" t="inlineStr"/>
+      <c r="AH224" t="inlineStr"/>
+      <c r="AI224" t="inlineStr"/>
+      <c r="AJ224" t="inlineStr"/>
+      <c r="AK224" t="inlineStr"/>
+      <c r="AL224" t="inlineStr"/>
+      <c r="AM224" t="inlineStr"/>
+      <c r="AN224" t="inlineStr"/>
+      <c r="AO224" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="AP224" t="n">
+        <v>177.875</v>
+      </c>
+      <c r="AQ224" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR224" t="n">
+        <v>72.3125</v>
+      </c>
+      <c r="AS224" t="n">
+        <v>7870312.5</v>
+      </c>
+      <c r="AT224" t="n">
+        <v>78.1875</v>
+      </c>
+      <c r="AU224" t="n">
+        <v>25.21052631578947</v>
+      </c>
+      <c r="AV224" t="n">
+        <v>183.6315789473684</v>
+      </c>
+      <c r="AW224" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AX224" t="n">
+        <v>71.05263157894737</v>
+      </c>
+      <c r="AY224" t="n">
+        <v>5059210.52631579</v>
+      </c>
+      <c r="AZ224" t="n">
+        <v>74.94736842105263</v>
+      </c>
+      <c r="BA224" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB224" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="BC224" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD224" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE224" t="n">
+        <v>145</v>
+      </c>
+      <c r="BF224" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="BG224" t="n">
+        <v>145</v>
+      </c>
+      <c r="BH224" t="inlineStr"/>
+      <c r="BI224" t="inlineStr"/>
+      <c r="BJ224" t="inlineStr"/>
+      <c r="BK224" t="inlineStr"/>
+      <c r="BL224" t="inlineStr"/>
+      <c r="BM224" t="inlineStr"/>
+      <c r="BN224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>hnqZAAAk</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="n">
+        <v>45520.6875</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F225" t="n">
+        <v>24843</v>
+      </c>
+      <c r="G225" t="n">
+        <v>2</v>
+      </c>
+      <c r="H225" t="n">
+        <v>2</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="K225" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L225" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M225" t="n">
+        <v>48</v>
+      </c>
+      <c r="N225" t="n">
+        <v>52</v>
+      </c>
+      <c r="O225" t="n">
+        <v>15</v>
+      </c>
+      <c r="P225" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>5</v>
+      </c>
+      <c r="R225" t="n">
+        <v>5</v>
+      </c>
+      <c r="S225" t="n">
+        <v>14</v>
+      </c>
+      <c r="T225" t="n">
+        <v>15</v>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="W225" t="n">
+        <v>148</v>
+      </c>
+      <c r="X225" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z225" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr"/>
+      <c r="AD225" t="inlineStr"/>
+      <c r="AE225" t="inlineStr"/>
+      <c r="AF225" t="inlineStr"/>
+      <c r="AG225" t="inlineStr"/>
+      <c r="AH225" t="inlineStr"/>
+      <c r="AI225" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="AJ225" t="n">
+        <v>185.5555555555555</v>
+      </c>
+      <c r="AK225" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AL225" t="n">
+        <v>75.11111111111111</v>
+      </c>
+      <c r="AM225" t="n">
+        <v>10622222.22222222</v>
+      </c>
+      <c r="AN225" t="n">
+        <v>79.44444444444444</v>
+      </c>
+      <c r="AO225" t="n">
+        <v>25.27272727272727</v>
+      </c>
+      <c r="AP225" t="n">
+        <v>177</v>
+      </c>
+      <c r="AQ225" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AR225" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AS225" t="n">
+        <v>6627272.727272728</v>
+      </c>
+      <c r="AT225" t="n">
+        <v>75.90909090909091</v>
+      </c>
+      <c r="AU225" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AV225" t="n">
+        <v>179</v>
+      </c>
+      <c r="AW225" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="AX225" t="n">
+        <v>75.88888888888889</v>
+      </c>
+      <c r="AY225" t="n">
+        <v>10522222.22222222</v>
+      </c>
+      <c r="AZ225" t="n">
+        <v>81</v>
+      </c>
+      <c r="BA225" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="BB225" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="BC225" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD225" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE225" t="n">
+        <v>291</v>
+      </c>
+      <c r="BF225" t="n">
+        <v>17700000</v>
+      </c>
+      <c r="BG225" t="n">
+        <v>294</v>
+      </c>
+      <c r="BH225" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI225" t="n">
+        <v>184</v>
+      </c>
+      <c r="BJ225" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK225" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL225" t="n">
+        <v>80</v>
+      </c>
+      <c r="BM225" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="BN225" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="n">
+        <v>45520.58333333334</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F226" t="n">
+        <v>22477</v>
+      </c>
+      <c r="G226" t="n">
+        <v>2</v>
+      </c>
+      <c r="H226" t="n">
+        <v>1</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="K226" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L226" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M226" t="n">
+        <v>64</v>
+      </c>
+      <c r="N226" t="n">
+        <v>36</v>
+      </c>
+      <c r="O226" t="n">
+        <v>6</v>
+      </c>
+      <c r="P226" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>4</v>
+      </c>
+      <c r="R226" t="n">
+        <v>2</v>
+      </c>
+      <c r="S226" t="n">
+        <v>8</v>
+      </c>
+      <c r="T226" t="n">
+        <v>23</v>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="W226" t="n">
+        <v>148</v>
+      </c>
+      <c r="X226" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr"/>
+      <c r="AC226" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="AD226" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF226" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AG226" t="n">
+        <v>8650000</v>
+      </c>
+      <c r="AH226" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="AI226" t="inlineStr"/>
+      <c r="AJ226" t="inlineStr"/>
+      <c r="AK226" t="inlineStr"/>
+      <c r="AL226" t="inlineStr"/>
+      <c r="AM226" t="inlineStr"/>
+      <c r="AN226" t="inlineStr"/>
+      <c r="AO226" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AP226" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AQ226" t="n">
+        <v>1.277777777777778</v>
+      </c>
+      <c r="AR226" t="n">
+        <v>72.77777777777777</v>
+      </c>
+      <c r="AS226" t="n">
+        <v>9987500</v>
+      </c>
+      <c r="AT226" t="n">
+        <v>76.77777777777777</v>
+      </c>
+      <c r="AU226" t="n">
+        <v>24.26315789473684</v>
+      </c>
+      <c r="AV226" t="n">
+        <v>180.6842105263158</v>
+      </c>
+      <c r="AW226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX226" t="n">
+        <v>71.05263157894737</v>
+      </c>
+      <c r="AY226" t="n">
+        <v>3814473.684210526</v>
+      </c>
+      <c r="AZ226" t="n">
+        <v>75.94736842105263</v>
+      </c>
+      <c r="BA226" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="BB226" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="BC226" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD226" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE226" t="n">
+        <v>151</v>
+      </c>
+      <c r="BF226" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="BG226" t="n">
+        <v>154</v>
+      </c>
+      <c r="BH226" t="inlineStr"/>
+      <c r="BI226" t="inlineStr"/>
+      <c r="BJ226" t="inlineStr"/>
+      <c r="BK226" t="inlineStr"/>
+      <c r="BL226" t="inlineStr"/>
+      <c r="BM226" t="inlineStr"/>
+      <c r="BN226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="n">
+        <v>45519.6875</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F227" t="n">
+        <v>54084</v>
+      </c>
+      <c r="G227" t="n">
+        <v>1</v>
+      </c>
+      <c r="H227" t="n">
+        <v>1</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="K227" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L227" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M227" t="n">
+        <v>39</v>
+      </c>
+      <c r="N227" t="n">
+        <v>61</v>
+      </c>
+      <c r="O227" t="n">
+        <v>19</v>
+      </c>
+      <c r="P227" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>4</v>
+      </c>
+      <c r="R227" t="n">
+        <v>2</v>
+      </c>
+      <c r="S227" t="n">
+        <v>11</v>
+      </c>
+      <c r="T227" t="n">
+        <v>7</v>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="W227" t="n">
+        <v>148</v>
+      </c>
+      <c r="X227" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr"/>
+      <c r="AD227" t="inlineStr"/>
+      <c r="AE227" t="inlineStr"/>
+      <c r="AF227" t="inlineStr"/>
+      <c r="AG227" t="inlineStr"/>
+      <c r="AH227" t="inlineStr"/>
+      <c r="AI227" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="AJ227" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="AK227" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL227" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="AM227" t="n">
+        <v>17512500</v>
+      </c>
+      <c r="AN227" t="n">
+        <v>81.375</v>
+      </c>
+      <c r="AO227" t="n">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="AP227" t="n">
+        <v>185</v>
+      </c>
+      <c r="AQ227" t="n">
+        <v>1.307692307692308</v>
+      </c>
+      <c r="AR227" t="n">
+        <v>72.76923076923077</v>
+      </c>
+      <c r="AS227" t="n">
+        <v>6384615.384615385</v>
+      </c>
+      <c r="AT227" t="n">
+        <v>79.92307692307692</v>
+      </c>
+      <c r="AU227" t="n">
+        <v>24.35714285714286</v>
+      </c>
+      <c r="AV227" t="n">
+        <v>180.9285714285714</v>
+      </c>
+      <c r="AW227" t="n">
+        <v>1.214285714285714</v>
+      </c>
+      <c r="AX227" t="n">
+        <v>70.71428571428571</v>
+      </c>
+      <c r="AY227" t="n">
+        <v>4835714.285714285</v>
+      </c>
+      <c r="AZ227" t="n">
+        <v>79.14285714285714</v>
+      </c>
+      <c r="BA227" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB227" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="BC227" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD227" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE227" t="n">
+        <v>216</v>
+      </c>
+      <c r="BF227" t="n">
+        <v>26650000</v>
+      </c>
+      <c r="BG227" t="n">
+        <v>230</v>
+      </c>
+      <c r="BH227" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="BI227" t="n">
+        <v>177.6</v>
+      </c>
+      <c r="BJ227" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BK227" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL227" t="n">
+        <v>358</v>
+      </c>
+      <c r="BM227" t="n">
+        <v>61400000</v>
+      </c>
+      <c r="BN227" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>hO0nKEm3</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="n">
+        <v>45519.58333333334</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F228" t="n">
+        <v>47845</v>
+      </c>
+      <c r="G228" t="n">
+        <v>1</v>
+      </c>
+      <c r="H228" t="n">
+        <v>1</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="K228" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L228" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="M228" t="n">
+        <v>69</v>
+      </c>
+      <c r="N228" t="n">
+        <v>31</v>
+      </c>
+      <c r="O228" t="n">
+        <v>7</v>
+      </c>
+      <c r="P228" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>4</v>
+      </c>
+      <c r="R228" t="n">
+        <v>2</v>
+      </c>
+      <c r="S228" t="n">
+        <v>15</v>
+      </c>
+      <c r="T228" t="n">
+        <v>12</v>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="W228" t="n">
+        <v>148</v>
+      </c>
+      <c r="X228" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA228" t="inlineStr"/>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="AC228" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="AD228" t="n">
+        <v>185</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="AF228" t="n">
+        <v>77.11111111111111</v>
+      </c>
+      <c r="AG228" t="n">
+        <v>18277777.77777778</v>
+      </c>
+      <c r="AH228" t="n">
+        <v>80.77777777777777</v>
+      </c>
+      <c r="AI228" t="n">
+        <v>26.77777777777778</v>
+      </c>
+      <c r="AJ228" t="n">
+        <v>179.8888888888889</v>
+      </c>
+      <c r="AK228" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AL228" t="n">
+        <v>74.66666666666667</v>
+      </c>
+      <c r="AM228" t="n">
+        <v>9352777.777777778</v>
+      </c>
+      <c r="AN228" t="n">
+        <v>77.33333333333333</v>
+      </c>
+      <c r="AO228" t="n">
+        <v>23.89473684210526</v>
+      </c>
+      <c r="AP228" t="n">
+        <v>182.2105263157895</v>
+      </c>
+      <c r="AQ228" t="n">
+        <v>1.473684210526316</v>
+      </c>
+      <c r="AR228" t="n">
+        <v>76.15789473684211</v>
+      </c>
+      <c r="AS228" t="n">
+        <v>17563157.89473684</v>
+      </c>
+      <c r="AT228" t="n">
+        <v>81.42105263157895</v>
+      </c>
+      <c r="AU228" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AV228" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="AW228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX228" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AY228" t="n">
+        <v>5260000</v>
+      </c>
+      <c r="AZ228" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="BA228" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="BB228" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BC228" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD228" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE228" t="n">
+        <v>310</v>
+      </c>
+      <c r="BF228" t="n">
+        <v>82500000</v>
+      </c>
+      <c r="BG228" t="n">
+        <v>330</v>
+      </c>
+      <c r="BH228" t="n">
+        <v>26</v>
+      </c>
+      <c r="BI228" t="n">
+        <v>182</v>
+      </c>
+      <c r="BJ228" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK228" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL228" t="n">
+        <v>78</v>
+      </c>
+      <c r="BM228" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="BN228" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>hIsKeIld</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="n">
+        <v>45522.60416666666</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de aza m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el plantio
+  burgos </t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>12194</v>
+      </c>
+      <c r="F229" t="n">
+        <v>9642</v>
+      </c>
+      <c r="G229" t="n">
+        <v>3</v>
+      </c>
+      <c r="H229" t="n">
+        <v>1</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="n">
+        <v>56</v>
+      </c>
+      <c r="N229" t="n">
+        <v>44</v>
+      </c>
+      <c r="O229" t="n">
+        <v>12</v>
+      </c>
+      <c r="P229" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>6</v>
+      </c>
+      <c r="R229" t="n">
+        <v>3</v>
+      </c>
+      <c r="S229" t="n">
+        <v>13</v>
+      </c>
+      <c r="T229" t="n">
+        <v>19</v>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>l6JQtDqc</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>M1vEw5An</t>
+        </is>
+      </c>
+      <c r="W229" t="n">
+        <v>148</v>
+      </c>
+      <c r="X229" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z229" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA229" t="inlineStr"/>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr"/>
+      <c r="AD229" t="inlineStr"/>
+      <c r="AE229" t="inlineStr"/>
+      <c r="AF229" t="inlineStr"/>
+      <c r="AG229" t="inlineStr"/>
+      <c r="AH229" t="inlineStr"/>
+      <c r="AI229" t="inlineStr"/>
+      <c r="AJ229" t="inlineStr"/>
+      <c r="AK229" t="inlineStr"/>
+      <c r="AL229" t="inlineStr"/>
+      <c r="AM229" t="inlineStr"/>
+      <c r="AN229" t="inlineStr"/>
+      <c r="AO229" t="n">
+        <v>22.625</v>
+      </c>
+      <c r="AP229" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="AQ229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR229" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="AS229" t="n">
+        <v>1884375</v>
+      </c>
+      <c r="AT229" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="AU229" t="n">
+        <v>25.16666666666667</v>
+      </c>
+      <c r="AV229" t="n">
+        <v>181</v>
+      </c>
+      <c r="AW229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX229" t="n">
+        <v>65</v>
+      </c>
+      <c r="AY229" t="n">
+        <v>858333.3333333334</v>
+      </c>
+      <c r="AZ229" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="BA229" t="inlineStr"/>
+      <c r="BB229" t="inlineStr"/>
+      <c r="BC229" t="inlineStr"/>
+      <c r="BD229" t="inlineStr"/>
+      <c r="BE229" t="inlineStr"/>
+      <c r="BF229" t="inlineStr"/>
+      <c r="BG229" t="inlineStr"/>
+      <c r="BH229" t="inlineStr"/>
+      <c r="BI229" t="inlineStr"/>
+      <c r="BJ229" t="inlineStr"/>
+      <c r="BK229" t="inlineStr"/>
+      <c r="BL229" t="inlineStr"/>
+      <c r="BM229" t="inlineStr"/>
+      <c r="BN229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>nigFFwtS</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="n">
+        <v>45522.60416666666</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">palencia caballero d 
+  esp </t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio manuel martinez valero
+  elche </t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>31388</v>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>1</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="n">
+        <v>71</v>
+      </c>
+      <c r="N230" t="n">
+        <v>29</v>
+      </c>
+      <c r="O230" t="n">
+        <v>12</v>
+      </c>
+      <c r="P230" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>3</v>
+      </c>
+      <c r="R230" t="n">
+        <v>3</v>
+      </c>
+      <c r="S230" t="n">
+        <v>16</v>
+      </c>
+      <c r="T230" t="n">
+        <v>18</v>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>zT9gi7i9</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="W230" t="n">
+        <v>148</v>
+      </c>
+      <c r="X230" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z230" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr"/>
+      <c r="AD230" t="inlineStr"/>
+      <c r="AE230" t="inlineStr"/>
+      <c r="AF230" t="inlineStr"/>
+      <c r="AG230" t="inlineStr"/>
+      <c r="AH230" t="inlineStr"/>
+      <c r="AI230" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ230" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="AK230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL230" t="n">
+        <v>67.875</v>
+      </c>
+      <c r="AM230" t="n">
+        <v>1365625</v>
+      </c>
+      <c r="AN230" t="n">
+        <v>70.625</v>
+      </c>
+      <c r="AO230" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AP230" t="n">
+        <v>179.1333333333333</v>
+      </c>
+      <c r="AQ230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR230" t="n">
+        <v>67.93333333333334</v>
+      </c>
+      <c r="AS230" t="n">
+        <v>1441666.666666667</v>
+      </c>
+      <c r="AT230" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AU230" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV230" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="AW230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX230" t="n">
+        <v>65.66666666666667</v>
+      </c>
+      <c r="AY230" t="n">
+        <v>1277777.777777778</v>
+      </c>
+      <c r="AZ230" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="BA230" t="inlineStr"/>
+      <c r="BB230" t="inlineStr"/>
+      <c r="BC230" t="inlineStr"/>
+      <c r="BD230" t="inlineStr"/>
+      <c r="BE230" t="inlineStr"/>
+      <c r="BF230" t="inlineStr"/>
+      <c r="BG230" t="inlineStr"/>
+      <c r="BH230" t="inlineStr"/>
+      <c r="BI230" t="inlineStr"/>
+      <c r="BJ230" t="inlineStr"/>
+      <c r="BK230" t="inlineStr"/>
+      <c r="BL230" t="inlineStr"/>
+      <c r="BM230" t="inlineStr"/>
+      <c r="BN230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>0I1yLYH7</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guzman mansilla j  l 
+  esp </t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el molinon
+  gijon </t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>29029</v>
+      </c>
+      <c r="F231" t="n">
+        <v>23319</v>
+      </c>
+      <c r="G231" t="n">
+        <v>1</v>
+      </c>
+      <c r="H231" t="n">
+        <v>2</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="n">
+        <v>66</v>
+      </c>
+      <c r="N231" t="n">
+        <v>34</v>
+      </c>
+      <c r="O231" t="n">
+        <v>11</v>
+      </c>
+      <c r="P231" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>1</v>
+      </c>
+      <c r="R231" t="n">
+        <v>5</v>
+      </c>
+      <c r="S231" t="n">
+        <v>15</v>
+      </c>
+      <c r="T231" t="n">
+        <v>16</v>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>fiZxGYJ3</t>
+        </is>
+      </c>
+      <c r="W231" t="n">
+        <v>148</v>
+      </c>
+      <c r="X231" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z231" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA231" t="inlineStr"/>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="AC231" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="AD231" t="n">
+        <v>179.1111111111111</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF231" t="n">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="AG231" t="n">
+        <v>2372222.222222222</v>
+      </c>
+      <c r="AH231" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AI231" t="inlineStr"/>
+      <c r="AJ231" t="inlineStr"/>
+      <c r="AK231" t="inlineStr"/>
+      <c r="AL231" t="inlineStr"/>
+      <c r="AM231" t="inlineStr"/>
+      <c r="AN231" t="inlineStr"/>
+      <c r="AO231" t="n">
+        <v>24.18181818181818</v>
+      </c>
+      <c r="AP231" t="n">
+        <v>177.3636363636364</v>
+      </c>
+      <c r="AQ231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR231" t="n">
+        <v>67.63636363636364</v>
+      </c>
+      <c r="AS231" t="n">
+        <v>1788636.363636364</v>
+      </c>
+      <c r="AT231" t="n">
+        <v>74.27272727272727</v>
+      </c>
+      <c r="AU231" t="n">
+        <v>23</v>
+      </c>
+      <c r="AV231" t="n">
+        <v>177.5833333333333</v>
+      </c>
+      <c r="AW231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX231" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AY231" t="n">
+        <v>1983333.333333333</v>
+      </c>
+      <c r="AZ231" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="BA231" t="inlineStr"/>
+      <c r="BB231" t="inlineStr"/>
+      <c r="BC231" t="inlineStr"/>
+      <c r="BD231" t="inlineStr"/>
+      <c r="BE231" t="inlineStr"/>
+      <c r="BF231" t="inlineStr"/>
+      <c r="BG231" t="inlineStr"/>
+      <c r="BH231" t="inlineStr"/>
+      <c r="BI231" t="inlineStr"/>
+      <c r="BJ231" t="inlineStr"/>
+      <c r="BK231" t="inlineStr"/>
+      <c r="BL231" t="inlineStr"/>
+      <c r="BM231" t="inlineStr"/>
+      <c r="BN231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>0fJlUxeL</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moreno a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sardinero
+  santander </t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>22222</v>
+      </c>
+      <c r="F232" t="n">
+        <v>19697</v>
+      </c>
+      <c r="G232" t="n">
+        <v>2</v>
+      </c>
+      <c r="H232" t="n">
+        <v>2</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="n">
+        <v>36</v>
+      </c>
+      <c r="N232" t="n">
+        <v>64</v>
+      </c>
+      <c r="O232" t="n">
+        <v>12</v>
+      </c>
+      <c r="P232" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>5</v>
+      </c>
+      <c r="R232" t="n">
+        <v>9</v>
+      </c>
+      <c r="S232" t="n">
+        <v>18</v>
+      </c>
+      <c r="T232" t="n">
+        <v>15</v>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>rak12p9n</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="W232" t="n">
+        <v>148</v>
+      </c>
+      <c r="X232" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA232" t="inlineStr"/>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr"/>
+      <c r="AD232" t="inlineStr"/>
+      <c r="AE232" t="inlineStr"/>
+      <c r="AF232" t="inlineStr"/>
+      <c r="AG232" t="inlineStr"/>
+      <c r="AH232" t="inlineStr"/>
+      <c r="AI232" t="inlineStr"/>
+      <c r="AJ232" t="inlineStr"/>
+      <c r="AK232" t="inlineStr"/>
+      <c r="AL232" t="inlineStr"/>
+      <c r="AM232" t="inlineStr"/>
+      <c r="AN232" t="inlineStr"/>
+      <c r="AO232" t="n">
+        <v>26.47058823529412</v>
+      </c>
+      <c r="AP232" t="n">
+        <v>180.6470588235294</v>
+      </c>
+      <c r="AQ232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR232" t="n">
+        <v>66.88235294117646</v>
+      </c>
+      <c r="AS232" t="n">
+        <v>1427941.176470588</v>
+      </c>
+      <c r="AT232" t="n">
+        <v>72.64705882352941</v>
+      </c>
+      <c r="AU232" t="n">
+        <v>22.57142857142857</v>
+      </c>
+      <c r="AV232" t="n">
+        <v>184.7619047619048</v>
+      </c>
+      <c r="AW232" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AX232" t="n">
+        <v>69.0952380952381</v>
+      </c>
+      <c r="AY232" t="n">
+        <v>3557142.857142857</v>
+      </c>
+      <c r="AZ232" t="n">
+        <v>76.42857142857143</v>
+      </c>
+      <c r="BA232" t="inlineStr"/>
+      <c r="BB232" t="inlineStr"/>
+      <c r="BC232" t="inlineStr"/>
+      <c r="BD232" t="inlineStr"/>
+      <c r="BE232" t="inlineStr"/>
+      <c r="BF232" t="inlineStr"/>
+      <c r="BG232" t="inlineStr"/>
+      <c r="BH232" t="inlineStr"/>
+      <c r="BI232" t="inlineStr"/>
+      <c r="BJ232" t="inlineStr"/>
+      <c r="BK232" t="inlineStr"/>
+      <c r="BL232" t="inlineStr"/>
+      <c r="BM232" t="inlineStr"/>
+      <c r="BN232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>tvOEHaBF</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lax franco s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de riazor
+  la coruna </t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>34889</v>
+      </c>
+      <c r="F233" t="n">
+        <v>25715</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>1</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="n">
+        <v>66</v>
+      </c>
+      <c r="N233" t="n">
+        <v>34</v>
+      </c>
+      <c r="O233" t="n">
+        <v>17</v>
+      </c>
+      <c r="P233" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>7</v>
+      </c>
+      <c r="R233" t="n">
+        <v>4</v>
+      </c>
+      <c r="S233" t="n">
+        <v>9</v>
+      </c>
+      <c r="T233" t="n">
+        <v>22</v>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="W233" t="n">
+        <v>148</v>
+      </c>
+      <c r="X233" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA233" t="inlineStr"/>
+      <c r="AB233" t="inlineStr"/>
+      <c r="AC233" t="inlineStr"/>
+      <c r="AD233" t="inlineStr"/>
+      <c r="AE233" t="inlineStr"/>
+      <c r="AF233" t="inlineStr"/>
+      <c r="AG233" t="inlineStr"/>
+      <c r="AH233" t="inlineStr"/>
+      <c r="AI233" t="inlineStr"/>
+      <c r="AJ233" t="inlineStr"/>
+      <c r="AK233" t="inlineStr"/>
+      <c r="AL233" t="inlineStr"/>
+      <c r="AM233" t="inlineStr"/>
+      <c r="AN233" t="inlineStr"/>
+      <c r="AO233" t="inlineStr"/>
+      <c r="AP233" t="inlineStr"/>
+      <c r="AQ233" t="inlineStr"/>
+      <c r="AR233" t="inlineStr"/>
+      <c r="AS233" t="inlineStr"/>
+      <c r="AT233" t="inlineStr"/>
+      <c r="AU233" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="AV233" t="n">
+        <v>177.55</v>
+      </c>
+      <c r="AW233" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AX233" t="n">
+        <v>69</v>
+      </c>
+      <c r="AY233" t="n">
+        <v>2176250</v>
+      </c>
+      <c r="AZ233" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="BA233" t="inlineStr"/>
+      <c r="BB233" t="inlineStr"/>
+      <c r="BC233" t="inlineStr"/>
+      <c r="BD233" t="inlineStr"/>
+      <c r="BE233" t="inlineStr"/>
+      <c r="BF233" t="inlineStr"/>
+      <c r="BG233" t="inlineStr"/>
+      <c r="BH233" t="inlineStr"/>
+      <c r="BI233" t="inlineStr"/>
+      <c r="BJ233" t="inlineStr"/>
+      <c r="BK233" t="inlineStr"/>
+      <c r="BL233" t="inlineStr"/>
+      <c r="BM233" t="inlineStr"/>
+      <c r="BN233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>dQ4KOGIr</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mallo e 
+  esp </t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de ipurua
+  eibar </t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>8164</v>
+      </c>
+      <c r="F234" t="n">
+        <v>3538</v>
+      </c>
+      <c r="G234" t="n">
+        <v>1</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="n">
+        <v>37</v>
+      </c>
+      <c r="N234" t="n">
+        <v>63</v>
+      </c>
+      <c r="O234" t="n">
+        <v>9</v>
+      </c>
+      <c r="P234" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>3</v>
+      </c>
+      <c r="R234" t="n">
+        <v>4</v>
+      </c>
+      <c r="S234" t="n">
+        <v>17</v>
+      </c>
+      <c r="T234" t="n">
+        <v>9</v>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="W234" t="n">
+        <v>148</v>
+      </c>
+      <c r="X234" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z234" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr"/>
+      <c r="AC234" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="AD234" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF234" t="n">
+        <v>68</v>
+      </c>
+      <c r="AG234" t="n">
+        <v>1625000</v>
+      </c>
+      <c r="AH234" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AI234" t="inlineStr"/>
+      <c r="AJ234" t="inlineStr"/>
+      <c r="AK234" t="inlineStr"/>
+      <c r="AL234" t="inlineStr"/>
+      <c r="AM234" t="inlineStr"/>
+      <c r="AN234" t="inlineStr"/>
+      <c r="AO234" t="n">
+        <v>24.85714285714286</v>
+      </c>
+      <c r="AP234" t="n">
+        <v>182.7857142857143</v>
+      </c>
+      <c r="AQ234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR234" t="n">
+        <v>66.85714285714286</v>
+      </c>
+      <c r="AS234" t="n">
+        <v>1801785.714285714</v>
+      </c>
+      <c r="AT234" t="n">
+        <v>72.07142857142857</v>
+      </c>
+      <c r="AU234" t="inlineStr"/>
+      <c r="AV234" t="inlineStr"/>
+      <c r="AW234" t="inlineStr"/>
+      <c r="AX234" t="inlineStr"/>
+      <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr"/>
+      <c r="BA234" t="inlineStr"/>
+      <c r="BB234" t="inlineStr"/>
+      <c r="BC234" t="inlineStr"/>
+      <c r="BD234" t="inlineStr"/>
+      <c r="BE234" t="inlineStr"/>
+      <c r="BF234" t="inlineStr"/>
+      <c r="BG234" t="inlineStr"/>
+      <c r="BH234" t="inlineStr"/>
+      <c r="BI234" t="inlineStr"/>
+      <c r="BJ234" t="inlineStr"/>
+      <c r="BK234" t="inlineStr"/>
+      <c r="BL234" t="inlineStr"/>
+      <c r="BM234" t="inlineStr"/>
+      <c r="BN234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>vkYg8eY1</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sesma espinosa m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal da malata
+  ferrol </t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>10450</v>
+      </c>
+      <c r="F235" t="n">
+        <v>7541</v>
+      </c>
+      <c r="G235" t="n">
+        <v>2</v>
+      </c>
+      <c r="H235" t="n">
+        <v>2</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="n">
+        <v>41</v>
+      </c>
+      <c r="N235" t="n">
+        <v>59</v>
+      </c>
+      <c r="O235" t="n">
+        <v>14</v>
+      </c>
+      <c r="P235" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>5</v>
+      </c>
+      <c r="R235" t="n">
+        <v>2</v>
+      </c>
+      <c r="S235" t="n">
+        <v>16</v>
+      </c>
+      <c r="T235" t="n">
+        <v>16</v>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>tjXr7SAp</t>
+        </is>
+      </c>
+      <c r="W235" t="n">
+        <v>148</v>
+      </c>
+      <c r="X235" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z235" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr"/>
+      <c r="AC235" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AD235" t="n">
+        <v>179.125</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF235" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="AG235" t="n">
+        <v>1190625</v>
+      </c>
+      <c r="AH235" t="n">
+        <v>69.875</v>
+      </c>
+      <c r="AI235" t="inlineStr"/>
+      <c r="AJ235" t="inlineStr"/>
+      <c r="AK235" t="inlineStr"/>
+      <c r="AL235" t="inlineStr"/>
+      <c r="AM235" t="inlineStr"/>
+      <c r="AN235" t="inlineStr"/>
+      <c r="AO235" t="n">
+        <v>27.72727272727273</v>
+      </c>
+      <c r="AP235" t="n">
+        <v>178</v>
+      </c>
+      <c r="AQ235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR235" t="n">
+        <v>66.54545454545455</v>
+      </c>
+      <c r="AS235" t="n">
+        <v>959090.9090909091</v>
+      </c>
+      <c r="AT235" t="n">
+        <v>68.63636363636364</v>
+      </c>
+      <c r="AU235" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="AV235" t="n">
+        <v>181.8333333333333</v>
+      </c>
+      <c r="AW235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX235" t="n">
+        <v>64.16666666666667</v>
+      </c>
+      <c r="AY235" t="n">
+        <v>1391666.666666667</v>
+      </c>
+      <c r="AZ235" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="BA235" t="inlineStr"/>
+      <c r="BB235" t="inlineStr"/>
+      <c r="BC235" t="inlineStr"/>
+      <c r="BD235" t="inlineStr"/>
+      <c r="BE235" t="inlineStr"/>
+      <c r="BF235" t="inlineStr"/>
+      <c r="BG235" t="inlineStr"/>
+      <c r="BH235" t="inlineStr"/>
+      <c r="BI235" t="inlineStr"/>
+      <c r="BJ235" t="inlineStr"/>
+      <c r="BK235" t="inlineStr"/>
+      <c r="BL235" t="inlineStr"/>
+      <c r="BM235" t="inlineStr"/>
+      <c r="BN235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>8QP6JLt3</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="n">
+        <v>45520.6875</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">monescillo d 
+  esp </t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo mirandilla
+  cadiz </t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>20776</v>
+      </c>
+      <c r="F236" t="n">
+        <v>16970</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>4</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="n">
+        <v>62</v>
+      </c>
+      <c r="N236" t="n">
+        <v>38</v>
+      </c>
+      <c r="O236" t="n">
+        <v>13</v>
+      </c>
+      <c r="P236" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>3</v>
+      </c>
+      <c r="R236" t="n">
+        <v>9</v>
+      </c>
+      <c r="S236" t="n">
+        <v>14</v>
+      </c>
+      <c r="T236" t="n">
+        <v>21</v>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="W236" t="n">
+        <v>148</v>
+      </c>
+      <c r="X236" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z236" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr"/>
+      <c r="AD236" t="inlineStr"/>
+      <c r="AE236" t="inlineStr"/>
+      <c r="AF236" t="inlineStr"/>
+      <c r="AG236" t="inlineStr"/>
+      <c r="AH236" t="inlineStr"/>
+      <c r="AI236" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="AJ236" t="n">
+        <v>175.8888888888889</v>
+      </c>
+      <c r="AK236" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL236" t="n">
+        <v>67.88888888888889</v>
+      </c>
+      <c r="AM236" t="n">
+        <v>1811111.111111111</v>
+      </c>
+      <c r="AN236" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AO236" t="n">
+        <v>25.5625</v>
+      </c>
+      <c r="AP236" t="n">
+        <v>178.8125</v>
+      </c>
+      <c r="AQ236" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AR236" t="n">
+        <v>70</v>
+      </c>
+      <c r="AS236" t="n">
+        <v>3395312.5</v>
+      </c>
+      <c r="AT236" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AU236" t="n">
+        <v>26.38888888888889</v>
+      </c>
+      <c r="AV236" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="AW236" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX236" t="n">
+        <v>69.61111111111111</v>
+      </c>
+      <c r="AY236" t="n">
+        <v>2075000</v>
+      </c>
+      <c r="AZ236" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="BA236" t="inlineStr"/>
+      <c r="BB236" t="inlineStr"/>
+      <c r="BC236" t="inlineStr"/>
+      <c r="BD236" t="inlineStr"/>
+      <c r="BE236" t="inlineStr"/>
+      <c r="BF236" t="inlineStr"/>
+      <c r="BG236" t="inlineStr"/>
+      <c r="BH236" t="inlineStr"/>
+      <c r="BI236" t="inlineStr"/>
+      <c r="BJ236" t="inlineStr"/>
+      <c r="BK236" t="inlineStr"/>
+      <c r="BL236" t="inlineStr"/>
+      <c r="BM236" t="inlineStr"/>
+      <c r="BN236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>hhbTMfme</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="n">
+        <v>45520.58333333334</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzalez diaz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de anduva
+  miranda de ebro </t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>5759</v>
+      </c>
+      <c r="F237" t="n">
+        <v>3005</v>
+      </c>
+      <c r="G237" t="n">
+        <v>1</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="n">
+        <v>32</v>
+      </c>
+      <c r="N237" t="n">
+        <v>68</v>
+      </c>
+      <c r="O237" t="n">
+        <v>3</v>
+      </c>
+      <c r="P237" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>2</v>
+      </c>
+      <c r="R237" t="n">
+        <v>7</v>
+      </c>
+      <c r="S237" t="n">
+        <v>6</v>
+      </c>
+      <c r="T237" t="n">
+        <v>14</v>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="W237" t="n">
+        <v>148</v>
+      </c>
+      <c r="X237" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y237" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z237" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="AB237" t="inlineStr"/>
+      <c r="AC237" t="inlineStr"/>
+      <c r="AD237" t="inlineStr"/>
+      <c r="AE237" t="inlineStr"/>
+      <c r="AF237" t="inlineStr"/>
+      <c r="AG237" t="inlineStr"/>
+      <c r="AH237" t="inlineStr"/>
+      <c r="AI237" t="inlineStr"/>
+      <c r="AJ237" t="inlineStr"/>
+      <c r="AK237" t="inlineStr"/>
+      <c r="AL237" t="inlineStr"/>
+      <c r="AM237" t="inlineStr"/>
+      <c r="AN237" t="inlineStr"/>
+      <c r="AO237" t="inlineStr"/>
+      <c r="AP237" t="inlineStr"/>
+      <c r="AQ237" t="inlineStr"/>
+      <c r="AR237" t="inlineStr"/>
+      <c r="AS237" t="inlineStr"/>
+      <c r="AT237" t="inlineStr"/>
+      <c r="AU237" t="inlineStr"/>
+      <c r="AV237" t="inlineStr"/>
+      <c r="AW237" t="inlineStr"/>
+      <c r="AX237" t="inlineStr"/>
+      <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr"/>
+      <c r="BA237" t="inlineStr"/>
+      <c r="BB237" t="inlineStr"/>
+      <c r="BC237" t="inlineStr"/>
+      <c r="BD237" t="inlineStr"/>
+      <c r="BE237" t="inlineStr"/>
+      <c r="BF237" t="inlineStr"/>
+      <c r="BG237" t="inlineStr"/>
+      <c r="BH237" t="inlineStr"/>
+      <c r="BI237" t="inlineStr"/>
+      <c r="BJ237" t="inlineStr"/>
+      <c r="BK237" t="inlineStr"/>
+      <c r="BL237" t="inlineStr"/>
+      <c r="BM237" t="inlineStr"/>
+      <c r="BN237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>6eQuWbQ8</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="n">
+        <v>45519.64583333334</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reig s  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo los carmenes
+  granada </t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>22524</v>
+      </c>
+      <c r="F238" t="n">
+        <v>13265</v>
+      </c>
+      <c r="G238" t="n">
+        <v>1</v>
+      </c>
+      <c r="H238" t="n">
+        <v>2</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="n">
+        <v>65</v>
+      </c>
+      <c r="N238" t="n">
+        <v>35</v>
+      </c>
+      <c r="O238" t="n">
+        <v>22</v>
+      </c>
+      <c r="P238" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>10</v>
+      </c>
+      <c r="R238" t="n">
+        <v>3</v>
+      </c>
+      <c r="S238" t="n">
+        <v>10</v>
+      </c>
+      <c r="T238" t="n">
+        <v>11</v>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>K4dMCgFa</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="W238" t="n">
+        <v>148</v>
+      </c>
+      <c r="X238" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y238" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z238" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC238" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD238" t="n">
+        <v>178.125</v>
+      </c>
+      <c r="AE238" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF238" t="n">
+        <v>72.625</v>
+      </c>
+      <c r="AG238" t="n">
+        <v>4237500</v>
+      </c>
+      <c r="AH238" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AI238" t="inlineStr"/>
+      <c r="AJ238" t="inlineStr"/>
+      <c r="AK238" t="inlineStr"/>
+      <c r="AL238" t="inlineStr"/>
+      <c r="AM238" t="inlineStr"/>
+      <c r="AN238" t="inlineStr"/>
+      <c r="AO238" t="n">
+        <v>25.13636363636364</v>
+      </c>
+      <c r="AP238" t="n">
+        <v>181.6363636363636</v>
+      </c>
+      <c r="AQ238" t="n">
+        <v>1.136363636363636</v>
+      </c>
+      <c r="AR238" t="n">
+        <v>70.86363636363636</v>
+      </c>
+      <c r="AS238" t="n">
+        <v>3861363.636363636</v>
+      </c>
+      <c r="AT238" t="n">
+        <v>75.31818181818181</v>
+      </c>
+      <c r="AU238" t="n">
+        <v>25.90909090909091</v>
+      </c>
+      <c r="AV238" t="n">
+        <v>180</v>
+      </c>
+      <c r="AW238" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AX238" t="n">
+        <v>66.72727272727273</v>
+      </c>
+      <c r="AY238" t="n">
+        <v>4729545.454545454</v>
+      </c>
+      <c r="AZ238" t="n">
+        <v>70.09090909090909</v>
+      </c>
+      <c r="BA238" t="inlineStr"/>
+      <c r="BB238" t="inlineStr"/>
+      <c r="BC238" t="inlineStr"/>
+      <c r="BD238" t="inlineStr"/>
+      <c r="BE238" t="inlineStr"/>
+      <c r="BF238" t="inlineStr"/>
+      <c r="BG238" t="inlineStr"/>
+      <c r="BH238" t="inlineStr"/>
+      <c r="BI238" t="inlineStr"/>
+      <c r="BJ238" t="inlineStr"/>
+      <c r="BK238" t="inlineStr"/>
+      <c r="BL238" t="inlineStr"/>
+      <c r="BM238" t="inlineStr"/>
+      <c r="BN238" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN220"/>
+  <dimension ref="A1:BN241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43125,6 +43125,3850 @@
       <c r="BM220" t="inlineStr"/>
       <c r="BN220" t="inlineStr"/>
     </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>M3h3GWnS</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="n">
+        <v>45522.6875</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>26020</v>
+      </c>
+      <c r="F221" t="n">
+        <v>23010</v>
+      </c>
+      <c r="G221" t="n">
+        <v>1</v>
+      </c>
+      <c r="H221" t="n">
+        <v>1</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="K221" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M221" t="n">
+        <v>35</v>
+      </c>
+      <c r="N221" t="n">
+        <v>65</v>
+      </c>
+      <c r="O221" t="n">
+        <v>12</v>
+      </c>
+      <c r="P221" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>5</v>
+      </c>
+      <c r="R221" t="n">
+        <v>4</v>
+      </c>
+      <c r="S221" t="n">
+        <v>11</v>
+      </c>
+      <c r="T221" t="n">
+        <v>7</v>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="W221" t="n">
+        <v>148</v>
+      </c>
+      <c r="X221" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AC221" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>185.1111111111111</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>76.55555555555556</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>12444444.44444444</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>78.44444444444444</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AK221" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AL221" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="AM221" t="n">
+        <v>80850000</v>
+      </c>
+      <c r="AN221" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="AO221" t="n">
+        <v>26.36842105263158</v>
+      </c>
+      <c r="AP221" t="n">
+        <v>182.8947368421053</v>
+      </c>
+      <c r="AQ221" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AR221" t="n">
+        <v>73.73684210526316</v>
+      </c>
+      <c r="AS221" t="n">
+        <v>6868947.368421053</v>
+      </c>
+      <c r="AT221" t="n">
+        <v>76.68421052631579</v>
+      </c>
+      <c r="AU221" t="n">
+        <v>24.52631578947368</v>
+      </c>
+      <c r="AV221" t="n">
+        <v>177.1052631578947</v>
+      </c>
+      <c r="AW221" t="n">
+        <v>2.052631578947369</v>
+      </c>
+      <c r="AX221" t="n">
+        <v>77.89473684210526</v>
+      </c>
+      <c r="AY221" t="n">
+        <v>34988157.89473684</v>
+      </c>
+      <c r="AZ221" t="n">
+        <v>83.36842105263158</v>
+      </c>
+      <c r="BA221" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB221" t="n">
+        <v>172</v>
+      </c>
+      <c r="BC221" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD221" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE221" t="n">
+        <v>69</v>
+      </c>
+      <c r="BF221" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="BG221" t="n">
+        <v>81</v>
+      </c>
+      <c r="BH221" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BI221" t="n">
+        <v>181</v>
+      </c>
+      <c r="BJ221" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BK221" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL221" t="n">
+        <v>168</v>
+      </c>
+      <c r="BM221" t="n">
+        <v>108500000</v>
+      </c>
+      <c r="BN221" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>Eax2EqHs</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="n">
+        <v>45522.58333333334</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F222" t="n">
+        <v>31763</v>
+      </c>
+      <c r="G222" t="n">
+        <v>1</v>
+      </c>
+      <c r="H222" t="n">
+        <v>2</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="K222" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L222" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M222" t="n">
+        <v>66</v>
+      </c>
+      <c r="N222" t="n">
+        <v>34</v>
+      </c>
+      <c r="O222" t="n">
+        <v>11</v>
+      </c>
+      <c r="P222" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>5</v>
+      </c>
+      <c r="R222" t="n">
+        <v>5</v>
+      </c>
+      <c r="S222" t="n">
+        <v>14</v>
+      </c>
+      <c r="T222" t="n">
+        <v>21</v>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="W222" t="n">
+        <v>148</v>
+      </c>
+      <c r="X222" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA222" t="inlineStr"/>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="AC222" t="n">
+        <v>25.88888888888889</v>
+      </c>
+      <c r="AD222" t="n">
+        <v>182</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>1.888888888888889</v>
+      </c>
+      <c r="AF222" t="n">
+        <v>77.66666666666667</v>
+      </c>
+      <c r="AG222" t="n">
+        <v>22555555.55555556</v>
+      </c>
+      <c r="AH222" t="n">
+        <v>81.22222222222223</v>
+      </c>
+      <c r="AI222" t="n">
+        <v>28.125</v>
+      </c>
+      <c r="AJ222" t="n">
+        <v>178.125</v>
+      </c>
+      <c r="AK222" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AL222" t="n">
+        <v>75.125</v>
+      </c>
+      <c r="AM222" t="n">
+        <v>6887500</v>
+      </c>
+      <c r="AN222" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="AO222" t="n">
+        <v>23.125</v>
+      </c>
+      <c r="AP222" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="AQ222" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AR222" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AS222" t="n">
+        <v>17412500</v>
+      </c>
+      <c r="AT222" t="n">
+        <v>81.1875</v>
+      </c>
+      <c r="AU222" t="n">
+        <v>28.06666666666667</v>
+      </c>
+      <c r="AV222" t="n">
+        <v>177.8666666666667</v>
+      </c>
+      <c r="AW222" t="n">
+        <v>1.133333333333333</v>
+      </c>
+      <c r="AX222" t="n">
+        <v>73.86666666666666</v>
+      </c>
+      <c r="AY222" t="n">
+        <v>4980000</v>
+      </c>
+      <c r="AZ222" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="BA222" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB222" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="BC222" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BD222" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE222" t="n">
+        <v>314</v>
+      </c>
+      <c r="BF222" t="n">
+        <v>89000000</v>
+      </c>
+      <c r="BG222" t="n">
+        <v>329</v>
+      </c>
+      <c r="BH222" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BI222" t="n">
+        <v>181</v>
+      </c>
+      <c r="BJ222" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK222" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL222" t="n">
+        <v>137</v>
+      </c>
+      <c r="BM222" t="n">
+        <v>11550000</v>
+      </c>
+      <c r="BN222" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>KbKTWiX8</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="n">
+        <v>45521.6875</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F223" t="n">
+        <v>46673</v>
+      </c>
+      <c r="G223" t="n">
+        <v>1</v>
+      </c>
+      <c r="H223" t="n">
+        <v>2</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="K223" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L223" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M223" t="n">
+        <v>36</v>
+      </c>
+      <c r="N223" t="n">
+        <v>64</v>
+      </c>
+      <c r="O223" t="n">
+        <v>6</v>
+      </c>
+      <c r="P223" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>1</v>
+      </c>
+      <c r="R223" t="n">
+        <v>8</v>
+      </c>
+      <c r="S223" t="n">
+        <v>11</v>
+      </c>
+      <c r="T223" t="n">
+        <v>13</v>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="W223" t="n">
+        <v>148</v>
+      </c>
+      <c r="X223" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="AC223" t="n">
+        <v>22.125</v>
+      </c>
+      <c r="AD223" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF223" t="n">
+        <v>72</v>
+      </c>
+      <c r="AG223" t="n">
+        <v>11602500</v>
+      </c>
+      <c r="AH223" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="AI223" t="inlineStr"/>
+      <c r="AJ223" t="inlineStr"/>
+      <c r="AK223" t="inlineStr"/>
+      <c r="AL223" t="inlineStr"/>
+      <c r="AM223" t="inlineStr"/>
+      <c r="AN223" t="inlineStr"/>
+      <c r="AO223" t="n">
+        <v>23.625</v>
+      </c>
+      <c r="AP223" t="n">
+        <v>178.875</v>
+      </c>
+      <c r="AQ223" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AR223" t="n">
+        <v>69.4375</v>
+      </c>
+      <c r="AS223" t="n">
+        <v>4559062.5</v>
+      </c>
+      <c r="AT223" t="n">
+        <v>76.1875</v>
+      </c>
+      <c r="AU223" t="n">
+        <v>21.3125</v>
+      </c>
+      <c r="AV223" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AW223" t="n">
+        <v>1.6875</v>
+      </c>
+      <c r="AX223" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="AY223" t="n">
+        <v>31759375</v>
+      </c>
+      <c r="AZ223" t="n">
+        <v>82.125</v>
+      </c>
+      <c r="BA223" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="BB223" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="BC223" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BD223" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE223" t="n">
+        <v>376</v>
+      </c>
+      <c r="BF223" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="BG223" t="n">
+        <v>388</v>
+      </c>
+      <c r="BH223" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="BI223" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="BJ223" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK223" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL223" t="n">
+        <v>397</v>
+      </c>
+      <c r="BM223" t="n">
+        <v>257600000</v>
+      </c>
+      <c r="BN223" t="n">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>ruUIA1G6</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F224" t="n">
+        <v>19561</v>
+      </c>
+      <c r="G224" t="n">
+        <v>1</v>
+      </c>
+      <c r="H224" t="n">
+        <v>1</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="K224" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L224" t="n">
+        <v>1</v>
+      </c>
+      <c r="M224" t="n">
+        <v>61</v>
+      </c>
+      <c r="N224" t="n">
+        <v>39</v>
+      </c>
+      <c r="O224" t="n">
+        <v>16</v>
+      </c>
+      <c r="P224" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>5</v>
+      </c>
+      <c r="R224" t="n">
+        <v>4</v>
+      </c>
+      <c r="S224" t="n">
+        <v>14</v>
+      </c>
+      <c r="T224" t="n">
+        <v>12</v>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="W224" t="n">
+        <v>148</v>
+      </c>
+      <c r="X224" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA224" t="inlineStr"/>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr"/>
+      <c r="AD224" t="inlineStr"/>
+      <c r="AE224" t="inlineStr"/>
+      <c r="AF224" t="inlineStr"/>
+      <c r="AG224" t="inlineStr"/>
+      <c r="AH224" t="inlineStr"/>
+      <c r="AI224" t="inlineStr"/>
+      <c r="AJ224" t="inlineStr"/>
+      <c r="AK224" t="inlineStr"/>
+      <c r="AL224" t="inlineStr"/>
+      <c r="AM224" t="inlineStr"/>
+      <c r="AN224" t="inlineStr"/>
+      <c r="AO224" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="AP224" t="n">
+        <v>177.875</v>
+      </c>
+      <c r="AQ224" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR224" t="n">
+        <v>72.3125</v>
+      </c>
+      <c r="AS224" t="n">
+        <v>7870312.5</v>
+      </c>
+      <c r="AT224" t="n">
+        <v>78.1875</v>
+      </c>
+      <c r="AU224" t="n">
+        <v>25.21052631578947</v>
+      </c>
+      <c r="AV224" t="n">
+        <v>183.6315789473684</v>
+      </c>
+      <c r="AW224" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AX224" t="n">
+        <v>71.05263157894737</v>
+      </c>
+      <c r="AY224" t="n">
+        <v>5059210.52631579</v>
+      </c>
+      <c r="AZ224" t="n">
+        <v>74.94736842105263</v>
+      </c>
+      <c r="BA224" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB224" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="BC224" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD224" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE224" t="n">
+        <v>145</v>
+      </c>
+      <c r="BF224" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="BG224" t="n">
+        <v>145</v>
+      </c>
+      <c r="BH224" t="inlineStr"/>
+      <c r="BI224" t="inlineStr"/>
+      <c r="BJ224" t="inlineStr"/>
+      <c r="BK224" t="inlineStr"/>
+      <c r="BL224" t="inlineStr"/>
+      <c r="BM224" t="inlineStr"/>
+      <c r="BN224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>hnqZAAAk</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="n">
+        <v>45520.6875</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F225" t="n">
+        <v>24843</v>
+      </c>
+      <c r="G225" t="n">
+        <v>2</v>
+      </c>
+      <c r="H225" t="n">
+        <v>2</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="K225" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L225" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M225" t="n">
+        <v>48</v>
+      </c>
+      <c r="N225" t="n">
+        <v>52</v>
+      </c>
+      <c r="O225" t="n">
+        <v>15</v>
+      </c>
+      <c r="P225" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>5</v>
+      </c>
+      <c r="R225" t="n">
+        <v>5</v>
+      </c>
+      <c r="S225" t="n">
+        <v>14</v>
+      </c>
+      <c r="T225" t="n">
+        <v>15</v>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="W225" t="n">
+        <v>148</v>
+      </c>
+      <c r="X225" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z225" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr"/>
+      <c r="AD225" t="inlineStr"/>
+      <c r="AE225" t="inlineStr"/>
+      <c r="AF225" t="inlineStr"/>
+      <c r="AG225" t="inlineStr"/>
+      <c r="AH225" t="inlineStr"/>
+      <c r="AI225" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="AJ225" t="n">
+        <v>185.5555555555555</v>
+      </c>
+      <c r="AK225" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AL225" t="n">
+        <v>75.11111111111111</v>
+      </c>
+      <c r="AM225" t="n">
+        <v>10622222.22222222</v>
+      </c>
+      <c r="AN225" t="n">
+        <v>79.44444444444444</v>
+      </c>
+      <c r="AO225" t="n">
+        <v>25.27272727272727</v>
+      </c>
+      <c r="AP225" t="n">
+        <v>177</v>
+      </c>
+      <c r="AQ225" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AR225" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AS225" t="n">
+        <v>6627272.727272728</v>
+      </c>
+      <c r="AT225" t="n">
+        <v>75.90909090909091</v>
+      </c>
+      <c r="AU225" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AV225" t="n">
+        <v>179</v>
+      </c>
+      <c r="AW225" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="AX225" t="n">
+        <v>75.88888888888889</v>
+      </c>
+      <c r="AY225" t="n">
+        <v>10522222.22222222</v>
+      </c>
+      <c r="AZ225" t="n">
+        <v>81</v>
+      </c>
+      <c r="BA225" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="BB225" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="BC225" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD225" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE225" t="n">
+        <v>291</v>
+      </c>
+      <c r="BF225" t="n">
+        <v>17700000</v>
+      </c>
+      <c r="BG225" t="n">
+        <v>294</v>
+      </c>
+      <c r="BH225" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI225" t="n">
+        <v>184</v>
+      </c>
+      <c r="BJ225" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK225" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL225" t="n">
+        <v>80</v>
+      </c>
+      <c r="BM225" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="BN225" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="n">
+        <v>45520.58333333334</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F226" t="n">
+        <v>22477</v>
+      </c>
+      <c r="G226" t="n">
+        <v>2</v>
+      </c>
+      <c r="H226" t="n">
+        <v>1</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="K226" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L226" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M226" t="n">
+        <v>64</v>
+      </c>
+      <c r="N226" t="n">
+        <v>36</v>
+      </c>
+      <c r="O226" t="n">
+        <v>6</v>
+      </c>
+      <c r="P226" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>4</v>
+      </c>
+      <c r="R226" t="n">
+        <v>2</v>
+      </c>
+      <c r="S226" t="n">
+        <v>8</v>
+      </c>
+      <c r="T226" t="n">
+        <v>23</v>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="W226" t="n">
+        <v>148</v>
+      </c>
+      <c r="X226" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr"/>
+      <c r="AC226" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="AD226" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF226" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AG226" t="n">
+        <v>8650000</v>
+      </c>
+      <c r="AH226" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="AI226" t="inlineStr"/>
+      <c r="AJ226" t="inlineStr"/>
+      <c r="AK226" t="inlineStr"/>
+      <c r="AL226" t="inlineStr"/>
+      <c r="AM226" t="inlineStr"/>
+      <c r="AN226" t="inlineStr"/>
+      <c r="AO226" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AP226" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AQ226" t="n">
+        <v>1.277777777777778</v>
+      </c>
+      <c r="AR226" t="n">
+        <v>72.77777777777777</v>
+      </c>
+      <c r="AS226" t="n">
+        <v>9987500</v>
+      </c>
+      <c r="AT226" t="n">
+        <v>76.77777777777777</v>
+      </c>
+      <c r="AU226" t="n">
+        <v>24.26315789473684</v>
+      </c>
+      <c r="AV226" t="n">
+        <v>180.6842105263158</v>
+      </c>
+      <c r="AW226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX226" t="n">
+        <v>71.05263157894737</v>
+      </c>
+      <c r="AY226" t="n">
+        <v>3814473.684210526</v>
+      </c>
+      <c r="AZ226" t="n">
+        <v>75.94736842105263</v>
+      </c>
+      <c r="BA226" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="BB226" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="BC226" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD226" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE226" t="n">
+        <v>151</v>
+      </c>
+      <c r="BF226" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="BG226" t="n">
+        <v>154</v>
+      </c>
+      <c r="BH226" t="inlineStr"/>
+      <c r="BI226" t="inlineStr"/>
+      <c r="BJ226" t="inlineStr"/>
+      <c r="BK226" t="inlineStr"/>
+      <c r="BL226" t="inlineStr"/>
+      <c r="BM226" t="inlineStr"/>
+      <c r="BN226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="n">
+        <v>45519.6875</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F227" t="n">
+        <v>54084</v>
+      </c>
+      <c r="G227" t="n">
+        <v>1</v>
+      </c>
+      <c r="H227" t="n">
+        <v>1</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="K227" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L227" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M227" t="n">
+        <v>39</v>
+      </c>
+      <c r="N227" t="n">
+        <v>61</v>
+      </c>
+      <c r="O227" t="n">
+        <v>19</v>
+      </c>
+      <c r="P227" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>4</v>
+      </c>
+      <c r="R227" t="n">
+        <v>2</v>
+      </c>
+      <c r="S227" t="n">
+        <v>11</v>
+      </c>
+      <c r="T227" t="n">
+        <v>7</v>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="W227" t="n">
+        <v>148</v>
+      </c>
+      <c r="X227" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr"/>
+      <c r="AD227" t="inlineStr"/>
+      <c r="AE227" t="inlineStr"/>
+      <c r="AF227" t="inlineStr"/>
+      <c r="AG227" t="inlineStr"/>
+      <c r="AH227" t="inlineStr"/>
+      <c r="AI227" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="AJ227" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="AK227" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL227" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="AM227" t="n">
+        <v>17512500</v>
+      </c>
+      <c r="AN227" t="n">
+        <v>81.375</v>
+      </c>
+      <c r="AO227" t="n">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="AP227" t="n">
+        <v>185</v>
+      </c>
+      <c r="AQ227" t="n">
+        <v>1.307692307692308</v>
+      </c>
+      <c r="AR227" t="n">
+        <v>72.76923076923077</v>
+      </c>
+      <c r="AS227" t="n">
+        <v>6384615.384615385</v>
+      </c>
+      <c r="AT227" t="n">
+        <v>79.92307692307692</v>
+      </c>
+      <c r="AU227" t="n">
+        <v>24.35714285714286</v>
+      </c>
+      <c r="AV227" t="n">
+        <v>180.9285714285714</v>
+      </c>
+      <c r="AW227" t="n">
+        <v>1.214285714285714</v>
+      </c>
+      <c r="AX227" t="n">
+        <v>70.71428571428571</v>
+      </c>
+      <c r="AY227" t="n">
+        <v>4835714.285714285</v>
+      </c>
+      <c r="AZ227" t="n">
+        <v>79.14285714285714</v>
+      </c>
+      <c r="BA227" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB227" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="BC227" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD227" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE227" t="n">
+        <v>216</v>
+      </c>
+      <c r="BF227" t="n">
+        <v>26650000</v>
+      </c>
+      <c r="BG227" t="n">
+        <v>230</v>
+      </c>
+      <c r="BH227" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="BI227" t="n">
+        <v>177.6</v>
+      </c>
+      <c r="BJ227" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BK227" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL227" t="n">
+        <v>358</v>
+      </c>
+      <c r="BM227" t="n">
+        <v>61400000</v>
+      </c>
+      <c r="BN227" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>hO0nKEm3</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="n">
+        <v>45519.58333333334</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F228" t="n">
+        <v>47845</v>
+      </c>
+      <c r="G228" t="n">
+        <v>1</v>
+      </c>
+      <c r="H228" t="n">
+        <v>1</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="K228" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L228" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="M228" t="n">
+        <v>69</v>
+      </c>
+      <c r="N228" t="n">
+        <v>31</v>
+      </c>
+      <c r="O228" t="n">
+        <v>7</v>
+      </c>
+      <c r="P228" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>4</v>
+      </c>
+      <c r="R228" t="n">
+        <v>2</v>
+      </c>
+      <c r="S228" t="n">
+        <v>15</v>
+      </c>
+      <c r="T228" t="n">
+        <v>12</v>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="W228" t="n">
+        <v>148</v>
+      </c>
+      <c r="X228" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA228" t="inlineStr"/>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="AC228" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="AD228" t="n">
+        <v>185</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="AF228" t="n">
+        <v>77.11111111111111</v>
+      </c>
+      <c r="AG228" t="n">
+        <v>18277777.77777778</v>
+      </c>
+      <c r="AH228" t="n">
+        <v>80.77777777777777</v>
+      </c>
+      <c r="AI228" t="n">
+        <v>26.77777777777778</v>
+      </c>
+      <c r="AJ228" t="n">
+        <v>179.8888888888889</v>
+      </c>
+      <c r="AK228" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AL228" t="n">
+        <v>74.66666666666667</v>
+      </c>
+      <c r="AM228" t="n">
+        <v>9352777.777777778</v>
+      </c>
+      <c r="AN228" t="n">
+        <v>77.33333333333333</v>
+      </c>
+      <c r="AO228" t="n">
+        <v>23.89473684210526</v>
+      </c>
+      <c r="AP228" t="n">
+        <v>182.2105263157895</v>
+      </c>
+      <c r="AQ228" t="n">
+        <v>1.473684210526316</v>
+      </c>
+      <c r="AR228" t="n">
+        <v>76.15789473684211</v>
+      </c>
+      <c r="AS228" t="n">
+        <v>17563157.89473684</v>
+      </c>
+      <c r="AT228" t="n">
+        <v>81.42105263157895</v>
+      </c>
+      <c r="AU228" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AV228" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="AW228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX228" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AY228" t="n">
+        <v>5260000</v>
+      </c>
+      <c r="AZ228" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="BA228" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="BB228" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BC228" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD228" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE228" t="n">
+        <v>310</v>
+      </c>
+      <c r="BF228" t="n">
+        <v>82500000</v>
+      </c>
+      <c r="BG228" t="n">
+        <v>330</v>
+      </c>
+      <c r="BH228" t="n">
+        <v>26</v>
+      </c>
+      <c r="BI228" t="n">
+        <v>182</v>
+      </c>
+      <c r="BJ228" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK228" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL228" t="n">
+        <v>78</v>
+      </c>
+      <c r="BM228" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="BN228" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>hIsKeIld</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="n">
+        <v>45522.60416666666</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de aza m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el plantio
+  burgos </t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>12194</v>
+      </c>
+      <c r="F229" t="n">
+        <v>9642</v>
+      </c>
+      <c r="G229" t="n">
+        <v>3</v>
+      </c>
+      <c r="H229" t="n">
+        <v>1</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="n">
+        <v>56</v>
+      </c>
+      <c r="N229" t="n">
+        <v>44</v>
+      </c>
+      <c r="O229" t="n">
+        <v>12</v>
+      </c>
+      <c r="P229" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>6</v>
+      </c>
+      <c r="R229" t="n">
+        <v>3</v>
+      </c>
+      <c r="S229" t="n">
+        <v>13</v>
+      </c>
+      <c r="T229" t="n">
+        <v>19</v>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>l6JQtDqc</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>M1vEw5An</t>
+        </is>
+      </c>
+      <c r="W229" t="n">
+        <v>148</v>
+      </c>
+      <c r="X229" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z229" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA229" t="inlineStr"/>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr"/>
+      <c r="AD229" t="inlineStr"/>
+      <c r="AE229" t="inlineStr"/>
+      <c r="AF229" t="inlineStr"/>
+      <c r="AG229" t="inlineStr"/>
+      <c r="AH229" t="inlineStr"/>
+      <c r="AI229" t="inlineStr"/>
+      <c r="AJ229" t="inlineStr"/>
+      <c r="AK229" t="inlineStr"/>
+      <c r="AL229" t="inlineStr"/>
+      <c r="AM229" t="inlineStr"/>
+      <c r="AN229" t="inlineStr"/>
+      <c r="AO229" t="n">
+        <v>22.625</v>
+      </c>
+      <c r="AP229" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="AQ229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR229" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="AS229" t="n">
+        <v>1884375</v>
+      </c>
+      <c r="AT229" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="AU229" t="n">
+        <v>25.16666666666667</v>
+      </c>
+      <c r="AV229" t="n">
+        <v>181</v>
+      </c>
+      <c r="AW229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX229" t="n">
+        <v>65</v>
+      </c>
+      <c r="AY229" t="n">
+        <v>858333.3333333334</v>
+      </c>
+      <c r="AZ229" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="BA229" t="inlineStr"/>
+      <c r="BB229" t="inlineStr"/>
+      <c r="BC229" t="inlineStr"/>
+      <c r="BD229" t="inlineStr"/>
+      <c r="BE229" t="inlineStr"/>
+      <c r="BF229" t="inlineStr"/>
+      <c r="BG229" t="inlineStr"/>
+      <c r="BH229" t="inlineStr"/>
+      <c r="BI229" t="inlineStr"/>
+      <c r="BJ229" t="inlineStr"/>
+      <c r="BK229" t="inlineStr"/>
+      <c r="BL229" t="inlineStr"/>
+      <c r="BM229" t="inlineStr"/>
+      <c r="BN229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>nigFFwtS</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="n">
+        <v>45522.60416666666</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">palencia caballero d 
+  esp </t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio manuel martinez valero
+  elche </t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>31388</v>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>1</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="n">
+        <v>71</v>
+      </c>
+      <c r="N230" t="n">
+        <v>29</v>
+      </c>
+      <c r="O230" t="n">
+        <v>12</v>
+      </c>
+      <c r="P230" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>3</v>
+      </c>
+      <c r="R230" t="n">
+        <v>3</v>
+      </c>
+      <c r="S230" t="n">
+        <v>16</v>
+      </c>
+      <c r="T230" t="n">
+        <v>18</v>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>zT9gi7i9</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="W230" t="n">
+        <v>148</v>
+      </c>
+      <c r="X230" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z230" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr"/>
+      <c r="AD230" t="inlineStr"/>
+      <c r="AE230" t="inlineStr"/>
+      <c r="AF230" t="inlineStr"/>
+      <c r="AG230" t="inlineStr"/>
+      <c r="AH230" t="inlineStr"/>
+      <c r="AI230" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ230" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="AK230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL230" t="n">
+        <v>67.875</v>
+      </c>
+      <c r="AM230" t="n">
+        <v>1365625</v>
+      </c>
+      <c r="AN230" t="n">
+        <v>70.625</v>
+      </c>
+      <c r="AO230" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AP230" t="n">
+        <v>179.1333333333333</v>
+      </c>
+      <c r="AQ230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR230" t="n">
+        <v>67.93333333333334</v>
+      </c>
+      <c r="AS230" t="n">
+        <v>1441666.666666667</v>
+      </c>
+      <c r="AT230" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AU230" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV230" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="AW230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX230" t="n">
+        <v>65.66666666666667</v>
+      </c>
+      <c r="AY230" t="n">
+        <v>1277777.777777778</v>
+      </c>
+      <c r="AZ230" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="BA230" t="inlineStr"/>
+      <c r="BB230" t="inlineStr"/>
+      <c r="BC230" t="inlineStr"/>
+      <c r="BD230" t="inlineStr"/>
+      <c r="BE230" t="inlineStr"/>
+      <c r="BF230" t="inlineStr"/>
+      <c r="BG230" t="inlineStr"/>
+      <c r="BH230" t="inlineStr"/>
+      <c r="BI230" t="inlineStr"/>
+      <c r="BJ230" t="inlineStr"/>
+      <c r="BK230" t="inlineStr"/>
+      <c r="BL230" t="inlineStr"/>
+      <c r="BM230" t="inlineStr"/>
+      <c r="BN230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>0I1yLYH7</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guzman mansilla j  l 
+  esp </t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el molinon
+  gijon </t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>29029</v>
+      </c>
+      <c r="F231" t="n">
+        <v>23319</v>
+      </c>
+      <c r="G231" t="n">
+        <v>1</v>
+      </c>
+      <c r="H231" t="n">
+        <v>2</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="n">
+        <v>66</v>
+      </c>
+      <c r="N231" t="n">
+        <v>34</v>
+      </c>
+      <c r="O231" t="n">
+        <v>11</v>
+      </c>
+      <c r="P231" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>1</v>
+      </c>
+      <c r="R231" t="n">
+        <v>5</v>
+      </c>
+      <c r="S231" t="n">
+        <v>15</v>
+      </c>
+      <c r="T231" t="n">
+        <v>16</v>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>fiZxGYJ3</t>
+        </is>
+      </c>
+      <c r="W231" t="n">
+        <v>148</v>
+      </c>
+      <c r="X231" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z231" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA231" t="inlineStr"/>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="AC231" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="AD231" t="n">
+        <v>179.1111111111111</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF231" t="n">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="AG231" t="n">
+        <v>2372222.222222222</v>
+      </c>
+      <c r="AH231" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AI231" t="inlineStr"/>
+      <c r="AJ231" t="inlineStr"/>
+      <c r="AK231" t="inlineStr"/>
+      <c r="AL231" t="inlineStr"/>
+      <c r="AM231" t="inlineStr"/>
+      <c r="AN231" t="inlineStr"/>
+      <c r="AO231" t="n">
+        <v>24.18181818181818</v>
+      </c>
+      <c r="AP231" t="n">
+        <v>177.3636363636364</v>
+      </c>
+      <c r="AQ231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR231" t="n">
+        <v>67.63636363636364</v>
+      </c>
+      <c r="AS231" t="n">
+        <v>1788636.363636364</v>
+      </c>
+      <c r="AT231" t="n">
+        <v>74.27272727272727</v>
+      </c>
+      <c r="AU231" t="n">
+        <v>23</v>
+      </c>
+      <c r="AV231" t="n">
+        <v>177.5833333333333</v>
+      </c>
+      <c r="AW231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX231" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AY231" t="n">
+        <v>1983333.333333333</v>
+      </c>
+      <c r="AZ231" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="BA231" t="inlineStr"/>
+      <c r="BB231" t="inlineStr"/>
+      <c r="BC231" t="inlineStr"/>
+      <c r="BD231" t="inlineStr"/>
+      <c r="BE231" t="inlineStr"/>
+      <c r="BF231" t="inlineStr"/>
+      <c r="BG231" t="inlineStr"/>
+      <c r="BH231" t="inlineStr"/>
+      <c r="BI231" t="inlineStr"/>
+      <c r="BJ231" t="inlineStr"/>
+      <c r="BK231" t="inlineStr"/>
+      <c r="BL231" t="inlineStr"/>
+      <c r="BM231" t="inlineStr"/>
+      <c r="BN231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>0fJlUxeL</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moreno a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sardinero
+  santander </t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>22222</v>
+      </c>
+      <c r="F232" t="n">
+        <v>19697</v>
+      </c>
+      <c r="G232" t="n">
+        <v>2</v>
+      </c>
+      <c r="H232" t="n">
+        <v>2</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="n">
+        <v>36</v>
+      </c>
+      <c r="N232" t="n">
+        <v>64</v>
+      </c>
+      <c r="O232" t="n">
+        <v>12</v>
+      </c>
+      <c r="P232" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>5</v>
+      </c>
+      <c r="R232" t="n">
+        <v>9</v>
+      </c>
+      <c r="S232" t="n">
+        <v>18</v>
+      </c>
+      <c r="T232" t="n">
+        <v>15</v>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>rak12p9n</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="W232" t="n">
+        <v>148</v>
+      </c>
+      <c r="X232" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA232" t="inlineStr"/>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr"/>
+      <c r="AD232" t="inlineStr"/>
+      <c r="AE232" t="inlineStr"/>
+      <c r="AF232" t="inlineStr"/>
+      <c r="AG232" t="inlineStr"/>
+      <c r="AH232" t="inlineStr"/>
+      <c r="AI232" t="inlineStr"/>
+      <c r="AJ232" t="inlineStr"/>
+      <c r="AK232" t="inlineStr"/>
+      <c r="AL232" t="inlineStr"/>
+      <c r="AM232" t="inlineStr"/>
+      <c r="AN232" t="inlineStr"/>
+      <c r="AO232" t="n">
+        <v>26.47058823529412</v>
+      </c>
+      <c r="AP232" t="n">
+        <v>180.6470588235294</v>
+      </c>
+      <c r="AQ232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR232" t="n">
+        <v>66.88235294117646</v>
+      </c>
+      <c r="AS232" t="n">
+        <v>1427941.176470588</v>
+      </c>
+      <c r="AT232" t="n">
+        <v>72.64705882352941</v>
+      </c>
+      <c r="AU232" t="n">
+        <v>22.57142857142857</v>
+      </c>
+      <c r="AV232" t="n">
+        <v>184.7619047619048</v>
+      </c>
+      <c r="AW232" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AX232" t="n">
+        <v>69.0952380952381</v>
+      </c>
+      <c r="AY232" t="n">
+        <v>3557142.857142857</v>
+      </c>
+      <c r="AZ232" t="n">
+        <v>76.42857142857143</v>
+      </c>
+      <c r="BA232" t="inlineStr"/>
+      <c r="BB232" t="inlineStr"/>
+      <c r="BC232" t="inlineStr"/>
+      <c r="BD232" t="inlineStr"/>
+      <c r="BE232" t="inlineStr"/>
+      <c r="BF232" t="inlineStr"/>
+      <c r="BG232" t="inlineStr"/>
+      <c r="BH232" t="inlineStr"/>
+      <c r="BI232" t="inlineStr"/>
+      <c r="BJ232" t="inlineStr"/>
+      <c r="BK232" t="inlineStr"/>
+      <c r="BL232" t="inlineStr"/>
+      <c r="BM232" t="inlineStr"/>
+      <c r="BN232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>tvOEHaBF</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lax franco s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de riazor
+  la coruna </t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>34889</v>
+      </c>
+      <c r="F233" t="n">
+        <v>25715</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>1</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="n">
+        <v>66</v>
+      </c>
+      <c r="N233" t="n">
+        <v>34</v>
+      </c>
+      <c r="O233" t="n">
+        <v>17</v>
+      </c>
+      <c r="P233" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>7</v>
+      </c>
+      <c r="R233" t="n">
+        <v>4</v>
+      </c>
+      <c r="S233" t="n">
+        <v>9</v>
+      </c>
+      <c r="T233" t="n">
+        <v>22</v>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="W233" t="n">
+        <v>148</v>
+      </c>
+      <c r="X233" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA233" t="inlineStr"/>
+      <c r="AB233" t="inlineStr"/>
+      <c r="AC233" t="inlineStr"/>
+      <c r="AD233" t="inlineStr"/>
+      <c r="AE233" t="inlineStr"/>
+      <c r="AF233" t="inlineStr"/>
+      <c r="AG233" t="inlineStr"/>
+      <c r="AH233" t="inlineStr"/>
+      <c r="AI233" t="inlineStr"/>
+      <c r="AJ233" t="inlineStr"/>
+      <c r="AK233" t="inlineStr"/>
+      <c r="AL233" t="inlineStr"/>
+      <c r="AM233" t="inlineStr"/>
+      <c r="AN233" t="inlineStr"/>
+      <c r="AO233" t="inlineStr"/>
+      <c r="AP233" t="inlineStr"/>
+      <c r="AQ233" t="inlineStr"/>
+      <c r="AR233" t="inlineStr"/>
+      <c r="AS233" t="inlineStr"/>
+      <c r="AT233" t="inlineStr"/>
+      <c r="AU233" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="AV233" t="n">
+        <v>177.55</v>
+      </c>
+      <c r="AW233" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AX233" t="n">
+        <v>69</v>
+      </c>
+      <c r="AY233" t="n">
+        <v>2176250</v>
+      </c>
+      <c r="AZ233" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="BA233" t="inlineStr"/>
+      <c r="BB233" t="inlineStr"/>
+      <c r="BC233" t="inlineStr"/>
+      <c r="BD233" t="inlineStr"/>
+      <c r="BE233" t="inlineStr"/>
+      <c r="BF233" t="inlineStr"/>
+      <c r="BG233" t="inlineStr"/>
+      <c r="BH233" t="inlineStr"/>
+      <c r="BI233" t="inlineStr"/>
+      <c r="BJ233" t="inlineStr"/>
+      <c r="BK233" t="inlineStr"/>
+      <c r="BL233" t="inlineStr"/>
+      <c r="BM233" t="inlineStr"/>
+      <c r="BN233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>dQ4KOGIr</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mallo e 
+  esp </t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de ipurua
+  eibar </t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>8164</v>
+      </c>
+      <c r="F234" t="n">
+        <v>3538</v>
+      </c>
+      <c r="G234" t="n">
+        <v>1</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="n">
+        <v>37</v>
+      </c>
+      <c r="N234" t="n">
+        <v>63</v>
+      </c>
+      <c r="O234" t="n">
+        <v>9</v>
+      </c>
+      <c r="P234" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>3</v>
+      </c>
+      <c r="R234" t="n">
+        <v>4</v>
+      </c>
+      <c r="S234" t="n">
+        <v>17</v>
+      </c>
+      <c r="T234" t="n">
+        <v>9</v>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="W234" t="n">
+        <v>148</v>
+      </c>
+      <c r="X234" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z234" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr"/>
+      <c r="AC234" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="AD234" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF234" t="n">
+        <v>68</v>
+      </c>
+      <c r="AG234" t="n">
+        <v>1625000</v>
+      </c>
+      <c r="AH234" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AI234" t="inlineStr"/>
+      <c r="AJ234" t="inlineStr"/>
+      <c r="AK234" t="inlineStr"/>
+      <c r="AL234" t="inlineStr"/>
+      <c r="AM234" t="inlineStr"/>
+      <c r="AN234" t="inlineStr"/>
+      <c r="AO234" t="n">
+        <v>24.85714285714286</v>
+      </c>
+      <c r="AP234" t="n">
+        <v>182.7857142857143</v>
+      </c>
+      <c r="AQ234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR234" t="n">
+        <v>66.85714285714286</v>
+      </c>
+      <c r="AS234" t="n">
+        <v>1801785.714285714</v>
+      </c>
+      <c r="AT234" t="n">
+        <v>72.07142857142857</v>
+      </c>
+      <c r="AU234" t="inlineStr"/>
+      <c r="AV234" t="inlineStr"/>
+      <c r="AW234" t="inlineStr"/>
+      <c r="AX234" t="inlineStr"/>
+      <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr"/>
+      <c r="BA234" t="inlineStr"/>
+      <c r="BB234" t="inlineStr"/>
+      <c r="BC234" t="inlineStr"/>
+      <c r="BD234" t="inlineStr"/>
+      <c r="BE234" t="inlineStr"/>
+      <c r="BF234" t="inlineStr"/>
+      <c r="BG234" t="inlineStr"/>
+      <c r="BH234" t="inlineStr"/>
+      <c r="BI234" t="inlineStr"/>
+      <c r="BJ234" t="inlineStr"/>
+      <c r="BK234" t="inlineStr"/>
+      <c r="BL234" t="inlineStr"/>
+      <c r="BM234" t="inlineStr"/>
+      <c r="BN234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>vkYg8eY1</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sesma espinosa m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal da malata
+  ferrol </t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>10450</v>
+      </c>
+      <c r="F235" t="n">
+        <v>7541</v>
+      </c>
+      <c r="G235" t="n">
+        <v>2</v>
+      </c>
+      <c r="H235" t="n">
+        <v>2</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="n">
+        <v>41</v>
+      </c>
+      <c r="N235" t="n">
+        <v>59</v>
+      </c>
+      <c r="O235" t="n">
+        <v>14</v>
+      </c>
+      <c r="P235" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>5</v>
+      </c>
+      <c r="R235" t="n">
+        <v>2</v>
+      </c>
+      <c r="S235" t="n">
+        <v>16</v>
+      </c>
+      <c r="T235" t="n">
+        <v>16</v>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>tjXr7SAp</t>
+        </is>
+      </c>
+      <c r="W235" t="n">
+        <v>148</v>
+      </c>
+      <c r="X235" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z235" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr"/>
+      <c r="AC235" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AD235" t="n">
+        <v>179.125</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF235" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="AG235" t="n">
+        <v>1190625</v>
+      </c>
+      <c r="AH235" t="n">
+        <v>69.875</v>
+      </c>
+      <c r="AI235" t="inlineStr"/>
+      <c r="AJ235" t="inlineStr"/>
+      <c r="AK235" t="inlineStr"/>
+      <c r="AL235" t="inlineStr"/>
+      <c r="AM235" t="inlineStr"/>
+      <c r="AN235" t="inlineStr"/>
+      <c r="AO235" t="n">
+        <v>27.72727272727273</v>
+      </c>
+      <c r="AP235" t="n">
+        <v>178</v>
+      </c>
+      <c r="AQ235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR235" t="n">
+        <v>66.54545454545455</v>
+      </c>
+      <c r="AS235" t="n">
+        <v>959090.9090909091</v>
+      </c>
+      <c r="AT235" t="n">
+        <v>68.63636363636364</v>
+      </c>
+      <c r="AU235" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="AV235" t="n">
+        <v>181.8333333333333</v>
+      </c>
+      <c r="AW235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX235" t="n">
+        <v>64.16666666666667</v>
+      </c>
+      <c r="AY235" t="n">
+        <v>1391666.666666667</v>
+      </c>
+      <c r="AZ235" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="BA235" t="inlineStr"/>
+      <c r="BB235" t="inlineStr"/>
+      <c r="BC235" t="inlineStr"/>
+      <c r="BD235" t="inlineStr"/>
+      <c r="BE235" t="inlineStr"/>
+      <c r="BF235" t="inlineStr"/>
+      <c r="BG235" t="inlineStr"/>
+      <c r="BH235" t="inlineStr"/>
+      <c r="BI235" t="inlineStr"/>
+      <c r="BJ235" t="inlineStr"/>
+      <c r="BK235" t="inlineStr"/>
+      <c r="BL235" t="inlineStr"/>
+      <c r="BM235" t="inlineStr"/>
+      <c r="BN235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>8QP6JLt3</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="n">
+        <v>45520.6875</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">monescillo d 
+  esp </t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo mirandilla
+  cadiz </t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>20776</v>
+      </c>
+      <c r="F236" t="n">
+        <v>16970</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>4</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="n">
+        <v>62</v>
+      </c>
+      <c r="N236" t="n">
+        <v>38</v>
+      </c>
+      <c r="O236" t="n">
+        <v>13</v>
+      </c>
+      <c r="P236" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>3</v>
+      </c>
+      <c r="R236" t="n">
+        <v>9</v>
+      </c>
+      <c r="S236" t="n">
+        <v>14</v>
+      </c>
+      <c r="T236" t="n">
+        <v>21</v>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="W236" t="n">
+        <v>148</v>
+      </c>
+      <c r="X236" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z236" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr"/>
+      <c r="AD236" t="inlineStr"/>
+      <c r="AE236" t="inlineStr"/>
+      <c r="AF236" t="inlineStr"/>
+      <c r="AG236" t="inlineStr"/>
+      <c r="AH236" t="inlineStr"/>
+      <c r="AI236" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="AJ236" t="n">
+        <v>175.8888888888889</v>
+      </c>
+      <c r="AK236" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL236" t="n">
+        <v>67.88888888888889</v>
+      </c>
+      <c r="AM236" t="n">
+        <v>1811111.111111111</v>
+      </c>
+      <c r="AN236" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AO236" t="n">
+        <v>25.5625</v>
+      </c>
+      <c r="AP236" t="n">
+        <v>178.8125</v>
+      </c>
+      <c r="AQ236" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AR236" t="n">
+        <v>70</v>
+      </c>
+      <c r="AS236" t="n">
+        <v>3395312.5</v>
+      </c>
+      <c r="AT236" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AU236" t="n">
+        <v>26.38888888888889</v>
+      </c>
+      <c r="AV236" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="AW236" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX236" t="n">
+        <v>69.61111111111111</v>
+      </c>
+      <c r="AY236" t="n">
+        <v>2075000</v>
+      </c>
+      <c r="AZ236" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="BA236" t="inlineStr"/>
+      <c r="BB236" t="inlineStr"/>
+      <c r="BC236" t="inlineStr"/>
+      <c r="BD236" t="inlineStr"/>
+      <c r="BE236" t="inlineStr"/>
+      <c r="BF236" t="inlineStr"/>
+      <c r="BG236" t="inlineStr"/>
+      <c r="BH236" t="inlineStr"/>
+      <c r="BI236" t="inlineStr"/>
+      <c r="BJ236" t="inlineStr"/>
+      <c r="BK236" t="inlineStr"/>
+      <c r="BL236" t="inlineStr"/>
+      <c r="BM236" t="inlineStr"/>
+      <c r="BN236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>hhbTMfme</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="n">
+        <v>45520.58333333334</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzalez diaz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de anduva
+  miranda de ebro </t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>5759</v>
+      </c>
+      <c r="F237" t="n">
+        <v>3005</v>
+      </c>
+      <c r="G237" t="n">
+        <v>1</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="n">
+        <v>32</v>
+      </c>
+      <c r="N237" t="n">
+        <v>68</v>
+      </c>
+      <c r="O237" t="n">
+        <v>3</v>
+      </c>
+      <c r="P237" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>2</v>
+      </c>
+      <c r="R237" t="n">
+        <v>7</v>
+      </c>
+      <c r="S237" t="n">
+        <v>6</v>
+      </c>
+      <c r="T237" t="n">
+        <v>14</v>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="W237" t="n">
+        <v>148</v>
+      </c>
+      <c r="X237" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y237" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z237" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="AB237" t="inlineStr"/>
+      <c r="AC237" t="inlineStr"/>
+      <c r="AD237" t="inlineStr"/>
+      <c r="AE237" t="inlineStr"/>
+      <c r="AF237" t="inlineStr"/>
+      <c r="AG237" t="inlineStr"/>
+      <c r="AH237" t="inlineStr"/>
+      <c r="AI237" t="inlineStr"/>
+      <c r="AJ237" t="inlineStr"/>
+      <c r="AK237" t="inlineStr"/>
+      <c r="AL237" t="inlineStr"/>
+      <c r="AM237" t="inlineStr"/>
+      <c r="AN237" t="inlineStr"/>
+      <c r="AO237" t="inlineStr"/>
+      <c r="AP237" t="inlineStr"/>
+      <c r="AQ237" t="inlineStr"/>
+      <c r="AR237" t="inlineStr"/>
+      <c r="AS237" t="inlineStr"/>
+      <c r="AT237" t="inlineStr"/>
+      <c r="AU237" t="inlineStr"/>
+      <c r="AV237" t="inlineStr"/>
+      <c r="AW237" t="inlineStr"/>
+      <c r="AX237" t="inlineStr"/>
+      <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr"/>
+      <c r="BA237" t="inlineStr"/>
+      <c r="BB237" t="inlineStr"/>
+      <c r="BC237" t="inlineStr"/>
+      <c r="BD237" t="inlineStr"/>
+      <c r="BE237" t="inlineStr"/>
+      <c r="BF237" t="inlineStr"/>
+      <c r="BG237" t="inlineStr"/>
+      <c r="BH237" t="inlineStr"/>
+      <c r="BI237" t="inlineStr"/>
+      <c r="BJ237" t="inlineStr"/>
+      <c r="BK237" t="inlineStr"/>
+      <c r="BL237" t="inlineStr"/>
+      <c r="BM237" t="inlineStr"/>
+      <c r="BN237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>6eQuWbQ8</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="n">
+        <v>45519.64583333334</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reig s  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo los carmenes
+  granada </t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>22524</v>
+      </c>
+      <c r="F238" t="n">
+        <v>13265</v>
+      </c>
+      <c r="G238" t="n">
+        <v>1</v>
+      </c>
+      <c r="H238" t="n">
+        <v>2</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="n">
+        <v>65</v>
+      </c>
+      <c r="N238" t="n">
+        <v>35</v>
+      </c>
+      <c r="O238" t="n">
+        <v>22</v>
+      </c>
+      <c r="P238" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>10</v>
+      </c>
+      <c r="R238" t="n">
+        <v>3</v>
+      </c>
+      <c r="S238" t="n">
+        <v>10</v>
+      </c>
+      <c r="T238" t="n">
+        <v>11</v>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>K4dMCgFa</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="W238" t="n">
+        <v>148</v>
+      </c>
+      <c r="X238" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y238" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z238" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC238" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD238" t="n">
+        <v>178.125</v>
+      </c>
+      <c r="AE238" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF238" t="n">
+        <v>72.625</v>
+      </c>
+      <c r="AG238" t="n">
+        <v>4237500</v>
+      </c>
+      <c r="AH238" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AI238" t="inlineStr"/>
+      <c r="AJ238" t="inlineStr"/>
+      <c r="AK238" t="inlineStr"/>
+      <c r="AL238" t="inlineStr"/>
+      <c r="AM238" t="inlineStr"/>
+      <c r="AN238" t="inlineStr"/>
+      <c r="AO238" t="n">
+        <v>25.13636363636364</v>
+      </c>
+      <c r="AP238" t="n">
+        <v>181.6363636363636</v>
+      </c>
+      <c r="AQ238" t="n">
+        <v>1.136363636363636</v>
+      </c>
+      <c r="AR238" t="n">
+        <v>70.86363636363636</v>
+      </c>
+      <c r="AS238" t="n">
+        <v>3861363.636363636</v>
+      </c>
+      <c r="AT238" t="n">
+        <v>75.31818181818181</v>
+      </c>
+      <c r="AU238" t="n">
+        <v>25.90909090909091</v>
+      </c>
+      <c r="AV238" t="n">
+        <v>180</v>
+      </c>
+      <c r="AW238" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AX238" t="n">
+        <v>66.72727272727273</v>
+      </c>
+      <c r="AY238" t="n">
+        <v>4729545.454545454</v>
+      </c>
+      <c r="AZ238" t="n">
+        <v>70.09090909090909</v>
+      </c>
+      <c r="BA238" t="inlineStr"/>
+      <c r="BB238" t="inlineStr"/>
+      <c r="BC238" t="inlineStr"/>
+      <c r="BD238" t="inlineStr"/>
+      <c r="BE238" t="inlineStr"/>
+      <c r="BF238" t="inlineStr"/>
+      <c r="BG238" t="inlineStr"/>
+      <c r="BH238" t="inlineStr"/>
+      <c r="BI238" t="inlineStr"/>
+      <c r="BJ238" t="inlineStr"/>
+      <c r="BK238" t="inlineStr"/>
+      <c r="BL238" t="inlineStr"/>
+      <c r="BM238" t="inlineStr"/>
+      <c r="BN238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>E1Xs9lu2</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="n">
+        <v>45523.6875</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F239" t="n">
+        <v>21566</v>
+      </c>
+      <c r="G239" t="n">
+        <v>2</v>
+      </c>
+      <c r="H239" t="n">
+        <v>2</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="K239" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L239" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="M239" t="n">
+        <v>44</v>
+      </c>
+      <c r="N239" t="n">
+        <v>56</v>
+      </c>
+      <c r="O239" t="n">
+        <v>8</v>
+      </c>
+      <c r="P239" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>3</v>
+      </c>
+      <c r="R239" t="n">
+        <v>5</v>
+      </c>
+      <c r="S239" t="n">
+        <v>6</v>
+      </c>
+      <c r="T239" t="n">
+        <v>10</v>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>Ii1Om118</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="W239" t="n">
+        <v>148</v>
+      </c>
+      <c r="X239" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y239" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z239" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr"/>
+      <c r="AC239" t="inlineStr"/>
+      <c r="AD239" t="inlineStr"/>
+      <c r="AE239" t="inlineStr"/>
+      <c r="AF239" t="inlineStr"/>
+      <c r="AG239" t="inlineStr"/>
+      <c r="AH239" t="inlineStr"/>
+      <c r="AI239" t="n">
+        <v>28.22222222222222</v>
+      </c>
+      <c r="AJ239" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AK239" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AL239" t="n">
+        <v>81.33333333333333</v>
+      </c>
+      <c r="AM239" t="n">
+        <v>30055555.55555556</v>
+      </c>
+      <c r="AN239" t="n">
+        <v>83.33333333333333</v>
+      </c>
+      <c r="AO239" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AP239" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="AQ239" t="n">
+        <v>1.416666666666667</v>
+      </c>
+      <c r="AR239" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="AS239" t="n">
+        <v>11625000</v>
+      </c>
+      <c r="AT239" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="AU239" t="n">
+        <v>26.10526315789474</v>
+      </c>
+      <c r="AV239" t="n">
+        <v>180.1052631578947</v>
+      </c>
+      <c r="AW239" t="n">
+        <v>1.684210526315789</v>
+      </c>
+      <c r="AX239" t="n">
+        <v>79.15789473684211</v>
+      </c>
+      <c r="AY239" t="n">
+        <v>25078947.36842105</v>
+      </c>
+      <c r="AZ239" t="n">
+        <v>82.52631578947368</v>
+      </c>
+      <c r="BA239" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB239" t="n">
+        <v>183</v>
+      </c>
+      <c r="BC239" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BD239" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE239" t="n">
+        <v>233</v>
+      </c>
+      <c r="BF239" t="n">
+        <v>44500000</v>
+      </c>
+      <c r="BG239" t="n">
+        <v>236</v>
+      </c>
+      <c r="BH239" t="inlineStr"/>
+      <c r="BI239" t="inlineStr"/>
+      <c r="BJ239" t="inlineStr"/>
+      <c r="BK239" t="inlineStr"/>
+      <c r="BL239" t="inlineStr"/>
+      <c r="BM239" t="inlineStr"/>
+      <c r="BN239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>ITdtTrn2</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="n">
+        <v>45523.58333333334</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="n">
+        <v>1</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="K240" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L240" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M240" t="n">
+        <v>45</v>
+      </c>
+      <c r="N240" t="n">
+        <v>55</v>
+      </c>
+      <c r="O240" t="n">
+        <v>12</v>
+      </c>
+      <c r="P240" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>3</v>
+      </c>
+      <c r="R240" t="n">
+        <v>2</v>
+      </c>
+      <c r="S240" t="n">
+        <v>15</v>
+      </c>
+      <c r="T240" t="n">
+        <v>8</v>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="W240" t="n">
+        <v>148</v>
+      </c>
+      <c r="X240" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z240" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AC240" t="n">
+        <v>24.88888888888889</v>
+      </c>
+      <c r="AD240" t="n">
+        <v>178.8888888888889</v>
+      </c>
+      <c r="AE240" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF240" t="n">
+        <v>71.44444444444444</v>
+      </c>
+      <c r="AG240" t="n">
+        <v>3622222.222222222</v>
+      </c>
+      <c r="AH240" t="n">
+        <v>75.55555555555556</v>
+      </c>
+      <c r="AI240" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AJ240" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="AK240" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL240" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="AM240" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="AN240" t="n">
+        <v>76.44444444444444</v>
+      </c>
+      <c r="AO240" t="n">
+        <v>24.4375</v>
+      </c>
+      <c r="AP240" t="n">
+        <v>180.8125</v>
+      </c>
+      <c r="AQ240" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AR240" t="n">
+        <v>69.875</v>
+      </c>
+      <c r="AS240" t="n">
+        <v>3392187.5</v>
+      </c>
+      <c r="AT240" t="n">
+        <v>76.125</v>
+      </c>
+      <c r="AU240" t="n">
+        <v>23.90909090909091</v>
+      </c>
+      <c r="AV240" t="n">
+        <v>178.8181818181818</v>
+      </c>
+      <c r="AW240" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX240" t="n">
+        <v>69.45454545454545</v>
+      </c>
+      <c r="AY240" t="n">
+        <v>3227272.727272727</v>
+      </c>
+      <c r="AZ240" t="n">
+        <v>76</v>
+      </c>
+      <c r="BA240" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="BB240" t="n">
+        <v>178</v>
+      </c>
+      <c r="BC240" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD240" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE240" t="n">
+        <v>142</v>
+      </c>
+      <c r="BF240" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="BG240" t="n">
+        <v>142</v>
+      </c>
+      <c r="BH240" t="n">
+        <v>26</v>
+      </c>
+      <c r="BI240" t="n">
+        <v>178</v>
+      </c>
+      <c r="BJ240" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK240" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL240" t="n">
+        <v>74</v>
+      </c>
+      <c r="BM240" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="BN240" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>IZqoAH3k</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="n">
+        <v>45523.64583333334</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de la fuente ramos o 
+  esp </t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo pepico amat
+  elda </t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>4038</v>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="n">
+        <v>2</v>
+      </c>
+      <c r="H241" t="n">
+        <v>1</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="n">
+        <v>46</v>
+      </c>
+      <c r="N241" t="n">
+        <v>54</v>
+      </c>
+      <c r="O241" t="n">
+        <v>15</v>
+      </c>
+      <c r="P241" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>4</v>
+      </c>
+      <c r="R241" t="n">
+        <v>5</v>
+      </c>
+      <c r="S241" t="n">
+        <v>11</v>
+      </c>
+      <c r="T241" t="n">
+        <v>17</v>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>hh4xt2Df</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>UBD9uzt0</t>
+        </is>
+      </c>
+      <c r="W241" t="n">
+        <v>148</v>
+      </c>
+      <c r="X241" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y241" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z241" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="AC241" t="inlineStr"/>
+      <c r="AD241" t="inlineStr"/>
+      <c r="AE241" t="inlineStr"/>
+      <c r="AF241" t="inlineStr"/>
+      <c r="AG241" t="inlineStr"/>
+      <c r="AH241" t="inlineStr"/>
+      <c r="AI241" t="inlineStr"/>
+      <c r="AJ241" t="inlineStr"/>
+      <c r="AK241" t="inlineStr"/>
+      <c r="AL241" t="inlineStr"/>
+      <c r="AM241" t="inlineStr"/>
+      <c r="AN241" t="inlineStr"/>
+      <c r="AO241" t="n">
+        <v>28.11111111111111</v>
+      </c>
+      <c r="AP241" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="AQ241" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR241" t="n">
+        <v>66.27777777777777</v>
+      </c>
+      <c r="AS241" t="n">
+        <v>1244722.222222222</v>
+      </c>
+      <c r="AT241" t="n">
+        <v>69.27777777777777</v>
+      </c>
+      <c r="AU241" t="n">
+        <v>30.14285714285714</v>
+      </c>
+      <c r="AV241" t="n">
+        <v>184.5714285714286</v>
+      </c>
+      <c r="AW241" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX241" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="AY241" t="n">
+        <v>1642857.142857143</v>
+      </c>
+      <c r="AZ241" t="n">
+        <v>72.85714285714286</v>
+      </c>
+      <c r="BA241" t="inlineStr"/>
+      <c r="BB241" t="inlineStr"/>
+      <c r="BC241" t="inlineStr"/>
+      <c r="BD241" t="inlineStr"/>
+      <c r="BE241" t="inlineStr"/>
+      <c r="BF241" t="inlineStr"/>
+      <c r="BG241" t="inlineStr"/>
+      <c r="BH241" t="inlineStr"/>
+      <c r="BI241" t="inlineStr"/>
+      <c r="BJ241" t="inlineStr"/>
+      <c r="BK241" t="inlineStr"/>
+      <c r="BL241" t="inlineStr"/>
+      <c r="BM241" t="inlineStr"/>
+      <c r="BN241" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN241"/>
+  <dimension ref="A1:BN250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46969,6 +46969,1698 @@
       <c r="BM241" t="inlineStr"/>
       <c r="BN241" t="inlineStr"/>
     </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>WhAFMMRi</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="n">
+        <v>45528.58333333334</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gil manzano j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>55926</v>
+      </c>
+      <c r="F242" t="n">
+        <v>46448</v>
+      </c>
+      <c r="G242" t="n">
+        <v>2</v>
+      </c>
+      <c r="H242" t="n">
+        <v>1</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="K242" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L242" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M242" t="n">
+        <v>63</v>
+      </c>
+      <c r="N242" t="n">
+        <v>37</v>
+      </c>
+      <c r="O242" t="n">
+        <v>9</v>
+      </c>
+      <c r="P242" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>4</v>
+      </c>
+      <c r="R242" t="n">
+        <v>3</v>
+      </c>
+      <c r="S242" t="n">
+        <v>8</v>
+      </c>
+      <c r="T242" t="n">
+        <v>11</v>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="W242" t="n">
+        <v>148</v>
+      </c>
+      <c r="X242" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y242" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z242" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr"/>
+      <c r="AC242" t="inlineStr"/>
+      <c r="AD242" t="inlineStr"/>
+      <c r="AE242" t="inlineStr"/>
+      <c r="AF242" t="inlineStr"/>
+      <c r="AG242" t="inlineStr"/>
+      <c r="AH242" t="inlineStr"/>
+      <c r="AI242" t="n">
+        <v>25.11111111111111</v>
+      </c>
+      <c r="AJ242" t="n">
+        <v>183.8888888888889</v>
+      </c>
+      <c r="AK242" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AL242" t="n">
+        <v>77.77777777777777</v>
+      </c>
+      <c r="AM242" t="n">
+        <v>22722222.22222222</v>
+      </c>
+      <c r="AN242" t="n">
+        <v>82</v>
+      </c>
+      <c r="AO242" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="AP242" t="n">
+        <v>182.3</v>
+      </c>
+      <c r="AQ242" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR242" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="AS242" t="n">
+        <v>7785000</v>
+      </c>
+      <c r="AT242" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="AU242" t="n">
+        <v>24.27272727272727</v>
+      </c>
+      <c r="AV242" t="n">
+        <v>183.1363636363636</v>
+      </c>
+      <c r="AW242" t="n">
+        <v>1.318181818181818</v>
+      </c>
+      <c r="AX242" t="n">
+        <v>74</v>
+      </c>
+      <c r="AY242" t="n">
+        <v>11668181.81818182</v>
+      </c>
+      <c r="AZ242" t="n">
+        <v>79.90909090909091</v>
+      </c>
+      <c r="BA242" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="BB242" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="BC242" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD242" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE242" t="n">
+        <v>331</v>
+      </c>
+      <c r="BF242" t="n">
+        <v>241500000</v>
+      </c>
+      <c r="BG242" t="n">
+        <v>353</v>
+      </c>
+      <c r="BH242" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BI242" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="BJ242" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK242" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL242" t="n">
+        <v>312</v>
+      </c>
+      <c r="BM242" t="n">
+        <v>85000000</v>
+      </c>
+      <c r="BN242" t="n">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>vJDNK0d4</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="n">
+        <v>45528.5</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F243" t="n">
+        <v>19900</v>
+      </c>
+      <c r="G243" t="n">
+        <v>1</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="K243" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L243" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M243" t="n">
+        <v>46</v>
+      </c>
+      <c r="N243" t="n">
+        <v>54</v>
+      </c>
+      <c r="O243" t="n">
+        <v>15</v>
+      </c>
+      <c r="P243" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>5</v>
+      </c>
+      <c r="R243" t="n">
+        <v>2</v>
+      </c>
+      <c r="S243" t="n">
+        <v>10</v>
+      </c>
+      <c r="T243" t="n">
+        <v>8</v>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="W243" t="n">
+        <v>148</v>
+      </c>
+      <c r="X243" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y243" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z243" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA243" t="inlineStr"/>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr"/>
+      <c r="AD243" t="inlineStr"/>
+      <c r="AE243" t="inlineStr"/>
+      <c r="AF243" t="inlineStr"/>
+      <c r="AG243" t="inlineStr"/>
+      <c r="AH243" t="inlineStr"/>
+      <c r="AI243" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AJ243" t="n">
+        <v>185.1111111111111</v>
+      </c>
+      <c r="AK243" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AL243" t="n">
+        <v>76.55555555555556</v>
+      </c>
+      <c r="AM243" t="n">
+        <v>12444444.44444444</v>
+      </c>
+      <c r="AN243" t="n">
+        <v>78.44444444444444</v>
+      </c>
+      <c r="AO243" t="n">
+        <v>24.3125</v>
+      </c>
+      <c r="AP243" t="n">
+        <v>179.6875</v>
+      </c>
+      <c r="AQ243" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AR243" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AS243" t="n">
+        <v>6357812.5</v>
+      </c>
+      <c r="AT243" t="n">
+        <v>76.8125</v>
+      </c>
+      <c r="AU243" t="n">
+        <v>27.10526315789474</v>
+      </c>
+      <c r="AV243" t="n">
+        <v>181.7368421052632</v>
+      </c>
+      <c r="AW243" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AX243" t="n">
+        <v>73.52631578947368</v>
+      </c>
+      <c r="AY243" t="n">
+        <v>5974210.52631579</v>
+      </c>
+      <c r="AZ243" t="n">
+        <v>75.63157894736842</v>
+      </c>
+      <c r="BA243" t="n">
+        <v>28.33333333333333</v>
+      </c>
+      <c r="BB243" t="n">
+        <v>174.3333333333333</v>
+      </c>
+      <c r="BC243" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD243" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE243" t="n">
+        <v>220</v>
+      </c>
+      <c r="BF243" t="n">
+        <v>11700000</v>
+      </c>
+      <c r="BG243" t="n">
+        <v>220</v>
+      </c>
+      <c r="BH243" t="n">
+        <v>21</v>
+      </c>
+      <c r="BI243" t="n">
+        <v>172</v>
+      </c>
+      <c r="BJ243" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK243" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL243" t="n">
+        <v>69</v>
+      </c>
+      <c r="BM243" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="BN243" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>QekfJmLa</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="n">
+        <v>45527.6875</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F244" t="n">
+        <v>34004</v>
+      </c>
+      <c r="G244" t="n">
+        <v>1</v>
+      </c>
+      <c r="H244" t="n">
+        <v>2</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="K244" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L244" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M244" t="n">
+        <v>60</v>
+      </c>
+      <c r="N244" t="n">
+        <v>40</v>
+      </c>
+      <c r="O244" t="n">
+        <v>16</v>
+      </c>
+      <c r="P244" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>9</v>
+      </c>
+      <c r="R244" t="n">
+        <v>5</v>
+      </c>
+      <c r="S244" t="n">
+        <v>16</v>
+      </c>
+      <c r="T244" t="n">
+        <v>8</v>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="W244" t="n">
+        <v>148</v>
+      </c>
+      <c r="X244" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y244" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z244" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC244" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AD244" t="n">
+        <v>186</v>
+      </c>
+      <c r="AE244" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AF244" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG244" t="n">
+        <v>11677777.77777778</v>
+      </c>
+      <c r="AH244" t="n">
+        <v>80</v>
+      </c>
+      <c r="AI244" t="inlineStr"/>
+      <c r="AJ244" t="inlineStr"/>
+      <c r="AK244" t="inlineStr"/>
+      <c r="AL244" t="inlineStr"/>
+      <c r="AM244" t="inlineStr"/>
+      <c r="AN244" t="inlineStr"/>
+      <c r="AO244" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="AP244" t="n">
+        <v>181.0666666666667</v>
+      </c>
+      <c r="AQ244" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR244" t="n">
+        <v>77.06666666666666</v>
+      </c>
+      <c r="AS244" t="n">
+        <v>12813333.33333333</v>
+      </c>
+      <c r="AT244" t="n">
+        <v>80.26666666666667</v>
+      </c>
+      <c r="AU244" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="AV244" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AW244" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX244" t="n">
+        <v>77.08333333333333</v>
+      </c>
+      <c r="AY244" t="n">
+        <v>10491666.66666667</v>
+      </c>
+      <c r="AZ244" t="n">
+        <v>79.58333333333333</v>
+      </c>
+      <c r="BA244" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB244" t="n">
+        <v>184</v>
+      </c>
+      <c r="BC244" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD244" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE244" t="n">
+        <v>78</v>
+      </c>
+      <c r="BF244" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="BG244" t="n">
+        <v>78</v>
+      </c>
+      <c r="BH244" t="n">
+        <v>27</v>
+      </c>
+      <c r="BI244" t="n">
+        <v>183</v>
+      </c>
+      <c r="BJ244" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BK244" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL244" t="n">
+        <v>233</v>
+      </c>
+      <c r="BM244" t="n">
+        <v>44500000</v>
+      </c>
+      <c r="BN244" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>8KIT2SzJ</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="n">
+        <v>45527.58333333334</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F245" t="n">
+        <v>23519</v>
+      </c>
+      <c r="G245" t="n">
+        <v>3</v>
+      </c>
+      <c r="H245" t="n">
+        <v>1</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="K245" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="L245" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M245" t="n">
+        <v>49</v>
+      </c>
+      <c r="N245" t="n">
+        <v>51</v>
+      </c>
+      <c r="O245" t="n">
+        <v>7</v>
+      </c>
+      <c r="P245" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>5</v>
+      </c>
+      <c r="R245" t="n">
+        <v>5</v>
+      </c>
+      <c r="S245" t="n">
+        <v>9</v>
+      </c>
+      <c r="T245" t="n">
+        <v>11</v>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="W245" t="n">
+        <v>148</v>
+      </c>
+      <c r="X245" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z245" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr"/>
+      <c r="AD245" t="inlineStr"/>
+      <c r="AE245" t="inlineStr"/>
+      <c r="AF245" t="inlineStr"/>
+      <c r="AG245" t="inlineStr"/>
+      <c r="AH245" t="inlineStr"/>
+      <c r="AI245" t="n">
+        <v>22.125</v>
+      </c>
+      <c r="AJ245" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AK245" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL245" t="n">
+        <v>72</v>
+      </c>
+      <c r="AM245" t="n">
+        <v>11602500</v>
+      </c>
+      <c r="AN245" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="AO245" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="AP245" t="n">
+        <v>180.1</v>
+      </c>
+      <c r="AQ245" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR245" t="n">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="AS245" t="n">
+        <v>10473750</v>
+      </c>
+      <c r="AT245" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="AU245" t="n">
+        <v>24.88235294117647</v>
+      </c>
+      <c r="AV245" t="n">
+        <v>178.7647058823529</v>
+      </c>
+      <c r="AW245" t="n">
+        <v>1.058823529411765</v>
+      </c>
+      <c r="AX245" t="n">
+        <v>70.70588235294117</v>
+      </c>
+      <c r="AY245" t="n">
+        <v>6037941.176470588</v>
+      </c>
+      <c r="AZ245" t="n">
+        <v>75.94117647058823</v>
+      </c>
+      <c r="BA245" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB245" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="BC245" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD245" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE245" t="n">
+        <v>146</v>
+      </c>
+      <c r="BF245" t="n">
+        <v>6900000</v>
+      </c>
+      <c r="BG245" t="n">
+        <v>149</v>
+      </c>
+      <c r="BH245" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="BI245" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="BJ245" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BK245" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL245" t="n">
+        <v>376</v>
+      </c>
+      <c r="BM245" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="BN245" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>fcYpyo85</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="n">
+        <v>45528.58333333334</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrera r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi ciutat de valencia
+  valencia </t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>26354</v>
+      </c>
+      <c r="F246" t="n">
+        <v>14068</v>
+      </c>
+      <c r="G246" t="n">
+        <v>1</v>
+      </c>
+      <c r="H246" t="n">
+        <v>1</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="n">
+        <v>44</v>
+      </c>
+      <c r="N246" t="n">
+        <v>56</v>
+      </c>
+      <c r="O246" t="n">
+        <v>17</v>
+      </c>
+      <c r="P246" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>6</v>
+      </c>
+      <c r="R246" t="n">
+        <v>8</v>
+      </c>
+      <c r="S246" t="n">
+        <v>16</v>
+      </c>
+      <c r="T246" t="n">
+        <v>16</v>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>fiZxGYJ3</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="W246" t="n">
+        <v>148</v>
+      </c>
+      <c r="X246" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z246" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr"/>
+      <c r="AD246" t="inlineStr"/>
+      <c r="AE246" t="inlineStr"/>
+      <c r="AF246" t="inlineStr"/>
+      <c r="AG246" t="inlineStr"/>
+      <c r="AH246" t="inlineStr"/>
+      <c r="AI246" t="n">
+        <v>28.875</v>
+      </c>
+      <c r="AJ246" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AK246" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AL246" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="AM246" t="n">
+        <v>5112500</v>
+      </c>
+      <c r="AN246" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="AO246" t="n">
+        <v>23.90909090909091</v>
+      </c>
+      <c r="AP246" t="n">
+        <v>180.0909090909091</v>
+      </c>
+      <c r="AQ246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR246" t="n">
+        <v>67.18181818181819</v>
+      </c>
+      <c r="AS246" t="n">
+        <v>1709090.909090909</v>
+      </c>
+      <c r="AT246" t="n">
+        <v>72</v>
+      </c>
+      <c r="AU246" t="n">
+        <v>26.46153846153846</v>
+      </c>
+      <c r="AV246" t="n">
+        <v>179.3076923076923</v>
+      </c>
+      <c r="AW246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX246" t="n">
+        <v>70.15384615384616</v>
+      </c>
+      <c r="AY246" t="n">
+        <v>2317307.692307692</v>
+      </c>
+      <c r="AZ246" t="n">
+        <v>72.53846153846153</v>
+      </c>
+      <c r="BA246" t="inlineStr"/>
+      <c r="BB246" t="inlineStr"/>
+      <c r="BC246" t="inlineStr"/>
+      <c r="BD246" t="inlineStr"/>
+      <c r="BE246" t="inlineStr"/>
+      <c r="BF246" t="inlineStr"/>
+      <c r="BG246" t="inlineStr"/>
+      <c r="BH246" t="inlineStr"/>
+      <c r="BI246" t="inlineStr"/>
+      <c r="BJ246" t="inlineStr"/>
+      <c r="BK246" t="inlineStr"/>
+      <c r="BL246" t="inlineStr"/>
+      <c r="BM246" t="inlineStr"/>
+      <c r="BN246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>fqgCMogC</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="n">
+        <v>45528.5</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuentes molina a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal da malata
+  ferrol </t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>10450</v>
+      </c>
+      <c r="F247" t="n">
+        <v>7397</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="n">
+        <v>1</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="n">
+        <v>48</v>
+      </c>
+      <c r="N247" t="n">
+        <v>52</v>
+      </c>
+      <c r="O247" t="n">
+        <v>18</v>
+      </c>
+      <c r="P247" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>3</v>
+      </c>
+      <c r="R247" t="n">
+        <v>7</v>
+      </c>
+      <c r="S247" t="n">
+        <v>12</v>
+      </c>
+      <c r="T247" t="n">
+        <v>18</v>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>K4dMCgFa</t>
+        </is>
+      </c>
+      <c r="W247" t="n">
+        <v>148</v>
+      </c>
+      <c r="X247" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AC247" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AD247" t="n">
+        <v>179.125</v>
+      </c>
+      <c r="AE247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF247" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="AG247" t="n">
+        <v>1190625</v>
+      </c>
+      <c r="AH247" t="n">
+        <v>69.875</v>
+      </c>
+      <c r="AI247" t="n">
+        <v>26.44444444444444</v>
+      </c>
+      <c r="AJ247" t="n">
+        <v>179.4444444444445</v>
+      </c>
+      <c r="AK247" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL247" t="n">
+        <v>73</v>
+      </c>
+      <c r="AM247" t="n">
+        <v>4133333.333333333</v>
+      </c>
+      <c r="AN247" t="n">
+        <v>75.11111111111111</v>
+      </c>
+      <c r="AO247" t="n">
+        <v>26.78571428571428</v>
+      </c>
+      <c r="AP247" t="n">
+        <v>175.8571428571429</v>
+      </c>
+      <c r="AQ247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR247" t="n">
+        <v>67.92857142857143</v>
+      </c>
+      <c r="AS247" t="n">
+        <v>1678571.428571429</v>
+      </c>
+      <c r="AT247" t="n">
+        <v>70.85714285714286</v>
+      </c>
+      <c r="AU247" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AV247" t="n">
+        <v>181.1818181818182</v>
+      </c>
+      <c r="AW247" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="AX247" t="n">
+        <v>70.68181818181819</v>
+      </c>
+      <c r="AY247" t="n">
+        <v>3993181.818181818</v>
+      </c>
+      <c r="AZ247" t="n">
+        <v>74.45454545454545</v>
+      </c>
+      <c r="BA247" t="inlineStr"/>
+      <c r="BB247" t="inlineStr"/>
+      <c r="BC247" t="inlineStr"/>
+      <c r="BD247" t="inlineStr"/>
+      <c r="BE247" t="inlineStr"/>
+      <c r="BF247" t="inlineStr"/>
+      <c r="BG247" t="inlineStr"/>
+      <c r="BH247" t="inlineStr"/>
+      <c r="BI247" t="inlineStr"/>
+      <c r="BJ247" t="inlineStr"/>
+      <c r="BK247" t="inlineStr"/>
+      <c r="BL247" t="inlineStr"/>
+      <c r="BM247" t="inlineStr"/>
+      <c r="BN247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>QwI4i6hn</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="n">
+        <v>45528.5</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el molinon
+  gijon </t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>29029</v>
+      </c>
+      <c r="F248" t="n">
+        <v>20890</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" t="n">
+        <v>0</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="n">
+        <v>60</v>
+      </c>
+      <c r="N248" t="n">
+        <v>40</v>
+      </c>
+      <c r="O248" t="n">
+        <v>21</v>
+      </c>
+      <c r="P248" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>4</v>
+      </c>
+      <c r="R248" t="n">
+        <v>4</v>
+      </c>
+      <c r="S248" t="n">
+        <v>10</v>
+      </c>
+      <c r="T248" t="n">
+        <v>6</v>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>hh4xt2Df</t>
+        </is>
+      </c>
+      <c r="W248" t="n">
+        <v>148</v>
+      </c>
+      <c r="X248" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z248" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA248" t="inlineStr"/>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="AC248" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AD248" t="n">
+        <v>178.7</v>
+      </c>
+      <c r="AE248" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF248" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AG248" t="n">
+        <v>2395000</v>
+      </c>
+      <c r="AH248" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AI248" t="inlineStr"/>
+      <c r="AJ248" t="inlineStr"/>
+      <c r="AK248" t="inlineStr"/>
+      <c r="AL248" t="inlineStr"/>
+      <c r="AM248" t="inlineStr"/>
+      <c r="AN248" t="inlineStr"/>
+      <c r="AO248" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP248" t="n">
+        <v>178</v>
+      </c>
+      <c r="AQ248" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR248" t="n">
+        <v>69.44444444444444</v>
+      </c>
+      <c r="AS248" t="n">
+        <v>2577777.777777778</v>
+      </c>
+      <c r="AT248" t="n">
+        <v>74</v>
+      </c>
+      <c r="AU248" t="n">
+        <v>28.05882352941176</v>
+      </c>
+      <c r="AV248" t="n">
+        <v>178.2941176470588</v>
+      </c>
+      <c r="AW248" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX248" t="n">
+        <v>66.11764705882354</v>
+      </c>
+      <c r="AY248" t="n">
+        <v>935588.2352941176</v>
+      </c>
+      <c r="AZ248" t="n">
+        <v>68.94117647058823</v>
+      </c>
+      <c r="BA248" t="inlineStr"/>
+      <c r="BB248" t="inlineStr"/>
+      <c r="BC248" t="inlineStr"/>
+      <c r="BD248" t="inlineStr"/>
+      <c r="BE248" t="inlineStr"/>
+      <c r="BF248" t="inlineStr"/>
+      <c r="BG248" t="inlineStr"/>
+      <c r="BH248" t="inlineStr"/>
+      <c r="BI248" t="inlineStr"/>
+      <c r="BJ248" t="inlineStr"/>
+      <c r="BK248" t="inlineStr"/>
+      <c r="BL248" t="inlineStr"/>
+      <c r="BM248" t="inlineStr"/>
+      <c r="BN248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>jPRgZOxI</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="n">
+        <v>45527.6875</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">galech i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el alcoraz
+  huesca </t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F249" t="n">
+        <v>6172</v>
+      </c>
+      <c r="G249" t="n">
+        <v>2</v>
+      </c>
+      <c r="H249" t="n">
+        <v>1</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="n">
+        <v>43</v>
+      </c>
+      <c r="N249" t="n">
+        <v>57</v>
+      </c>
+      <c r="O249" t="n">
+        <v>10</v>
+      </c>
+      <c r="P249" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>4</v>
+      </c>
+      <c r="R249" t="n">
+        <v>4</v>
+      </c>
+      <c r="S249" t="n">
+        <v>13</v>
+      </c>
+      <c r="T249" t="n">
+        <v>5</v>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="W249" t="n">
+        <v>148</v>
+      </c>
+      <c r="X249" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr"/>
+      <c r="AC249" t="inlineStr"/>
+      <c r="AD249" t="inlineStr"/>
+      <c r="AE249" t="inlineStr"/>
+      <c r="AF249" t="inlineStr"/>
+      <c r="AG249" t="inlineStr"/>
+      <c r="AH249" t="inlineStr"/>
+      <c r="AI249" t="inlineStr"/>
+      <c r="AJ249" t="inlineStr"/>
+      <c r="AK249" t="inlineStr"/>
+      <c r="AL249" t="inlineStr"/>
+      <c r="AM249" t="inlineStr"/>
+      <c r="AN249" t="inlineStr"/>
+      <c r="AO249" t="n">
+        <v>24.91666666666667</v>
+      </c>
+      <c r="AP249" t="n">
+        <v>178.75</v>
+      </c>
+      <c r="AQ249" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR249" t="n">
+        <v>66.33333333333333</v>
+      </c>
+      <c r="AS249" t="n">
+        <v>1304166.666666667</v>
+      </c>
+      <c r="AT249" t="n">
+        <v>70.83333333333333</v>
+      </c>
+      <c r="AU249" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AV249" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AW249" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX249" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AY249" t="n">
+        <v>1515625</v>
+      </c>
+      <c r="AZ249" t="n">
+        <v>70.875</v>
+      </c>
+      <c r="BA249" t="inlineStr"/>
+      <c r="BB249" t="inlineStr"/>
+      <c r="BC249" t="inlineStr"/>
+      <c r="BD249" t="inlineStr"/>
+      <c r="BE249" t="inlineStr"/>
+      <c r="BF249" t="inlineStr"/>
+      <c r="BG249" t="inlineStr"/>
+      <c r="BH249" t="inlineStr"/>
+      <c r="BI249" t="inlineStr"/>
+      <c r="BJ249" t="inlineStr"/>
+      <c r="BK249" t="inlineStr"/>
+      <c r="BL249" t="inlineStr"/>
+      <c r="BM249" t="inlineStr"/>
+      <c r="BN249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>OxQ1X27U</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="n">
+        <v>45527.58333333334</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sardinero
+  santander </t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>22222</v>
+      </c>
+      <c r="F250" t="n">
+        <v>19205</v>
+      </c>
+      <c r="G250" t="n">
+        <v>2</v>
+      </c>
+      <c r="H250" t="n">
+        <v>2</v>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="n">
+        <v>54</v>
+      </c>
+      <c r="N250" t="n">
+        <v>46</v>
+      </c>
+      <c r="O250" t="n">
+        <v>15</v>
+      </c>
+      <c r="P250" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>6</v>
+      </c>
+      <c r="R250" t="n">
+        <v>3</v>
+      </c>
+      <c r="S250" t="n">
+        <v>11</v>
+      </c>
+      <c r="T250" t="n">
+        <v>14</v>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>rak12p9n</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="W250" t="n">
+        <v>148</v>
+      </c>
+      <c r="X250" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z250" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA250" t="inlineStr"/>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr"/>
+      <c r="AD250" t="inlineStr"/>
+      <c r="AE250" t="inlineStr"/>
+      <c r="AF250" t="inlineStr"/>
+      <c r="AG250" t="inlineStr"/>
+      <c r="AH250" t="inlineStr"/>
+      <c r="AI250" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ250" t="n">
+        <v>180.375</v>
+      </c>
+      <c r="AK250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL250" t="n">
+        <v>68.625</v>
+      </c>
+      <c r="AM250" t="n">
+        <v>1675000</v>
+      </c>
+      <c r="AN250" t="n">
+        <v>74.125</v>
+      </c>
+      <c r="AO250" t="n">
+        <v>25.35714285714286</v>
+      </c>
+      <c r="AP250" t="n">
+        <v>180.2142857142857</v>
+      </c>
+      <c r="AQ250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR250" t="n">
+        <v>67</v>
+      </c>
+      <c r="AS250" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AT250" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AU250" t="n">
+        <v>23.11111111111111</v>
+      </c>
+      <c r="AV250" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AW250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX250" t="n">
+        <v>66</v>
+      </c>
+      <c r="AY250" t="n">
+        <v>1869444.444444444</v>
+      </c>
+      <c r="AZ250" t="n">
+        <v>73.22222222222223</v>
+      </c>
+      <c r="BA250" t="inlineStr"/>
+      <c r="BB250" t="inlineStr"/>
+      <c r="BC250" t="inlineStr"/>
+      <c r="BD250" t="inlineStr"/>
+      <c r="BE250" t="inlineStr"/>
+      <c r="BF250" t="inlineStr"/>
+      <c r="BG250" t="inlineStr"/>
+      <c r="BH250" t="inlineStr"/>
+      <c r="BI250" t="inlineStr"/>
+      <c r="BJ250" t="inlineStr"/>
+      <c r="BK250" t="inlineStr"/>
+      <c r="BL250" t="inlineStr"/>
+      <c r="BM250" t="inlineStr"/>
+      <c r="BN250" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN250"/>
+  <dimension ref="A1:BN258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48661,6 +48661,1510 @@
       <c r="BM250" t="inlineStr"/>
       <c r="BN250" t="inlineStr"/>
     </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="n">
+        <v>45529.59375</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F251" t="n">
+        <v>16623</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0</v>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="K251" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L251" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M251" t="n">
+        <v>39</v>
+      </c>
+      <c r="N251" t="n">
+        <v>61</v>
+      </c>
+      <c r="O251" t="n">
+        <v>3</v>
+      </c>
+      <c r="P251" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>1</v>
+      </c>
+      <c r="R251" t="n">
+        <v>3</v>
+      </c>
+      <c r="S251" t="n">
+        <v>16</v>
+      </c>
+      <c r="T251" t="n">
+        <v>13</v>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="W251" t="n">
+        <v>148</v>
+      </c>
+      <c r="X251" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z251" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA251" t="inlineStr"/>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr"/>
+      <c r="AD251" t="inlineStr"/>
+      <c r="AE251" t="inlineStr"/>
+      <c r="AF251" t="inlineStr"/>
+      <c r="AG251" t="inlineStr"/>
+      <c r="AH251" t="inlineStr"/>
+      <c r="AI251" t="inlineStr"/>
+      <c r="AJ251" t="inlineStr"/>
+      <c r="AK251" t="inlineStr"/>
+      <c r="AL251" t="inlineStr"/>
+      <c r="AM251" t="inlineStr"/>
+      <c r="AN251" t="inlineStr"/>
+      <c r="AO251" t="n">
+        <v>23.53333333333333</v>
+      </c>
+      <c r="AP251" t="n">
+        <v>177.9333333333333</v>
+      </c>
+      <c r="AQ251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR251" t="n">
+        <v>71.46666666666667</v>
+      </c>
+      <c r="AS251" t="n">
+        <v>3713333.333333333</v>
+      </c>
+      <c r="AT251" t="n">
+        <v>76.53333333333333</v>
+      </c>
+      <c r="AU251" t="n">
+        <v>23.85714285714286</v>
+      </c>
+      <c r="AV251" t="n">
+        <v>182</v>
+      </c>
+      <c r="AW251" t="n">
+        <v>1.714285714285714</v>
+      </c>
+      <c r="AX251" t="n">
+        <v>73.57142857142857</v>
+      </c>
+      <c r="AY251" t="n">
+        <v>6514285.714285715</v>
+      </c>
+      <c r="AZ251" t="n">
+        <v>79.85714285714286</v>
+      </c>
+      <c r="BA251" t="inlineStr"/>
+      <c r="BB251" t="inlineStr"/>
+      <c r="BC251" t="inlineStr"/>
+      <c r="BD251" t="inlineStr"/>
+      <c r="BE251" t="inlineStr"/>
+      <c r="BF251" t="inlineStr"/>
+      <c r="BG251" t="inlineStr"/>
+      <c r="BH251" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="BI251" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="BJ251" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BK251" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL251" t="n">
+        <v>285</v>
+      </c>
+      <c r="BM251" t="n">
+        <v>29350000</v>
+      </c>
+      <c r="BN251" t="n">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="n">
+        <v>45529.58333333334</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F252" t="n">
+        <v>10052</v>
+      </c>
+      <c r="G252" t="n">
+        <v>2</v>
+      </c>
+      <c r="H252" t="n">
+        <v>1</v>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="K252" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="L252" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M252" t="n">
+        <v>40</v>
+      </c>
+      <c r="N252" t="n">
+        <v>60</v>
+      </c>
+      <c r="O252" t="n">
+        <v>10</v>
+      </c>
+      <c r="P252" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>5</v>
+      </c>
+      <c r="R252" t="n">
+        <v>5</v>
+      </c>
+      <c r="S252" t="n">
+        <v>11</v>
+      </c>
+      <c r="T252" t="n">
+        <v>10</v>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="W252" t="n">
+        <v>148</v>
+      </c>
+      <c r="X252" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z252" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr"/>
+      <c r="AD252" t="inlineStr"/>
+      <c r="AE252" t="inlineStr"/>
+      <c r="AF252" t="inlineStr"/>
+      <c r="AG252" t="inlineStr"/>
+      <c r="AH252" t="inlineStr"/>
+      <c r="AI252" t="inlineStr"/>
+      <c r="AJ252" t="inlineStr"/>
+      <c r="AK252" t="inlineStr"/>
+      <c r="AL252" t="inlineStr"/>
+      <c r="AM252" t="inlineStr"/>
+      <c r="AN252" t="inlineStr"/>
+      <c r="AO252" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP252" t="n">
+        <v>180.8</v>
+      </c>
+      <c r="AQ252" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AR252" t="n">
+        <v>70.55</v>
+      </c>
+      <c r="AS252" t="n">
+        <v>4871250</v>
+      </c>
+      <c r="AT252" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="AU252" t="n">
+        <v>25.14285714285714</v>
+      </c>
+      <c r="AV252" t="n">
+        <v>176.4285714285714</v>
+      </c>
+      <c r="AW252" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AX252" t="n">
+        <v>74.21428571428571</v>
+      </c>
+      <c r="AY252" t="n">
+        <v>7907142.857142857</v>
+      </c>
+      <c r="AZ252" t="n">
+        <v>77.42857142857143</v>
+      </c>
+      <c r="BA252" t="inlineStr"/>
+      <c r="BB252" t="inlineStr"/>
+      <c r="BC252" t="inlineStr"/>
+      <c r="BD252" t="inlineStr"/>
+      <c r="BE252" t="inlineStr"/>
+      <c r="BF252" t="inlineStr"/>
+      <c r="BG252" t="inlineStr"/>
+      <c r="BH252" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="BI252" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="BJ252" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BK252" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL252" t="n">
+        <v>219</v>
+      </c>
+      <c r="BM252" t="n">
+        <v>15400000</v>
+      </c>
+      <c r="BN252" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F253" t="n">
+        <v>70178</v>
+      </c>
+      <c r="G253" t="n">
+        <v>3</v>
+      </c>
+      <c r="H253" t="n">
+        <v>0</v>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="K253" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="L253" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M253" t="n">
+        <v>64</v>
+      </c>
+      <c r="N253" t="n">
+        <v>36</v>
+      </c>
+      <c r="O253" t="n">
+        <v>17</v>
+      </c>
+      <c r="P253" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>9</v>
+      </c>
+      <c r="R253" t="n">
+        <v>2</v>
+      </c>
+      <c r="S253" t="n">
+        <v>10</v>
+      </c>
+      <c r="T253" t="n">
+        <v>15</v>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="W253" t="n">
+        <v>148</v>
+      </c>
+      <c r="X253" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z253" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="AC253" t="n">
+        <v>25.11111111111111</v>
+      </c>
+      <c r="AD253" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="AE253" t="n">
+        <v>3.222222222222222</v>
+      </c>
+      <c r="AF253" t="n">
+        <v>85.33333333333333</v>
+      </c>
+      <c r="AG253" t="n">
+        <v>74944444.44444445</v>
+      </c>
+      <c r="AH253" t="n">
+        <v>89</v>
+      </c>
+      <c r="AI253" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="AJ253" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="AK253" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AL253" t="n">
+        <v>71.625</v>
+      </c>
+      <c r="AM253" t="n">
+        <v>4487500</v>
+      </c>
+      <c r="AN253" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="AO253" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP253" t="n">
+        <v>175</v>
+      </c>
+      <c r="AQ253" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AR253" t="n">
+        <v>80.08333333333333</v>
+      </c>
+      <c r="AS253" t="n">
+        <v>40756250</v>
+      </c>
+      <c r="AT253" t="n">
+        <v>84.41666666666667</v>
+      </c>
+      <c r="AU253" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AV253" t="n">
+        <v>178.5555555555555</v>
+      </c>
+      <c r="AW253" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="AX253" t="n">
+        <v>70.88888888888889</v>
+      </c>
+      <c r="AY253" t="n">
+        <v>3048611.111111111</v>
+      </c>
+      <c r="AZ253" t="n">
+        <v>74.44444444444444</v>
+      </c>
+      <c r="BA253" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB253" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="BC253" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BD253" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE253" t="n">
+        <v>411</v>
+      </c>
+      <c r="BF253" t="n">
+        <v>267600000</v>
+      </c>
+      <c r="BG253" t="n">
+        <v>423</v>
+      </c>
+      <c r="BH253" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI253" t="n">
+        <v>174</v>
+      </c>
+      <c r="BJ253" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK253" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL253" t="n">
+        <v>69</v>
+      </c>
+      <c r="BM253" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="BN253" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="n">
+        <v>45528.6875</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F254" t="n">
+        <v>20900</v>
+      </c>
+      <c r="G254" t="n">
+        <v>0</v>
+      </c>
+      <c r="H254" t="n">
+        <v>1</v>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="K254" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L254" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="M254" t="n">
+        <v>34</v>
+      </c>
+      <c r="N254" t="n">
+        <v>66</v>
+      </c>
+      <c r="O254" t="n">
+        <v>13</v>
+      </c>
+      <c r="P254" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>3</v>
+      </c>
+      <c r="R254" t="n">
+        <v>4</v>
+      </c>
+      <c r="S254" t="n">
+        <v>14</v>
+      </c>
+      <c r="T254" t="n">
+        <v>18</v>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="W254" t="n">
+        <v>148</v>
+      </c>
+      <c r="X254" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z254" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr"/>
+      <c r="AC254" t="inlineStr"/>
+      <c r="AD254" t="inlineStr"/>
+      <c r="AE254" t="inlineStr"/>
+      <c r="AF254" t="inlineStr"/>
+      <c r="AG254" t="inlineStr"/>
+      <c r="AH254" t="inlineStr"/>
+      <c r="AI254" t="n">
+        <v>26.625</v>
+      </c>
+      <c r="AJ254" t="n">
+        <v>182.125</v>
+      </c>
+      <c r="AK254" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL254" t="n">
+        <v>79.125</v>
+      </c>
+      <c r="AM254" t="n">
+        <v>23025000</v>
+      </c>
+      <c r="AN254" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="AO254" t="n">
+        <v>26.17647058823529</v>
+      </c>
+      <c r="AP254" t="n">
+        <v>178.5882352941177</v>
+      </c>
+      <c r="AQ254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR254" t="n">
+        <v>70.29411764705883</v>
+      </c>
+      <c r="AS254" t="n">
+        <v>2370588.235294118</v>
+      </c>
+      <c r="AT254" t="n">
+        <v>74.05882352941177</v>
+      </c>
+      <c r="AU254" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="AV254" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="AW254" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX254" t="n">
+        <v>73.05</v>
+      </c>
+      <c r="AY254" t="n">
+        <v>15505000</v>
+      </c>
+      <c r="AZ254" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="BA254" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB254" t="n">
+        <v>178</v>
+      </c>
+      <c r="BC254" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD254" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE254" t="n">
+        <v>74</v>
+      </c>
+      <c r="BF254" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="BG254" t="n">
+        <v>75</v>
+      </c>
+      <c r="BH254" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BI254" t="n">
+        <v>178.25</v>
+      </c>
+      <c r="BJ254" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK254" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL254" t="n">
+        <v>305</v>
+      </c>
+      <c r="BM254" t="n">
+        <v>53500000</v>
+      </c>
+      <c r="BN254" t="n">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="n">
+        <v>45528.6875</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F255" t="n">
+        <v>9529</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
+      <c r="H255" t="n">
+        <v>0</v>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="K255" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L255" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M255" t="n">
+        <v>48</v>
+      </c>
+      <c r="N255" t="n">
+        <v>52</v>
+      </c>
+      <c r="O255" t="n">
+        <v>12</v>
+      </c>
+      <c r="P255" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>0</v>
+      </c>
+      <c r="R255" t="n">
+        <v>1</v>
+      </c>
+      <c r="S255" t="n">
+        <v>16</v>
+      </c>
+      <c r="T255" t="n">
+        <v>18</v>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="W255" t="n">
+        <v>148</v>
+      </c>
+      <c r="X255" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z255" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="AC255" t="n">
+        <v>26.55555555555556</v>
+      </c>
+      <c r="AD255" t="n">
+        <v>180.4444444444445</v>
+      </c>
+      <c r="AE255" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AF255" t="n">
+        <v>74</v>
+      </c>
+      <c r="AG255" t="n">
+        <v>7963888.888888889</v>
+      </c>
+      <c r="AH255" t="n">
+        <v>77</v>
+      </c>
+      <c r="AI255" t="n">
+        <v>29.77777777777778</v>
+      </c>
+      <c r="AJ255" t="n">
+        <v>178.8888888888889</v>
+      </c>
+      <c r="AK255" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AL255" t="n">
+        <v>75.77777777777777</v>
+      </c>
+      <c r="AM255" t="n">
+        <v>6888888.888888889</v>
+      </c>
+      <c r="AN255" t="n">
+        <v>76.55555555555556</v>
+      </c>
+      <c r="AO255" t="n">
+        <v>23.83333333333333</v>
+      </c>
+      <c r="AP255" t="n">
+        <v>179.1666666666667</v>
+      </c>
+      <c r="AQ255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR255" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AS255" t="n">
+        <v>6772916.666666667</v>
+      </c>
+      <c r="AT255" t="n">
+        <v>77.41666666666667</v>
+      </c>
+      <c r="AU255" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AV255" t="n">
+        <v>176.1</v>
+      </c>
+      <c r="AW255" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AX255" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AY255" t="n">
+        <v>6730000</v>
+      </c>
+      <c r="AZ255" t="n">
+        <v>76</v>
+      </c>
+      <c r="BA255" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB255" t="n">
+        <v>182</v>
+      </c>
+      <c r="BC255" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD255" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE255" t="n">
+        <v>78</v>
+      </c>
+      <c r="BF255" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="BG255" t="n">
+        <v>79</v>
+      </c>
+      <c r="BH255" t="n">
+        <v>22</v>
+      </c>
+      <c r="BI255" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BJ255" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK255" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL255" t="n">
+        <v>133</v>
+      </c>
+      <c r="BM255" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="BN255" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>tEvOrxAE</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="n">
+        <v>45529.58333333334</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orellana m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio carlos belmonte
+  albacete </t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>17524</v>
+      </c>
+      <c r="F256" t="n">
+        <v>11400</v>
+      </c>
+      <c r="G256" t="n">
+        <v>1</v>
+      </c>
+      <c r="H256" t="n">
+        <v>0</v>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="n">
+        <v>22</v>
+      </c>
+      <c r="N256" t="n">
+        <v>78</v>
+      </c>
+      <c r="O256" t="n">
+        <v>8</v>
+      </c>
+      <c r="P256" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>2</v>
+      </c>
+      <c r="R256" t="n">
+        <v>4</v>
+      </c>
+      <c r="S256" t="n">
+        <v>14</v>
+      </c>
+      <c r="T256" t="n">
+        <v>8</v>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>zT9gi7i9</t>
+        </is>
+      </c>
+      <c r="W256" t="n">
+        <v>148</v>
+      </c>
+      <c r="X256" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z256" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr"/>
+      <c r="AD256" t="inlineStr"/>
+      <c r="AE256" t="inlineStr"/>
+      <c r="AF256" t="inlineStr"/>
+      <c r="AG256" t="inlineStr"/>
+      <c r="AH256" t="inlineStr"/>
+      <c r="AI256" t="inlineStr"/>
+      <c r="AJ256" t="inlineStr"/>
+      <c r="AK256" t="inlineStr"/>
+      <c r="AL256" t="inlineStr"/>
+      <c r="AM256" t="inlineStr"/>
+      <c r="AN256" t="inlineStr"/>
+      <c r="AO256" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AP256" t="n">
+        <v>180</v>
+      </c>
+      <c r="AQ256" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AR256" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="AS256" t="n">
+        <v>4843750</v>
+      </c>
+      <c r="AT256" t="n">
+        <v>72.08333333333333</v>
+      </c>
+      <c r="AU256" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AV256" t="n">
+        <v>180.2666666666667</v>
+      </c>
+      <c r="AW256" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX256" t="n">
+        <v>67</v>
+      </c>
+      <c r="AY256" t="n">
+        <v>1320000</v>
+      </c>
+      <c r="AZ256" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="BA256" t="inlineStr"/>
+      <c r="BB256" t="inlineStr"/>
+      <c r="BC256" t="inlineStr"/>
+      <c r="BD256" t="inlineStr"/>
+      <c r="BE256" t="inlineStr"/>
+      <c r="BF256" t="inlineStr"/>
+      <c r="BG256" t="inlineStr"/>
+      <c r="BH256" t="inlineStr"/>
+      <c r="BI256" t="inlineStr"/>
+      <c r="BJ256" t="inlineStr"/>
+      <c r="BK256" t="inlineStr"/>
+      <c r="BL256" t="inlineStr"/>
+      <c r="BM256" t="inlineStr"/>
+      <c r="BN256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>jBnLKPNO</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="n">
+        <v>45528.6875</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">muresan s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio la rosaleda
+  malaga </t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>30044</v>
+      </c>
+      <c r="F257" t="n">
+        <v>26066</v>
+      </c>
+      <c r="G257" t="n">
+        <v>1</v>
+      </c>
+      <c r="H257" t="n">
+        <v>1</v>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="n">
+        <v>65</v>
+      </c>
+      <c r="N257" t="n">
+        <v>35</v>
+      </c>
+      <c r="O257" t="n">
+        <v>8</v>
+      </c>
+      <c r="P257" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>3</v>
+      </c>
+      <c r="R257" t="n">
+        <v>3</v>
+      </c>
+      <c r="S257" t="n">
+        <v>21</v>
+      </c>
+      <c r="T257" t="n">
+        <v>23</v>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>tjXr7SAp</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="W257" t="n">
+        <v>148</v>
+      </c>
+      <c r="X257" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z257" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA257" t="inlineStr"/>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr"/>
+      <c r="AD257" t="inlineStr"/>
+      <c r="AE257" t="inlineStr"/>
+      <c r="AF257" t="inlineStr"/>
+      <c r="AG257" t="inlineStr"/>
+      <c r="AH257" t="inlineStr"/>
+      <c r="AI257" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="AJ257" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="AK257" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL257" t="n">
+        <v>65.625</v>
+      </c>
+      <c r="AM257" t="n">
+        <v>972500</v>
+      </c>
+      <c r="AN257" t="n">
+        <v>71.375</v>
+      </c>
+      <c r="AO257" t="n">
+        <v>21.71428571428572</v>
+      </c>
+      <c r="AP257" t="n">
+        <v>181.4285714285714</v>
+      </c>
+      <c r="AQ257" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR257" t="n">
+        <v>64.14285714285714</v>
+      </c>
+      <c r="AS257" t="n">
+        <v>1392857.142857143</v>
+      </c>
+      <c r="AT257" t="n">
+        <v>73.28571428571429</v>
+      </c>
+      <c r="AU257" t="n">
+        <v>20.46153846153846</v>
+      </c>
+      <c r="AV257" t="n">
+        <v>178.8461538461538</v>
+      </c>
+      <c r="AW257" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX257" t="n">
+        <v>64.84615384615384</v>
+      </c>
+      <c r="AY257" t="n">
+        <v>1555769.230769231</v>
+      </c>
+      <c r="AZ257" t="n">
+        <v>77.61538461538461</v>
+      </c>
+      <c r="BA257" t="inlineStr"/>
+      <c r="BB257" t="inlineStr"/>
+      <c r="BC257" t="inlineStr"/>
+      <c r="BD257" t="inlineStr"/>
+      <c r="BE257" t="inlineStr"/>
+      <c r="BF257" t="inlineStr"/>
+      <c r="BG257" t="inlineStr"/>
+      <c r="BH257" t="inlineStr"/>
+      <c r="BI257" t="inlineStr"/>
+      <c r="BJ257" t="inlineStr"/>
+      <c r="BK257" t="inlineStr"/>
+      <c r="BL257" t="inlineStr"/>
+      <c r="BM257" t="inlineStr"/>
+      <c r="BN257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>QHtUvT8t</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="n">
+        <v>45528.6875</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez lopez r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio heliodoro rodriguez lopez
+  santa cruz de tenerife </t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>22824</v>
+      </c>
+      <c r="F258" t="n">
+        <v>14308</v>
+      </c>
+      <c r="G258" t="n">
+        <v>0</v>
+      </c>
+      <c r="H258" t="n">
+        <v>1</v>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="n">
+        <v>41</v>
+      </c>
+      <c r="N258" t="n">
+        <v>59</v>
+      </c>
+      <c r="O258" t="n">
+        <v>12</v>
+      </c>
+      <c r="P258" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>5</v>
+      </c>
+      <c r="R258" t="n">
+        <v>2</v>
+      </c>
+      <c r="S258" t="n">
+        <v>11</v>
+      </c>
+      <c r="T258" t="n">
+        <v>9</v>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>UBD9uzt0</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="W258" t="n">
+        <v>148</v>
+      </c>
+      <c r="X258" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y258" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z258" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr"/>
+      <c r="AD258" t="inlineStr"/>
+      <c r="AE258" t="inlineStr"/>
+      <c r="AF258" t="inlineStr"/>
+      <c r="AG258" t="inlineStr"/>
+      <c r="AH258" t="inlineStr"/>
+      <c r="AI258" t="inlineStr"/>
+      <c r="AJ258" t="inlineStr"/>
+      <c r="AK258" t="inlineStr"/>
+      <c r="AL258" t="inlineStr"/>
+      <c r="AM258" t="inlineStr"/>
+      <c r="AN258" t="inlineStr"/>
+      <c r="AO258" t="n">
+        <v>28.22222222222222</v>
+      </c>
+      <c r="AP258" t="n">
+        <v>183.1111111111111</v>
+      </c>
+      <c r="AQ258" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR258" t="n">
+        <v>70.77777777777777</v>
+      </c>
+      <c r="AS258" t="n">
+        <v>1822222.222222222</v>
+      </c>
+      <c r="AT258" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="AU258" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="AV258" t="n">
+        <v>184.1333333333333</v>
+      </c>
+      <c r="AW258" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX258" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="AY258" t="n">
+        <v>3886666.666666667</v>
+      </c>
+      <c r="AZ258" t="n">
+        <v>76.86666666666666</v>
+      </c>
+      <c r="BA258" t="inlineStr"/>
+      <c r="BB258" t="inlineStr"/>
+      <c r="BC258" t="inlineStr"/>
+      <c r="BD258" t="inlineStr"/>
+      <c r="BE258" t="inlineStr"/>
+      <c r="BF258" t="inlineStr"/>
+      <c r="BG258" t="inlineStr"/>
+      <c r="BH258" t="inlineStr"/>
+      <c r="BI258" t="inlineStr"/>
+      <c r="BJ258" t="inlineStr"/>
+      <c r="BK258" t="inlineStr"/>
+      <c r="BL258" t="inlineStr"/>
+      <c r="BM258" t="inlineStr"/>
+      <c r="BN258" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN258"/>
+  <dimension ref="A1:BN264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50165,6 +50165,1114 @@
       <c r="BM258" t="inlineStr"/>
       <c r="BN258" t="inlineStr"/>
     </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="n">
+        <v>45531.58333333334</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>26020</v>
+      </c>
+      <c r="F259" t="n">
+        <v>20470</v>
+      </c>
+      <c r="G259" t="n">
+        <v>0</v>
+      </c>
+      <c r="H259" t="n">
+        <v>0</v>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="K259" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L259" t="n">
+        <v>1</v>
+      </c>
+      <c r="M259" t="n">
+        <v>47</v>
+      </c>
+      <c r="N259" t="n">
+        <v>53</v>
+      </c>
+      <c r="O259" t="n">
+        <v>12</v>
+      </c>
+      <c r="P259" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>4</v>
+      </c>
+      <c r="R259" t="n">
+        <v>7</v>
+      </c>
+      <c r="S259" t="n">
+        <v>15</v>
+      </c>
+      <c r="T259" t="n">
+        <v>10</v>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="W259" t="n">
+        <v>148</v>
+      </c>
+      <c r="X259" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z259" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AC259" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AD259" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="AE259" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF259" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="AG259" t="n">
+        <v>12060000</v>
+      </c>
+      <c r="AH259" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="AI259" t="n">
+        <v>26.375</v>
+      </c>
+      <c r="AJ259" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="AK259" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AL259" t="n">
+        <v>76.625</v>
+      </c>
+      <c r="AM259" t="n">
+        <v>13487500</v>
+      </c>
+      <c r="AN259" t="n">
+        <v>79.625</v>
+      </c>
+      <c r="AO259" t="n">
+        <v>27.88235294117647</v>
+      </c>
+      <c r="AP259" t="n">
+        <v>183.2941176470588</v>
+      </c>
+      <c r="AQ259" t="n">
+        <v>1.117647058823529</v>
+      </c>
+      <c r="AR259" t="n">
+        <v>73.70588235294117</v>
+      </c>
+      <c r="AS259" t="n">
+        <v>6800588.235294118</v>
+      </c>
+      <c r="AT259" t="n">
+        <v>75.70588235294117</v>
+      </c>
+      <c r="AU259" t="n">
+        <v>25.73333333333333</v>
+      </c>
+      <c r="AV259" t="n">
+        <v>182.5333333333333</v>
+      </c>
+      <c r="AW259" t="n">
+        <v>1.533333333333333</v>
+      </c>
+      <c r="AX259" t="n">
+        <v>74.26666666666667</v>
+      </c>
+      <c r="AY259" t="n">
+        <v>8006666.666666667</v>
+      </c>
+      <c r="AZ259" t="n">
+        <v>80.66666666666667</v>
+      </c>
+      <c r="BA259" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB259" t="n">
+        <v>172</v>
+      </c>
+      <c r="BC259" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD259" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE259" t="n">
+        <v>69</v>
+      </c>
+      <c r="BF259" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="BG259" t="n">
+        <v>81</v>
+      </c>
+      <c r="BH259" t="n">
+        <v>27</v>
+      </c>
+      <c r="BI259" t="n">
+        <v>181</v>
+      </c>
+      <c r="BJ259" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK259" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL259" t="n">
+        <v>159</v>
+      </c>
+      <c r="BM259" t="n">
+        <v>41000000</v>
+      </c>
+      <c r="BN259" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="n">
+        <v>45530.6875</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F260" t="n">
+        <v>19651</v>
+      </c>
+      <c r="G260" t="n">
+        <v>4</v>
+      </c>
+      <c r="H260" t="n">
+        <v>3</v>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="K260" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="L260" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="M260" t="n">
+        <v>45</v>
+      </c>
+      <c r="N260" t="n">
+        <v>55</v>
+      </c>
+      <c r="O260" t="n">
+        <v>24</v>
+      </c>
+      <c r="P260" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>9</v>
+      </c>
+      <c r="R260" t="n">
+        <v>8</v>
+      </c>
+      <c r="S260" t="n">
+        <v>8</v>
+      </c>
+      <c r="T260" t="n">
+        <v>7</v>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="W260" t="n">
+        <v>148</v>
+      </c>
+      <c r="X260" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr"/>
+      <c r="AD260" t="inlineStr"/>
+      <c r="AE260" t="inlineStr"/>
+      <c r="AF260" t="inlineStr"/>
+      <c r="AG260" t="inlineStr"/>
+      <c r="AH260" t="inlineStr"/>
+      <c r="AI260" t="n">
+        <v>26.22222222222222</v>
+      </c>
+      <c r="AJ260" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="AK260" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AL260" t="n">
+        <v>72.88888888888889</v>
+      </c>
+      <c r="AM260" t="n">
+        <v>7788888.888888889</v>
+      </c>
+      <c r="AN260" t="n">
+        <v>75.88888888888889</v>
+      </c>
+      <c r="AO260" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP260" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AQ260" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR260" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="AS260" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="AT260" t="n">
+        <v>79.875</v>
+      </c>
+      <c r="AU260" t="n">
+        <v>26.29411764705882</v>
+      </c>
+      <c r="AV260" t="n">
+        <v>178.1176470588235</v>
+      </c>
+      <c r="AW260" t="n">
+        <v>1.529411764705882</v>
+      </c>
+      <c r="AX260" t="n">
+        <v>74.64705882352941</v>
+      </c>
+      <c r="AY260" t="n">
+        <v>10710294.11764706</v>
+      </c>
+      <c r="AZ260" t="n">
+        <v>79.35294117647059</v>
+      </c>
+      <c r="BA260" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB260" t="n">
+        <v>183</v>
+      </c>
+      <c r="BC260" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BD260" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE260" t="n">
+        <v>233</v>
+      </c>
+      <c r="BF260" t="n">
+        <v>44500000</v>
+      </c>
+      <c r="BG260" t="n">
+        <v>236</v>
+      </c>
+      <c r="BH260" t="n">
+        <v>26</v>
+      </c>
+      <c r="BI260" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="BJ260" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK260" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL260" t="n">
+        <v>146</v>
+      </c>
+      <c r="BM260" t="n">
+        <v>6900000</v>
+      </c>
+      <c r="BN260" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="n">
+        <v>45529.6875</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>70460</v>
+      </c>
+      <c r="F261" t="n">
+        <v>60414</v>
+      </c>
+      <c r="G261" t="n">
+        <v>3</v>
+      </c>
+      <c r="H261" t="n">
+        <v>0</v>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="K261" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L261" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M261" t="n">
+        <v>42</v>
+      </c>
+      <c r="N261" t="n">
+        <v>58</v>
+      </c>
+      <c r="O261" t="n">
+        <v>11</v>
+      </c>
+      <c r="P261" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>6</v>
+      </c>
+      <c r="R261" t="n">
+        <v>5</v>
+      </c>
+      <c r="S261" t="n">
+        <v>11</v>
+      </c>
+      <c r="T261" t="n">
+        <v>11</v>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="W261" t="n">
+        <v>148</v>
+      </c>
+      <c r="X261" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA261" t="inlineStr"/>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr"/>
+      <c r="AD261" t="inlineStr"/>
+      <c r="AE261" t="inlineStr"/>
+      <c r="AF261" t="inlineStr"/>
+      <c r="AG261" t="inlineStr"/>
+      <c r="AH261" t="inlineStr"/>
+      <c r="AI261" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="AJ261" t="n">
+        <v>184.125</v>
+      </c>
+      <c r="AK261" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AL261" t="n">
+        <v>78.125</v>
+      </c>
+      <c r="AM261" t="n">
+        <v>22200000</v>
+      </c>
+      <c r="AN261" t="n">
+        <v>82.375</v>
+      </c>
+      <c r="AO261" t="n">
+        <v>26.27777777777778</v>
+      </c>
+      <c r="AP261" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="AQ261" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AR261" t="n">
+        <v>78.22222222222223</v>
+      </c>
+      <c r="AS261" t="n">
+        <v>21811111.11111111</v>
+      </c>
+      <c r="AT261" t="n">
+        <v>81.33333333333333</v>
+      </c>
+      <c r="AU261" t="n">
+        <v>23.76923076923077</v>
+      </c>
+      <c r="AV261" t="n">
+        <v>178.3076923076923</v>
+      </c>
+      <c r="AW261" t="n">
+        <v>1.153846153846154</v>
+      </c>
+      <c r="AX261" t="n">
+        <v>71.76923076923077</v>
+      </c>
+      <c r="AY261" t="n">
+        <v>8484615.384615384</v>
+      </c>
+      <c r="AZ261" t="n">
+        <v>79.46153846153847</v>
+      </c>
+      <c r="BA261" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB261" t="n">
+        <v>171</v>
+      </c>
+      <c r="BC261" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD261" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE261" t="n">
+        <v>81</v>
+      </c>
+      <c r="BF261" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="BG261" t="n">
+        <v>81</v>
+      </c>
+      <c r="BH261" t="n">
+        <v>20.66666666666667</v>
+      </c>
+      <c r="BI261" t="n">
+        <v>181</v>
+      </c>
+      <c r="BJ261" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK261" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL261" t="n">
+        <v>202</v>
+      </c>
+      <c r="BM261" t="n">
+        <v>13900000</v>
+      </c>
+      <c r="BN261" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>nXUxw7wg</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="n">
+        <v>45530.6875</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">muniz munoz c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo arcangel
+  cordoba </t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>21822</v>
+      </c>
+      <c r="F262" t="n">
+        <v>14415</v>
+      </c>
+      <c r="G262" t="n">
+        <v>2</v>
+      </c>
+      <c r="H262" t="n">
+        <v>2</v>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="n">
+        <v>54</v>
+      </c>
+      <c r="N262" t="n">
+        <v>46</v>
+      </c>
+      <c r="O262" t="n">
+        <v>11</v>
+      </c>
+      <c r="P262" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>4</v>
+      </c>
+      <c r="R262" t="n">
+        <v>5</v>
+      </c>
+      <c r="S262" t="n">
+        <v>17</v>
+      </c>
+      <c r="T262" t="n">
+        <v>11</v>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>l6JQtDqc</t>
+        </is>
+      </c>
+      <c r="W262" t="n">
+        <v>148</v>
+      </c>
+      <c r="X262" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA262" t="inlineStr"/>
+      <c r="AB262" t="inlineStr"/>
+      <c r="AC262" t="inlineStr"/>
+      <c r="AD262" t="inlineStr"/>
+      <c r="AE262" t="inlineStr"/>
+      <c r="AF262" t="inlineStr"/>
+      <c r="AG262" t="inlineStr"/>
+      <c r="AH262" t="inlineStr"/>
+      <c r="AI262" t="inlineStr"/>
+      <c r="AJ262" t="inlineStr"/>
+      <c r="AK262" t="inlineStr"/>
+      <c r="AL262" t="inlineStr"/>
+      <c r="AM262" t="inlineStr"/>
+      <c r="AN262" t="inlineStr"/>
+      <c r="AO262" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AP262" t="n">
+        <v>184.4</v>
+      </c>
+      <c r="AQ262" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR262" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="AS262" t="n">
+        <v>1220000</v>
+      </c>
+      <c r="AT262" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="AU262" t="n">
+        <v>23.16666666666667</v>
+      </c>
+      <c r="AV262" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="AW262" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX262" t="n">
+        <v>67.33333333333333</v>
+      </c>
+      <c r="AY262" t="n">
+        <v>2147916.666666667</v>
+      </c>
+      <c r="AZ262" t="n">
+        <v>74.16666666666667</v>
+      </c>
+      <c r="BA262" t="inlineStr"/>
+      <c r="BB262" t="inlineStr"/>
+      <c r="BC262" t="inlineStr"/>
+      <c r="BD262" t="inlineStr"/>
+      <c r="BE262" t="inlineStr"/>
+      <c r="BF262" t="inlineStr"/>
+      <c r="BG262" t="inlineStr"/>
+      <c r="BH262" t="inlineStr"/>
+      <c r="BI262" t="inlineStr"/>
+      <c r="BJ262" t="inlineStr"/>
+      <c r="BK262" t="inlineStr"/>
+      <c r="BL262" t="inlineStr"/>
+      <c r="BM262" t="inlineStr"/>
+      <c r="BN262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>Q31eQTgm</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="n">
+        <v>45530.58333333334</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cid camacho g 
+  esp </t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal cartagonova
+  cartagena </t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>13745</v>
+      </c>
+      <c r="F263" t="n">
+        <v>8800</v>
+      </c>
+      <c r="G263" t="n">
+        <v>1</v>
+      </c>
+      <c r="H263" t="n">
+        <v>2</v>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="n">
+        <v>40</v>
+      </c>
+      <c r="N263" t="n">
+        <v>60</v>
+      </c>
+      <c r="O263" t="n">
+        <v>9</v>
+      </c>
+      <c r="P263" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>3</v>
+      </c>
+      <c r="R263" t="n">
+        <v>8</v>
+      </c>
+      <c r="S263" t="n">
+        <v>10</v>
+      </c>
+      <c r="T263" t="n">
+        <v>14</v>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>M1vEw5An</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="W263" t="n">
+        <v>148</v>
+      </c>
+      <c r="X263" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr"/>
+      <c r="AD263" t="inlineStr"/>
+      <c r="AE263" t="inlineStr"/>
+      <c r="AF263" t="inlineStr"/>
+      <c r="AG263" t="inlineStr"/>
+      <c r="AH263" t="inlineStr"/>
+      <c r="AI263" t="n">
+        <v>23.55555555555556</v>
+      </c>
+      <c r="AJ263" t="n">
+        <v>176</v>
+      </c>
+      <c r="AK263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL263" t="n">
+        <v>67.55555555555556</v>
+      </c>
+      <c r="AM263" t="n">
+        <v>1777777.777777778</v>
+      </c>
+      <c r="AN263" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AO263" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP263" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="AQ263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR263" t="n">
+        <v>65.11111111111111</v>
+      </c>
+      <c r="AS263" t="n">
+        <v>916666.6666666666</v>
+      </c>
+      <c r="AT263" t="n">
+        <v>69.55555555555556</v>
+      </c>
+      <c r="AU263" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV263" t="n">
+        <v>178.4166666666667</v>
+      </c>
+      <c r="AW263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX263" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="AY263" t="n">
+        <v>2187500</v>
+      </c>
+      <c r="AZ263" t="n">
+        <v>74.58333333333333</v>
+      </c>
+      <c r="BA263" t="inlineStr"/>
+      <c r="BB263" t="inlineStr"/>
+      <c r="BC263" t="inlineStr"/>
+      <c r="BD263" t="inlineStr"/>
+      <c r="BE263" t="inlineStr"/>
+      <c r="BF263" t="inlineStr"/>
+      <c r="BG263" t="inlineStr"/>
+      <c r="BH263" t="inlineStr"/>
+      <c r="BI263" t="inlineStr"/>
+      <c r="BJ263" t="inlineStr"/>
+      <c r="BK263" t="inlineStr"/>
+      <c r="BL263" t="inlineStr"/>
+      <c r="BM263" t="inlineStr"/>
+      <c r="BN263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>MVf4O7Oa</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="n">
+        <v>45529.6875</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzalez esteban j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de castalia
+  castellon de la plana </t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>15500</v>
+      </c>
+      <c r="F264" t="n">
+        <v>13709</v>
+      </c>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" t="n">
+        <v>0</v>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="n">
+        <v>61</v>
+      </c>
+      <c r="N264" t="n">
+        <v>39</v>
+      </c>
+      <c r="O264" t="n">
+        <v>20</v>
+      </c>
+      <c r="P264" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>6</v>
+      </c>
+      <c r="R264" t="n">
+        <v>1</v>
+      </c>
+      <c r="S264" t="n">
+        <v>14</v>
+      </c>
+      <c r="T264" t="n">
+        <v>16</v>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="W264" t="n">
+        <v>148</v>
+      </c>
+      <c r="X264" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA264" t="inlineStr"/>
+      <c r="AB264" t="inlineStr"/>
+      <c r="AC264" t="inlineStr"/>
+      <c r="AD264" t="inlineStr"/>
+      <c r="AE264" t="inlineStr"/>
+      <c r="AF264" t="inlineStr"/>
+      <c r="AG264" t="inlineStr"/>
+      <c r="AH264" t="inlineStr"/>
+      <c r="AI264" t="inlineStr"/>
+      <c r="AJ264" t="inlineStr"/>
+      <c r="AK264" t="inlineStr"/>
+      <c r="AL264" t="inlineStr"/>
+      <c r="AM264" t="inlineStr"/>
+      <c r="AN264" t="inlineStr"/>
+      <c r="AO264" t="inlineStr"/>
+      <c r="AP264" t="inlineStr"/>
+      <c r="AQ264" t="inlineStr"/>
+      <c r="AR264" t="inlineStr"/>
+      <c r="AS264" t="inlineStr"/>
+      <c r="AT264" t="inlineStr"/>
+      <c r="AU264" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="AV264" t="n">
+        <v>179.2</v>
+      </c>
+      <c r="AW264" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AX264" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="AY264" t="n">
+        <v>2401250</v>
+      </c>
+      <c r="AZ264" t="n">
+        <v>75.65000000000001</v>
+      </c>
+      <c r="BA264" t="inlineStr"/>
+      <c r="BB264" t="inlineStr"/>
+      <c r="BC264" t="inlineStr"/>
+      <c r="BD264" t="inlineStr"/>
+      <c r="BE264" t="inlineStr"/>
+      <c r="BF264" t="inlineStr"/>
+      <c r="BG264" t="inlineStr"/>
+      <c r="BH264" t="inlineStr"/>
+      <c r="BI264" t="inlineStr"/>
+      <c r="BJ264" t="inlineStr"/>
+      <c r="BK264" t="inlineStr"/>
+      <c r="BL264" t="inlineStr"/>
+      <c r="BM264" t="inlineStr"/>
+      <c r="BN264" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN264"/>
+  <dimension ref="A1:BN273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51273,6 +51273,1758 @@
       <c r="BM264" t="inlineStr"/>
       <c r="BN264" t="inlineStr"/>
     </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="n">
+        <v>45533.6875</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F265" t="n">
+        <v>31192</v>
+      </c>
+      <c r="G265" t="n">
+        <v>1</v>
+      </c>
+      <c r="H265" t="n">
+        <v>1</v>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="K265" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L265" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M265" t="n">
+        <v>44</v>
+      </c>
+      <c r="N265" t="n">
+        <v>56</v>
+      </c>
+      <c r="O265" t="n">
+        <v>7</v>
+      </c>
+      <c r="P265" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>3</v>
+      </c>
+      <c r="R265" t="n">
+        <v>8</v>
+      </c>
+      <c r="S265" t="n">
+        <v>16</v>
+      </c>
+      <c r="T265" t="n">
+        <v>13</v>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="W265" t="n">
+        <v>148</v>
+      </c>
+      <c r="X265" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr"/>
+      <c r="AD265" t="inlineStr"/>
+      <c r="AE265" t="inlineStr"/>
+      <c r="AF265" t="inlineStr"/>
+      <c r="AG265" t="inlineStr"/>
+      <c r="AH265" t="inlineStr"/>
+      <c r="AI265" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AJ265" t="n">
+        <v>182.3</v>
+      </c>
+      <c r="AK265" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AL265" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="AM265" t="n">
+        <v>63280000</v>
+      </c>
+      <c r="AN265" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="AO265" t="n">
+        <v>24.30769230769231</v>
+      </c>
+      <c r="AP265" t="n">
+        <v>176.5384615384615</v>
+      </c>
+      <c r="AQ265" t="n">
+        <v>1.076923076923077</v>
+      </c>
+      <c r="AR265" t="n">
+        <v>73.07692307692308</v>
+      </c>
+      <c r="AS265" t="n">
+        <v>7965384.615384615</v>
+      </c>
+      <c r="AT265" t="n">
+        <v>77.69230769230769</v>
+      </c>
+      <c r="AU265" t="n">
+        <v>24.5625</v>
+      </c>
+      <c r="AV265" t="n">
+        <v>175.8125</v>
+      </c>
+      <c r="AW265" t="n">
+        <v>2.1875</v>
+      </c>
+      <c r="AX265" t="n">
+        <v>80</v>
+      </c>
+      <c r="AY265" t="n">
+        <v>42692187.5</v>
+      </c>
+      <c r="AZ265" t="n">
+        <v>84.875</v>
+      </c>
+      <c r="BA265" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB265" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BC265" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD265" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE265" t="n">
+        <v>150</v>
+      </c>
+      <c r="BF265" t="n">
+        <v>13800000</v>
+      </c>
+      <c r="BG265" t="n">
+        <v>150</v>
+      </c>
+      <c r="BH265" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="BI265" t="n">
+        <v>183</v>
+      </c>
+      <c r="BJ265" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK265" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL265" t="n">
+        <v>329</v>
+      </c>
+      <c r="BM265" t="n">
+        <v>240100000</v>
+      </c>
+      <c r="BN265" t="n">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="n">
+        <v>45533.58333333334</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F266" t="n">
+        <v>13275</v>
+      </c>
+      <c r="G266" t="n">
+        <v>4</v>
+      </c>
+      <c r="H266" t="n">
+        <v>0</v>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="K266" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="L266" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M266" t="n">
+        <v>60</v>
+      </c>
+      <c r="N266" t="n">
+        <v>40</v>
+      </c>
+      <c r="O266" t="n">
+        <v>10</v>
+      </c>
+      <c r="P266" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>5</v>
+      </c>
+      <c r="R266" t="n">
+        <v>0</v>
+      </c>
+      <c r="S266" t="n">
+        <v>10</v>
+      </c>
+      <c r="T266" t="n">
+        <v>9</v>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="W266" t="n">
+        <v>148</v>
+      </c>
+      <c r="X266" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="AB266" t="inlineStr"/>
+      <c r="AC266" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>183.875</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AF266" t="n">
+        <v>77</v>
+      </c>
+      <c r="AG266" t="n">
+        <v>18862500</v>
+      </c>
+      <c r="AH266" t="n">
+        <v>81.625</v>
+      </c>
+      <c r="AI266" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ266" t="n">
+        <v>184.2222222222222</v>
+      </c>
+      <c r="AK266" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL266" t="n">
+        <v>76.44444444444444</v>
+      </c>
+      <c r="AM266" t="n">
+        <v>11555555.55555556</v>
+      </c>
+      <c r="AN266" t="n">
+        <v>79.11111111111111</v>
+      </c>
+      <c r="AO266" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="AP266" t="n">
+        <v>179.2</v>
+      </c>
+      <c r="AQ266" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR266" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="AS266" t="n">
+        <v>13580000</v>
+      </c>
+      <c r="AT266" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="AU266" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AV266" t="n">
+        <v>181</v>
+      </c>
+      <c r="AW266" t="n">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="AX266" t="n">
+        <v>70.41666666666667</v>
+      </c>
+      <c r="AY266" t="n">
+        <v>5818750</v>
+      </c>
+      <c r="AZ266" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="BA266" t="n">
+        <v>20.66666666666667</v>
+      </c>
+      <c r="BB266" t="n">
+        <v>181</v>
+      </c>
+      <c r="BC266" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD266" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE266" t="n">
+        <v>202</v>
+      </c>
+      <c r="BF266" t="n">
+        <v>13900000</v>
+      </c>
+      <c r="BG266" t="n">
+        <v>237</v>
+      </c>
+      <c r="BH266" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="BI266" t="n">
+        <v>176</v>
+      </c>
+      <c r="BJ266" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK266" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL266" t="n">
+        <v>213</v>
+      </c>
+      <c r="BM266" t="n">
+        <v>11300000</v>
+      </c>
+      <c r="BN266" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>KhwykQ8L</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="n">
+        <v>45532.6875</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>70460</v>
+      </c>
+      <c r="F267" t="n">
+        <v>56669</v>
+      </c>
+      <c r="G267" t="n">
+        <v>0</v>
+      </c>
+      <c r="H267" t="n">
+        <v>0</v>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="K267" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="L267" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M267" t="n">
+        <v>62</v>
+      </c>
+      <c r="N267" t="n">
+        <v>38</v>
+      </c>
+      <c r="O267" t="n">
+        <v>25</v>
+      </c>
+      <c r="P267" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>7</v>
+      </c>
+      <c r="R267" t="n">
+        <v>1</v>
+      </c>
+      <c r="S267" t="n">
+        <v>6</v>
+      </c>
+      <c r="T267" t="n">
+        <v>9</v>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="W267" t="n">
+        <v>148</v>
+      </c>
+      <c r="X267" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA267" t="inlineStr"/>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr"/>
+      <c r="AD267" t="inlineStr"/>
+      <c r="AE267" t="inlineStr"/>
+      <c r="AF267" t="inlineStr"/>
+      <c r="AG267" t="inlineStr"/>
+      <c r="AH267" t="inlineStr"/>
+      <c r="AI267" t="inlineStr"/>
+      <c r="AJ267" t="inlineStr"/>
+      <c r="AK267" t="inlineStr"/>
+      <c r="AL267" t="inlineStr"/>
+      <c r="AM267" t="inlineStr"/>
+      <c r="AN267" t="inlineStr"/>
+      <c r="AO267" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AP267" t="n">
+        <v>178.3</v>
+      </c>
+      <c r="AQ267" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AR267" t="n">
+        <v>80.05</v>
+      </c>
+      <c r="AS267" t="n">
+        <v>29300000</v>
+      </c>
+      <c r="AT267" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="AU267" t="n">
+        <v>26.26666666666667</v>
+      </c>
+      <c r="AV267" t="n">
+        <v>180.2666666666667</v>
+      </c>
+      <c r="AW267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX267" t="n">
+        <v>70.93333333333334</v>
+      </c>
+      <c r="AY267" t="n">
+        <v>3013333.333333333</v>
+      </c>
+      <c r="AZ267" t="n">
+        <v>75</v>
+      </c>
+      <c r="BA267" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB267" t="n">
+        <v>171</v>
+      </c>
+      <c r="BC267" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD267" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE267" t="n">
+        <v>81</v>
+      </c>
+      <c r="BF267" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="BG267" t="n">
+        <v>81</v>
+      </c>
+      <c r="BH267" t="n">
+        <v>29</v>
+      </c>
+      <c r="BI267" t="n">
+        <v>184</v>
+      </c>
+      <c r="BJ267" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK267" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL267" t="n">
+        <v>146</v>
+      </c>
+      <c r="BM267" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="BN267" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>v1KiOZ2d</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="n">
+        <v>45532.6875</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F268" t="n">
+        <v>32220</v>
+      </c>
+      <c r="G268" t="n">
+        <v>1</v>
+      </c>
+      <c r="H268" t="n">
+        <v>2</v>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="K268" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L268" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M268" t="n">
+        <v>53</v>
+      </c>
+      <c r="N268" t="n">
+        <v>47</v>
+      </c>
+      <c r="O268" t="n">
+        <v>10</v>
+      </c>
+      <c r="P268" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>1</v>
+      </c>
+      <c r="R268" t="n">
+        <v>5</v>
+      </c>
+      <c r="S268" t="n">
+        <v>16</v>
+      </c>
+      <c r="T268" t="n">
+        <v>13</v>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="W268" t="n">
+        <v>148</v>
+      </c>
+      <c r="X268" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA268" t="inlineStr"/>
+      <c r="AB268" t="inlineStr"/>
+      <c r="AC268" t="n">
+        <v>26.375</v>
+      </c>
+      <c r="AD268" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="AE268" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF268" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="AG268" t="n">
+        <v>30125000</v>
+      </c>
+      <c r="AH268" t="n">
+        <v>83</v>
+      </c>
+      <c r="AI268" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="AJ268" t="n">
+        <v>181.625</v>
+      </c>
+      <c r="AK268" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL268" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="AM268" t="n">
+        <v>3587500</v>
+      </c>
+      <c r="AN268" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AO268" t="n">
+        <v>22.88888888888889</v>
+      </c>
+      <c r="AP268" t="n">
+        <v>181.8333333333333</v>
+      </c>
+      <c r="AQ268" t="n">
+        <v>1.277777777777778</v>
+      </c>
+      <c r="AR268" t="n">
+        <v>70.61111111111111</v>
+      </c>
+      <c r="AS268" t="n">
+        <v>7083333.333333333</v>
+      </c>
+      <c r="AT268" t="n">
+        <v>78.22222222222223</v>
+      </c>
+      <c r="AU268" t="n">
+        <v>24.27272727272727</v>
+      </c>
+      <c r="AV268" t="n">
+        <v>180.8181818181818</v>
+      </c>
+      <c r="AW268" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX268" t="n">
+        <v>69.63636363636364</v>
+      </c>
+      <c r="AY268" t="n">
+        <v>2536363.636363636</v>
+      </c>
+      <c r="AZ268" t="n">
+        <v>74.09090909090909</v>
+      </c>
+      <c r="BA268" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="BB268" t="n">
+        <v>178</v>
+      </c>
+      <c r="BC268" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD268" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE268" t="n">
+        <v>305</v>
+      </c>
+      <c r="BF268" t="n">
+        <v>46500000</v>
+      </c>
+      <c r="BG268" t="n">
+        <v>324</v>
+      </c>
+      <c r="BH268" t="n">
+        <v>31</v>
+      </c>
+      <c r="BI268" t="n">
+        <v>180</v>
+      </c>
+      <c r="BJ268" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK268" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL268" t="n">
+        <v>73</v>
+      </c>
+      <c r="BM268" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="BN268" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>0Y1WIvRG</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="n">
+        <v>45532.58333333334</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F269" t="n">
+        <v>48644</v>
+      </c>
+      <c r="G269" t="n">
+        <v>1</v>
+      </c>
+      <c r="H269" t="n">
+        <v>0</v>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="K269" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L269" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M269" t="n">
+        <v>51</v>
+      </c>
+      <c r="N269" t="n">
+        <v>49</v>
+      </c>
+      <c r="O269" t="n">
+        <v>13</v>
+      </c>
+      <c r="P269" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>4</v>
+      </c>
+      <c r="R269" t="n">
+        <v>0</v>
+      </c>
+      <c r="S269" t="n">
+        <v>14</v>
+      </c>
+      <c r="T269" t="n">
+        <v>9</v>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="W269" t="n">
+        <v>148</v>
+      </c>
+      <c r="X269" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA269" t="inlineStr"/>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr"/>
+      <c r="AD269" t="inlineStr"/>
+      <c r="AE269" t="inlineStr"/>
+      <c r="AF269" t="inlineStr"/>
+      <c r="AG269" t="inlineStr"/>
+      <c r="AH269" t="inlineStr"/>
+      <c r="AI269" t="n">
+        <v>23.88888888888889</v>
+      </c>
+      <c r="AJ269" t="n">
+        <v>182.8888888888889</v>
+      </c>
+      <c r="AK269" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="AL269" t="n">
+        <v>71.55555555555556</v>
+      </c>
+      <c r="AM269" t="n">
+        <v>9380000</v>
+      </c>
+      <c r="AN269" t="n">
+        <v>76.66666666666667</v>
+      </c>
+      <c r="AO269" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="AP269" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AQ269" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR269" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="AS269" t="n">
+        <v>15535000</v>
+      </c>
+      <c r="AT269" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="AU269" t="n">
+        <v>22.33333333333333</v>
+      </c>
+      <c r="AV269" t="n">
+        <v>176.4</v>
+      </c>
+      <c r="AW269" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="AX269" t="n">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="AY269" t="n">
+        <v>8109666.666666667</v>
+      </c>
+      <c r="AZ269" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="BA269" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="BB269" t="n">
+        <v>183</v>
+      </c>
+      <c r="BC269" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BD269" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE269" t="n">
+        <v>322</v>
+      </c>
+      <c r="BF269" t="n">
+        <v>92500000</v>
+      </c>
+      <c r="BG269" t="n">
+        <v>327</v>
+      </c>
+      <c r="BH269" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="BI269" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="BJ269" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BK269" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL269" t="n">
+        <v>447</v>
+      </c>
+      <c r="BM269" t="n">
+        <v>50500000</v>
+      </c>
+      <c r="BN269" t="n">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>f92vnwe3</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="n">
+        <v>45532.58333333334</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F270" t="n">
+        <v>21764</v>
+      </c>
+      <c r="G270" t="n">
+        <v>0</v>
+      </c>
+      <c r="H270" t="n">
+        <v>0</v>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="K270" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L270" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M270" t="n">
+        <v>58</v>
+      </c>
+      <c r="N270" t="n">
+        <v>42</v>
+      </c>
+      <c r="O270" t="n">
+        <v>12</v>
+      </c>
+      <c r="P270" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>2</v>
+      </c>
+      <c r="R270" t="n">
+        <v>1</v>
+      </c>
+      <c r="S270" t="n">
+        <v>13</v>
+      </c>
+      <c r="T270" t="n">
+        <v>19</v>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="W270" t="n">
+        <v>148</v>
+      </c>
+      <c r="X270" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="AC270" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD270" t="n">
+        <v>179.4444444444445</v>
+      </c>
+      <c r="AE270" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF270" t="n">
+        <v>70.55555555555556</v>
+      </c>
+      <c r="AG270" t="n">
+        <v>2666666.666666667</v>
+      </c>
+      <c r="AH270" t="n">
+        <v>74.44444444444444</v>
+      </c>
+      <c r="AI270" t="inlineStr"/>
+      <c r="AJ270" t="inlineStr"/>
+      <c r="AK270" t="inlineStr"/>
+      <c r="AL270" t="inlineStr"/>
+      <c r="AM270" t="inlineStr"/>
+      <c r="AN270" t="inlineStr"/>
+      <c r="AO270" t="n">
+        <v>23.5625</v>
+      </c>
+      <c r="AP270" t="n">
+        <v>181</v>
+      </c>
+      <c r="AQ270" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AR270" t="n">
+        <v>70.5625</v>
+      </c>
+      <c r="AS270" t="n">
+        <v>4100000</v>
+      </c>
+      <c r="AT270" t="n">
+        <v>77.6875</v>
+      </c>
+      <c r="AU270" t="n">
+        <v>26</v>
+      </c>
+      <c r="AV270" t="n">
+        <v>180.4761904761905</v>
+      </c>
+      <c r="AW270" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AX270" t="n">
+        <v>72.33333333333333</v>
+      </c>
+      <c r="AY270" t="n">
+        <v>5729761.904761905</v>
+      </c>
+      <c r="AZ270" t="n">
+        <v>75.52380952380952</v>
+      </c>
+      <c r="BA270" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB270" t="n">
+        <v>174</v>
+      </c>
+      <c r="BC270" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD270" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE270" t="n">
+        <v>69</v>
+      </c>
+      <c r="BF270" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="BG270" t="n">
+        <v>69</v>
+      </c>
+      <c r="BH270" t="inlineStr"/>
+      <c r="BI270" t="inlineStr"/>
+      <c r="BJ270" t="inlineStr"/>
+      <c r="BK270" t="inlineStr"/>
+      <c r="BL270" t="inlineStr"/>
+      <c r="BM270" t="inlineStr"/>
+      <c r="BN270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="n">
+        <v>45531.6875</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>14505</v>
+      </c>
+      <c r="F271" t="n">
+        <v>14031</v>
+      </c>
+      <c r="G271" t="n">
+        <v>1</v>
+      </c>
+      <c r="H271" t="n">
+        <v>2</v>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="K271" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L271" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M271" t="n">
+        <v>37</v>
+      </c>
+      <c r="N271" t="n">
+        <v>63</v>
+      </c>
+      <c r="O271" t="n">
+        <v>8</v>
+      </c>
+      <c r="P271" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>4</v>
+      </c>
+      <c r="R271" t="n">
+        <v>5</v>
+      </c>
+      <c r="S271" t="n">
+        <v>17</v>
+      </c>
+      <c r="T271" t="n">
+        <v>11</v>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="W271" t="n">
+        <v>148</v>
+      </c>
+      <c r="X271" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr"/>
+      <c r="AD271" t="inlineStr"/>
+      <c r="AE271" t="inlineStr"/>
+      <c r="AF271" t="inlineStr"/>
+      <c r="AG271" t="inlineStr"/>
+      <c r="AH271" t="inlineStr"/>
+      <c r="AI271" t="inlineStr"/>
+      <c r="AJ271" t="inlineStr"/>
+      <c r="AK271" t="inlineStr"/>
+      <c r="AL271" t="inlineStr"/>
+      <c r="AM271" t="inlineStr"/>
+      <c r="AN271" t="inlineStr"/>
+      <c r="AO271" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AP271" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="AQ271" t="n">
+        <v>1.266666666666667</v>
+      </c>
+      <c r="AR271" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="AS271" t="n">
+        <v>5306666.666666667</v>
+      </c>
+      <c r="AT271" t="n">
+        <v>75.53333333333333</v>
+      </c>
+      <c r="AU271" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="AV271" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="AW271" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AX271" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AY271" t="n">
+        <v>18035000</v>
+      </c>
+      <c r="AZ271" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="BA271" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BB271" t="n">
+        <v>181</v>
+      </c>
+      <c r="BC271" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD271" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE271" t="n">
+        <v>137</v>
+      </c>
+      <c r="BF271" t="n">
+        <v>11550000</v>
+      </c>
+      <c r="BG271" t="n">
+        <v>151</v>
+      </c>
+      <c r="BH271" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI271" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="BJ271" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK271" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL271" t="n">
+        <v>417</v>
+      </c>
+      <c r="BM271" t="n">
+        <v>334500000</v>
+      </c>
+      <c r="BN271" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>x2RBbu6T</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="n">
+        <v>45534.6875</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mallo e 
+  esp </t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo carlos tartiere
+  oviedo </t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>30500</v>
+      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="n">
+        <v>1</v>
+      </c>
+      <c r="H272" t="n">
+        <v>3</v>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>65</v>
+      </c>
+      <c r="N272" t="n">
+        <v>35</v>
+      </c>
+      <c r="O272" t="n">
+        <v>18</v>
+      </c>
+      <c r="P272" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>3</v>
+      </c>
+      <c r="R272" t="n">
+        <v>5</v>
+      </c>
+      <c r="S272" t="n">
+        <v>11</v>
+      </c>
+      <c r="T272" t="n">
+        <v>24</v>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>rak12p9n</t>
+        </is>
+      </c>
+      <c r="W272" t="n">
+        <v>148</v>
+      </c>
+      <c r="X272" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA272" t="inlineStr"/>
+      <c r="AB272" t="inlineStr"/>
+      <c r="AC272" t="inlineStr"/>
+      <c r="AD272" t="inlineStr"/>
+      <c r="AE272" t="inlineStr"/>
+      <c r="AF272" t="inlineStr"/>
+      <c r="AG272" t="inlineStr"/>
+      <c r="AH272" t="inlineStr"/>
+      <c r="AI272" t="inlineStr"/>
+      <c r="AJ272" t="inlineStr"/>
+      <c r="AK272" t="inlineStr"/>
+      <c r="AL272" t="inlineStr"/>
+      <c r="AM272" t="inlineStr"/>
+      <c r="AN272" t="inlineStr"/>
+      <c r="AO272" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP272" t="n">
+        <v>179.6521739130435</v>
+      </c>
+      <c r="AQ272" t="n">
+        <v>1.08695652173913</v>
+      </c>
+      <c r="AR272" t="n">
+        <v>69.56521739130434</v>
+      </c>
+      <c r="AS272" t="n">
+        <v>2908695.652173913</v>
+      </c>
+      <c r="AT272" t="n">
+        <v>75.21739130434783</v>
+      </c>
+      <c r="AU272" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="AV272" t="n">
+        <v>181.3125</v>
+      </c>
+      <c r="AW272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX272" t="n">
+        <v>66.1875</v>
+      </c>
+      <c r="AY272" t="n">
+        <v>1429687.5</v>
+      </c>
+      <c r="AZ272" t="n">
+        <v>73.3125</v>
+      </c>
+      <c r="BA272" t="inlineStr"/>
+      <c r="BB272" t="inlineStr"/>
+      <c r="BC272" t="inlineStr"/>
+      <c r="BD272" t="inlineStr"/>
+      <c r="BE272" t="inlineStr"/>
+      <c r="BF272" t="inlineStr"/>
+      <c r="BG272" t="inlineStr"/>
+      <c r="BH272" t="inlineStr"/>
+      <c r="BI272" t="inlineStr"/>
+      <c r="BJ272" t="inlineStr"/>
+      <c r="BK272" t="inlineStr"/>
+      <c r="BL272" t="inlineStr"/>
+      <c r="BM272" t="inlineStr"/>
+      <c r="BN272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>8MZf2N64</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="n">
+        <v>45534.58333333334</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzalez diaz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo los carmenes
+  granada </t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>22524</v>
+      </c>
+      <c r="F273" t="n">
+        <v>15089</v>
+      </c>
+      <c r="G273" t="n">
+        <v>1</v>
+      </c>
+      <c r="H273" t="n">
+        <v>3</v>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>63</v>
+      </c>
+      <c r="N273" t="n">
+        <v>37</v>
+      </c>
+      <c r="O273" t="n">
+        <v>16</v>
+      </c>
+      <c r="P273" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>6</v>
+      </c>
+      <c r="R273" t="n">
+        <v>6</v>
+      </c>
+      <c r="S273" t="n">
+        <v>9</v>
+      </c>
+      <c r="T273" t="n">
+        <v>10</v>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>K4dMCgFa</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="W273" t="n">
+        <v>148</v>
+      </c>
+      <c r="X273" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y273" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="AC273" t="n">
+        <v>26.22222222222222</v>
+      </c>
+      <c r="AD273" t="n">
+        <v>180.4444444444445</v>
+      </c>
+      <c r="AE273" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF273" t="n">
+        <v>73.22222222222223</v>
+      </c>
+      <c r="AG273" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="AH273" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="AI273" t="inlineStr"/>
+      <c r="AJ273" t="inlineStr"/>
+      <c r="AK273" t="inlineStr"/>
+      <c r="AL273" t="inlineStr"/>
+      <c r="AM273" t="inlineStr"/>
+      <c r="AN273" t="inlineStr"/>
+      <c r="AO273" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AP273" t="n">
+        <v>180.7</v>
+      </c>
+      <c r="AQ273" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AR273" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="AS273" t="n">
+        <v>3267500</v>
+      </c>
+      <c r="AT273" t="n">
+        <v>74.95</v>
+      </c>
+      <c r="AU273" t="n">
+        <v>24.73333333333333</v>
+      </c>
+      <c r="AV273" t="n">
+        <v>178.7333333333333</v>
+      </c>
+      <c r="AW273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX273" t="n">
+        <v>66.13333333333334</v>
+      </c>
+      <c r="AY273" t="n">
+        <v>1276666.666666667</v>
+      </c>
+      <c r="AZ273" t="n">
+        <v>70.73333333333333</v>
+      </c>
+      <c r="BA273" t="inlineStr"/>
+      <c r="BB273" t="inlineStr"/>
+      <c r="BC273" t="inlineStr"/>
+      <c r="BD273" t="inlineStr"/>
+      <c r="BE273" t="inlineStr"/>
+      <c r="BF273" t="inlineStr"/>
+      <c r="BG273" t="inlineStr"/>
+      <c r="BH273" t="inlineStr"/>
+      <c r="BI273" t="inlineStr"/>
+      <c r="BJ273" t="inlineStr"/>
+      <c r="BK273" t="inlineStr"/>
+      <c r="BL273" t="inlineStr"/>
+      <c r="BM273" t="inlineStr"/>
+      <c r="BN273" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN273"/>
+  <dimension ref="A1:BN277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53025,6 +53025,772 @@
       <c r="BM273" t="inlineStr"/>
       <c r="BN273" t="inlineStr"/>
     </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="n">
+        <v>45535.59375</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F274" t="n">
+        <v>22405</v>
+      </c>
+      <c r="G274" t="n">
+        <v>2</v>
+      </c>
+      <c r="H274" t="n">
+        <v>1</v>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="K274" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="L274" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M274" t="n">
+        <v>48</v>
+      </c>
+      <c r="N274" t="n">
+        <v>52</v>
+      </c>
+      <c r="O274" t="n">
+        <v>10</v>
+      </c>
+      <c r="P274" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>5</v>
+      </c>
+      <c r="R274" t="n">
+        <v>5</v>
+      </c>
+      <c r="S274" t="n">
+        <v>10</v>
+      </c>
+      <c r="T274" t="n">
+        <v>11</v>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="W274" t="n">
+        <v>148</v>
+      </c>
+      <c r="X274" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y274" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr"/>
+      <c r="AD274" t="inlineStr"/>
+      <c r="AE274" t="inlineStr"/>
+      <c r="AF274" t="inlineStr"/>
+      <c r="AG274" t="inlineStr"/>
+      <c r="AH274" t="inlineStr"/>
+      <c r="AI274" t="n">
+        <v>28.125</v>
+      </c>
+      <c r="AJ274" t="n">
+        <v>178.125</v>
+      </c>
+      <c r="AK274" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AL274" t="n">
+        <v>75.125</v>
+      </c>
+      <c r="AM274" t="n">
+        <v>6887500</v>
+      </c>
+      <c r="AN274" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="AO274" t="n">
+        <v>26.30769230769231</v>
+      </c>
+      <c r="AP274" t="n">
+        <v>179.6923076923077</v>
+      </c>
+      <c r="AQ274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR274" t="n">
+        <v>71.07692307692308</v>
+      </c>
+      <c r="AS274" t="n">
+        <v>2930769.230769231</v>
+      </c>
+      <c r="AT274" t="n">
+        <v>74.38461538461539</v>
+      </c>
+      <c r="AU274" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="AV274" t="n">
+        <v>177.0666666666667</v>
+      </c>
+      <c r="AW274" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AX274" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AY274" t="n">
+        <v>6553333.333333333</v>
+      </c>
+      <c r="AZ274" t="n">
+        <v>76</v>
+      </c>
+      <c r="BA274" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB274" t="n">
+        <v>184</v>
+      </c>
+      <c r="BC274" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD274" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE274" t="n">
+        <v>146</v>
+      </c>
+      <c r="BF274" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="BG274" t="n">
+        <v>147</v>
+      </c>
+      <c r="BH274" t="n">
+        <v>19</v>
+      </c>
+      <c r="BI274" t="n">
+        <v>182</v>
+      </c>
+      <c r="BJ274" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK274" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL274" t="n">
+        <v>60</v>
+      </c>
+      <c r="BM274" t="n">
+        <v>550000</v>
+      </c>
+      <c r="BN274" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="n">
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F275" t="n">
+        <v>48617</v>
+      </c>
+      <c r="G275" t="n">
+        <v>0</v>
+      </c>
+      <c r="H275" t="n">
+        <v>1</v>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="K275" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L275" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="M275" t="n">
+        <v>53</v>
+      </c>
+      <c r="N275" t="n">
+        <v>47</v>
+      </c>
+      <c r="O275" t="n">
+        <v>8</v>
+      </c>
+      <c r="P275" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>1</v>
+      </c>
+      <c r="R275" t="n">
+        <v>2</v>
+      </c>
+      <c r="S275" t="n">
+        <v>10</v>
+      </c>
+      <c r="T275" t="n">
+        <v>5</v>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="W275" t="n">
+        <v>148</v>
+      </c>
+      <c r="X275" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y275" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z275" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA275" t="inlineStr"/>
+      <c r="AB275" t="inlineStr"/>
+      <c r="AC275" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AD275" t="n">
+        <v>184</v>
+      </c>
+      <c r="AE275" t="n">
+        <v>1.555555555555556</v>
+      </c>
+      <c r="AF275" t="n">
+        <v>79.22222222222223</v>
+      </c>
+      <c r="AG275" t="n">
+        <v>23777777.77777778</v>
+      </c>
+      <c r="AH275" t="n">
+        <v>82.77777777777777</v>
+      </c>
+      <c r="AI275" t="inlineStr"/>
+      <c r="AJ275" t="inlineStr"/>
+      <c r="AK275" t="inlineStr"/>
+      <c r="AL275" t="inlineStr"/>
+      <c r="AM275" t="inlineStr"/>
+      <c r="AN275" t="inlineStr"/>
+      <c r="AO275" t="n">
+        <v>24.22727272727273</v>
+      </c>
+      <c r="AP275" t="n">
+        <v>182.9545454545455</v>
+      </c>
+      <c r="AQ275" t="n">
+        <v>1.136363636363636</v>
+      </c>
+      <c r="AR275" t="n">
+        <v>74</v>
+      </c>
+      <c r="AS275" t="n">
+        <v>12086363.63636364</v>
+      </c>
+      <c r="AT275" t="n">
+        <v>79.59090909090909</v>
+      </c>
+      <c r="AU275" t="n">
+        <v>26.35294117647059</v>
+      </c>
+      <c r="AV275" t="n">
+        <v>179.1764705882353</v>
+      </c>
+      <c r="AW275" t="n">
+        <v>1.882352941176471</v>
+      </c>
+      <c r="AX275" t="n">
+        <v>78.35294117647059</v>
+      </c>
+      <c r="AY275" t="n">
+        <v>20588235.29411765</v>
+      </c>
+      <c r="AZ275" t="n">
+        <v>81.41176470588235</v>
+      </c>
+      <c r="BA275" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="BB275" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BC275" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD275" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE275" t="n">
+        <v>165</v>
+      </c>
+      <c r="BF275" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="BG275" t="n">
+        <v>166</v>
+      </c>
+      <c r="BH275" t="inlineStr"/>
+      <c r="BI275" t="inlineStr"/>
+      <c r="BJ275" t="inlineStr"/>
+      <c r="BK275" t="inlineStr"/>
+      <c r="BL275" t="inlineStr"/>
+      <c r="BM275" t="inlineStr"/>
+      <c r="BN275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="n">
+        <v>45535.5</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>55926</v>
+      </c>
+      <c r="F276" t="n">
+        <v>44359</v>
+      </c>
+      <c r="G276" t="n">
+        <v>7</v>
+      </c>
+      <c r="H276" t="n">
+        <v>0</v>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="K276" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="L276" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M276" t="n">
+        <v>70</v>
+      </c>
+      <c r="N276" t="n">
+        <v>30</v>
+      </c>
+      <c r="O276" t="n">
+        <v>23</v>
+      </c>
+      <c r="P276" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>10</v>
+      </c>
+      <c r="R276" t="n">
+        <v>2</v>
+      </c>
+      <c r="S276" t="n">
+        <v>6</v>
+      </c>
+      <c r="T276" t="n">
+        <v>12</v>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="W276" t="n">
+        <v>148</v>
+      </c>
+      <c r="X276" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y276" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z276" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr"/>
+      <c r="AD276" t="inlineStr"/>
+      <c r="AE276" t="inlineStr"/>
+      <c r="AF276" t="inlineStr"/>
+      <c r="AG276" t="inlineStr"/>
+      <c r="AH276" t="inlineStr"/>
+      <c r="AI276" t="inlineStr"/>
+      <c r="AJ276" t="inlineStr"/>
+      <c r="AK276" t="inlineStr"/>
+      <c r="AL276" t="inlineStr"/>
+      <c r="AM276" t="inlineStr"/>
+      <c r="AN276" t="inlineStr"/>
+      <c r="AO276" t="n">
+        <v>20.30769230769231</v>
+      </c>
+      <c r="AP276" t="n">
+        <v>180.1538461538462</v>
+      </c>
+      <c r="AQ276" t="n">
+        <v>1.615384615384615</v>
+      </c>
+      <c r="AR276" t="n">
+        <v>72.76923076923077</v>
+      </c>
+      <c r="AS276" t="n">
+        <v>23842307.69230769</v>
+      </c>
+      <c r="AT276" t="n">
+        <v>83.38461538461539</v>
+      </c>
+      <c r="AU276" t="n">
+        <v>23.22222222222222</v>
+      </c>
+      <c r="AV276" t="n">
+        <v>181.8888888888889</v>
+      </c>
+      <c r="AW276" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="AX276" t="n">
+        <v>70.33333333333333</v>
+      </c>
+      <c r="AY276" t="n">
+        <v>3672222.222222222</v>
+      </c>
+      <c r="AZ276" t="n">
+        <v>77.55555555555556</v>
+      </c>
+      <c r="BA276" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB276" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="BC276" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD276" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE276" t="n">
+        <v>417</v>
+      </c>
+      <c r="BF276" t="n">
+        <v>334500000</v>
+      </c>
+      <c r="BG276" t="n">
+        <v>444</v>
+      </c>
+      <c r="BH276" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="BI276" t="n">
+        <v>178</v>
+      </c>
+      <c r="BJ276" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK276" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL276" t="n">
+        <v>142</v>
+      </c>
+      <c r="BM276" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="BN276" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>2qDTo2MN</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="n">
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lax franco s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo mirandilla
+  cadiz </t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>20776</v>
+      </c>
+      <c r="F277" t="n">
+        <v>16518</v>
+      </c>
+      <c r="G277" t="n">
+        <v>2</v>
+      </c>
+      <c r="H277" t="n">
+        <v>2</v>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>67</v>
+      </c>
+      <c r="N277" t="n">
+        <v>33</v>
+      </c>
+      <c r="O277" t="n">
+        <v>4</v>
+      </c>
+      <c r="P277" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q277" t="n">
+        <v>3</v>
+      </c>
+      <c r="R277" t="n">
+        <v>2</v>
+      </c>
+      <c r="S277" t="n">
+        <v>5</v>
+      </c>
+      <c r="T277" t="n">
+        <v>9</v>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>UBD9uzt0</t>
+        </is>
+      </c>
+      <c r="W277" t="n">
+        <v>148</v>
+      </c>
+      <c r="X277" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y277" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z277" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="AC277" t="n">
+        <v>28.875</v>
+      </c>
+      <c r="AD277" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AE277" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AF277" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="AG277" t="n">
+        <v>5112500</v>
+      </c>
+      <c r="AH277" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="AI277" t="inlineStr"/>
+      <c r="AJ277" t="inlineStr"/>
+      <c r="AK277" t="inlineStr"/>
+      <c r="AL277" t="inlineStr"/>
+      <c r="AM277" t="inlineStr"/>
+      <c r="AN277" t="inlineStr"/>
+      <c r="AO277" t="n">
+        <v>26.54545454545455</v>
+      </c>
+      <c r="AP277" t="n">
+        <v>177.4545454545455</v>
+      </c>
+      <c r="AQ277" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="AR277" t="n">
+        <v>69.40909090909091</v>
+      </c>
+      <c r="AS277" t="n">
+        <v>2676136.363636364</v>
+      </c>
+      <c r="AT277" t="n">
+        <v>72.31818181818181</v>
+      </c>
+      <c r="AU277" t="n">
+        <v>27.58333333333333</v>
+      </c>
+      <c r="AV277" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="AW277" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX277" t="n">
+        <v>69.83333333333333</v>
+      </c>
+      <c r="AY277" t="n">
+        <v>1766666.666666667</v>
+      </c>
+      <c r="AZ277" t="n">
+        <v>73.08333333333333</v>
+      </c>
+      <c r="BA277" t="inlineStr"/>
+      <c r="BB277" t="inlineStr"/>
+      <c r="BC277" t="inlineStr"/>
+      <c r="BD277" t="inlineStr"/>
+      <c r="BE277" t="inlineStr"/>
+      <c r="BF277" t="inlineStr"/>
+      <c r="BG277" t="inlineStr"/>
+      <c r="BH277" t="inlineStr"/>
+      <c r="BI277" t="inlineStr"/>
+      <c r="BJ277" t="inlineStr"/>
+      <c r="BK277" t="inlineStr"/>
+      <c r="BL277" t="inlineStr"/>
+      <c r="BM277" t="inlineStr"/>
+      <c r="BN277" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN277"/>
+  <dimension ref="A1:BN290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53791,6 +53791,2420 @@
       <c r="BM277" t="inlineStr"/>
       <c r="BN277" t="inlineStr"/>
     </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="n">
+        <v>45536.6875</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F278" t="n">
+        <v>73072</v>
+      </c>
+      <c r="G278" t="n">
+        <v>2</v>
+      </c>
+      <c r="H278" t="n">
+        <v>0</v>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="K278" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="L278" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M278" t="n">
+        <v>60</v>
+      </c>
+      <c r="N278" t="n">
+        <v>40</v>
+      </c>
+      <c r="O278" t="n">
+        <v>22</v>
+      </c>
+      <c r="P278" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>8</v>
+      </c>
+      <c r="R278" t="n">
+        <v>2</v>
+      </c>
+      <c r="S278" t="n">
+        <v>9</v>
+      </c>
+      <c r="T278" t="n">
+        <v>17</v>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="W278" t="n">
+        <v>148</v>
+      </c>
+      <c r="X278" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y278" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z278" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AB278" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AC278" t="n">
+        <v>26.22222222222222</v>
+      </c>
+      <c r="AD278" t="n">
+        <v>183.2222222222222</v>
+      </c>
+      <c r="AE278" t="n">
+        <v>3.222222222222222</v>
+      </c>
+      <c r="AF278" t="n">
+        <v>85.88888888888889</v>
+      </c>
+      <c r="AG278" t="n">
+        <v>75555555.55555555</v>
+      </c>
+      <c r="AH278" t="n">
+        <v>88.33333333333333</v>
+      </c>
+      <c r="AI278" t="inlineStr"/>
+      <c r="AJ278" t="inlineStr"/>
+      <c r="AK278" t="inlineStr"/>
+      <c r="AL278" t="inlineStr"/>
+      <c r="AM278" t="inlineStr"/>
+      <c r="AN278" t="inlineStr"/>
+      <c r="AO278" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AP278" t="n">
+        <v>175.3333333333333</v>
+      </c>
+      <c r="AQ278" t="n">
+        <v>1.916666666666667</v>
+      </c>
+      <c r="AR278" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="AS278" t="n">
+        <v>29839583.33333333</v>
+      </c>
+      <c r="AT278" t="n">
+        <v>83.41666666666667</v>
+      </c>
+      <c r="AU278" t="n">
+        <v>21.29411764705882</v>
+      </c>
+      <c r="AV278" t="n">
+        <v>181.2352941176471</v>
+      </c>
+      <c r="AW278" t="n">
+        <v>1.235294117647059</v>
+      </c>
+      <c r="AX278" t="n">
+        <v>73.23529411764706</v>
+      </c>
+      <c r="AY278" t="n">
+        <v>8341176.470588235</v>
+      </c>
+      <c r="AZ278" t="n">
+        <v>82.41176470588235</v>
+      </c>
+      <c r="BA278" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="BB278" t="n">
+        <v>183</v>
+      </c>
+      <c r="BC278" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD278" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE278" t="n">
+        <v>329</v>
+      </c>
+      <c r="BF278" t="n">
+        <v>240100000</v>
+      </c>
+      <c r="BG278" t="n">
+        <v>341</v>
+      </c>
+      <c r="BH278" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="BI278" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="BJ278" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK278" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL278" t="n">
+        <v>294</v>
+      </c>
+      <c r="BM278" t="n">
+        <v>35650000</v>
+      </c>
+      <c r="BN278" t="n">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="n">
+        <v>45536.59375</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F279" t="n">
+        <v>10929</v>
+      </c>
+      <c r="G279" t="n">
+        <v>0</v>
+      </c>
+      <c r="H279" t="n">
+        <v>0</v>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="K279" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L279" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M279" t="n">
+        <v>53</v>
+      </c>
+      <c r="N279" t="n">
+        <v>47</v>
+      </c>
+      <c r="O279" t="n">
+        <v>16</v>
+      </c>
+      <c r="P279" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q279" t="n">
+        <v>1</v>
+      </c>
+      <c r="R279" t="n">
+        <v>0</v>
+      </c>
+      <c r="S279" t="n">
+        <v>14</v>
+      </c>
+      <c r="T279" t="n">
+        <v>16</v>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="W279" t="n">
+        <v>148</v>
+      </c>
+      <c r="X279" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y279" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z279" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="AB279" t="inlineStr"/>
+      <c r="AC279" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="AD279" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AE279" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AF279" t="n">
+        <v>74.125</v>
+      </c>
+      <c r="AG279" t="n">
+        <v>8459375</v>
+      </c>
+      <c r="AH279" t="n">
+        <v>77.125</v>
+      </c>
+      <c r="AI279" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AJ279" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="AK279" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL279" t="n">
+        <v>79</v>
+      </c>
+      <c r="AM279" t="n">
+        <v>26150000</v>
+      </c>
+      <c r="AN279" t="n">
+        <v>82.75</v>
+      </c>
+      <c r="AO279" t="n">
+        <v>23.11764705882353</v>
+      </c>
+      <c r="AP279" t="n">
+        <v>181.7058823529412</v>
+      </c>
+      <c r="AQ279" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR279" t="n">
+        <v>70.11764705882354</v>
+      </c>
+      <c r="AS279" t="n">
+        <v>5427941.176470588</v>
+      </c>
+      <c r="AT279" t="n">
+        <v>77.35294117647059</v>
+      </c>
+      <c r="AU279" t="n">
+        <v>24.41176470588235</v>
+      </c>
+      <c r="AV279" t="n">
+        <v>178.3529411764706</v>
+      </c>
+      <c r="AW279" t="n">
+        <v>1.470588235294118</v>
+      </c>
+      <c r="AX279" t="n">
+        <v>74.64705882352941</v>
+      </c>
+      <c r="AY279" t="n">
+        <v>12652941.17647059</v>
+      </c>
+      <c r="AZ279" t="n">
+        <v>79.35294117647059</v>
+      </c>
+      <c r="BA279" t="inlineStr"/>
+      <c r="BB279" t="inlineStr"/>
+      <c r="BC279" t="inlineStr"/>
+      <c r="BD279" t="inlineStr"/>
+      <c r="BE279" t="inlineStr"/>
+      <c r="BF279" t="inlineStr"/>
+      <c r="BG279" t="inlineStr"/>
+      <c r="BH279" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BI279" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="BJ279" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK279" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL279" t="n">
+        <v>313</v>
+      </c>
+      <c r="BM279" t="n">
+        <v>73500000</v>
+      </c>
+      <c r="BN279" t="n">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="n">
+        <v>45536.58333333334</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F280" t="n">
+        <v>35735</v>
+      </c>
+      <c r="G280" t="n">
+        <v>0</v>
+      </c>
+      <c r="H280" t="n">
+        <v>2</v>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="K280" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L280" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M280" t="n">
+        <v>50</v>
+      </c>
+      <c r="N280" t="n">
+        <v>50</v>
+      </c>
+      <c r="O280" t="n">
+        <v>16</v>
+      </c>
+      <c r="P280" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q280" t="n">
+        <v>5</v>
+      </c>
+      <c r="R280" t="n">
+        <v>4</v>
+      </c>
+      <c r="S280" t="n">
+        <v>6</v>
+      </c>
+      <c r="T280" t="n">
+        <v>14</v>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="W280" t="n">
+        <v>148</v>
+      </c>
+      <c r="X280" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y280" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z280" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AB280" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="AC280" t="inlineStr"/>
+      <c r="AD280" t="inlineStr"/>
+      <c r="AE280" t="inlineStr"/>
+      <c r="AF280" t="inlineStr"/>
+      <c r="AG280" t="inlineStr"/>
+      <c r="AH280" t="inlineStr"/>
+      <c r="AI280" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="AJ280" t="n">
+        <v>183.875</v>
+      </c>
+      <c r="AK280" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AL280" t="n">
+        <v>77</v>
+      </c>
+      <c r="AM280" t="n">
+        <v>18862500</v>
+      </c>
+      <c r="AN280" t="n">
+        <v>81.625</v>
+      </c>
+      <c r="AO280" t="n">
+        <v>25.6875</v>
+      </c>
+      <c r="AP280" t="n">
+        <v>178.9375</v>
+      </c>
+      <c r="AQ280" t="n">
+        <v>1.6875</v>
+      </c>
+      <c r="AR280" t="n">
+        <v>73.875</v>
+      </c>
+      <c r="AS280" t="n">
+        <v>8950000</v>
+      </c>
+      <c r="AT280" t="n">
+        <v>80.3125</v>
+      </c>
+      <c r="AU280" t="n">
+        <v>24.07142857142857</v>
+      </c>
+      <c r="AV280" t="n">
+        <v>180</v>
+      </c>
+      <c r="AW280" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AX280" t="n">
+        <v>76.21428571428571</v>
+      </c>
+      <c r="AY280" t="n">
+        <v>16092857.14285714</v>
+      </c>
+      <c r="AZ280" t="n">
+        <v>80.92857142857143</v>
+      </c>
+      <c r="BA280" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB280" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="BC280" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD280" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE280" t="n">
+        <v>160</v>
+      </c>
+      <c r="BF280" t="n">
+        <v>42000000</v>
+      </c>
+      <c r="BG280" t="n">
+        <v>160</v>
+      </c>
+      <c r="BH280" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BI280" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="BJ280" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK280" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL280" t="n">
+        <v>126</v>
+      </c>
+      <c r="BM280" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="BN280" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F281" t="n">
+        <v>16386</v>
+      </c>
+      <c r="G281" t="n">
+        <v>2</v>
+      </c>
+      <c r="H281" t="n">
+        <v>0</v>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="K281" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L281" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="M281" t="n">
+        <v>29</v>
+      </c>
+      <c r="N281" t="n">
+        <v>71</v>
+      </c>
+      <c r="O281" t="n">
+        <v>15</v>
+      </c>
+      <c r="P281" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q281" t="n">
+        <v>5</v>
+      </c>
+      <c r="R281" t="n">
+        <v>7</v>
+      </c>
+      <c r="S281" t="n">
+        <v>13</v>
+      </c>
+      <c r="T281" t="n">
+        <v>9</v>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="W281" t="n">
+        <v>148</v>
+      </c>
+      <c r="X281" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y281" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z281" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA281" t="inlineStr"/>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr"/>
+      <c r="AD281" t="inlineStr"/>
+      <c r="AE281" t="inlineStr"/>
+      <c r="AF281" t="inlineStr"/>
+      <c r="AG281" t="inlineStr"/>
+      <c r="AH281" t="inlineStr"/>
+      <c r="AI281" t="inlineStr"/>
+      <c r="AJ281" t="inlineStr"/>
+      <c r="AK281" t="inlineStr"/>
+      <c r="AL281" t="inlineStr"/>
+      <c r="AM281" t="inlineStr"/>
+      <c r="AN281" t="inlineStr"/>
+      <c r="AO281" t="n">
+        <v>22.375</v>
+      </c>
+      <c r="AP281" t="n">
+        <v>178.1875</v>
+      </c>
+      <c r="AQ281" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR281" t="n">
+        <v>71.125</v>
+      </c>
+      <c r="AS281" t="n">
+        <v>4181250</v>
+      </c>
+      <c r="AT281" t="n">
+        <v>77.9375</v>
+      </c>
+      <c r="AU281" t="n">
+        <v>23.72222222222222</v>
+      </c>
+      <c r="AV281" t="n">
+        <v>177.8333333333333</v>
+      </c>
+      <c r="AW281" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="AX281" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AY281" t="n">
+        <v>8713888.888888888</v>
+      </c>
+      <c r="AZ281" t="n">
+        <v>78.27777777777777</v>
+      </c>
+      <c r="BA281" t="inlineStr"/>
+      <c r="BB281" t="inlineStr"/>
+      <c r="BC281" t="inlineStr"/>
+      <c r="BD281" t="inlineStr"/>
+      <c r="BE281" t="inlineStr"/>
+      <c r="BF281" t="inlineStr"/>
+      <c r="BG281" t="inlineStr"/>
+      <c r="BH281" t="n">
+        <v>27</v>
+      </c>
+      <c r="BI281" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BJ281" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK281" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL281" t="n">
+        <v>150</v>
+      </c>
+      <c r="BM281" t="n">
+        <v>13800000</v>
+      </c>
+      <c r="BN281" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F282" t="n">
+        <v>19908</v>
+      </c>
+      <c r="G282" t="n">
+        <v>3</v>
+      </c>
+      <c r="H282" t="n">
+        <v>2</v>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="K282" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="L282" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M282" t="n">
+        <v>50</v>
+      </c>
+      <c r="N282" t="n">
+        <v>50</v>
+      </c>
+      <c r="O282" t="n">
+        <v>10</v>
+      </c>
+      <c r="P282" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q282" t="n">
+        <v>4</v>
+      </c>
+      <c r="R282" t="n">
+        <v>3</v>
+      </c>
+      <c r="S282" t="n">
+        <v>19</v>
+      </c>
+      <c r="T282" t="n">
+        <v>10</v>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="W282" t="n">
+        <v>148</v>
+      </c>
+      <c r="X282" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y282" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z282" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA282" t="inlineStr"/>
+      <c r="AB282" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="AC282" t="inlineStr"/>
+      <c r="AD282" t="inlineStr"/>
+      <c r="AE282" t="inlineStr"/>
+      <c r="AF282" t="inlineStr"/>
+      <c r="AG282" t="inlineStr"/>
+      <c r="AH282" t="inlineStr"/>
+      <c r="AI282" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="AJ282" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AK282" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AL282" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AM282" t="n">
+        <v>11650000</v>
+      </c>
+      <c r="AN282" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="AO282" t="n">
+        <v>26.1875</v>
+      </c>
+      <c r="AP282" t="n">
+        <v>176.625</v>
+      </c>
+      <c r="AQ282" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AR282" t="n">
+        <v>73.4375</v>
+      </c>
+      <c r="AS282" t="n">
+        <v>7787500</v>
+      </c>
+      <c r="AT282" t="n">
+        <v>77.4375</v>
+      </c>
+      <c r="AU282" t="n">
+        <v>26.13333333333333</v>
+      </c>
+      <c r="AV282" t="n">
+        <v>179.2666666666667</v>
+      </c>
+      <c r="AW282" t="n">
+        <v>1.266666666666667</v>
+      </c>
+      <c r="AX282" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="AY282" t="n">
+        <v>7253333.333333333</v>
+      </c>
+      <c r="AZ282" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="BA282" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB282" t="n">
+        <v>179</v>
+      </c>
+      <c r="BC282" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD282" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE282" t="n">
+        <v>138</v>
+      </c>
+      <c r="BF282" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="BG282" t="n">
+        <v>150</v>
+      </c>
+      <c r="BH282" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="BI282" t="n">
+        <v>176.75</v>
+      </c>
+      <c r="BJ282" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK282" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL282" t="n">
+        <v>294</v>
+      </c>
+      <c r="BM282" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="BN282" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F283" t="n">
+        <v>10482</v>
+      </c>
+      <c r="G283" t="n">
+        <v>0</v>
+      </c>
+      <c r="H283" t="n">
+        <v>1</v>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="K283" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L283" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M283" t="n">
+        <v>54</v>
+      </c>
+      <c r="N283" t="n">
+        <v>46</v>
+      </c>
+      <c r="O283" t="n">
+        <v>4</v>
+      </c>
+      <c r="P283" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q283" t="n">
+        <v>2</v>
+      </c>
+      <c r="R283" t="n">
+        <v>3</v>
+      </c>
+      <c r="S283" t="n">
+        <v>11</v>
+      </c>
+      <c r="T283" t="n">
+        <v>17</v>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="W283" t="n">
+        <v>148</v>
+      </c>
+      <c r="X283" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y283" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z283" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="AC283" t="n">
+        <v>25.875</v>
+      </c>
+      <c r="AD283" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="AE283" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF283" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AG283" t="n">
+        <v>5125000</v>
+      </c>
+      <c r="AH283" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AI283" t="n">
+        <v>26.125</v>
+      </c>
+      <c r="AJ283" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="AK283" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL283" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AM283" t="n">
+        <v>9937500</v>
+      </c>
+      <c r="AN283" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="AO283" t="n">
+        <v>24.94444444444444</v>
+      </c>
+      <c r="AP283" t="n">
+        <v>180.0555555555555</v>
+      </c>
+      <c r="AQ283" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="AR283" t="n">
+        <v>70.16666666666667</v>
+      </c>
+      <c r="AS283" t="n">
+        <v>3623611.111111111</v>
+      </c>
+      <c r="AT283" t="n">
+        <v>74.44444444444444</v>
+      </c>
+      <c r="AU283" t="n">
+        <v>26.65384615384615</v>
+      </c>
+      <c r="AV283" t="n">
+        <v>181.7692307692308</v>
+      </c>
+      <c r="AW283" t="n">
+        <v>1.115384615384615</v>
+      </c>
+      <c r="AX283" t="n">
+        <v>74.73076923076923</v>
+      </c>
+      <c r="AY283" t="n">
+        <v>9250384.615384616</v>
+      </c>
+      <c r="AZ283" t="n">
+        <v>77.53846153846153</v>
+      </c>
+      <c r="BA283" t="inlineStr"/>
+      <c r="BB283" t="inlineStr"/>
+      <c r="BC283" t="inlineStr"/>
+      <c r="BD283" t="inlineStr"/>
+      <c r="BE283" t="inlineStr"/>
+      <c r="BF283" t="inlineStr"/>
+      <c r="BG283" t="inlineStr"/>
+      <c r="BH283" t="n">
+        <v>21</v>
+      </c>
+      <c r="BI283" t="n">
+        <v>172</v>
+      </c>
+      <c r="BJ283" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK283" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL283" t="n">
+        <v>69</v>
+      </c>
+      <c r="BM283" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="BN283" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gil manzano j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F284" t="n">
+        <v>43857</v>
+      </c>
+      <c r="G284" t="n">
+        <v>1</v>
+      </c>
+      <c r="H284" t="n">
+        <v>1</v>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="K284" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L284" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M284" t="n">
+        <v>58</v>
+      </c>
+      <c r="N284" t="n">
+        <v>42</v>
+      </c>
+      <c r="O284" t="n">
+        <v>22</v>
+      </c>
+      <c r="P284" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q284" t="n">
+        <v>6</v>
+      </c>
+      <c r="R284" t="n">
+        <v>3</v>
+      </c>
+      <c r="S284" t="n">
+        <v>15</v>
+      </c>
+      <c r="T284" t="n">
+        <v>11</v>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="W284" t="n">
+        <v>148</v>
+      </c>
+      <c r="X284" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y284" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z284" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB284" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC284" t="n">
+        <v>22.88888888888889</v>
+      </c>
+      <c r="AD284" t="n">
+        <v>180.4444444444445</v>
+      </c>
+      <c r="AE284" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF284" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AG284" t="n">
+        <v>10091111.11111111</v>
+      </c>
+      <c r="AH284" t="n">
+        <v>77.66666666666667</v>
+      </c>
+      <c r="AI284" t="inlineStr"/>
+      <c r="AJ284" t="inlineStr"/>
+      <c r="AK284" t="inlineStr"/>
+      <c r="AL284" t="inlineStr"/>
+      <c r="AM284" t="inlineStr"/>
+      <c r="AN284" t="inlineStr"/>
+      <c r="AO284" t="n">
+        <v>25.4375</v>
+      </c>
+      <c r="AP284" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AQ284" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AR284" t="n">
+        <v>73.3125</v>
+      </c>
+      <c r="AS284" t="n">
+        <v>6448437.5</v>
+      </c>
+      <c r="AT284" t="n">
+        <v>77.0625</v>
+      </c>
+      <c r="AU284" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AV284" t="n">
+        <v>178.6</v>
+      </c>
+      <c r="AW284" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AX284" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AY284" t="n">
+        <v>7580000</v>
+      </c>
+      <c r="AZ284" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="BA284" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BB284" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="BC284" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD284" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE284" t="n">
+        <v>303</v>
+      </c>
+      <c r="BF284" t="n">
+        <v>43700000</v>
+      </c>
+      <c r="BG284" t="n">
+        <v>315</v>
+      </c>
+      <c r="BH284" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="BI284" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="BJ284" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK284" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL284" t="n">
+        <v>392</v>
+      </c>
+      <c r="BM284" t="n">
+        <v>81500000</v>
+      </c>
+      <c r="BN284" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>lfATGMLc</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="n">
+        <v>45536.58333333334</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guzman mansilla j  l 
+  esp </t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo pepico amat
+  elda </t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>4038</v>
+      </c>
+      <c r="F285" t="n">
+        <v>4830</v>
+      </c>
+      <c r="G285" t="n">
+        <v>1</v>
+      </c>
+      <c r="H285" t="n">
+        <v>2</v>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="n">
+        <v>54</v>
+      </c>
+      <c r="N285" t="n">
+        <v>46</v>
+      </c>
+      <c r="O285" t="n">
+        <v>10</v>
+      </c>
+      <c r="P285" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q285" t="n">
+        <v>7</v>
+      </c>
+      <c r="R285" t="n">
+        <v>3</v>
+      </c>
+      <c r="S285" t="n">
+        <v>10</v>
+      </c>
+      <c r="T285" t="n">
+        <v>14</v>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>hh4xt2Df</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>M1vEw5An</t>
+        </is>
+      </c>
+      <c r="W285" t="n">
+        <v>148</v>
+      </c>
+      <c r="X285" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y285" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z285" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="AB285" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="AC285" t="inlineStr"/>
+      <c r="AD285" t="inlineStr"/>
+      <c r="AE285" t="inlineStr"/>
+      <c r="AF285" t="inlineStr"/>
+      <c r="AG285" t="inlineStr"/>
+      <c r="AH285" t="inlineStr"/>
+      <c r="AI285" t="inlineStr"/>
+      <c r="AJ285" t="inlineStr"/>
+      <c r="AK285" t="inlineStr"/>
+      <c r="AL285" t="inlineStr"/>
+      <c r="AM285" t="inlineStr"/>
+      <c r="AN285" t="inlineStr"/>
+      <c r="AO285" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="AP285" t="n">
+        <v>180.2</v>
+      </c>
+      <c r="AQ285" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR285" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AS285" t="n">
+        <v>1003666.666666667</v>
+      </c>
+      <c r="AT285" t="n">
+        <v>69.93333333333334</v>
+      </c>
+      <c r="AU285" t="n">
+        <v>26.23076923076923</v>
+      </c>
+      <c r="AV285" t="n">
+        <v>185.6923076923077</v>
+      </c>
+      <c r="AW285" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX285" t="n">
+        <v>65.92307692307692</v>
+      </c>
+      <c r="AY285" t="n">
+        <v>950000</v>
+      </c>
+      <c r="AZ285" t="n">
+        <v>70</v>
+      </c>
+      <c r="BA285" t="inlineStr"/>
+      <c r="BB285" t="inlineStr"/>
+      <c r="BC285" t="inlineStr"/>
+      <c r="BD285" t="inlineStr"/>
+      <c r="BE285" t="inlineStr"/>
+      <c r="BF285" t="inlineStr"/>
+      <c r="BG285" t="inlineStr"/>
+      <c r="BH285" t="inlineStr"/>
+      <c r="BI285" t="inlineStr"/>
+      <c r="BJ285" t="inlineStr"/>
+      <c r="BK285" t="inlineStr"/>
+      <c r="BL285" t="inlineStr"/>
+      <c r="BM285" t="inlineStr"/>
+      <c r="BN285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>Gnw301yH</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="n">
+        <v>45536.58333333334</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reig s  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de anduva
+  miranda de ebro </t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>5759</v>
+      </c>
+      <c r="F286" t="n">
+        <v>4747</v>
+      </c>
+      <c r="G286" t="n">
+        <v>0</v>
+      </c>
+      <c r="H286" t="n">
+        <v>0</v>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
+      <c r="M286" t="n">
+        <v>45</v>
+      </c>
+      <c r="N286" t="n">
+        <v>55</v>
+      </c>
+      <c r="O286" t="n">
+        <v>19</v>
+      </c>
+      <c r="P286" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q286" t="n">
+        <v>2</v>
+      </c>
+      <c r="R286" t="n">
+        <v>1</v>
+      </c>
+      <c r="S286" t="n">
+        <v>8</v>
+      </c>
+      <c r="T286" t="n">
+        <v>21</v>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="W286" t="n">
+        <v>148</v>
+      </c>
+      <c r="X286" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y286" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z286" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="AB286" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="AC286" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AD286" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AE286" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF286" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="AG286" t="n">
+        <v>1053750</v>
+      </c>
+      <c r="AH286" t="n">
+        <v>73</v>
+      </c>
+      <c r="AI286" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AJ286" t="n">
+        <v>176.75</v>
+      </c>
+      <c r="AK286" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL286" t="n">
+        <v>67.375</v>
+      </c>
+      <c r="AM286" t="n">
+        <v>1787500</v>
+      </c>
+      <c r="AN286" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="AO286" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP286" t="n">
+        <v>177.6666666666667</v>
+      </c>
+      <c r="AQ286" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR286" t="n">
+        <v>65.41666666666667</v>
+      </c>
+      <c r="AS286" t="n">
+        <v>1658333.333333333</v>
+      </c>
+      <c r="AT286" t="n">
+        <v>76.66666666666667</v>
+      </c>
+      <c r="AU286" t="n">
+        <v>23.85714285714286</v>
+      </c>
+      <c r="AV286" t="n">
+        <v>179.8571428571429</v>
+      </c>
+      <c r="AW286" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX286" t="n">
+        <v>69.85714285714286</v>
+      </c>
+      <c r="AY286" t="n">
+        <v>2560714.285714286</v>
+      </c>
+      <c r="AZ286" t="n">
+        <v>76.14285714285714</v>
+      </c>
+      <c r="BA286" t="inlineStr"/>
+      <c r="BB286" t="inlineStr"/>
+      <c r="BC286" t="inlineStr"/>
+      <c r="BD286" t="inlineStr"/>
+      <c r="BE286" t="inlineStr"/>
+      <c r="BF286" t="inlineStr"/>
+      <c r="BG286" t="inlineStr"/>
+      <c r="BH286" t="inlineStr"/>
+      <c r="BI286" t="inlineStr"/>
+      <c r="BJ286" t="inlineStr"/>
+      <c r="BK286" t="inlineStr"/>
+      <c r="BL286" t="inlineStr"/>
+      <c r="BM286" t="inlineStr"/>
+      <c r="BN286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>fJ9LmOiB</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moreno a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el plantio
+  burgos </t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>12194</v>
+      </c>
+      <c r="F287" t="n">
+        <v>9105</v>
+      </c>
+      <c r="G287" t="n">
+        <v>0</v>
+      </c>
+      <c r="H287" t="n">
+        <v>2</v>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="n">
+        <v>39</v>
+      </c>
+      <c r="N287" t="n">
+        <v>61</v>
+      </c>
+      <c r="O287" t="n">
+        <v>10</v>
+      </c>
+      <c r="P287" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q287" t="n">
+        <v>1</v>
+      </c>
+      <c r="R287" t="n">
+        <v>6</v>
+      </c>
+      <c r="S287" t="n">
+        <v>5</v>
+      </c>
+      <c r="T287" t="n">
+        <v>7</v>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>l6JQtDqc</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="W287" t="n">
+        <v>148</v>
+      </c>
+      <c r="X287" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y287" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z287" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA287" t="inlineStr"/>
+      <c r="AB287" t="inlineStr"/>
+      <c r="AC287" t="inlineStr"/>
+      <c r="AD287" t="inlineStr"/>
+      <c r="AE287" t="inlineStr"/>
+      <c r="AF287" t="inlineStr"/>
+      <c r="AG287" t="inlineStr"/>
+      <c r="AH287" t="inlineStr"/>
+      <c r="AI287" t="inlineStr"/>
+      <c r="AJ287" t="inlineStr"/>
+      <c r="AK287" t="inlineStr"/>
+      <c r="AL287" t="inlineStr"/>
+      <c r="AM287" t="inlineStr"/>
+      <c r="AN287" t="inlineStr"/>
+      <c r="AO287" t="n">
+        <v>24.72727272727273</v>
+      </c>
+      <c r="AP287" t="n">
+        <v>183</v>
+      </c>
+      <c r="AQ287" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR287" t="n">
+        <v>68.63636363636364</v>
+      </c>
+      <c r="AS287" t="n">
+        <v>2265909.090909091</v>
+      </c>
+      <c r="AT287" t="n">
+        <v>73.54545454545455</v>
+      </c>
+      <c r="AU287" t="inlineStr"/>
+      <c r="AV287" t="inlineStr"/>
+      <c r="AW287" t="inlineStr"/>
+      <c r="AX287" t="inlineStr"/>
+      <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr"/>
+      <c r="BA287" t="inlineStr"/>
+      <c r="BB287" t="inlineStr"/>
+      <c r="BC287" t="inlineStr"/>
+      <c r="BD287" t="inlineStr"/>
+      <c r="BE287" t="inlineStr"/>
+      <c r="BF287" t="inlineStr"/>
+      <c r="BG287" t="inlineStr"/>
+      <c r="BH287" t="inlineStr"/>
+      <c r="BI287" t="inlineStr"/>
+      <c r="BJ287" t="inlineStr"/>
+      <c r="BK287" t="inlineStr"/>
+      <c r="BL287" t="inlineStr"/>
+      <c r="BM287" t="inlineStr"/>
+      <c r="BN287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>K0g0ttpo</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">monescillo d 
+  esp </t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de riazor
+  la coruna </t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>34889</v>
+      </c>
+      <c r="F288" t="n">
+        <v>26452</v>
+      </c>
+      <c r="G288" t="n">
+        <v>1</v>
+      </c>
+      <c r="H288" t="n">
+        <v>0</v>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="n">
+        <v>55</v>
+      </c>
+      <c r="N288" t="n">
+        <v>45</v>
+      </c>
+      <c r="O288" t="n">
+        <v>15</v>
+      </c>
+      <c r="P288" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>2</v>
+      </c>
+      <c r="R288" t="n">
+        <v>1</v>
+      </c>
+      <c r="S288" t="n">
+        <v>18</v>
+      </c>
+      <c r="T288" t="n">
+        <v>14</v>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="W288" t="n">
+        <v>148</v>
+      </c>
+      <c r="X288" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y288" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z288" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA288" t="inlineStr"/>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="AC288" t="inlineStr"/>
+      <c r="AD288" t="inlineStr"/>
+      <c r="AE288" t="inlineStr"/>
+      <c r="AF288" t="inlineStr"/>
+      <c r="AG288" t="inlineStr"/>
+      <c r="AH288" t="inlineStr"/>
+      <c r="AI288" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AJ288" t="n">
+        <v>179.125</v>
+      </c>
+      <c r="AK288" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL288" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="AM288" t="n">
+        <v>1190625</v>
+      </c>
+      <c r="AN288" t="n">
+        <v>69.875</v>
+      </c>
+      <c r="AO288" t="n">
+        <v>25.30769230769231</v>
+      </c>
+      <c r="AP288" t="n">
+        <v>181.3846153846154</v>
+      </c>
+      <c r="AQ288" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR288" t="n">
+        <v>68.15384615384616</v>
+      </c>
+      <c r="AS288" t="n">
+        <v>1528846.153846154</v>
+      </c>
+      <c r="AT288" t="n">
+        <v>71.92307692307692</v>
+      </c>
+      <c r="AU288" t="n">
+        <v>26.23529411764706</v>
+      </c>
+      <c r="AV288" t="n">
+        <v>177.5294117647059</v>
+      </c>
+      <c r="AW288" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX288" t="n">
+        <v>66.52941176470588</v>
+      </c>
+      <c r="AY288" t="n">
+        <v>1226470.588235294</v>
+      </c>
+      <c r="AZ288" t="n">
+        <v>69.94117647058823</v>
+      </c>
+      <c r="BA288" t="inlineStr"/>
+      <c r="BB288" t="inlineStr"/>
+      <c r="BC288" t="inlineStr"/>
+      <c r="BD288" t="inlineStr"/>
+      <c r="BE288" t="inlineStr"/>
+      <c r="BF288" t="inlineStr"/>
+      <c r="BG288" t="inlineStr"/>
+      <c r="BH288" t="inlineStr"/>
+      <c r="BI288" t="inlineStr"/>
+      <c r="BJ288" t="inlineStr"/>
+      <c r="BK288" t="inlineStr"/>
+      <c r="BL288" t="inlineStr"/>
+      <c r="BM288" t="inlineStr"/>
+      <c r="BN288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>Y3LCkpNb</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de la fuente ramos o 
+  esp </t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">power horse stadium
+  almeria </t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>17400</v>
+      </c>
+      <c r="F289" t="n">
+        <v>12787</v>
+      </c>
+      <c r="G289" t="n">
+        <v>1</v>
+      </c>
+      <c r="H289" t="n">
+        <v>1</v>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr"/>
+      <c r="M289" t="n">
+        <v>56</v>
+      </c>
+      <c r="N289" t="n">
+        <v>44</v>
+      </c>
+      <c r="O289" t="n">
+        <v>27</v>
+      </c>
+      <c r="P289" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q289" t="n">
+        <v>7</v>
+      </c>
+      <c r="R289" t="n">
+        <v>4</v>
+      </c>
+      <c r="S289" t="n">
+        <v>16</v>
+      </c>
+      <c r="T289" t="n">
+        <v>14</v>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="W289" t="n">
+        <v>148</v>
+      </c>
+      <c r="X289" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y289" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z289" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="AB289" t="inlineStr"/>
+      <c r="AC289" t="inlineStr"/>
+      <c r="AD289" t="inlineStr"/>
+      <c r="AE289" t="inlineStr"/>
+      <c r="AF289" t="inlineStr"/>
+      <c r="AG289" t="inlineStr"/>
+      <c r="AH289" t="inlineStr"/>
+      <c r="AI289" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="AJ289" t="n">
+        <v>179.1111111111111</v>
+      </c>
+      <c r="AK289" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL289" t="n">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="AM289" t="n">
+        <v>2372222.222222222</v>
+      </c>
+      <c r="AN289" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AO289" t="n">
+        <v>23.78947368421053</v>
+      </c>
+      <c r="AP289" t="n">
+        <v>184.3157894736842</v>
+      </c>
+      <c r="AQ289" t="n">
+        <v>1.315789473684211</v>
+      </c>
+      <c r="AR289" t="n">
+        <v>72.21052631578948</v>
+      </c>
+      <c r="AS289" t="n">
+        <v>6506578.947368421</v>
+      </c>
+      <c r="AT289" t="n">
+        <v>77.78947368421052</v>
+      </c>
+      <c r="AU289" t="n">
+        <v>26.11111111111111</v>
+      </c>
+      <c r="AV289" t="n">
+        <v>177.3333333333333</v>
+      </c>
+      <c r="AW289" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX289" t="n">
+        <v>69.33333333333333</v>
+      </c>
+      <c r="AY289" t="n">
+        <v>2127777.777777778</v>
+      </c>
+      <c r="AZ289" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="BA289" t="inlineStr"/>
+      <c r="BB289" t="inlineStr"/>
+      <c r="BC289" t="inlineStr"/>
+      <c r="BD289" t="inlineStr"/>
+      <c r="BE289" t="inlineStr"/>
+      <c r="BF289" t="inlineStr"/>
+      <c r="BG289" t="inlineStr"/>
+      <c r="BH289" t="inlineStr"/>
+      <c r="BI289" t="inlineStr"/>
+      <c r="BJ289" t="inlineStr"/>
+      <c r="BK289" t="inlineStr"/>
+      <c r="BL289" t="inlineStr"/>
+      <c r="BM289" t="inlineStr"/>
+      <c r="BN289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>YoStgJTj</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">palencia caballero d 
+  esp </t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio la rosaleda
+  malaga </t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>30044</v>
+      </c>
+      <c r="F290" t="n">
+        <v>25861</v>
+      </c>
+      <c r="G290" t="n">
+        <v>2</v>
+      </c>
+      <c r="H290" t="n">
+        <v>1</v>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr"/>
+      <c r="M290" t="n">
+        <v>44</v>
+      </c>
+      <c r="N290" t="n">
+        <v>56</v>
+      </c>
+      <c r="O290" t="n">
+        <v>16</v>
+      </c>
+      <c r="P290" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q290" t="n">
+        <v>6</v>
+      </c>
+      <c r="R290" t="n">
+        <v>7</v>
+      </c>
+      <c r="S290" t="n">
+        <v>17</v>
+      </c>
+      <c r="T290" t="n">
+        <v>20</v>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>tjXr7SAp</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="W290" t="n">
+        <v>148</v>
+      </c>
+      <c r="X290" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z290" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA290" t="inlineStr"/>
+      <c r="AB290" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC290" t="inlineStr"/>
+      <c r="AD290" t="inlineStr"/>
+      <c r="AE290" t="inlineStr"/>
+      <c r="AF290" t="inlineStr"/>
+      <c r="AG290" t="inlineStr"/>
+      <c r="AH290" t="inlineStr"/>
+      <c r="AI290" t="inlineStr"/>
+      <c r="AJ290" t="inlineStr"/>
+      <c r="AK290" t="inlineStr"/>
+      <c r="AL290" t="inlineStr"/>
+      <c r="AM290" t="inlineStr"/>
+      <c r="AN290" t="inlineStr"/>
+      <c r="AO290" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="AP290" t="n">
+        <v>184.8333333333333</v>
+      </c>
+      <c r="AQ290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR290" t="n">
+        <v>64</v>
+      </c>
+      <c r="AS290" t="n">
+        <v>1158333.333333333</v>
+      </c>
+      <c r="AT290" t="n">
+        <v>73.66666666666667</v>
+      </c>
+      <c r="AU290" t="n">
+        <v>25.07692307692308</v>
+      </c>
+      <c r="AV290" t="n">
+        <v>180.8461538461538</v>
+      </c>
+      <c r="AW290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX290" t="n">
+        <v>67.15384615384616</v>
+      </c>
+      <c r="AY290" t="n">
+        <v>1455769.230769231</v>
+      </c>
+      <c r="AZ290" t="n">
+        <v>70.69230769230769</v>
+      </c>
+      <c r="BA290" t="inlineStr"/>
+      <c r="BB290" t="inlineStr"/>
+      <c r="BC290" t="inlineStr"/>
+      <c r="BD290" t="inlineStr"/>
+      <c r="BE290" t="inlineStr"/>
+      <c r="BF290" t="inlineStr"/>
+      <c r="BG290" t="inlineStr"/>
+      <c r="BH290" t="inlineStr"/>
+      <c r="BI290" t="inlineStr"/>
+      <c r="BJ290" t="inlineStr"/>
+      <c r="BK290" t="inlineStr"/>
+      <c r="BL290" t="inlineStr"/>
+      <c r="BM290" t="inlineStr"/>
+      <c r="BN290" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN292"/>
+  <dimension ref="A1:BN312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56909,6 +56909,3524 @@
       <c r="BM292" t="inlineStr"/>
       <c r="BN292" t="inlineStr"/>
     </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>G8Q9dhzq</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="n">
+        <v>45544.66666666666</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">muresan s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio carlos belmonte
+  albacete </t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>17524</v>
+      </c>
+      <c r="F293" t="n">
+        <v>10433</v>
+      </c>
+      <c r="G293" t="n">
+        <v>0</v>
+      </c>
+      <c r="H293" t="n">
+        <v>1</v>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
+      <c r="M293" t="n">
+        <v>49</v>
+      </c>
+      <c r="N293" t="n">
+        <v>51</v>
+      </c>
+      <c r="O293" t="n">
+        <v>18</v>
+      </c>
+      <c r="P293" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q293" t="n">
+        <v>4</v>
+      </c>
+      <c r="R293" t="n">
+        <v>1</v>
+      </c>
+      <c r="S293" t="n">
+        <v>9</v>
+      </c>
+      <c r="T293" t="n">
+        <v>7</v>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="W293" t="n">
+        <v>148</v>
+      </c>
+      <c r="X293" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y293" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z293" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB293" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="AC293" t="inlineStr"/>
+      <c r="AD293" t="inlineStr"/>
+      <c r="AE293" t="inlineStr"/>
+      <c r="AF293" t="inlineStr"/>
+      <c r="AG293" t="inlineStr"/>
+      <c r="AH293" t="inlineStr"/>
+      <c r="AI293" t="inlineStr"/>
+      <c r="AJ293" t="inlineStr"/>
+      <c r="AK293" t="inlineStr"/>
+      <c r="AL293" t="inlineStr"/>
+      <c r="AM293" t="inlineStr"/>
+      <c r="AN293" t="inlineStr"/>
+      <c r="AO293" t="n">
+        <v>25.14285714285714</v>
+      </c>
+      <c r="AP293" t="n">
+        <v>179.6428571428571</v>
+      </c>
+      <c r="AQ293" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR293" t="n">
+        <v>65.42857142857143</v>
+      </c>
+      <c r="AS293" t="n">
+        <v>1155357.142857143</v>
+      </c>
+      <c r="AT293" t="n">
+        <v>69.42857142857143</v>
+      </c>
+      <c r="AU293" t="n">
+        <v>22.70588235294118</v>
+      </c>
+      <c r="AV293" t="n">
+        <v>182.8823529411765</v>
+      </c>
+      <c r="AW293" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX293" t="n">
+        <v>64.70588235294117</v>
+      </c>
+      <c r="AY293" t="n">
+        <v>1602941.176470588</v>
+      </c>
+      <c r="AZ293" t="n">
+        <v>72.76470588235294</v>
+      </c>
+      <c r="BA293" t="inlineStr"/>
+      <c r="BB293" t="inlineStr"/>
+      <c r="BC293" t="inlineStr"/>
+      <c r="BD293" t="inlineStr"/>
+      <c r="BE293" t="inlineStr"/>
+      <c r="BF293" t="inlineStr"/>
+      <c r="BG293" t="inlineStr"/>
+      <c r="BH293" t="inlineStr"/>
+      <c r="BI293" t="inlineStr"/>
+      <c r="BJ293" t="inlineStr"/>
+      <c r="BK293" t="inlineStr"/>
+      <c r="BL293" t="inlineStr"/>
+      <c r="BM293" t="inlineStr"/>
+      <c r="BN293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>MR4h79l1</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="n">
+        <v>45544.66666666666</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sesma espinosa m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de castalia
+  castellon de la plana </t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>15500</v>
+      </c>
+      <c r="F294" t="n">
+        <v>13218</v>
+      </c>
+      <c r="G294" t="n">
+        <v>1</v>
+      </c>
+      <c r="H294" t="n">
+        <v>3</v>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
+      <c r="M294" t="n">
+        <v>70</v>
+      </c>
+      <c r="N294" t="n">
+        <v>30</v>
+      </c>
+      <c r="O294" t="n">
+        <v>17</v>
+      </c>
+      <c r="P294" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q294" t="n">
+        <v>5</v>
+      </c>
+      <c r="R294" t="n">
+        <v>5</v>
+      </c>
+      <c r="S294" t="n">
+        <v>13</v>
+      </c>
+      <c r="T294" t="n">
+        <v>15</v>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="V294" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="W294" t="n">
+        <v>148</v>
+      </c>
+      <c r="X294" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y294" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z294" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA294" t="inlineStr"/>
+      <c r="AB294" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AC294" t="inlineStr"/>
+      <c r="AD294" t="inlineStr"/>
+      <c r="AE294" t="inlineStr"/>
+      <c r="AF294" t="inlineStr"/>
+      <c r="AG294" t="inlineStr"/>
+      <c r="AH294" t="inlineStr"/>
+      <c r="AI294" t="n">
+        <v>28.77777777777778</v>
+      </c>
+      <c r="AJ294" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="AK294" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL294" t="n">
+        <v>73.66666666666667</v>
+      </c>
+      <c r="AM294" t="n">
+        <v>4688888.888888889</v>
+      </c>
+      <c r="AN294" t="n">
+        <v>74.55555555555556</v>
+      </c>
+      <c r="AO294" t="inlineStr"/>
+      <c r="AP294" t="inlineStr"/>
+      <c r="AQ294" t="inlineStr"/>
+      <c r="AR294" t="inlineStr"/>
+      <c r="AS294" t="inlineStr"/>
+      <c r="AT294" t="inlineStr"/>
+      <c r="AU294" t="n">
+        <v>25.53846153846154</v>
+      </c>
+      <c r="AV294" t="n">
+        <v>179.7692307692308</v>
+      </c>
+      <c r="AW294" t="n">
+        <v>1.076923076923077</v>
+      </c>
+      <c r="AX294" t="n">
+        <v>68.69230769230769</v>
+      </c>
+      <c r="AY294" t="n">
+        <v>3344230.769230769</v>
+      </c>
+      <c r="AZ294" t="n">
+        <v>73.92307692307692</v>
+      </c>
+      <c r="BA294" t="inlineStr"/>
+      <c r="BB294" t="inlineStr"/>
+      <c r="BC294" t="inlineStr"/>
+      <c r="BD294" t="inlineStr"/>
+      <c r="BE294" t="inlineStr"/>
+      <c r="BF294" t="inlineStr"/>
+      <c r="BG294" t="inlineStr"/>
+      <c r="BH294" t="inlineStr"/>
+      <c r="BI294" t="inlineStr"/>
+      <c r="BJ294" t="inlineStr"/>
+      <c r="BK294" t="inlineStr"/>
+      <c r="BL294" t="inlineStr"/>
+      <c r="BM294" t="inlineStr"/>
+      <c r="BN294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>6g3LEidR</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="n">
+        <v>45543.5625</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">muniz munoz c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo pepico amat
+  elda </t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>4038</v>
+      </c>
+      <c r="F295" t="n">
+        <v>4957</v>
+      </c>
+      <c r="G295" t="n">
+        <v>1</v>
+      </c>
+      <c r="H295" t="n">
+        <v>0</v>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
+      <c r="M295" t="n">
+        <v>46</v>
+      </c>
+      <c r="N295" t="n">
+        <v>54</v>
+      </c>
+      <c r="O295" t="n">
+        <v>7</v>
+      </c>
+      <c r="P295" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>3</v>
+      </c>
+      <c r="R295" t="n">
+        <v>2</v>
+      </c>
+      <c r="S295" t="n">
+        <v>19</v>
+      </c>
+      <c r="T295" t="n">
+        <v>12</v>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>hh4xt2Df</t>
+        </is>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="W295" t="n">
+        <v>148</v>
+      </c>
+      <c r="X295" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y295" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z295" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="AB295" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="AC295" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="AD295" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="AE295" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF295" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AG295" t="n">
+        <v>919375</v>
+      </c>
+      <c r="AH295" t="n">
+        <v>70.375</v>
+      </c>
+      <c r="AI295" t="n">
+        <v>24.44444444444444</v>
+      </c>
+      <c r="AJ295" t="n">
+        <v>184</v>
+      </c>
+      <c r="AK295" t="n">
+        <v>1.555555555555556</v>
+      </c>
+      <c r="AL295" t="n">
+        <v>72.88888888888889</v>
+      </c>
+      <c r="AM295" t="n">
+        <v>7350000</v>
+      </c>
+      <c r="AN295" t="n">
+        <v>78.44444444444444</v>
+      </c>
+      <c r="AO295" t="n">
+        <v>26.70588235294118</v>
+      </c>
+      <c r="AP295" t="n">
+        <v>181.2352941176471</v>
+      </c>
+      <c r="AQ295" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR295" t="n">
+        <v>68.23529411764706</v>
+      </c>
+      <c r="AS295" t="n">
+        <v>2364705.882352941</v>
+      </c>
+      <c r="AT295" t="n">
+        <v>71.41176470588235</v>
+      </c>
+      <c r="AU295" t="n">
+        <v>22</v>
+      </c>
+      <c r="AV295" t="n">
+        <v>183.125</v>
+      </c>
+      <c r="AW295" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AX295" t="n">
+        <v>68.1875</v>
+      </c>
+      <c r="AY295" t="n">
+        <v>3607812.5</v>
+      </c>
+      <c r="AZ295" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="BA295" t="inlineStr"/>
+      <c r="BB295" t="inlineStr"/>
+      <c r="BC295" t="inlineStr"/>
+      <c r="BD295" t="inlineStr"/>
+      <c r="BE295" t="inlineStr"/>
+      <c r="BF295" t="inlineStr"/>
+      <c r="BG295" t="inlineStr"/>
+      <c r="BH295" t="inlineStr"/>
+      <c r="BI295" t="inlineStr"/>
+      <c r="BJ295" t="inlineStr"/>
+      <c r="BK295" t="inlineStr"/>
+      <c r="BL295" t="inlineStr"/>
+      <c r="BM295" t="inlineStr"/>
+      <c r="BN295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>CGXpDaxK</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="n">
+        <v>45543.5625</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrera r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la romareda
+  zaragoza </t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>33608</v>
+      </c>
+      <c r="F296" t="n">
+        <v>21024</v>
+      </c>
+      <c r="G296" t="n">
+        <v>3</v>
+      </c>
+      <c r="H296" t="n">
+        <v>0</v>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="M296" t="n">
+        <v>51</v>
+      </c>
+      <c r="N296" t="n">
+        <v>49</v>
+      </c>
+      <c r="O296" t="n">
+        <v>21</v>
+      </c>
+      <c r="P296" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q296" t="n">
+        <v>9</v>
+      </c>
+      <c r="R296" t="n">
+        <v>3</v>
+      </c>
+      <c r="S296" t="n">
+        <v>15</v>
+      </c>
+      <c r="T296" t="n">
+        <v>15</v>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>zT9gi7i9</t>
+        </is>
+      </c>
+      <c r="W296" t="n">
+        <v>148</v>
+      </c>
+      <c r="X296" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y296" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z296" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="AB296" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC296" t="n">
+        <v>23.55555555555556</v>
+      </c>
+      <c r="AD296" t="n">
+        <v>176</v>
+      </c>
+      <c r="AE296" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF296" t="n">
+        <v>67.55555555555556</v>
+      </c>
+      <c r="AG296" t="n">
+        <v>1777777.777777778</v>
+      </c>
+      <c r="AH296" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AI296" t="n">
+        <v>26.875</v>
+      </c>
+      <c r="AJ296" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AK296" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL296" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AM296" t="n">
+        <v>2278125</v>
+      </c>
+      <c r="AN296" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AO296" t="n">
+        <v>24.46666666666667</v>
+      </c>
+      <c r="AP296" t="n">
+        <v>180.5333333333333</v>
+      </c>
+      <c r="AQ296" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR296" t="n">
+        <v>69.86666666666666</v>
+      </c>
+      <c r="AS296" t="n">
+        <v>2440000</v>
+      </c>
+      <c r="AT296" t="n">
+        <v>75.73333333333333</v>
+      </c>
+      <c r="AU296" t="n">
+        <v>26.27777777777778</v>
+      </c>
+      <c r="AV296" t="n">
+        <v>183.7222222222222</v>
+      </c>
+      <c r="AW296" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AX296" t="n">
+        <v>68.33333333333333</v>
+      </c>
+      <c r="AY296" t="n">
+        <v>1659722.222222222</v>
+      </c>
+      <c r="AZ296" t="n">
+        <v>72</v>
+      </c>
+      <c r="BA296" t="inlineStr"/>
+      <c r="BB296" t="inlineStr"/>
+      <c r="BC296" t="inlineStr"/>
+      <c r="BD296" t="inlineStr"/>
+      <c r="BE296" t="inlineStr"/>
+      <c r="BF296" t="inlineStr"/>
+      <c r="BG296" t="inlineStr"/>
+      <c r="BH296" t="inlineStr"/>
+      <c r="BI296" t="inlineStr"/>
+      <c r="BJ296" t="inlineStr"/>
+      <c r="BK296" t="inlineStr"/>
+      <c r="BL296" t="inlineStr"/>
+      <c r="BM296" t="inlineStr"/>
+      <c r="BN296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>M5THfW4e</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="n">
+        <v>45543.46875</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal cartagonova
+  cartagena </t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>13745</v>
+      </c>
+      <c r="F297" t="n">
+        <v>7963</v>
+      </c>
+      <c r="G297" t="n">
+        <v>0</v>
+      </c>
+      <c r="H297" t="n">
+        <v>1</v>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
+      <c r="M297" t="n">
+        <v>48</v>
+      </c>
+      <c r="N297" t="n">
+        <v>52</v>
+      </c>
+      <c r="O297" t="n">
+        <v>14</v>
+      </c>
+      <c r="P297" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q297" t="n">
+        <v>3</v>
+      </c>
+      <c r="R297" t="n">
+        <v>8</v>
+      </c>
+      <c r="S297" t="n">
+        <v>9</v>
+      </c>
+      <c r="T297" t="n">
+        <v>14</v>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>M1vEw5An</t>
+        </is>
+      </c>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>fiZxGYJ3</t>
+        </is>
+      </c>
+      <c r="W297" t="n">
+        <v>148</v>
+      </c>
+      <c r="X297" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y297" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z297" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="AB297" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="AC297" t="inlineStr"/>
+      <c r="AD297" t="inlineStr"/>
+      <c r="AE297" t="inlineStr"/>
+      <c r="AF297" t="inlineStr"/>
+      <c r="AG297" t="inlineStr"/>
+      <c r="AH297" t="inlineStr"/>
+      <c r="AI297" t="inlineStr"/>
+      <c r="AJ297" t="inlineStr"/>
+      <c r="AK297" t="inlineStr"/>
+      <c r="AL297" t="inlineStr"/>
+      <c r="AM297" t="inlineStr"/>
+      <c r="AN297" t="inlineStr"/>
+      <c r="AO297" t="n">
+        <v>24.625</v>
+      </c>
+      <c r="AP297" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="AQ297" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR297" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="AS297" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="AT297" t="n">
+        <v>71.125</v>
+      </c>
+      <c r="AU297" t="n">
+        <v>22.63636363636364</v>
+      </c>
+      <c r="AV297" t="n">
+        <v>177</v>
+      </c>
+      <c r="AW297" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX297" t="n">
+        <v>66.36363636363636</v>
+      </c>
+      <c r="AY297" t="n">
+        <v>1736363.636363636</v>
+      </c>
+      <c r="AZ297" t="n">
+        <v>72.45454545454545</v>
+      </c>
+      <c r="BA297" t="inlineStr"/>
+      <c r="BB297" t="inlineStr"/>
+      <c r="BC297" t="inlineStr"/>
+      <c r="BD297" t="inlineStr"/>
+      <c r="BE297" t="inlineStr"/>
+      <c r="BF297" t="inlineStr"/>
+      <c r="BG297" t="inlineStr"/>
+      <c r="BH297" t="inlineStr"/>
+      <c r="BI297" t="inlineStr"/>
+      <c r="BJ297" t="inlineStr"/>
+      <c r="BK297" t="inlineStr"/>
+      <c r="BL297" t="inlineStr"/>
+      <c r="BM297" t="inlineStr"/>
+      <c r="BN297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>AR9CGDRE</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="n">
+        <v>45543.375</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez lopez r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal da malata
+  ferrol </t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>10450</v>
+      </c>
+      <c r="F298" t="n">
+        <v>6425</v>
+      </c>
+      <c r="G298" t="n">
+        <v>0</v>
+      </c>
+      <c r="H298" t="n">
+        <v>0</v>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr"/>
+      <c r="M298" t="n">
+        <v>58</v>
+      </c>
+      <c r="N298" t="n">
+        <v>42</v>
+      </c>
+      <c r="O298" t="n">
+        <v>12</v>
+      </c>
+      <c r="P298" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q298" t="n">
+        <v>1</v>
+      </c>
+      <c r="R298" t="n">
+        <v>4</v>
+      </c>
+      <c r="S298" t="n">
+        <v>13</v>
+      </c>
+      <c r="T298" t="n">
+        <v>15</v>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="W298" t="n">
+        <v>148</v>
+      </c>
+      <c r="X298" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y298" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z298" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="AB298" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="AC298" t="inlineStr"/>
+      <c r="AD298" t="inlineStr"/>
+      <c r="AE298" t="inlineStr"/>
+      <c r="AF298" t="inlineStr"/>
+      <c r="AG298" t="inlineStr"/>
+      <c r="AH298" t="inlineStr"/>
+      <c r="AI298" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AJ298" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AK298" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL298" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="AM298" t="n">
+        <v>1053750</v>
+      </c>
+      <c r="AN298" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="AO298" t="n">
+        <v>27.76470588235294</v>
+      </c>
+      <c r="AP298" t="n">
+        <v>178.1176470588235</v>
+      </c>
+      <c r="AQ298" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR298" t="n">
+        <v>68.47058823529412</v>
+      </c>
+      <c r="AS298" t="n">
+        <v>1695588.235294118</v>
+      </c>
+      <c r="AT298" t="n">
+        <v>70.64705882352941</v>
+      </c>
+      <c r="AU298" t="n">
+        <v>20.86666666666667</v>
+      </c>
+      <c r="AV298" t="n">
+        <v>175.8666666666667</v>
+      </c>
+      <c r="AW298" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX298" t="n">
+        <v>64.73333333333333</v>
+      </c>
+      <c r="AY298" t="n">
+        <v>1555000</v>
+      </c>
+      <c r="AZ298" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="BA298" t="inlineStr"/>
+      <c r="BB298" t="inlineStr"/>
+      <c r="BC298" t="inlineStr"/>
+      <c r="BD298" t="inlineStr"/>
+      <c r="BE298" t="inlineStr"/>
+      <c r="BF298" t="inlineStr"/>
+      <c r="BG298" t="inlineStr"/>
+      <c r="BH298" t="inlineStr"/>
+      <c r="BI298" t="inlineStr"/>
+      <c r="BJ298" t="inlineStr"/>
+      <c r="BK298" t="inlineStr"/>
+      <c r="BL298" t="inlineStr"/>
+      <c r="BM298" t="inlineStr"/>
+      <c r="BN298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>rLHQhAZ7</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="n">
+        <v>45542.66666666666</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuentes molina a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo arcangel
+  cordoba </t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>21822</v>
+      </c>
+      <c r="F299" t="n">
+        <v>18110</v>
+      </c>
+      <c r="G299" t="n">
+        <v>0</v>
+      </c>
+      <c r="H299" t="n">
+        <v>0</v>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
+      <c r="M299" t="n">
+        <v>53</v>
+      </c>
+      <c r="N299" t="n">
+        <v>47</v>
+      </c>
+      <c r="O299" t="n">
+        <v>13</v>
+      </c>
+      <c r="P299" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q299" t="n">
+        <v>3</v>
+      </c>
+      <c r="R299" t="n">
+        <v>0</v>
+      </c>
+      <c r="S299" t="n">
+        <v>9</v>
+      </c>
+      <c r="T299" t="n">
+        <v>8</v>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>tjXr7SAp</t>
+        </is>
+      </c>
+      <c r="W299" t="n">
+        <v>148</v>
+      </c>
+      <c r="X299" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y299" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z299" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA299" t="inlineStr"/>
+      <c r="AB299" t="inlineStr"/>
+      <c r="AC299" t="inlineStr"/>
+      <c r="AD299" t="inlineStr"/>
+      <c r="AE299" t="inlineStr"/>
+      <c r="AF299" t="inlineStr"/>
+      <c r="AG299" t="inlineStr"/>
+      <c r="AH299" t="inlineStr"/>
+      <c r="AI299" t="inlineStr"/>
+      <c r="AJ299" t="inlineStr"/>
+      <c r="AK299" t="inlineStr"/>
+      <c r="AL299" t="inlineStr"/>
+      <c r="AM299" t="inlineStr"/>
+      <c r="AN299" t="inlineStr"/>
+      <c r="AO299" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="AP299" t="n">
+        <v>188.3333333333333</v>
+      </c>
+      <c r="AQ299" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR299" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="AS299" t="n">
+        <v>1233333.333333333</v>
+      </c>
+      <c r="AT299" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AU299" t="n">
+        <v>23</v>
+      </c>
+      <c r="AV299" t="n">
+        <v>185.1666666666667</v>
+      </c>
+      <c r="AW299" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX299" t="n">
+        <v>64.66666666666667</v>
+      </c>
+      <c r="AY299" t="n">
+        <v>1325000</v>
+      </c>
+      <c r="AZ299" t="n">
+        <v>73</v>
+      </c>
+      <c r="BA299" t="inlineStr"/>
+      <c r="BB299" t="inlineStr"/>
+      <c r="BC299" t="inlineStr"/>
+      <c r="BD299" t="inlineStr"/>
+      <c r="BE299" t="inlineStr"/>
+      <c r="BF299" t="inlineStr"/>
+      <c r="BG299" t="inlineStr"/>
+      <c r="BH299" t="inlineStr"/>
+      <c r="BI299" t="inlineStr"/>
+      <c r="BJ299" t="inlineStr"/>
+      <c r="BK299" t="inlineStr"/>
+      <c r="BL299" t="inlineStr"/>
+      <c r="BM299" t="inlineStr"/>
+      <c r="BN299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>raOG7w0s</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="n">
+        <v>45542.5625</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orellana m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el molinon
+  gijon </t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>29029</v>
+      </c>
+      <c r="F300" t="n">
+        <v>25706</v>
+      </c>
+      <c r="G300" t="n">
+        <v>3</v>
+      </c>
+      <c r="H300" t="n">
+        <v>1</v>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr"/>
+      <c r="M300" t="n">
+        <v>31</v>
+      </c>
+      <c r="N300" t="n">
+        <v>69</v>
+      </c>
+      <c r="O300" t="n">
+        <v>10</v>
+      </c>
+      <c r="P300" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q300" t="n">
+        <v>8</v>
+      </c>
+      <c r="R300" t="n">
+        <v>3</v>
+      </c>
+      <c r="S300" t="n">
+        <v>22</v>
+      </c>
+      <c r="T300" t="n">
+        <v>11</v>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="W300" t="n">
+        <v>148</v>
+      </c>
+      <c r="X300" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y300" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z300" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA300" t="inlineStr"/>
+      <c r="AB300" t="inlineStr"/>
+      <c r="AC300" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD300" t="n">
+        <v>180.2222222222222</v>
+      </c>
+      <c r="AE300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF300" t="n">
+        <v>71.11111111111111</v>
+      </c>
+      <c r="AG300" t="n">
+        <v>2622222.222222222</v>
+      </c>
+      <c r="AH300" t="n">
+        <v>73.55555555555556</v>
+      </c>
+      <c r="AI300" t="inlineStr"/>
+      <c r="AJ300" t="inlineStr"/>
+      <c r="AK300" t="inlineStr"/>
+      <c r="AL300" t="inlineStr"/>
+      <c r="AM300" t="inlineStr"/>
+      <c r="AN300" t="inlineStr"/>
+      <c r="AO300" t="n">
+        <v>23.73333333333333</v>
+      </c>
+      <c r="AP300" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="AQ300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR300" t="n">
+        <v>69.33333333333333</v>
+      </c>
+      <c r="AS300" t="n">
+        <v>2780000</v>
+      </c>
+      <c r="AT300" t="n">
+        <v>75.33333333333333</v>
+      </c>
+      <c r="AU300" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="AV300" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="AW300" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AX300" t="n">
+        <v>68.65000000000001</v>
+      </c>
+      <c r="AY300" t="n">
+        <v>2301250</v>
+      </c>
+      <c r="AZ300" t="n">
+        <v>75.55</v>
+      </c>
+      <c r="BA300" t="inlineStr"/>
+      <c r="BB300" t="inlineStr"/>
+      <c r="BC300" t="inlineStr"/>
+      <c r="BD300" t="inlineStr"/>
+      <c r="BE300" t="inlineStr"/>
+      <c r="BF300" t="inlineStr"/>
+      <c r="BG300" t="inlineStr"/>
+      <c r="BH300" t="inlineStr"/>
+      <c r="BI300" t="inlineStr"/>
+      <c r="BJ300" t="inlineStr"/>
+      <c r="BK300" t="inlineStr"/>
+      <c r="BL300" t="inlineStr"/>
+      <c r="BM300" t="inlineStr"/>
+      <c r="BN300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>2Pli9VJl</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="n">
+        <v>45542.5625</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el alcoraz
+  huesca </t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F301" t="n">
+        <v>6024</v>
+      </c>
+      <c r="G301" t="n">
+        <v>0</v>
+      </c>
+      <c r="H301" t="n">
+        <v>1</v>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
+      <c r="M301" t="n">
+        <v>45</v>
+      </c>
+      <c r="N301" t="n">
+        <v>55</v>
+      </c>
+      <c r="O301" t="n">
+        <v>12</v>
+      </c>
+      <c r="P301" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q301" t="n">
+        <v>1</v>
+      </c>
+      <c r="R301" t="n">
+        <v>7</v>
+      </c>
+      <c r="S301" t="n">
+        <v>10</v>
+      </c>
+      <c r="T301" t="n">
+        <v>9</v>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>l6JQtDqc</t>
+        </is>
+      </c>
+      <c r="W301" t="n">
+        <v>148</v>
+      </c>
+      <c r="X301" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y301" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z301" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="AB301" t="inlineStr"/>
+      <c r="AC301" t="inlineStr"/>
+      <c r="AD301" t="inlineStr"/>
+      <c r="AE301" t="inlineStr"/>
+      <c r="AF301" t="inlineStr"/>
+      <c r="AG301" t="inlineStr"/>
+      <c r="AH301" t="inlineStr"/>
+      <c r="AI301" t="inlineStr"/>
+      <c r="AJ301" t="inlineStr"/>
+      <c r="AK301" t="inlineStr"/>
+      <c r="AL301" t="inlineStr"/>
+      <c r="AM301" t="inlineStr"/>
+      <c r="AN301" t="inlineStr"/>
+      <c r="AO301" t="n">
+        <v>24.93333333333333</v>
+      </c>
+      <c r="AP301" t="n">
+        <v>180</v>
+      </c>
+      <c r="AQ301" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR301" t="n">
+        <v>66.53333333333333</v>
+      </c>
+      <c r="AS301" t="n">
+        <v>1313333.333333333</v>
+      </c>
+      <c r="AT301" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AU301" t="n">
+        <v>24.45454545454545</v>
+      </c>
+      <c r="AV301" t="n">
+        <v>183.2727272727273</v>
+      </c>
+      <c r="AW301" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX301" t="n">
+        <v>69.18181818181819</v>
+      </c>
+      <c r="AY301" t="n">
+        <v>2265909.090909091</v>
+      </c>
+      <c r="AZ301" t="n">
+        <v>72.90909090909091</v>
+      </c>
+      <c r="BA301" t="inlineStr"/>
+      <c r="BB301" t="inlineStr"/>
+      <c r="BC301" t="inlineStr"/>
+      <c r="BD301" t="inlineStr"/>
+      <c r="BE301" t="inlineStr"/>
+      <c r="BF301" t="inlineStr"/>
+      <c r="BG301" t="inlineStr"/>
+      <c r="BH301" t="inlineStr"/>
+      <c r="BI301" t="inlineStr"/>
+      <c r="BJ301" t="inlineStr"/>
+      <c r="BK301" t="inlineStr"/>
+      <c r="BL301" t="inlineStr"/>
+      <c r="BM301" t="inlineStr"/>
+      <c r="BN301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>Ui805mJD</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="n">
+        <v>45542.46875</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cid camacho g 
+  esp </t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo los carmenes
+  granada </t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>22524</v>
+      </c>
+      <c r="F302" t="n">
+        <v>15308</v>
+      </c>
+      <c r="G302" t="n">
+        <v>1</v>
+      </c>
+      <c r="H302" t="n">
+        <v>1</v>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
+      <c r="M302" t="n">
+        <v>49</v>
+      </c>
+      <c r="N302" t="n">
+        <v>51</v>
+      </c>
+      <c r="O302" t="n">
+        <v>13</v>
+      </c>
+      <c r="P302" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q302" t="n">
+        <v>2</v>
+      </c>
+      <c r="R302" t="n">
+        <v>4</v>
+      </c>
+      <c r="S302" t="n">
+        <v>14</v>
+      </c>
+      <c r="T302" t="n">
+        <v>10</v>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>K4dMCgFa</t>
+        </is>
+      </c>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="W302" t="n">
+        <v>148</v>
+      </c>
+      <c r="X302" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z302" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AB302" t="inlineStr"/>
+      <c r="AC302" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD302" t="n">
+        <v>180.9</v>
+      </c>
+      <c r="AE302" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF302" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AG302" t="n">
+        <v>3185000</v>
+      </c>
+      <c r="AH302" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="AI302" t="inlineStr"/>
+      <c r="AJ302" t="inlineStr"/>
+      <c r="AK302" t="inlineStr"/>
+      <c r="AL302" t="inlineStr"/>
+      <c r="AM302" t="inlineStr"/>
+      <c r="AN302" t="inlineStr"/>
+      <c r="AO302" t="n">
+        <v>24.63636363636364</v>
+      </c>
+      <c r="AP302" t="n">
+        <v>182.5909090909091</v>
+      </c>
+      <c r="AQ302" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="AR302" t="n">
+        <v>71.18181818181819</v>
+      </c>
+      <c r="AS302" t="n">
+        <v>3779545.454545455</v>
+      </c>
+      <c r="AT302" t="n">
+        <v>75.68181818181819</v>
+      </c>
+      <c r="AU302" t="n">
+        <v>24.46666666666667</v>
+      </c>
+      <c r="AV302" t="n">
+        <v>179.0666666666667</v>
+      </c>
+      <c r="AW302" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX302" t="n">
+        <v>68.73333333333333</v>
+      </c>
+      <c r="AY302" t="n">
+        <v>1978333.333333333</v>
+      </c>
+      <c r="AZ302" t="n">
+        <v>73.93333333333334</v>
+      </c>
+      <c r="BA302" t="inlineStr"/>
+      <c r="BB302" t="inlineStr"/>
+      <c r="BC302" t="inlineStr"/>
+      <c r="BD302" t="inlineStr"/>
+      <c r="BE302" t="inlineStr"/>
+      <c r="BF302" t="inlineStr"/>
+      <c r="BG302" t="inlineStr"/>
+      <c r="BH302" t="inlineStr"/>
+      <c r="BI302" t="inlineStr"/>
+      <c r="BJ302" t="inlineStr"/>
+      <c r="BK302" t="inlineStr"/>
+      <c r="BL302" t="inlineStr"/>
+      <c r="BM302" t="inlineStr"/>
+      <c r="BN302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>O8WO5HUg</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="n">
+        <v>45541.66666666666</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">galech i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio heliodoro rodriguez lopez
+  santa cruz de tenerife </t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>22824</v>
+      </c>
+      <c r="F303" t="n">
+        <v>15284</v>
+      </c>
+      <c r="G303" t="n">
+        <v>0</v>
+      </c>
+      <c r="H303" t="n">
+        <v>1</v>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr"/>
+      <c r="M303" t="n">
+        <v>51</v>
+      </c>
+      <c r="N303" t="n">
+        <v>49</v>
+      </c>
+      <c r="O303" t="n">
+        <v>4</v>
+      </c>
+      <c r="P303" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q303" t="n">
+        <v>3</v>
+      </c>
+      <c r="R303" t="n">
+        <v>2</v>
+      </c>
+      <c r="S303" t="n">
+        <v>9</v>
+      </c>
+      <c r="T303" t="n">
+        <v>4</v>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>UBD9uzt0</t>
+        </is>
+      </c>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>rak12p9n</t>
+        </is>
+      </c>
+      <c r="W303" t="n">
+        <v>148</v>
+      </c>
+      <c r="X303" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y303" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z303" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="AB303" t="inlineStr"/>
+      <c r="AC303" t="inlineStr"/>
+      <c r="AD303" t="inlineStr"/>
+      <c r="AE303" t="inlineStr"/>
+      <c r="AF303" t="inlineStr"/>
+      <c r="AG303" t="inlineStr"/>
+      <c r="AH303" t="inlineStr"/>
+      <c r="AI303" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ303" t="n">
+        <v>181.125</v>
+      </c>
+      <c r="AK303" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL303" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="AM303" t="n">
+        <v>2912500</v>
+      </c>
+      <c r="AN303" t="n">
+        <v>75.125</v>
+      </c>
+      <c r="AO303" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AP303" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="AQ303" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR303" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AS303" t="n">
+        <v>1538000</v>
+      </c>
+      <c r="AT303" t="n">
+        <v>72.26666666666667</v>
+      </c>
+      <c r="AU303" t="n">
+        <v>27.8125</v>
+      </c>
+      <c r="AV303" t="n">
+        <v>180.9375</v>
+      </c>
+      <c r="AW303" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX303" t="n">
+        <v>67.875</v>
+      </c>
+      <c r="AY303" t="n">
+        <v>1651562.5</v>
+      </c>
+      <c r="AZ303" t="n">
+        <v>71.8125</v>
+      </c>
+      <c r="BA303" t="inlineStr"/>
+      <c r="BB303" t="inlineStr"/>
+      <c r="BC303" t="inlineStr"/>
+      <c r="BD303" t="inlineStr"/>
+      <c r="BE303" t="inlineStr"/>
+      <c r="BF303" t="inlineStr"/>
+      <c r="BG303" t="inlineStr"/>
+      <c r="BH303" t="inlineStr"/>
+      <c r="BI303" t="inlineStr"/>
+      <c r="BJ303" t="inlineStr"/>
+      <c r="BK303" t="inlineStr"/>
+      <c r="BL303" t="inlineStr"/>
+      <c r="BM303" t="inlineStr"/>
+      <c r="BN303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>8EcB5Oig</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="n">
+        <v>1</v>
+      </c>
+      <c r="H304" t="n">
+        <v>0</v>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="K304" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L304" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M304" t="n">
+        <v>60</v>
+      </c>
+      <c r="N304" t="n">
+        <v>40</v>
+      </c>
+      <c r="O304" t="n">
+        <v>10</v>
+      </c>
+      <c r="P304" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q304" t="n">
+        <v>4</v>
+      </c>
+      <c r="R304" t="n">
+        <v>5</v>
+      </c>
+      <c r="S304" t="n">
+        <v>19</v>
+      </c>
+      <c r="T304" t="n">
+        <v>15</v>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="V304" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="W304" t="n">
+        <v>148</v>
+      </c>
+      <c r="X304" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y304" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z304" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AB304" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="AC304" t="inlineStr"/>
+      <c r="AD304" t="inlineStr"/>
+      <c r="AE304" t="inlineStr"/>
+      <c r="AF304" t="inlineStr"/>
+      <c r="AG304" t="inlineStr"/>
+      <c r="AH304" t="inlineStr"/>
+      <c r="AI304" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="AJ304" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="AK304" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AL304" t="n">
+        <v>76</v>
+      </c>
+      <c r="AM304" t="n">
+        <v>9387500</v>
+      </c>
+      <c r="AN304" t="n">
+        <v>78</v>
+      </c>
+      <c r="AO304" t="n">
+        <v>23.14285714285714</v>
+      </c>
+      <c r="AP304" t="n">
+        <v>181.1904761904762</v>
+      </c>
+      <c r="AQ304" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="AR304" t="n">
+        <v>73.71428571428571</v>
+      </c>
+      <c r="AS304" t="n">
+        <v>8638095.238095239</v>
+      </c>
+      <c r="AT304" t="n">
+        <v>80.33333333333333</v>
+      </c>
+      <c r="AU304" t="n">
+        <v>22.8125</v>
+      </c>
+      <c r="AV304" t="n">
+        <v>182.9375</v>
+      </c>
+      <c r="AW304" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX304" t="n">
+        <v>69.5625</v>
+      </c>
+      <c r="AY304" t="n">
+        <v>4459375</v>
+      </c>
+      <c r="AZ304" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="BA304" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="BB304" t="n">
+        <v>186</v>
+      </c>
+      <c r="BC304" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="BD304" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE304" t="n">
+        <v>232</v>
+      </c>
+      <c r="BF304" t="n">
+        <v>49000000</v>
+      </c>
+      <c r="BG304" t="n">
+        <v>244</v>
+      </c>
+      <c r="BH304" t="n">
+        <v>24</v>
+      </c>
+      <c r="BI304" t="n">
+        <v>183</v>
+      </c>
+      <c r="BJ304" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BK304" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL304" t="n">
+        <v>212</v>
+      </c>
+      <c r="BM304" t="n">
+        <v>29375000</v>
+      </c>
+      <c r="BN304" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>CjIFsr1e</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="n">
+        <v>45549.46875</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rcde stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F305" t="n">
+        <v>24238</v>
+      </c>
+      <c r="G305" t="n">
+        <v>3</v>
+      </c>
+      <c r="H305" t="n">
+        <v>2</v>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="K305" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L305" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="M305" t="n">
+        <v>38</v>
+      </c>
+      <c r="N305" t="n">
+        <v>62</v>
+      </c>
+      <c r="O305" t="n">
+        <v>9</v>
+      </c>
+      <c r="P305" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q305" t="n">
+        <v>4</v>
+      </c>
+      <c r="R305" t="n">
+        <v>6</v>
+      </c>
+      <c r="S305" t="n">
+        <v>17</v>
+      </c>
+      <c r="T305" t="n">
+        <v>14</v>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="W305" t="n">
+        <v>148</v>
+      </c>
+      <c r="X305" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y305" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z305" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AB305" t="inlineStr"/>
+      <c r="AC305" t="inlineStr"/>
+      <c r="AD305" t="inlineStr"/>
+      <c r="AE305" t="inlineStr"/>
+      <c r="AF305" t="inlineStr"/>
+      <c r="AG305" t="inlineStr"/>
+      <c r="AH305" t="inlineStr"/>
+      <c r="AI305" t="inlineStr"/>
+      <c r="AJ305" t="inlineStr"/>
+      <c r="AK305" t="inlineStr"/>
+      <c r="AL305" t="inlineStr"/>
+      <c r="AM305" t="inlineStr"/>
+      <c r="AN305" t="inlineStr"/>
+      <c r="AO305" t="n">
+        <v>25.90909090909091</v>
+      </c>
+      <c r="AP305" t="n">
+        <v>182.5909090909091</v>
+      </c>
+      <c r="AQ305" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR305" t="n">
+        <v>71.59090909090909</v>
+      </c>
+      <c r="AS305" t="n">
+        <v>3431818.181818182</v>
+      </c>
+      <c r="AT305" t="n">
+        <v>75.18181818181819</v>
+      </c>
+      <c r="AU305" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="AV305" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="AW305" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AX305" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AY305" t="n">
+        <v>5365000</v>
+      </c>
+      <c r="AZ305" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="BA305" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB305" t="n">
+        <v>178</v>
+      </c>
+      <c r="BC305" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD305" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE305" t="n">
+        <v>74</v>
+      </c>
+      <c r="BF305" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="BG305" t="n">
+        <v>75</v>
+      </c>
+      <c r="BH305" t="n">
+        <v>20</v>
+      </c>
+      <c r="BI305" t="n">
+        <v>182</v>
+      </c>
+      <c r="BJ305" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK305" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL305" t="n">
+        <v>69</v>
+      </c>
+      <c r="BM305" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="BN305" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>08zpk37C</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="n">
+        <v>45549.375</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>26020</v>
+      </c>
+      <c r="F306" t="n">
+        <v>18303</v>
+      </c>
+      <c r="G306" t="n">
+        <v>1</v>
+      </c>
+      <c r="H306" t="n">
+        <v>2</v>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="K306" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L306" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M306" t="n">
+        <v>54</v>
+      </c>
+      <c r="N306" t="n">
+        <v>46</v>
+      </c>
+      <c r="O306" t="n">
+        <v>10</v>
+      </c>
+      <c r="P306" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q306" t="n">
+        <v>5</v>
+      </c>
+      <c r="R306" t="n">
+        <v>4</v>
+      </c>
+      <c r="S306" t="n">
+        <v>11</v>
+      </c>
+      <c r="T306" t="n">
+        <v>10</v>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="W306" t="n">
+        <v>148</v>
+      </c>
+      <c r="X306" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y306" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z306" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="AB306" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC306" t="n">
+        <v>26.44444444444444</v>
+      </c>
+      <c r="AD306" t="n">
+        <v>183.1111111111111</v>
+      </c>
+      <c r="AE306" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AF306" t="n">
+        <v>74.66666666666667</v>
+      </c>
+      <c r="AG306" t="n">
+        <v>7422222.222222222</v>
+      </c>
+      <c r="AH306" t="n">
+        <v>77.11111111111111</v>
+      </c>
+      <c r="AI306" t="inlineStr"/>
+      <c r="AJ306" t="inlineStr"/>
+      <c r="AK306" t="inlineStr"/>
+      <c r="AL306" t="inlineStr"/>
+      <c r="AM306" t="inlineStr"/>
+      <c r="AN306" t="inlineStr"/>
+      <c r="AO306" t="n">
+        <v>26.08333333333333</v>
+      </c>
+      <c r="AP306" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AQ306" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AR306" t="n">
+        <v>74.70833333333333</v>
+      </c>
+      <c r="AS306" t="n">
+        <v>9837916.666666666</v>
+      </c>
+      <c r="AT306" t="n">
+        <v>78.375</v>
+      </c>
+      <c r="AU306" t="n">
+        <v>26.14285714285714</v>
+      </c>
+      <c r="AV306" t="n">
+        <v>179.2857142857143</v>
+      </c>
+      <c r="AW306" t="n">
+        <v>1.571428571428571</v>
+      </c>
+      <c r="AX306" t="n">
+        <v>76</v>
+      </c>
+      <c r="AY306" t="n">
+        <v>9785714.285714285</v>
+      </c>
+      <c r="AZ306" t="n">
+        <v>78.64285714285714</v>
+      </c>
+      <c r="BA306" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BB306" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="BC306" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD306" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE306" t="n">
+        <v>292</v>
+      </c>
+      <c r="BF306" t="n">
+        <v>31100000</v>
+      </c>
+      <c r="BG306" t="n">
+        <v>315</v>
+      </c>
+      <c r="BH306" t="n">
+        <v>25</v>
+      </c>
+      <c r="BI306" t="n">
+        <v>186</v>
+      </c>
+      <c r="BJ306" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BK306" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL306" t="n">
+        <v>378</v>
+      </c>
+      <c r="BM306" t="n">
+        <v>80275000</v>
+      </c>
+      <c r="BN306" t="n">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>YeqTho8m</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="n">
+        <v>45548.66666666666</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F307" t="n">
+        <v>48089</v>
+      </c>
+      <c r="G307" t="n">
+        <v>2</v>
+      </c>
+      <c r="H307" t="n">
+        <v>0</v>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="K307" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="L307" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M307" t="n">
+        <v>64</v>
+      </c>
+      <c r="N307" t="n">
+        <v>36</v>
+      </c>
+      <c r="O307" t="n">
+        <v>14</v>
+      </c>
+      <c r="P307" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q307" t="n">
+        <v>5</v>
+      </c>
+      <c r="R307" t="n">
+        <v>0</v>
+      </c>
+      <c r="S307" t="n">
+        <v>11</v>
+      </c>
+      <c r="T307" t="n">
+        <v>18</v>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="W307" t="n">
+        <v>148</v>
+      </c>
+      <c r="X307" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y307" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z307" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AB307" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="AC307" t="n">
+        <v>25.875</v>
+      </c>
+      <c r="AD307" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AE307" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF307" t="n">
+        <v>76</v>
+      </c>
+      <c r="AG307" t="n">
+        <v>9937500</v>
+      </c>
+      <c r="AH307" t="n">
+        <v>79.875</v>
+      </c>
+      <c r="AI307" t="n">
+        <v>27.125</v>
+      </c>
+      <c r="AJ307" t="n">
+        <v>182.125</v>
+      </c>
+      <c r="AK307" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AL307" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AM307" t="n">
+        <v>6125000</v>
+      </c>
+      <c r="AN307" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="AO307" t="n">
+        <v>23.84210526315789</v>
+      </c>
+      <c r="AP307" t="n">
+        <v>180.2631578947368</v>
+      </c>
+      <c r="AQ307" t="n">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="AR307" t="n">
+        <v>75</v>
+      </c>
+      <c r="AS307" t="n">
+        <v>11289473.68421053</v>
+      </c>
+      <c r="AT307" t="n">
+        <v>80.68421052631579</v>
+      </c>
+      <c r="AU307" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AV307" t="n">
+        <v>182.2727272727273</v>
+      </c>
+      <c r="AW307" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="AX307" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AY307" t="n">
+        <v>4990909.090909091</v>
+      </c>
+      <c r="AZ307" t="n">
+        <v>75.04545454545455</v>
+      </c>
+      <c r="BA307" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="BB307" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="BC307" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD307" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE307" t="n">
+        <v>371</v>
+      </c>
+      <c r="BF307" t="n">
+        <v>49100000</v>
+      </c>
+      <c r="BG307" t="n">
+        <v>385</v>
+      </c>
+      <c r="BH307" t="n">
+        <v>21</v>
+      </c>
+      <c r="BI307" t="n">
+        <v>180</v>
+      </c>
+      <c r="BJ307" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK307" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL307" t="n">
+        <v>63</v>
+      </c>
+      <c r="BM307" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="BN307" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>YR7dTBSH</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reig s  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio la rosaleda
+  malaga </t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>30044</v>
+      </c>
+      <c r="F308" t="n">
+        <v>26672</v>
+      </c>
+      <c r="G308" t="n">
+        <v>1</v>
+      </c>
+      <c r="H308" t="n">
+        <v>0</v>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr"/>
+      <c r="M308" t="n">
+        <v>57</v>
+      </c>
+      <c r="N308" t="n">
+        <v>43</v>
+      </c>
+      <c r="O308" t="n">
+        <v>13</v>
+      </c>
+      <c r="P308" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q308" t="n">
+        <v>3</v>
+      </c>
+      <c r="R308" t="n">
+        <v>2</v>
+      </c>
+      <c r="S308" t="n">
+        <v>16</v>
+      </c>
+      <c r="T308" t="n">
+        <v>12</v>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>tjXr7SAp</t>
+        </is>
+      </c>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="W308" t="n">
+        <v>148</v>
+      </c>
+      <c r="X308" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y308" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z308" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA308" t="inlineStr"/>
+      <c r="AB308" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="AC308" t="inlineStr"/>
+      <c r="AD308" t="inlineStr"/>
+      <c r="AE308" t="inlineStr"/>
+      <c r="AF308" t="inlineStr"/>
+      <c r="AG308" t="inlineStr"/>
+      <c r="AH308" t="inlineStr"/>
+      <c r="AI308" t="inlineStr"/>
+      <c r="AJ308" t="inlineStr"/>
+      <c r="AK308" t="inlineStr"/>
+      <c r="AL308" t="inlineStr"/>
+      <c r="AM308" t="inlineStr"/>
+      <c r="AN308" t="inlineStr"/>
+      <c r="AO308" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="AP308" t="n">
+        <v>185.125</v>
+      </c>
+      <c r="AQ308" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR308" t="n">
+        <v>64.125</v>
+      </c>
+      <c r="AS308" t="n">
+        <v>1243750</v>
+      </c>
+      <c r="AT308" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="AU308" t="n">
+        <v>23.90909090909091</v>
+      </c>
+      <c r="AV308" t="n">
+        <v>180.2727272727273</v>
+      </c>
+      <c r="AW308" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX308" t="n">
+        <v>64.81818181818181</v>
+      </c>
+      <c r="AY308" t="n">
+        <v>1122727.272727273</v>
+      </c>
+      <c r="AZ308" t="n">
+        <v>70.45454545454545</v>
+      </c>
+      <c r="BA308" t="inlineStr"/>
+      <c r="BB308" t="inlineStr"/>
+      <c r="BC308" t="inlineStr"/>
+      <c r="BD308" t="inlineStr"/>
+      <c r="BE308" t="inlineStr"/>
+      <c r="BF308" t="inlineStr"/>
+      <c r="BG308" t="inlineStr"/>
+      <c r="BH308" t="inlineStr"/>
+      <c r="BI308" t="inlineStr"/>
+      <c r="BJ308" t="inlineStr"/>
+      <c r="BK308" t="inlineStr"/>
+      <c r="BL308" t="inlineStr"/>
+      <c r="BM308" t="inlineStr"/>
+      <c r="BN308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>KOsNECDO</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">monescillo d 
+  esp </t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sardinero
+  santander </t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>22222</v>
+      </c>
+      <c r="F309" t="n">
+        <v>20846</v>
+      </c>
+      <c r="G309" t="n">
+        <v>1</v>
+      </c>
+      <c r="H309" t="n">
+        <v>0</v>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr"/>
+      <c r="L309" t="inlineStr"/>
+      <c r="M309" t="n">
+        <v>42</v>
+      </c>
+      <c r="N309" t="n">
+        <v>58</v>
+      </c>
+      <c r="O309" t="n">
+        <v>13</v>
+      </c>
+      <c r="P309" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q309" t="n">
+        <v>3</v>
+      </c>
+      <c r="R309" t="n">
+        <v>2</v>
+      </c>
+      <c r="S309" t="n">
+        <v>5</v>
+      </c>
+      <c r="T309" t="n">
+        <v>19</v>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>rak12p9n</t>
+        </is>
+      </c>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="W309" t="n">
+        <v>148</v>
+      </c>
+      <c r="X309" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y309" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z309" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA309" t="inlineStr"/>
+      <c r="AB309" t="inlineStr"/>
+      <c r="AC309" t="inlineStr"/>
+      <c r="AD309" t="inlineStr"/>
+      <c r="AE309" t="inlineStr"/>
+      <c r="AF309" t="inlineStr"/>
+      <c r="AG309" t="inlineStr"/>
+      <c r="AH309" t="inlineStr"/>
+      <c r="AI309" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AJ309" t="n">
+        <v>179.7</v>
+      </c>
+      <c r="AK309" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL309" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AM309" t="n">
+        <v>2620000</v>
+      </c>
+      <c r="AN309" t="n">
+        <v>74</v>
+      </c>
+      <c r="AO309" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AP309" t="n">
+        <v>181.1111111111111</v>
+      </c>
+      <c r="AQ309" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR309" t="n">
+        <v>67.33333333333333</v>
+      </c>
+      <c r="AS309" t="n">
+        <v>1798611.111111111</v>
+      </c>
+      <c r="AT309" t="n">
+        <v>73.83333333333333</v>
+      </c>
+      <c r="AU309" t="n">
+        <v>24.91666666666667</v>
+      </c>
+      <c r="AV309" t="n">
+        <v>178.75</v>
+      </c>
+      <c r="AW309" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX309" t="n">
+        <v>70.41666666666667</v>
+      </c>
+      <c r="AY309" t="n">
+        <v>3050000</v>
+      </c>
+      <c r="AZ309" t="n">
+        <v>75.41666666666667</v>
+      </c>
+      <c r="BA309" t="inlineStr"/>
+      <c r="BB309" t="inlineStr"/>
+      <c r="BC309" t="inlineStr"/>
+      <c r="BD309" t="inlineStr"/>
+      <c r="BE309" t="inlineStr"/>
+      <c r="BF309" t="inlineStr"/>
+      <c r="BG309" t="inlineStr"/>
+      <c r="BH309" t="inlineStr"/>
+      <c r="BI309" t="inlineStr"/>
+      <c r="BJ309" t="inlineStr"/>
+      <c r="BK309" t="inlineStr"/>
+      <c r="BL309" t="inlineStr"/>
+      <c r="BM309" t="inlineStr"/>
+      <c r="BN309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>jqj6IfEa</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="n">
+        <v>45549.46875</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moreno a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de ipurua
+  eibar </t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>8164</v>
+      </c>
+      <c r="F310" t="n">
+        <v>5030</v>
+      </c>
+      <c r="G310" t="n">
+        <v>1</v>
+      </c>
+      <c r="H310" t="n">
+        <v>0</v>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr"/>
+      <c r="L310" t="inlineStr"/>
+      <c r="M310" t="n">
+        <v>49</v>
+      </c>
+      <c r="N310" t="n">
+        <v>51</v>
+      </c>
+      <c r="O310" t="n">
+        <v>5</v>
+      </c>
+      <c r="P310" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q310" t="n">
+        <v>3</v>
+      </c>
+      <c r="R310" t="n">
+        <v>0</v>
+      </c>
+      <c r="S310" t="n">
+        <v>11</v>
+      </c>
+      <c r="T310" t="n">
+        <v>14</v>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="V310" t="inlineStr">
+        <is>
+          <t>UBD9uzt0</t>
+        </is>
+      </c>
+      <c r="W310" t="n">
+        <v>148</v>
+      </c>
+      <c r="X310" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y310" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z310" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="AB310" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="AC310" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="AD310" t="n">
+        <v>182.375</v>
+      </c>
+      <c r="AE310" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF310" t="n">
+        <v>69</v>
+      </c>
+      <c r="AG310" t="n">
+        <v>1893750</v>
+      </c>
+      <c r="AH310" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AI310" t="inlineStr"/>
+      <c r="AJ310" t="inlineStr"/>
+      <c r="AK310" t="inlineStr"/>
+      <c r="AL310" t="inlineStr"/>
+      <c r="AM310" t="inlineStr"/>
+      <c r="AN310" t="inlineStr"/>
+      <c r="AO310" t="n">
+        <v>24.68421052631579</v>
+      </c>
+      <c r="AP310" t="n">
+        <v>178.6315789473684</v>
+      </c>
+      <c r="AQ310" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR310" t="n">
+        <v>66.47368421052632</v>
+      </c>
+      <c r="AS310" t="n">
+        <v>1907894.736842105</v>
+      </c>
+      <c r="AT310" t="n">
+        <v>72.10526315789474</v>
+      </c>
+      <c r="AU310" t="n">
+        <v>28.16666666666667</v>
+      </c>
+      <c r="AV310" t="n">
+        <v>182.0833333333333</v>
+      </c>
+      <c r="AW310" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX310" t="n">
+        <v>69.83333333333333</v>
+      </c>
+      <c r="AY310" t="n">
+        <v>1747500</v>
+      </c>
+      <c r="AZ310" t="n">
+        <v>72.16666666666667</v>
+      </c>
+      <c r="BA310" t="inlineStr"/>
+      <c r="BB310" t="inlineStr"/>
+      <c r="BC310" t="inlineStr"/>
+      <c r="BD310" t="inlineStr"/>
+      <c r="BE310" t="inlineStr"/>
+      <c r="BF310" t="inlineStr"/>
+      <c r="BG310" t="inlineStr"/>
+      <c r="BH310" t="inlineStr"/>
+      <c r="BI310" t="inlineStr"/>
+      <c r="BJ310" t="inlineStr"/>
+      <c r="BK310" t="inlineStr"/>
+      <c r="BL310" t="inlineStr"/>
+      <c r="BM310" t="inlineStr"/>
+      <c r="BN310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>Q14lVXc5</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="n">
+        <v>45549.46875</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">palencia caballero d 
+  esp </t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi ciutat de valencia
+  valencia </t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>26354</v>
+      </c>
+      <c r="F311" t="n">
+        <v>14904</v>
+      </c>
+      <c r="G311" t="n">
+        <v>3</v>
+      </c>
+      <c r="H311" t="n">
+        <v>1</v>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr"/>
+      <c r="M311" t="n">
+        <v>68</v>
+      </c>
+      <c r="N311" t="n">
+        <v>32</v>
+      </c>
+      <c r="O311" t="n">
+        <v>26</v>
+      </c>
+      <c r="P311" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q311" t="n">
+        <v>6</v>
+      </c>
+      <c r="R311" t="n">
+        <v>3</v>
+      </c>
+      <c r="S311" t="n">
+        <v>13</v>
+      </c>
+      <c r="T311" t="n">
+        <v>8</v>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>fiZxGYJ3</t>
+        </is>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>hh4xt2Df</t>
+        </is>
+      </c>
+      <c r="W311" t="n">
+        <v>148</v>
+      </c>
+      <c r="X311" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y311" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z311" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="AB311" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="AC311" t="inlineStr"/>
+      <c r="AD311" t="inlineStr"/>
+      <c r="AE311" t="inlineStr"/>
+      <c r="AF311" t="inlineStr"/>
+      <c r="AG311" t="inlineStr"/>
+      <c r="AH311" t="inlineStr"/>
+      <c r="AI311" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="AJ311" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="AK311" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL311" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AM311" t="n">
+        <v>919375</v>
+      </c>
+      <c r="AN311" t="n">
+        <v>70.375</v>
+      </c>
+      <c r="AO311" t="n">
+        <v>22.58333333333333</v>
+      </c>
+      <c r="AP311" t="n">
+        <v>177.75</v>
+      </c>
+      <c r="AQ311" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR311" t="n">
+        <v>66.16666666666667</v>
+      </c>
+      <c r="AS311" t="n">
+        <v>1704166.666666667</v>
+      </c>
+      <c r="AT311" t="n">
+        <v>73.66666666666667</v>
+      </c>
+      <c r="AU311" t="n">
+        <v>27.05882352941176</v>
+      </c>
+      <c r="AV311" t="n">
+        <v>181.2352941176471</v>
+      </c>
+      <c r="AW311" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX311" t="n">
+        <v>68.17647058823529</v>
+      </c>
+      <c r="AY311" t="n">
+        <v>2327941.176470588</v>
+      </c>
+      <c r="AZ311" t="n">
+        <v>71.35294117647059</v>
+      </c>
+      <c r="BA311" t="inlineStr"/>
+      <c r="BB311" t="inlineStr"/>
+      <c r="BC311" t="inlineStr"/>
+      <c r="BD311" t="inlineStr"/>
+      <c r="BE311" t="inlineStr"/>
+      <c r="BF311" t="inlineStr"/>
+      <c r="BG311" t="inlineStr"/>
+      <c r="BH311" t="inlineStr"/>
+      <c r="BI311" t="inlineStr"/>
+      <c r="BJ311" t="inlineStr"/>
+      <c r="BK311" t="inlineStr"/>
+      <c r="BL311" t="inlineStr"/>
+      <c r="BM311" t="inlineStr"/>
+      <c r="BN311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>4SibKGqm</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="n">
+        <v>45548.64583333334</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mallo e 
+  esp </t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo arcangel
+  cordoba </t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>21822</v>
+      </c>
+      <c r="F312" t="n">
+        <v>16435</v>
+      </c>
+      <c r="G312" t="n">
+        <v>2</v>
+      </c>
+      <c r="H312" t="n">
+        <v>0</v>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr"/>
+      <c r="M312" t="n">
+        <v>44</v>
+      </c>
+      <c r="N312" t="n">
+        <v>56</v>
+      </c>
+      <c r="O312" t="n">
+        <v>16</v>
+      </c>
+      <c r="P312" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q312" t="n">
+        <v>6</v>
+      </c>
+      <c r="R312" t="n">
+        <v>5</v>
+      </c>
+      <c r="S312" t="n">
+        <v>18</v>
+      </c>
+      <c r="T312" t="n">
+        <v>5</v>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="W312" t="n">
+        <v>148</v>
+      </c>
+      <c r="X312" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y312" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z312" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA312" t="inlineStr"/>
+      <c r="AB312" t="inlineStr"/>
+      <c r="AC312" t="inlineStr"/>
+      <c r="AD312" t="inlineStr"/>
+      <c r="AE312" t="inlineStr"/>
+      <c r="AF312" t="inlineStr"/>
+      <c r="AG312" t="inlineStr"/>
+      <c r="AH312" t="inlineStr"/>
+      <c r="AI312" t="inlineStr"/>
+      <c r="AJ312" t="inlineStr"/>
+      <c r="AK312" t="inlineStr"/>
+      <c r="AL312" t="inlineStr"/>
+      <c r="AM312" t="inlineStr"/>
+      <c r="AN312" t="inlineStr"/>
+      <c r="AO312" t="inlineStr"/>
+      <c r="AP312" t="inlineStr"/>
+      <c r="AQ312" t="inlineStr"/>
+      <c r="AR312" t="inlineStr"/>
+      <c r="AS312" t="inlineStr"/>
+      <c r="AT312" t="inlineStr"/>
+      <c r="AU312" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="AV312" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="AW312" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX312" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="AY312" t="n">
+        <v>1687500</v>
+      </c>
+      <c r="AZ312" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="BA312" t="inlineStr"/>
+      <c r="BB312" t="inlineStr"/>
+      <c r="BC312" t="inlineStr"/>
+      <c r="BD312" t="inlineStr"/>
+      <c r="BE312" t="inlineStr"/>
+      <c r="BF312" t="inlineStr"/>
+      <c r="BG312" t="inlineStr"/>
+      <c r="BH312" t="inlineStr"/>
+      <c r="BI312" t="inlineStr"/>
+      <c r="BJ312" t="inlineStr"/>
+      <c r="BK312" t="inlineStr"/>
+      <c r="BL312" t="inlineStr"/>
+      <c r="BM312" t="inlineStr"/>
+      <c r="BN312" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN312"/>
+  <dimension ref="A1:BN324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60427,6 +60427,2282 @@
       <c r="BM312" t="inlineStr"/>
       <c r="BN312" t="inlineStr"/>
     </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>fVeJ32M5</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="n">
+        <v>45551.66666666666</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>14505</v>
+      </c>
+      <c r="F313" t="n">
+        <v>13073</v>
+      </c>
+      <c r="G313" t="n">
+        <v>3</v>
+      </c>
+      <c r="H313" t="n">
+        <v>1</v>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="K313" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="L313" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M313" t="n">
+        <v>66</v>
+      </c>
+      <c r="N313" t="n">
+        <v>34</v>
+      </c>
+      <c r="O313" t="n">
+        <v>17</v>
+      </c>
+      <c r="P313" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q313" t="n">
+        <v>6</v>
+      </c>
+      <c r="R313" t="n">
+        <v>2</v>
+      </c>
+      <c r="S313" t="n">
+        <v>12</v>
+      </c>
+      <c r="T313" t="n">
+        <v>15</v>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="W313" t="n">
+        <v>148</v>
+      </c>
+      <c r="X313" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y313" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z313" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="AB313" t="inlineStr"/>
+      <c r="AC313" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AD313" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="AE313" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AF313" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AG313" t="n">
+        <v>4925000</v>
+      </c>
+      <c r="AH313" t="n">
+        <v>76.625</v>
+      </c>
+      <c r="AI313" t="inlineStr"/>
+      <c r="AJ313" t="inlineStr"/>
+      <c r="AK313" t="inlineStr"/>
+      <c r="AL313" t="inlineStr"/>
+      <c r="AM313" t="inlineStr"/>
+      <c r="AN313" t="inlineStr"/>
+      <c r="AO313" t="n">
+        <v>28.93333333333333</v>
+      </c>
+      <c r="AP313" t="n">
+        <v>176.1333333333333</v>
+      </c>
+      <c r="AQ313" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR313" t="n">
+        <v>74.86666666666666</v>
+      </c>
+      <c r="AS313" t="n">
+        <v>6593333.333333333</v>
+      </c>
+      <c r="AT313" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AU313" t="n">
+        <v>27.26315789473684</v>
+      </c>
+      <c r="AV313" t="n">
+        <v>177.1578947368421</v>
+      </c>
+      <c r="AW313" t="n">
+        <v>1.157894736842105</v>
+      </c>
+      <c r="AX313" t="n">
+        <v>74.26315789473684</v>
+      </c>
+      <c r="AY313" t="n">
+        <v>7973684.210526315</v>
+      </c>
+      <c r="AZ313" t="n">
+        <v>77</v>
+      </c>
+      <c r="BA313" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB313" t="n">
+        <v>177</v>
+      </c>
+      <c r="BC313" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD313" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE313" t="n">
+        <v>138</v>
+      </c>
+      <c r="BF313" t="n">
+        <v>10550000</v>
+      </c>
+      <c r="BG313" t="n">
+        <v>152</v>
+      </c>
+      <c r="BH313" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI313" t="n">
+        <v>179</v>
+      </c>
+      <c r="BJ313" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK313" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL313" t="n">
+        <v>138</v>
+      </c>
+      <c r="BM313" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="BN313" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>SdHeBgOE</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="n">
+        <v>45550.66666666666</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>70460</v>
+      </c>
+      <c r="F314" t="n">
+        <v>61752</v>
+      </c>
+      <c r="G314" t="n">
+        <v>3</v>
+      </c>
+      <c r="H314" t="n">
+        <v>0</v>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="K314" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L314" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M314" t="n">
+        <v>53</v>
+      </c>
+      <c r="N314" t="n">
+        <v>47</v>
+      </c>
+      <c r="O314" t="n">
+        <v>14</v>
+      </c>
+      <c r="P314" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q314" t="n">
+        <v>5</v>
+      </c>
+      <c r="R314" t="n">
+        <v>1</v>
+      </c>
+      <c r="S314" t="n">
+        <v>10</v>
+      </c>
+      <c r="T314" t="n">
+        <v>8</v>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="V314" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="W314" t="n">
+        <v>148</v>
+      </c>
+      <c r="X314" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y314" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z314" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA314" t="inlineStr"/>
+      <c r="AB314" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC314" t="n">
+        <v>27.88888888888889</v>
+      </c>
+      <c r="AD314" t="n">
+        <v>182</v>
+      </c>
+      <c r="AE314" t="n">
+        <v>2.555555555555555</v>
+      </c>
+      <c r="AF314" t="n">
+        <v>82.33333333333333</v>
+      </c>
+      <c r="AG314" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="AH314" t="n">
+        <v>83.66666666666667</v>
+      </c>
+      <c r="AI314" t="inlineStr"/>
+      <c r="AJ314" t="inlineStr"/>
+      <c r="AK314" t="inlineStr"/>
+      <c r="AL314" t="inlineStr"/>
+      <c r="AM314" t="inlineStr"/>
+      <c r="AN314" t="inlineStr"/>
+      <c r="AO314" t="n">
+        <v>26.03846153846154</v>
+      </c>
+      <c r="AP314" t="n">
+        <v>177.6923076923077</v>
+      </c>
+      <c r="AQ314" t="n">
+        <v>1.692307692307692</v>
+      </c>
+      <c r="AR314" t="n">
+        <v>79.30769230769231</v>
+      </c>
+      <c r="AS314" t="n">
+        <v>25134615.38461538</v>
+      </c>
+      <c r="AT314" t="n">
+        <v>82.42307692307692</v>
+      </c>
+      <c r="AU314" t="n">
+        <v>23.11111111111111</v>
+      </c>
+      <c r="AV314" t="n">
+        <v>177.6666666666667</v>
+      </c>
+      <c r="AW314" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX314" t="n">
+        <v>70</v>
+      </c>
+      <c r="AY314" t="n">
+        <v>3534722.222222222</v>
+      </c>
+      <c r="AZ314" t="n">
+        <v>76.66666666666667</v>
+      </c>
+      <c r="BA314" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BB314" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="BC314" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD314" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE314" t="n">
+        <v>157</v>
+      </c>
+      <c r="BF314" t="n">
+        <v>44000000</v>
+      </c>
+      <c r="BG314" t="n">
+        <v>167</v>
+      </c>
+      <c r="BH314" t="n">
+        <v>25.42857142857143</v>
+      </c>
+      <c r="BI314" t="n">
+        <v>181.2857142857143</v>
+      </c>
+      <c r="BJ314" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="BK314" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL314" t="n">
+        <v>532</v>
+      </c>
+      <c r="BM314" t="n">
+        <v>82200000</v>
+      </c>
+      <c r="BN314" t="n">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>dzUhmsxP</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="n">
+        <v>45550.5625</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F315" t="n">
+        <v>25908</v>
+      </c>
+      <c r="G315" t="n">
+        <v>2</v>
+      </c>
+      <c r="H315" t="n">
+        <v>3</v>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="K315" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L315" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M315" t="n">
+        <v>64</v>
+      </c>
+      <c r="N315" t="n">
+        <v>36</v>
+      </c>
+      <c r="O315" t="n">
+        <v>15</v>
+      </c>
+      <c r="P315" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q315" t="n">
+        <v>6</v>
+      </c>
+      <c r="R315" t="n">
+        <v>4</v>
+      </c>
+      <c r="S315" t="n">
+        <v>8</v>
+      </c>
+      <c r="T315" t="n">
+        <v>12</v>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="W315" t="n">
+        <v>148</v>
+      </c>
+      <c r="X315" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y315" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z315" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="AB315" t="inlineStr"/>
+      <c r="AC315" t="inlineStr"/>
+      <c r="AD315" t="inlineStr"/>
+      <c r="AE315" t="inlineStr"/>
+      <c r="AF315" t="inlineStr"/>
+      <c r="AG315" t="inlineStr"/>
+      <c r="AH315" t="inlineStr"/>
+      <c r="AI315" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AJ315" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="AK315" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL315" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="AM315" t="n">
+        <v>22890000</v>
+      </c>
+      <c r="AN315" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="AO315" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="AP315" t="n">
+        <v>180.9375</v>
+      </c>
+      <c r="AQ315" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AR315" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="AS315" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="AT315" t="n">
+        <v>75.8125</v>
+      </c>
+      <c r="AU315" t="n">
+        <v>24.65</v>
+      </c>
+      <c r="AV315" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="AW315" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AX315" t="n">
+        <v>76.05</v>
+      </c>
+      <c r="AY315" t="n">
+        <v>15175000</v>
+      </c>
+      <c r="AZ315" t="n">
+        <v>80.65000000000001</v>
+      </c>
+      <c r="BA315" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB315" t="n">
+        <v>182</v>
+      </c>
+      <c r="BC315" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD315" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE315" t="n">
+        <v>77</v>
+      </c>
+      <c r="BF315" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="BG315" t="n">
+        <v>77</v>
+      </c>
+      <c r="BH315" t="n">
+        <v>26</v>
+      </c>
+      <c r="BI315" t="n">
+        <v>190</v>
+      </c>
+      <c r="BJ315" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK315" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL315" t="n">
+        <v>85</v>
+      </c>
+      <c r="BM315" t="n">
+        <v>47500000</v>
+      </c>
+      <c r="BN315" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>na927pNt</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="n">
+        <v>45550.46875</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F316" t="n">
+        <v>13891</v>
+      </c>
+      <c r="G316" t="n">
+        <v>1</v>
+      </c>
+      <c r="H316" t="n">
+        <v>4</v>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="K316" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L316" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M316" t="n">
+        <v>45</v>
+      </c>
+      <c r="N316" t="n">
+        <v>55</v>
+      </c>
+      <c r="O316" t="n">
+        <v>9</v>
+      </c>
+      <c r="P316" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q316" t="n">
+        <v>4</v>
+      </c>
+      <c r="R316" t="n">
+        <v>9</v>
+      </c>
+      <c r="S316" t="n">
+        <v>13</v>
+      </c>
+      <c r="T316" t="n">
+        <v>4</v>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="W316" t="n">
+        <v>148</v>
+      </c>
+      <c r="X316" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y316" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z316" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="AB316" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="AC316" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="AD316" t="n">
+        <v>183.4444444444445</v>
+      </c>
+      <c r="AE316" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AF316" t="n">
+        <v>75.77777777777777</v>
+      </c>
+      <c r="AG316" t="n">
+        <v>16033333.33333333</v>
+      </c>
+      <c r="AH316" t="n">
+        <v>81.55555555555556</v>
+      </c>
+      <c r="AI316" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="AJ316" t="n">
+        <v>179</v>
+      </c>
+      <c r="AK316" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL316" t="n">
+        <v>79.125</v>
+      </c>
+      <c r="AM316" t="n">
+        <v>42187500</v>
+      </c>
+      <c r="AN316" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO316" t="n">
+        <v>25.84210526315789</v>
+      </c>
+      <c r="AP316" t="n">
+        <v>178.8421052631579</v>
+      </c>
+      <c r="AQ316" t="n">
+        <v>1.578947368421053</v>
+      </c>
+      <c r="AR316" t="n">
+        <v>76.52631578947368</v>
+      </c>
+      <c r="AS316" t="n">
+        <v>13442105.26315789</v>
+      </c>
+      <c r="AT316" t="n">
+        <v>80.57894736842105</v>
+      </c>
+      <c r="AU316" t="n">
+        <v>20.35714285714286</v>
+      </c>
+      <c r="AV316" t="n">
+        <v>182.2142857142857</v>
+      </c>
+      <c r="AW316" t="n">
+        <v>1.714285714285714</v>
+      </c>
+      <c r="AX316" t="n">
+        <v>71.92857142857143</v>
+      </c>
+      <c r="AY316" t="n">
+        <v>24478571.42857143</v>
+      </c>
+      <c r="AZ316" t="n">
+        <v>81.92857142857143</v>
+      </c>
+      <c r="BA316" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BB316" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="BC316" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD316" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE316" t="n">
+        <v>126</v>
+      </c>
+      <c r="BF316" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="BG316" t="n">
+        <v>156</v>
+      </c>
+      <c r="BH316" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI316" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="BJ316" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK316" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL316" t="n">
+        <v>417</v>
+      </c>
+      <c r="BM316" t="n">
+        <v>334500000</v>
+      </c>
+      <c r="BN316" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>SfxxiPx0</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="n">
+        <v>45550.375</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F317" t="n">
+        <v>21670</v>
+      </c>
+      <c r="G317" t="n">
+        <v>3</v>
+      </c>
+      <c r="H317" t="n">
+        <v>1</v>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="K317" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L317" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M317" t="n">
+        <v>54</v>
+      </c>
+      <c r="N317" t="n">
+        <v>46</v>
+      </c>
+      <c r="O317" t="n">
+        <v>14</v>
+      </c>
+      <c r="P317" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>7</v>
+      </c>
+      <c r="R317" t="n">
+        <v>1</v>
+      </c>
+      <c r="S317" t="n">
+        <v>14</v>
+      </c>
+      <c r="T317" t="n">
+        <v>15</v>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="W317" t="n">
+        <v>148</v>
+      </c>
+      <c r="X317" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y317" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z317" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="AB317" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="AC317" t="inlineStr"/>
+      <c r="AD317" t="inlineStr"/>
+      <c r="AE317" t="inlineStr"/>
+      <c r="AF317" t="inlineStr"/>
+      <c r="AG317" t="inlineStr"/>
+      <c r="AH317" t="inlineStr"/>
+      <c r="AI317" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AJ317" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="AK317" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL317" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AM317" t="n">
+        <v>3110000</v>
+      </c>
+      <c r="AN317" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AO317" t="n">
+        <v>26.125</v>
+      </c>
+      <c r="AP317" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="AQ317" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AR317" t="n">
+        <v>74.6875</v>
+      </c>
+      <c r="AS317" t="n">
+        <v>9043750</v>
+      </c>
+      <c r="AT317" t="n">
+        <v>78.4375</v>
+      </c>
+      <c r="AU317" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="AV317" t="n">
+        <v>179.95</v>
+      </c>
+      <c r="AW317" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AX317" t="n">
+        <v>70.55</v>
+      </c>
+      <c r="AY317" t="n">
+        <v>3063750</v>
+      </c>
+      <c r="AZ317" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="BA317" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="BB317" t="n">
+        <v>179</v>
+      </c>
+      <c r="BC317" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BD317" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE317" t="n">
+        <v>353</v>
+      </c>
+      <c r="BF317" t="n">
+        <v>13400000</v>
+      </c>
+      <c r="BG317" t="n">
+        <v>369</v>
+      </c>
+      <c r="BH317" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI317" t="n">
+        <v>174</v>
+      </c>
+      <c r="BJ317" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK317" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL317" t="n">
+        <v>69</v>
+      </c>
+      <c r="BM317" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="BN317" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>jckS1tiI</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="n">
+        <v>45549.66666666666</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F318" t="n">
+        <v>37370</v>
+      </c>
+      <c r="G318" t="n">
+        <v>0</v>
+      </c>
+      <c r="H318" t="n">
+        <v>2</v>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="K318" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L318" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M318" t="n">
+        <v>48</v>
+      </c>
+      <c r="N318" t="n">
+        <v>52</v>
+      </c>
+      <c r="O318" t="n">
+        <v>11</v>
+      </c>
+      <c r="P318" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q318" t="n">
+        <v>2</v>
+      </c>
+      <c r="R318" t="n">
+        <v>7</v>
+      </c>
+      <c r="S318" t="n">
+        <v>12</v>
+      </c>
+      <c r="T318" t="n">
+        <v>9</v>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="W318" t="n">
+        <v>148</v>
+      </c>
+      <c r="X318" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y318" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z318" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA318" t="inlineStr"/>
+      <c r="AB318" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AC318" t="inlineStr"/>
+      <c r="AD318" t="inlineStr"/>
+      <c r="AE318" t="inlineStr"/>
+      <c r="AF318" t="inlineStr"/>
+      <c r="AG318" t="inlineStr"/>
+      <c r="AH318" t="inlineStr"/>
+      <c r="AI318" t="n">
+        <v>26.63636363636364</v>
+      </c>
+      <c r="AJ318" t="n">
+        <v>180.5454545454545</v>
+      </c>
+      <c r="AK318" t="n">
+        <v>3.090909090909091</v>
+      </c>
+      <c r="AL318" t="n">
+        <v>85.45454545454545</v>
+      </c>
+      <c r="AM318" t="n">
+        <v>73045454.54545455</v>
+      </c>
+      <c r="AN318" t="n">
+        <v>88.09090909090909</v>
+      </c>
+      <c r="AO318" t="n">
+        <v>23.625</v>
+      </c>
+      <c r="AP318" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="AQ318" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR318" t="n">
+        <v>73.5625</v>
+      </c>
+      <c r="AS318" t="n">
+        <v>9725000</v>
+      </c>
+      <c r="AT318" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="AU318" t="n">
+        <v>21.90909090909091</v>
+      </c>
+      <c r="AV318" t="n">
+        <v>178.2727272727273</v>
+      </c>
+      <c r="AW318" t="n">
+        <v>1.909090909090909</v>
+      </c>
+      <c r="AX318" t="n">
+        <v>76.45454545454545</v>
+      </c>
+      <c r="AY318" t="n">
+        <v>48863636.36363637</v>
+      </c>
+      <c r="AZ318" t="n">
+        <v>83.81818181818181</v>
+      </c>
+      <c r="BA318" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="BB318" t="n">
+        <v>181.3333333333333</v>
+      </c>
+      <c r="BC318" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="BD318" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE318" t="n">
+        <v>235</v>
+      </c>
+      <c r="BF318" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="BG318" t="n">
+        <v>247</v>
+      </c>
+      <c r="BH318" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="BI318" t="n">
+        <v>182.1666666666667</v>
+      </c>
+      <c r="BJ318" t="n">
+        <v>2.833333333333333</v>
+      </c>
+      <c r="BK318" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL318" t="n">
+        <v>484</v>
+      </c>
+      <c r="BM318" t="n">
+        <v>316775000</v>
+      </c>
+      <c r="BN318" t="n">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>dMUW3ea6</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="n">
+        <v>45551.64583333334</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzalez diaz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">power horse stadium
+  almeria </t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>17400</v>
+      </c>
+      <c r="F319" t="n">
+        <v>11952</v>
+      </c>
+      <c r="G319" t="n">
+        <v>2</v>
+      </c>
+      <c r="H319" t="n">
+        <v>5</v>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr"/>
+      <c r="M319" t="n">
+        <v>44</v>
+      </c>
+      <c r="N319" t="n">
+        <v>56</v>
+      </c>
+      <c r="O319" t="n">
+        <v>17</v>
+      </c>
+      <c r="P319" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q319" t="n">
+        <v>5</v>
+      </c>
+      <c r="R319" t="n">
+        <v>7</v>
+      </c>
+      <c r="S319" t="n">
+        <v>7</v>
+      </c>
+      <c r="T319" t="n">
+        <v>11</v>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="W319" t="n">
+        <v>148</v>
+      </c>
+      <c r="X319" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y319" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z319" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="AB319" t="inlineStr"/>
+      <c r="AC319" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AD319" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="AE319" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF319" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="AG319" t="n">
+        <v>7296875</v>
+      </c>
+      <c r="AH319" t="n">
+        <v>79</v>
+      </c>
+      <c r="AI319" t="inlineStr"/>
+      <c r="AJ319" t="inlineStr"/>
+      <c r="AK319" t="inlineStr"/>
+      <c r="AL319" t="inlineStr"/>
+      <c r="AM319" t="inlineStr"/>
+      <c r="AN319" t="inlineStr"/>
+      <c r="AO319" t="n">
+        <v>21.9375</v>
+      </c>
+      <c r="AP319" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="AQ319" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AR319" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AS319" t="n">
+        <v>4060937.5</v>
+      </c>
+      <c r="AT319" t="n">
+        <v>77.4375</v>
+      </c>
+      <c r="AU319" t="inlineStr"/>
+      <c r="AV319" t="inlineStr"/>
+      <c r="AW319" t="inlineStr"/>
+      <c r="AX319" t="inlineStr"/>
+      <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr"/>
+      <c r="BA319" t="inlineStr"/>
+      <c r="BB319" t="inlineStr"/>
+      <c r="BC319" t="inlineStr"/>
+      <c r="BD319" t="inlineStr"/>
+      <c r="BE319" t="inlineStr"/>
+      <c r="BF319" t="inlineStr"/>
+      <c r="BG319" t="inlineStr"/>
+      <c r="BH319" t="inlineStr"/>
+      <c r="BI319" t="inlineStr"/>
+      <c r="BJ319" t="inlineStr"/>
+      <c r="BK319" t="inlineStr"/>
+      <c r="BL319" t="inlineStr"/>
+      <c r="BM319" t="inlineStr"/>
+      <c r="BN319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>nBqFGYrC</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="n">
+        <v>45550.66666666666</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de la fuente ramos o 
+  esp </t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio manuel martinez valero
+  elche </t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>31388</v>
+      </c>
+      <c r="F320" t="n">
+        <v>15455</v>
+      </c>
+      <c r="G320" t="n">
+        <v>2</v>
+      </c>
+      <c r="H320" t="n">
+        <v>2</v>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr"/>
+      <c r="M320" t="n">
+        <v>61</v>
+      </c>
+      <c r="N320" t="n">
+        <v>39</v>
+      </c>
+      <c r="O320" t="n">
+        <v>13</v>
+      </c>
+      <c r="P320" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q320" t="n">
+        <v>3</v>
+      </c>
+      <c r="R320" t="n">
+        <v>3</v>
+      </c>
+      <c r="S320" t="n">
+        <v>22</v>
+      </c>
+      <c r="T320" t="n">
+        <v>13</v>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>zT9gi7i9</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>K4dMCgFa</t>
+        </is>
+      </c>
+      <c r="W320" t="n">
+        <v>148</v>
+      </c>
+      <c r="X320" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y320" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z320" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB320" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AC320" t="n">
+        <v>27.625</v>
+      </c>
+      <c r="AD320" t="n">
+        <v>182.375</v>
+      </c>
+      <c r="AE320" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF320" t="n">
+        <v>70.875</v>
+      </c>
+      <c r="AG320" t="n">
+        <v>2190625</v>
+      </c>
+      <c r="AH320" t="n">
+        <v>73.875</v>
+      </c>
+      <c r="AI320" t="n">
+        <v>25.88888888888889</v>
+      </c>
+      <c r="AJ320" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AK320" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL320" t="n">
+        <v>71.77777777777777</v>
+      </c>
+      <c r="AM320" t="n">
+        <v>3455555.555555556</v>
+      </c>
+      <c r="AN320" t="n">
+        <v>75.33333333333333</v>
+      </c>
+      <c r="AO320" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="AP320" t="n">
+        <v>182.1111111111111</v>
+      </c>
+      <c r="AQ320" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AR320" t="n">
+        <v>67.22222222222223</v>
+      </c>
+      <c r="AS320" t="n">
+        <v>1368055.555555556</v>
+      </c>
+      <c r="AT320" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="AU320" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="AV320" t="n">
+        <v>180.45</v>
+      </c>
+      <c r="AW320" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AX320" t="n">
+        <v>71.45</v>
+      </c>
+      <c r="AY320" t="n">
+        <v>4190000</v>
+      </c>
+      <c r="AZ320" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="BA320" t="inlineStr"/>
+      <c r="BB320" t="inlineStr"/>
+      <c r="BC320" t="inlineStr"/>
+      <c r="BD320" t="inlineStr"/>
+      <c r="BE320" t="inlineStr"/>
+      <c r="BF320" t="inlineStr"/>
+      <c r="BG320" t="inlineStr"/>
+      <c r="BH320" t="inlineStr"/>
+      <c r="BI320" t="inlineStr"/>
+      <c r="BJ320" t="inlineStr"/>
+      <c r="BK320" t="inlineStr"/>
+      <c r="BL320" t="inlineStr"/>
+      <c r="BM320" t="inlineStr"/>
+      <c r="BN320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>hlOu2ZTI</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="n">
+        <v>45550.5625</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guzman mansilla j  l 
+  esp </t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el plantio
+  burgos </t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>12194</v>
+      </c>
+      <c r="F321" t="n">
+        <v>10150</v>
+      </c>
+      <c r="G321" t="n">
+        <v>1</v>
+      </c>
+      <c r="H321" t="n">
+        <v>0</v>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr"/>
+      <c r="M321" t="n">
+        <v>48</v>
+      </c>
+      <c r="N321" t="n">
+        <v>52</v>
+      </c>
+      <c r="O321" t="n">
+        <v>16</v>
+      </c>
+      <c r="P321" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>7</v>
+      </c>
+      <c r="R321" t="n">
+        <v>4</v>
+      </c>
+      <c r="S321" t="n">
+        <v>10</v>
+      </c>
+      <c r="T321" t="n">
+        <v>13</v>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>l6JQtDqc</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="W321" t="n">
+        <v>148</v>
+      </c>
+      <c r="X321" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y321" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z321" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA321" t="inlineStr"/>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="AC321" t="inlineStr"/>
+      <c r="AD321" t="inlineStr"/>
+      <c r="AE321" t="inlineStr"/>
+      <c r="AF321" t="inlineStr"/>
+      <c r="AG321" t="inlineStr"/>
+      <c r="AH321" t="inlineStr"/>
+      <c r="AI321" t="n">
+        <v>23.11111111111111</v>
+      </c>
+      <c r="AJ321" t="n">
+        <v>178.1111111111111</v>
+      </c>
+      <c r="AK321" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL321" t="n">
+        <v>67.55555555555556</v>
+      </c>
+      <c r="AM321" t="n">
+        <v>1977777.777777778</v>
+      </c>
+      <c r="AN321" t="n">
+        <v>74.88888888888889</v>
+      </c>
+      <c r="AO321" t="n">
+        <v>25.36363636363636</v>
+      </c>
+      <c r="AP321" t="n">
+        <v>180.1818181818182</v>
+      </c>
+      <c r="AQ321" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR321" t="n">
+        <v>68.27272727272727</v>
+      </c>
+      <c r="AS321" t="n">
+        <v>1884090.909090909</v>
+      </c>
+      <c r="AT321" t="n">
+        <v>71.18181818181819</v>
+      </c>
+      <c r="AU321" t="n">
+        <v>23.36363636363636</v>
+      </c>
+      <c r="AV321" t="n">
+        <v>177.3636363636364</v>
+      </c>
+      <c r="AW321" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX321" t="n">
+        <v>68.81818181818181</v>
+      </c>
+      <c r="AY321" t="n">
+        <v>2309090.909090909</v>
+      </c>
+      <c r="AZ321" t="n">
+        <v>74.54545454545455</v>
+      </c>
+      <c r="BA321" t="inlineStr"/>
+      <c r="BB321" t="inlineStr"/>
+      <c r="BC321" t="inlineStr"/>
+      <c r="BD321" t="inlineStr"/>
+      <c r="BE321" t="inlineStr"/>
+      <c r="BF321" t="inlineStr"/>
+      <c r="BG321" t="inlineStr"/>
+      <c r="BH321" t="inlineStr"/>
+      <c r="BI321" t="inlineStr"/>
+      <c r="BJ321" t="inlineStr"/>
+      <c r="BK321" t="inlineStr"/>
+      <c r="BL321" t="inlineStr"/>
+      <c r="BM321" t="inlineStr"/>
+      <c r="BN321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>KfGRPxMP</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="n">
+        <v>45550.5625</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzalez esteban j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo mirandilla
+  cadiz </t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>20776</v>
+      </c>
+      <c r="F322" t="n">
+        <v>16868</v>
+      </c>
+      <c r="G322" t="n">
+        <v>0</v>
+      </c>
+      <c r="H322" t="n">
+        <v>0</v>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="M322" t="n">
+        <v>50</v>
+      </c>
+      <c r="N322" t="n">
+        <v>50</v>
+      </c>
+      <c r="O322" t="n">
+        <v>13</v>
+      </c>
+      <c r="P322" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>3</v>
+      </c>
+      <c r="R322" t="n">
+        <v>1</v>
+      </c>
+      <c r="S322" t="n">
+        <v>24</v>
+      </c>
+      <c r="T322" t="n">
+        <v>13</v>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="W322" t="n">
+        <v>148</v>
+      </c>
+      <c r="X322" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y322" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z322" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AB322" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="AC322" t="n">
+        <v>28.77777777777778</v>
+      </c>
+      <c r="AD322" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="AE322" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF322" t="n">
+        <v>73.66666666666667</v>
+      </c>
+      <c r="AG322" t="n">
+        <v>4688888.888888889</v>
+      </c>
+      <c r="AH322" t="n">
+        <v>74.55555555555556</v>
+      </c>
+      <c r="AI322" t="inlineStr"/>
+      <c r="AJ322" t="inlineStr"/>
+      <c r="AK322" t="inlineStr"/>
+      <c r="AL322" t="inlineStr"/>
+      <c r="AM322" t="inlineStr"/>
+      <c r="AN322" t="inlineStr"/>
+      <c r="AO322" t="n">
+        <v>25.13333333333333</v>
+      </c>
+      <c r="AP322" t="n">
+        <v>177.2</v>
+      </c>
+      <c r="AQ322" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="AR322" t="n">
+        <v>68.13333333333334</v>
+      </c>
+      <c r="AS322" t="n">
+        <v>2471666.666666667</v>
+      </c>
+      <c r="AT322" t="n">
+        <v>72.93333333333334</v>
+      </c>
+      <c r="AU322" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="AV322" t="n">
+        <v>178.3333333333333</v>
+      </c>
+      <c r="AW322" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX322" t="n">
+        <v>67.06666666666666</v>
+      </c>
+      <c r="AY322" t="n">
+        <v>1395000</v>
+      </c>
+      <c r="AZ322" t="n">
+        <v>70.46666666666667</v>
+      </c>
+      <c r="BA322" t="inlineStr"/>
+      <c r="BB322" t="inlineStr"/>
+      <c r="BC322" t="inlineStr"/>
+      <c r="BD322" t="inlineStr"/>
+      <c r="BE322" t="inlineStr"/>
+      <c r="BF322" t="inlineStr"/>
+      <c r="BG322" t="inlineStr"/>
+      <c r="BH322" t="inlineStr"/>
+      <c r="BI322" t="inlineStr"/>
+      <c r="BJ322" t="inlineStr"/>
+      <c r="BK322" t="inlineStr"/>
+      <c r="BL322" t="inlineStr"/>
+      <c r="BM322" t="inlineStr"/>
+      <c r="BN322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>4nGuXgTh</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="n">
+        <v>45550.46875</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrera r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo carlos tartiere
+  oviedo </t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>30500</v>
+      </c>
+      <c r="F323" t="n">
+        <v>19492</v>
+      </c>
+      <c r="G323" t="n">
+        <v>1</v>
+      </c>
+      <c r="H323" t="n">
+        <v>0</v>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr"/>
+      <c r="M323" t="n">
+        <v>67</v>
+      </c>
+      <c r="N323" t="n">
+        <v>33</v>
+      </c>
+      <c r="O323" t="n">
+        <v>16</v>
+      </c>
+      <c r="P323" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q323" t="n">
+        <v>3</v>
+      </c>
+      <c r="R323" t="n">
+        <v>2</v>
+      </c>
+      <c r="S323" t="n">
+        <v>17</v>
+      </c>
+      <c r="T323" t="n">
+        <v>7</v>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>M1vEw5An</t>
+        </is>
+      </c>
+      <c r="W323" t="n">
+        <v>148</v>
+      </c>
+      <c r="X323" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y323" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z323" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA323" t="inlineStr"/>
+      <c r="AB323" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="AC323" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AD323" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="AE323" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF323" t="n">
+        <v>69.375</v>
+      </c>
+      <c r="AG323" t="n">
+        <v>2475000</v>
+      </c>
+      <c r="AH323" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="AI323" t="inlineStr"/>
+      <c r="AJ323" t="inlineStr"/>
+      <c r="AK323" t="inlineStr"/>
+      <c r="AL323" t="inlineStr"/>
+      <c r="AM323" t="inlineStr"/>
+      <c r="AN323" t="inlineStr"/>
+      <c r="AO323" t="n">
+        <v>24.35294117647059</v>
+      </c>
+      <c r="AP323" t="n">
+        <v>180.2941176470588</v>
+      </c>
+      <c r="AQ323" t="n">
+        <v>1.117647058823529</v>
+      </c>
+      <c r="AR323" t="n">
+        <v>69.23529411764706</v>
+      </c>
+      <c r="AS323" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="AT323" t="n">
+        <v>75.94117647058823</v>
+      </c>
+      <c r="AU323" t="n">
+        <v>22.11111111111111</v>
+      </c>
+      <c r="AV323" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="AW323" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX323" t="n">
+        <v>64.88888888888889</v>
+      </c>
+      <c r="AY323" t="n">
+        <v>1283333.333333333</v>
+      </c>
+      <c r="AZ323" t="n">
+        <v>72.77777777777777</v>
+      </c>
+      <c r="BA323" t="inlineStr"/>
+      <c r="BB323" t="inlineStr"/>
+      <c r="BC323" t="inlineStr"/>
+      <c r="BD323" t="inlineStr"/>
+      <c r="BE323" t="inlineStr"/>
+      <c r="BF323" t="inlineStr"/>
+      <c r="BG323" t="inlineStr"/>
+      <c r="BH323" t="inlineStr"/>
+      <c r="BI323" t="inlineStr"/>
+      <c r="BJ323" t="inlineStr"/>
+      <c r="BK323" t="inlineStr"/>
+      <c r="BL323" t="inlineStr"/>
+      <c r="BM323" t="inlineStr"/>
+      <c r="BN323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>bkDXYFbt</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="n">
+        <v>45550.375</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lax franco s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de anduva
+  miranda de ebro </t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>5759</v>
+      </c>
+      <c r="F324" t="n">
+        <v>2713</v>
+      </c>
+      <c r="G324" t="n">
+        <v>2</v>
+      </c>
+      <c r="H324" t="n">
+        <v>0</v>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr"/>
+      <c r="L324" t="inlineStr"/>
+      <c r="M324" t="n">
+        <v>48</v>
+      </c>
+      <c r="N324" t="n">
+        <v>52</v>
+      </c>
+      <c r="O324" t="n">
+        <v>18</v>
+      </c>
+      <c r="P324" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>5</v>
+      </c>
+      <c r="R324" t="n">
+        <v>2</v>
+      </c>
+      <c r="S324" t="n">
+        <v>11</v>
+      </c>
+      <c r="T324" t="n">
+        <v>11</v>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="W324" t="n">
+        <v>148</v>
+      </c>
+      <c r="X324" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y324" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z324" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="AB324" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC324" t="inlineStr"/>
+      <c r="AD324" t="inlineStr"/>
+      <c r="AE324" t="inlineStr"/>
+      <c r="AF324" t="inlineStr"/>
+      <c r="AG324" t="inlineStr"/>
+      <c r="AH324" t="inlineStr"/>
+      <c r="AI324" t="inlineStr"/>
+      <c r="AJ324" t="inlineStr"/>
+      <c r="AK324" t="inlineStr"/>
+      <c r="AL324" t="inlineStr"/>
+      <c r="AM324" t="inlineStr"/>
+      <c r="AN324" t="inlineStr"/>
+      <c r="AO324" t="n">
+        <v>21.38461538461538</v>
+      </c>
+      <c r="AP324" t="n">
+        <v>179</v>
+      </c>
+      <c r="AQ324" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR324" t="n">
+        <v>65.38461538461539</v>
+      </c>
+      <c r="AS324" t="n">
+        <v>1630769.230769231</v>
+      </c>
+      <c r="AT324" t="n">
+        <v>76.23076923076923</v>
+      </c>
+      <c r="AU324" t="n">
+        <v>25.58333333333333</v>
+      </c>
+      <c r="AV324" t="n">
+        <v>180.9166666666667</v>
+      </c>
+      <c r="AW324" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX324" t="n">
+        <v>66.58333333333333</v>
+      </c>
+      <c r="AY324" t="n">
+        <v>1331250</v>
+      </c>
+      <c r="AZ324" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="BA324" t="inlineStr"/>
+      <c r="BB324" t="inlineStr"/>
+      <c r="BC324" t="inlineStr"/>
+      <c r="BD324" t="inlineStr"/>
+      <c r="BE324" t="inlineStr"/>
+      <c r="BF324" t="inlineStr"/>
+      <c r="BG324" t="inlineStr"/>
+      <c r="BH324" t="inlineStr"/>
+      <c r="BI324" t="inlineStr"/>
+      <c r="BJ324" t="inlineStr"/>
+      <c r="BK324" t="inlineStr"/>
+      <c r="BL324" t="inlineStr"/>
+      <c r="BM324" t="inlineStr"/>
+      <c r="BN324" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD346"/>
+  <dimension ref="A1:CD348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80962,6 +80962,440 @@
       <c r="CC346" t="inlineStr"/>
       <c r="CD346" t="inlineStr"/>
     </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="n">
+        <v>45558.66666666666</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F347" t="n">
+        <v>47017</v>
+      </c>
+      <c r="G347" t="n">
+        <v>1</v>
+      </c>
+      <c r="H347" t="n">
+        <v>2</v>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="K347" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L347" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M347" t="n">
+        <v>61</v>
+      </c>
+      <c r="N347" t="n">
+        <v>39</v>
+      </c>
+      <c r="O347" t="n">
+        <v>16</v>
+      </c>
+      <c r="P347" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>6</v>
+      </c>
+      <c r="R347" t="n">
+        <v>6</v>
+      </c>
+      <c r="S347" t="n">
+        <v>5</v>
+      </c>
+      <c r="T347" t="n">
+        <v>1</v>
+      </c>
+      <c r="U347" t="n">
+        <v>5</v>
+      </c>
+      <c r="V347" t="n">
+        <v>0</v>
+      </c>
+      <c r="W347" t="n">
+        <v>19</v>
+      </c>
+      <c r="X347" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y347" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z347" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA347" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB347" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC347" t="n">
+        <v>33</v>
+      </c>
+      <c r="AD347" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE347" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF347" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG347" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH347" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI347" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ347" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK347" t="inlineStr"/>
+      <c r="AL347" t="inlineStr"/>
+      <c r="AM347" t="inlineStr"/>
+      <c r="AN347" t="inlineStr"/>
+      <c r="AO347" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="AP347" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="AQ347" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR347" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS347" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT347" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU347" t="inlineStr"/>
+      <c r="AV347" t="inlineStr"/>
+      <c r="AW347" t="inlineStr"/>
+      <c r="AX347" t="inlineStr"/>
+      <c r="AY347" t="inlineStr"/>
+      <c r="AZ347" t="inlineStr"/>
+      <c r="BA347" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="BB347" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="BC347" t="inlineStr"/>
+      <c r="BD347" t="inlineStr"/>
+      <c r="BE347" t="inlineStr"/>
+      <c r="BF347" t="inlineStr"/>
+      <c r="BG347" t="n">
+        <v>27</v>
+      </c>
+      <c r="BH347" t="n">
+        <v>184.4</v>
+      </c>
+      <c r="BI347" t="n">
+        <v>75</v>
+      </c>
+      <c r="BJ347" t="n">
+        <v>23000</v>
+      </c>
+      <c r="BK347" t="n">
+        <v>25.84210526315789</v>
+      </c>
+      <c r="BL347" t="n">
+        <v>178.5263157894737</v>
+      </c>
+      <c r="BM347" t="n">
+        <v>74.05263157894737</v>
+      </c>
+      <c r="BN347" t="inlineStr"/>
+      <c r="BO347" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="BP347" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="BQ347" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="BR347" t="n">
+        <v>20791.66666666667</v>
+      </c>
+      <c r="BS347" t="n">
+        <v>29</v>
+      </c>
+      <c r="BT347" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="BU347" t="n">
+        <v>78</v>
+      </c>
+      <c r="BV347" t="n">
+        <v>24000</v>
+      </c>
+      <c r="BW347" t="n">
+        <v>5</v>
+      </c>
+      <c r="BX347" t="n">
+        <v>390</v>
+      </c>
+      <c r="BY347" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="BZ347" t="n">
+        <v>181</v>
+      </c>
+      <c r="CA347" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="CB347" t="n">
+        <v>22750</v>
+      </c>
+      <c r="CC347" t="n">
+        <v>4</v>
+      </c>
+      <c r="CD347" t="n">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>8Ia7s2mS</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="n">
+        <v>45558.64583333334</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">muresan s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el alcoraz
+  huesca </t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F348" t="n">
+        <v>5899</v>
+      </c>
+      <c r="G348" t="n">
+        <v>4</v>
+      </c>
+      <c r="H348" t="n">
+        <v>1</v>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr"/>
+      <c r="L348" t="inlineStr"/>
+      <c r="M348" t="n">
+        <v>34</v>
+      </c>
+      <c r="N348" t="n">
+        <v>66</v>
+      </c>
+      <c r="O348" t="n">
+        <v>9</v>
+      </c>
+      <c r="P348" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>5</v>
+      </c>
+      <c r="R348" t="n">
+        <v>4</v>
+      </c>
+      <c r="S348" t="n">
+        <v>3</v>
+      </c>
+      <c r="T348" t="n">
+        <v>6</v>
+      </c>
+      <c r="U348" t="n">
+        <v>1</v>
+      </c>
+      <c r="V348" t="n">
+        <v>6</v>
+      </c>
+      <c r="W348" t="n">
+        <v>10</v>
+      </c>
+      <c r="X348" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y348" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z348" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA348" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB348" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC348" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD348" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE348" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF348" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG348" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH348" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI348" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ348" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK348" t="inlineStr"/>
+      <c r="AL348" t="inlineStr"/>
+      <c r="AM348" t="inlineStr"/>
+      <c r="AN348" t="inlineStr"/>
+      <c r="AO348" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="AP348" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="AQ348" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR348" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS348" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT348" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU348" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV348" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW348" t="inlineStr"/>
+      <c r="AX348" t="inlineStr"/>
+      <c r="AY348" t="inlineStr"/>
+      <c r="AZ348" t="inlineStr"/>
+      <c r="BA348" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="BB348" t="inlineStr"/>
+      <c r="BC348" t="inlineStr"/>
+      <c r="BD348" t="inlineStr"/>
+      <c r="BE348" t="inlineStr"/>
+      <c r="BF348" t="inlineStr"/>
+      <c r="BG348" t="inlineStr"/>
+      <c r="BH348" t="inlineStr"/>
+      <c r="BI348" t="inlineStr"/>
+      <c r="BJ348" t="inlineStr"/>
+      <c r="BK348" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="BL348" t="n">
+        <v>179.9333333333333</v>
+      </c>
+      <c r="BM348" t="n">
+        <v>65.66666666666667</v>
+      </c>
+      <c r="BN348" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BO348" t="inlineStr"/>
+      <c r="BP348" t="inlineStr"/>
+      <c r="BQ348" t="inlineStr"/>
+      <c r="BR348" t="inlineStr"/>
+      <c r="BS348" t="inlineStr"/>
+      <c r="BT348" t="inlineStr"/>
+      <c r="BU348" t="inlineStr"/>
+      <c r="BV348" t="inlineStr"/>
+      <c r="BW348" t="inlineStr"/>
+      <c r="BX348" t="inlineStr"/>
+      <c r="BY348" t="inlineStr"/>
+      <c r="BZ348" t="inlineStr"/>
+      <c r="CA348" t="inlineStr"/>
+      <c r="CB348" t="inlineStr"/>
+      <c r="CC348" t="inlineStr"/>
+      <c r="CD348" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD346"/>
+  <dimension ref="A1:CD356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80962,6 +80962,2162 @@
       <c r="CC346" t="inlineStr"/>
       <c r="CD346" t="inlineStr"/>
     </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="n">
+        <v>45561.66666666666</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F347" t="n">
+        <v>21533</v>
+      </c>
+      <c r="G347" t="n">
+        <v>0</v>
+      </c>
+      <c r="H347" t="n">
+        <v>1</v>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="K347" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L347" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M347" t="n">
+        <v>59</v>
+      </c>
+      <c r="N347" t="n">
+        <v>41</v>
+      </c>
+      <c r="O347" t="n">
+        <v>10</v>
+      </c>
+      <c r="P347" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>4</v>
+      </c>
+      <c r="R347" t="n">
+        <v>2</v>
+      </c>
+      <c r="S347" t="n">
+        <v>6</v>
+      </c>
+      <c r="T347" t="n">
+        <v>2</v>
+      </c>
+      <c r="U347" t="n">
+        <v>0</v>
+      </c>
+      <c r="V347" t="n">
+        <v>4</v>
+      </c>
+      <c r="W347" t="n">
+        <v>12</v>
+      </c>
+      <c r="X347" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y347" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z347" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA347" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB347" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC347" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD347" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE347" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF347" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG347" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH347" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI347" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ347" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK347" t="inlineStr"/>
+      <c r="AL347" t="inlineStr"/>
+      <c r="AM347" t="inlineStr"/>
+      <c r="AN347" t="inlineStr"/>
+      <c r="AO347" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="AP347" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="AQ347" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR347" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS347" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT347" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU347" t="inlineStr"/>
+      <c r="AV347" t="inlineStr"/>
+      <c r="AW347" t="inlineStr"/>
+      <c r="AX347" t="inlineStr"/>
+      <c r="AY347" t="inlineStr"/>
+      <c r="AZ347" t="inlineStr"/>
+      <c r="BA347" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="BB347" t="inlineStr"/>
+      <c r="BC347" t="n">
+        <v>28.33333333333333</v>
+      </c>
+      <c r="BD347" t="n">
+        <v>180.4444444444445</v>
+      </c>
+      <c r="BE347" t="n">
+        <v>76</v>
+      </c>
+      <c r="BF347" t="n">
+        <v>34222.22222222222</v>
+      </c>
+      <c r="BG347" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="BH347" t="n">
+        <v>182.2222222222222</v>
+      </c>
+      <c r="BI347" t="n">
+        <v>81.55555555555556</v>
+      </c>
+      <c r="BJ347" t="n">
+        <v>67888.88888888889</v>
+      </c>
+      <c r="BK347" t="n">
+        <v>26.30769230769231</v>
+      </c>
+      <c r="BL347" t="n">
+        <v>179.2307692307692</v>
+      </c>
+      <c r="BM347" t="n">
+        <v>72.84615384615384</v>
+      </c>
+      <c r="BN347" t="n">
+        <v>19769.23076923077</v>
+      </c>
+      <c r="BO347" t="n">
+        <v>25.85714285714286</v>
+      </c>
+      <c r="BP347" t="n">
+        <v>177.9047619047619</v>
+      </c>
+      <c r="BQ347" t="n">
+        <v>79.80952380952381</v>
+      </c>
+      <c r="BR347" t="n">
+        <v>71142.85714285714</v>
+      </c>
+      <c r="BS347" t="inlineStr"/>
+      <c r="BT347" t="inlineStr"/>
+      <c r="BU347" t="inlineStr"/>
+      <c r="BV347" t="inlineStr"/>
+      <c r="BW347" t="inlineStr"/>
+      <c r="BX347" t="inlineStr"/>
+      <c r="BY347" t="inlineStr"/>
+      <c r="BZ347" t="inlineStr"/>
+      <c r="CA347" t="inlineStr"/>
+      <c r="CB347" t="inlineStr"/>
+      <c r="CC347" t="inlineStr"/>
+      <c r="CD347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="n">
+        <v>45561.58333333334</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rcde stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F348" t="n">
+        <v>23147</v>
+      </c>
+      <c r="G348" t="n">
+        <v>1</v>
+      </c>
+      <c r="H348" t="n">
+        <v>2</v>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="K348" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L348" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="M348" t="n">
+        <v>56</v>
+      </c>
+      <c r="N348" t="n">
+        <v>44</v>
+      </c>
+      <c r="O348" t="n">
+        <v>11</v>
+      </c>
+      <c r="P348" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>2</v>
+      </c>
+      <c r="R348" t="n">
+        <v>4</v>
+      </c>
+      <c r="S348" t="n">
+        <v>4</v>
+      </c>
+      <c r="T348" t="n">
+        <v>7</v>
+      </c>
+      <c r="U348" t="n">
+        <v>5</v>
+      </c>
+      <c r="V348" t="n">
+        <v>4</v>
+      </c>
+      <c r="W348" t="n">
+        <v>16</v>
+      </c>
+      <c r="X348" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y348" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z348" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA348" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB348" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC348" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD348" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE348" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF348" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG348" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH348" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI348" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ348" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK348" t="inlineStr"/>
+      <c r="AL348" t="inlineStr"/>
+      <c r="AM348" t="inlineStr"/>
+      <c r="AN348" t="inlineStr"/>
+      <c r="AO348" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="AP348" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="AQ348" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR348" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS348" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT348" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU348" t="inlineStr"/>
+      <c r="AV348" t="inlineStr"/>
+      <c r="AW348" t="inlineStr"/>
+      <c r="AX348" t="inlineStr"/>
+      <c r="AY348" t="inlineStr"/>
+      <c r="AZ348" t="inlineStr"/>
+      <c r="BA348" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="BB348" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="BC348" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="BD348" t="n">
+        <v>183</v>
+      </c>
+      <c r="BE348" t="n">
+        <v>72.375</v>
+      </c>
+      <c r="BF348" t="n">
+        <v>15250</v>
+      </c>
+      <c r="BG348" t="n">
+        <v>26.22222222222222</v>
+      </c>
+      <c r="BH348" t="n">
+        <v>183.4444444444445</v>
+      </c>
+      <c r="BI348" t="n">
+        <v>75</v>
+      </c>
+      <c r="BJ348" t="n">
+        <v>20666.66666666667</v>
+      </c>
+      <c r="BK348" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="BL348" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="BM348" t="n">
+        <v>71.95</v>
+      </c>
+      <c r="BN348" t="n">
+        <v>15950</v>
+      </c>
+      <c r="BO348" t="n">
+        <v>25.76190476190476</v>
+      </c>
+      <c r="BP348" t="n">
+        <v>181.952380952381</v>
+      </c>
+      <c r="BQ348" t="n">
+        <v>73.66666666666667</v>
+      </c>
+      <c r="BR348" t="inlineStr"/>
+      <c r="BS348" t="inlineStr"/>
+      <c r="BT348" t="inlineStr"/>
+      <c r="BU348" t="inlineStr"/>
+      <c r="BV348" t="inlineStr"/>
+      <c r="BW348" t="inlineStr"/>
+      <c r="BX348" t="inlineStr"/>
+      <c r="BY348" t="inlineStr"/>
+      <c r="BZ348" t="inlineStr"/>
+      <c r="CA348" t="inlineStr"/>
+      <c r="CB348" t="inlineStr"/>
+      <c r="CC348" t="inlineStr"/>
+      <c r="CD348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="n">
+        <v>45561.58333333334</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F349" t="n">
+        <v>22722</v>
+      </c>
+      <c r="G349" t="n">
+        <v>1</v>
+      </c>
+      <c r="H349" t="n">
+        <v>1</v>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="K349" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L349" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="M349" t="n">
+        <v>55</v>
+      </c>
+      <c r="N349" t="n">
+        <v>45</v>
+      </c>
+      <c r="O349" t="n">
+        <v>8</v>
+      </c>
+      <c r="P349" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>2</v>
+      </c>
+      <c r="R349" t="n">
+        <v>5</v>
+      </c>
+      <c r="S349" t="n">
+        <v>4</v>
+      </c>
+      <c r="T349" t="n">
+        <v>7</v>
+      </c>
+      <c r="U349" t="n">
+        <v>2</v>
+      </c>
+      <c r="V349" t="n">
+        <v>2</v>
+      </c>
+      <c r="W349" t="n">
+        <v>16</v>
+      </c>
+      <c r="X349" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y349" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z349" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA349" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB349" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC349" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD349" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE349" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF349" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG349" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH349" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI349" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ349" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK349" t="inlineStr"/>
+      <c r="AL349" t="inlineStr"/>
+      <c r="AM349" t="inlineStr"/>
+      <c r="AN349" t="inlineStr"/>
+      <c r="AO349" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="AP349" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="AQ349" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR349" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS349" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT349" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU349" t="inlineStr"/>
+      <c r="AV349" t="inlineStr"/>
+      <c r="AW349" t="inlineStr"/>
+      <c r="AX349" t="inlineStr"/>
+      <c r="AY349" t="inlineStr"/>
+      <c r="AZ349" t="inlineStr"/>
+      <c r="BA349" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="BB349" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="BC349" t="inlineStr"/>
+      <c r="BD349" t="inlineStr"/>
+      <c r="BE349" t="inlineStr"/>
+      <c r="BF349" t="inlineStr"/>
+      <c r="BG349" t="inlineStr"/>
+      <c r="BH349" t="inlineStr"/>
+      <c r="BI349" t="inlineStr"/>
+      <c r="BJ349" t="inlineStr"/>
+      <c r="BK349" t="n">
+        <v>26.47058823529412</v>
+      </c>
+      <c r="BL349" t="n">
+        <v>177.9411764705882</v>
+      </c>
+      <c r="BM349" t="n">
+        <v>73.70588235294117</v>
+      </c>
+      <c r="BN349" t="n">
+        <v>18588.23529411765</v>
+      </c>
+      <c r="BO349" t="n">
+        <v>24.6875</v>
+      </c>
+      <c r="BP349" t="n">
+        <v>182.1875</v>
+      </c>
+      <c r="BQ349" t="n">
+        <v>72.0625</v>
+      </c>
+      <c r="BR349" t="inlineStr"/>
+      <c r="BS349" t="inlineStr"/>
+      <c r="BT349" t="inlineStr"/>
+      <c r="BU349" t="inlineStr"/>
+      <c r="BV349" t="inlineStr"/>
+      <c r="BW349" t="inlineStr"/>
+      <c r="BX349" t="inlineStr"/>
+      <c r="BY349" t="inlineStr"/>
+      <c r="BZ349" t="inlineStr"/>
+      <c r="CA349" t="inlineStr"/>
+      <c r="CB349" t="inlineStr"/>
+      <c r="CC349" t="inlineStr"/>
+      <c r="CD349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>QDjsB5oT</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="n">
+        <v>45560.66666666666</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>55926</v>
+      </c>
+      <c r="F350" t="n">
+        <v>44407</v>
+      </c>
+      <c r="G350" t="n">
+        <v>1</v>
+      </c>
+      <c r="H350" t="n">
+        <v>0</v>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="K350" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L350" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M350" t="n">
+        <v>78</v>
+      </c>
+      <c r="N350" t="n">
+        <v>22</v>
+      </c>
+      <c r="O350" t="n">
+        <v>15</v>
+      </c>
+      <c r="P350" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>4</v>
+      </c>
+      <c r="R350" t="n">
+        <v>1</v>
+      </c>
+      <c r="S350" t="n">
+        <v>6</v>
+      </c>
+      <c r="T350" t="n">
+        <v>3</v>
+      </c>
+      <c r="U350" t="n">
+        <v>5</v>
+      </c>
+      <c r="V350" t="n">
+        <v>3</v>
+      </c>
+      <c r="W350" t="n">
+        <v>24</v>
+      </c>
+      <c r="X350" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y350" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z350" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA350" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB350" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC350" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD350" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE350" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF350" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG350" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH350" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI350" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ350" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK350" t="inlineStr"/>
+      <c r="AL350" t="inlineStr"/>
+      <c r="AM350" t="inlineStr"/>
+      <c r="AN350" t="inlineStr"/>
+      <c r="AO350" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="AP350" t="inlineStr">
+        <is>
+          <t>A7eo6U2U</t>
+        </is>
+      </c>
+      <c r="AQ350" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR350" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS350" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT350" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU350" t="inlineStr"/>
+      <c r="AV350" t="inlineStr"/>
+      <c r="AW350" t="inlineStr"/>
+      <c r="AX350" t="inlineStr"/>
+      <c r="AY350" t="inlineStr"/>
+      <c r="AZ350" t="inlineStr"/>
+      <c r="BA350" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="BB350" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="BC350" t="inlineStr"/>
+      <c r="BD350" t="inlineStr"/>
+      <c r="BE350" t="inlineStr"/>
+      <c r="BF350" t="inlineStr"/>
+      <c r="BG350" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BH350" t="n">
+        <v>181</v>
+      </c>
+      <c r="BI350" t="n">
+        <v>75.125</v>
+      </c>
+      <c r="BJ350" t="n">
+        <v>21375</v>
+      </c>
+      <c r="BK350" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BL350" t="n">
+        <v>181.1428571428571</v>
+      </c>
+      <c r="BM350" t="n">
+        <v>74.14285714285714</v>
+      </c>
+      <c r="BN350" t="n">
+        <v>82571.42857142857</v>
+      </c>
+      <c r="BO350" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="BP350" t="n">
+        <v>180.5333333333333</v>
+      </c>
+      <c r="BQ350" t="n">
+        <v>75.06666666666666</v>
+      </c>
+      <c r="BR350" t="inlineStr"/>
+      <c r="BS350" t="inlineStr"/>
+      <c r="BT350" t="inlineStr"/>
+      <c r="BU350" t="inlineStr"/>
+      <c r="BV350" t="inlineStr"/>
+      <c r="BW350" t="inlineStr"/>
+      <c r="BX350" t="inlineStr"/>
+      <c r="BY350" t="inlineStr"/>
+      <c r="BZ350" t="inlineStr"/>
+      <c r="CA350" t="inlineStr"/>
+      <c r="CB350" t="inlineStr"/>
+      <c r="CC350" t="inlineStr"/>
+      <c r="CD350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>ddsD5q9j</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="n">
+        <v>45560.58333333334</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F351" t="n">
+        <v>12272</v>
+      </c>
+      <c r="G351" t="n">
+        <v>0</v>
+      </c>
+      <c r="H351" t="n">
+        <v>0</v>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="K351" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L351" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M351" t="n">
+        <v>71</v>
+      </c>
+      <c r="N351" t="n">
+        <v>29</v>
+      </c>
+      <c r="O351" t="n">
+        <v>11</v>
+      </c>
+      <c r="P351" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>0</v>
+      </c>
+      <c r="R351" t="n">
+        <v>0</v>
+      </c>
+      <c r="S351" t="n">
+        <v>9</v>
+      </c>
+      <c r="T351" t="n">
+        <v>2</v>
+      </c>
+      <c r="U351" t="n">
+        <v>2</v>
+      </c>
+      <c r="V351" t="n">
+        <v>0</v>
+      </c>
+      <c r="W351" t="n">
+        <v>17</v>
+      </c>
+      <c r="X351" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y351" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z351" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA351" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB351" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC351" t="n">
+        <v>43</v>
+      </c>
+      <c r="AD351" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE351" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF351" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG351" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH351" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI351" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ351" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK351" t="inlineStr"/>
+      <c r="AL351" t="inlineStr"/>
+      <c r="AM351" t="inlineStr"/>
+      <c r="AN351" t="inlineStr"/>
+      <c r="AO351" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="AP351" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="AQ351" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR351" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS351" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT351" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU351" t="inlineStr"/>
+      <c r="AV351" t="inlineStr"/>
+      <c r="AW351" t="inlineStr"/>
+      <c r="AX351" t="inlineStr"/>
+      <c r="AY351" t="inlineStr"/>
+      <c r="AZ351" t="inlineStr"/>
+      <c r="BA351" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="BB351" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="BC351" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD351" t="n">
+        <v>182.3</v>
+      </c>
+      <c r="BE351" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="BF351" t="n">
+        <v>28000</v>
+      </c>
+      <c r="BG351" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="BH351" t="n">
+        <v>180.1111111111111</v>
+      </c>
+      <c r="BI351" t="n">
+        <v>74</v>
+      </c>
+      <c r="BJ351" t="n">
+        <v>15333.33333333333</v>
+      </c>
+      <c r="BK351" t="n">
+        <v>27.54545454545455</v>
+      </c>
+      <c r="BL351" t="n">
+        <v>181.2727272727273</v>
+      </c>
+      <c r="BM351" t="n">
+        <v>75.81818181818181</v>
+      </c>
+      <c r="BN351" t="n">
+        <v>40272.72727272727</v>
+      </c>
+      <c r="BO351" t="n">
+        <v>28</v>
+      </c>
+      <c r="BP351" t="n">
+        <v>175.0769230769231</v>
+      </c>
+      <c r="BQ351" t="n">
+        <v>74.84615384615384</v>
+      </c>
+      <c r="BR351" t="n">
+        <v>18230.76923076923</v>
+      </c>
+      <c r="BS351" t="inlineStr"/>
+      <c r="BT351" t="inlineStr"/>
+      <c r="BU351" t="inlineStr"/>
+      <c r="BV351" t="inlineStr"/>
+      <c r="BW351" t="inlineStr"/>
+      <c r="BX351" t="inlineStr"/>
+      <c r="BY351" t="inlineStr"/>
+      <c r="BZ351" t="inlineStr"/>
+      <c r="CA351" t="inlineStr"/>
+      <c r="CB351" t="inlineStr"/>
+      <c r="CC351" t="inlineStr"/>
+      <c r="CD351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="n">
+        <v>45559.66666666666</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F352" t="n">
+        <v>67480</v>
+      </c>
+      <c r="G352" t="n">
+        <v>3</v>
+      </c>
+      <c r="H352" t="n">
+        <v>2</v>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="K352" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L352" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M352" t="n">
+        <v>69</v>
+      </c>
+      <c r="N352" t="n">
+        <v>31</v>
+      </c>
+      <c r="O352" t="n">
+        <v>10</v>
+      </c>
+      <c r="P352" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>4</v>
+      </c>
+      <c r="R352" t="n">
+        <v>3</v>
+      </c>
+      <c r="S352" t="n">
+        <v>4</v>
+      </c>
+      <c r="T352" t="n">
+        <v>7</v>
+      </c>
+      <c r="U352" t="n">
+        <v>2</v>
+      </c>
+      <c r="V352" t="n">
+        <v>2</v>
+      </c>
+      <c r="W352" t="n">
+        <v>11</v>
+      </c>
+      <c r="X352" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y352" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z352" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA352" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB352" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC352" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD352" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE352" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF352" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG352" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH352" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI352" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ352" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK352" t="inlineStr"/>
+      <c r="AL352" t="inlineStr"/>
+      <c r="AM352" t="inlineStr"/>
+      <c r="AN352" t="inlineStr"/>
+      <c r="AO352" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="AP352" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="AQ352" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR352" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS352" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT352" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU352" t="inlineStr"/>
+      <c r="AV352" t="inlineStr"/>
+      <c r="AW352" t="inlineStr"/>
+      <c r="AX352" t="inlineStr"/>
+      <c r="AY352" t="inlineStr"/>
+      <c r="AZ352" t="inlineStr"/>
+      <c r="BA352" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="BB352" t="inlineStr"/>
+      <c r="BC352" t="n">
+        <v>24.45454545454545</v>
+      </c>
+      <c r="BD352" t="n">
+        <v>183.5454545454545</v>
+      </c>
+      <c r="BE352" t="n">
+        <v>84.54545454545455</v>
+      </c>
+      <c r="BF352" t="n">
+        <v>204636.3636363636</v>
+      </c>
+      <c r="BG352" t="n">
+        <v>23</v>
+      </c>
+      <c r="BH352" t="n">
+        <v>181.1111111111111</v>
+      </c>
+      <c r="BI352" t="n">
+        <v>70.44444444444444</v>
+      </c>
+      <c r="BJ352" t="n">
+        <v>12222.22222222222</v>
+      </c>
+      <c r="BK352" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="BL352" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="BM352" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="BN352" t="n">
+        <v>138312.5</v>
+      </c>
+      <c r="BO352" t="n">
+        <v>25.29411764705882</v>
+      </c>
+      <c r="BP352" t="n">
+        <v>179.4117647058823</v>
+      </c>
+      <c r="BQ352" t="n">
+        <v>72</v>
+      </c>
+      <c r="BR352" t="n">
+        <v>16058.82352941176</v>
+      </c>
+      <c r="BS352" t="inlineStr"/>
+      <c r="BT352" t="inlineStr"/>
+      <c r="BU352" t="inlineStr"/>
+      <c r="BV352" t="inlineStr"/>
+      <c r="BW352" t="inlineStr"/>
+      <c r="BX352" t="inlineStr"/>
+      <c r="BY352" t="inlineStr"/>
+      <c r="BZ352" t="inlineStr"/>
+      <c r="CA352" t="inlineStr"/>
+      <c r="CB352" t="inlineStr"/>
+      <c r="CC352" t="inlineStr"/>
+      <c r="CD352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F353" t="n">
+        <v>35292</v>
+      </c>
+      <c r="G353" t="n">
+        <v>2</v>
+      </c>
+      <c r="H353" t="n">
+        <v>1</v>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="K353" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L353" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M353" t="n">
+        <v>55</v>
+      </c>
+      <c r="N353" t="n">
+        <v>45</v>
+      </c>
+      <c r="O353" t="n">
+        <v>22</v>
+      </c>
+      <c r="P353" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>5</v>
+      </c>
+      <c r="R353" t="n">
+        <v>2</v>
+      </c>
+      <c r="S353" t="n">
+        <v>11</v>
+      </c>
+      <c r="T353" t="n">
+        <v>2</v>
+      </c>
+      <c r="U353" t="n">
+        <v>6</v>
+      </c>
+      <c r="V353" t="n">
+        <v>4</v>
+      </c>
+      <c r="W353" t="n">
+        <v>19</v>
+      </c>
+      <c r="X353" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y353" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z353" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA353" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB353" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC353" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD353" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE353" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF353" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG353" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH353" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI353" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ353" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK353" t="inlineStr"/>
+      <c r="AL353" t="inlineStr"/>
+      <c r="AM353" t="inlineStr"/>
+      <c r="AN353" t="inlineStr"/>
+      <c r="AO353" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="AP353" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="AQ353" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR353" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS353" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT353" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU353" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV353" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW353" t="inlineStr"/>
+      <c r="AX353" t="inlineStr"/>
+      <c r="AY353" t="inlineStr"/>
+      <c r="AZ353" t="inlineStr"/>
+      <c r="BA353" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="BB353" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="BC353" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="BD353" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="BE353" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="BF353" t="n">
+        <v>25100</v>
+      </c>
+      <c r="BG353" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="BH353" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="BI353" t="n">
+        <v>71.125</v>
+      </c>
+      <c r="BJ353" t="n">
+        <v>11375</v>
+      </c>
+      <c r="BK353" t="n">
+        <v>24.07142857142857</v>
+      </c>
+      <c r="BL353" t="n">
+        <v>179.9285714285714</v>
+      </c>
+      <c r="BM353" t="n">
+        <v>73.85714285714286</v>
+      </c>
+      <c r="BN353" t="n">
+        <v>22857.14285714286</v>
+      </c>
+      <c r="BO353" t="n">
+        <v>24.38888888888889</v>
+      </c>
+      <c r="BP353" t="n">
+        <v>180.7222222222222</v>
+      </c>
+      <c r="BQ353" t="n">
+        <v>70.61111111111111</v>
+      </c>
+      <c r="BR353" t="n">
+        <v>22000</v>
+      </c>
+      <c r="BS353" t="inlineStr"/>
+      <c r="BT353" t="inlineStr"/>
+      <c r="BU353" t="inlineStr"/>
+      <c r="BV353" t="inlineStr"/>
+      <c r="BW353" t="inlineStr"/>
+      <c r="BX353" t="inlineStr"/>
+      <c r="BY353" t="inlineStr"/>
+      <c r="BZ353" t="inlineStr"/>
+      <c r="CA353" t="inlineStr"/>
+      <c r="CB353" t="inlineStr"/>
+      <c r="CC353" t="inlineStr"/>
+      <c r="CD353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F354" t="n">
+        <v>40425</v>
+      </c>
+      <c r="G354" t="n">
+        <v>0</v>
+      </c>
+      <c r="H354" t="n">
+        <v>0</v>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="K354" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L354" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M354" t="n">
+        <v>52</v>
+      </c>
+      <c r="N354" t="n">
+        <v>48</v>
+      </c>
+      <c r="O354" t="n">
+        <v>10</v>
+      </c>
+      <c r="P354" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>2</v>
+      </c>
+      <c r="R354" t="n">
+        <v>2</v>
+      </c>
+      <c r="S354" t="n">
+        <v>4</v>
+      </c>
+      <c r="T354" t="n">
+        <v>5</v>
+      </c>
+      <c r="U354" t="n">
+        <v>4</v>
+      </c>
+      <c r="V354" t="n">
+        <v>2</v>
+      </c>
+      <c r="W354" t="n">
+        <v>13</v>
+      </c>
+      <c r="X354" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y354" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z354" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA354" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB354" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC354" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD354" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE354" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF354" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG354" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH354" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI354" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ354" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK354" t="inlineStr"/>
+      <c r="AL354" t="inlineStr"/>
+      <c r="AM354" t="inlineStr"/>
+      <c r="AN354" t="inlineStr"/>
+      <c r="AO354" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="AP354" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="AQ354" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR354" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS354" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT354" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU354" t="inlineStr"/>
+      <c r="AV354" t="inlineStr"/>
+      <c r="AW354" t="inlineStr"/>
+      <c r="AX354" t="inlineStr"/>
+      <c r="AY354" t="inlineStr"/>
+      <c r="AZ354" t="inlineStr"/>
+      <c r="BA354" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="BB354" t="inlineStr"/>
+      <c r="BC354" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="BD354" t="n">
+        <v>181.875</v>
+      </c>
+      <c r="BE354" t="n">
+        <v>70.625</v>
+      </c>
+      <c r="BF354" t="n">
+        <v>20000</v>
+      </c>
+      <c r="BG354" t="inlineStr"/>
+      <c r="BH354" t="inlineStr"/>
+      <c r="BI354" t="inlineStr"/>
+      <c r="BJ354" t="inlineStr"/>
+      <c r="BK354" t="n">
+        <v>23.90476190476191</v>
+      </c>
+      <c r="BL354" t="n">
+        <v>178.952380952381</v>
+      </c>
+      <c r="BM354" t="n">
+        <v>72.04761904761905</v>
+      </c>
+      <c r="BN354" t="n">
+        <v>23333.33333333333</v>
+      </c>
+      <c r="BO354" t="n">
+        <v>25.53333333333333</v>
+      </c>
+      <c r="BP354" t="n">
+        <v>178.1333333333333</v>
+      </c>
+      <c r="BQ354" t="n">
+        <v>74.06666666666666</v>
+      </c>
+      <c r="BR354" t="n">
+        <v>20266.66666666667</v>
+      </c>
+      <c r="BS354" t="inlineStr"/>
+      <c r="BT354" t="inlineStr"/>
+      <c r="BU354" t="inlineStr"/>
+      <c r="BV354" t="inlineStr"/>
+      <c r="BW354" t="inlineStr"/>
+      <c r="BX354" t="inlineStr"/>
+      <c r="BY354" t="inlineStr"/>
+      <c r="BZ354" t="inlineStr"/>
+      <c r="CA354" t="inlineStr"/>
+      <c r="CB354" t="inlineStr"/>
+      <c r="CC354" t="inlineStr"/>
+      <c r="CD354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="n">
+        <v>45558.66666666666</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F355" t="n">
+        <v>47017</v>
+      </c>
+      <c r="G355" t="n">
+        <v>1</v>
+      </c>
+      <c r="H355" t="n">
+        <v>2</v>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="K355" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L355" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M355" t="n">
+        <v>61</v>
+      </c>
+      <c r="N355" t="n">
+        <v>39</v>
+      </c>
+      <c r="O355" t="n">
+        <v>16</v>
+      </c>
+      <c r="P355" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>6</v>
+      </c>
+      <c r="R355" t="n">
+        <v>6</v>
+      </c>
+      <c r="S355" t="n">
+        <v>5</v>
+      </c>
+      <c r="T355" t="n">
+        <v>1</v>
+      </c>
+      <c r="U355" t="n">
+        <v>5</v>
+      </c>
+      <c r="V355" t="n">
+        <v>0</v>
+      </c>
+      <c r="W355" t="n">
+        <v>19</v>
+      </c>
+      <c r="X355" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y355" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z355" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA355" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB355" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC355" t="n">
+        <v>33</v>
+      </c>
+      <c r="AD355" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE355" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF355" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG355" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH355" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI355" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ355" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK355" t="inlineStr"/>
+      <c r="AL355" t="inlineStr"/>
+      <c r="AM355" t="inlineStr"/>
+      <c r="AN355" t="inlineStr"/>
+      <c r="AO355" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="AP355" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="AQ355" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR355" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS355" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT355" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU355" t="inlineStr"/>
+      <c r="AV355" t="inlineStr"/>
+      <c r="AW355" t="inlineStr"/>
+      <c r="AX355" t="inlineStr"/>
+      <c r="AY355" t="inlineStr"/>
+      <c r="AZ355" t="inlineStr"/>
+      <c r="BA355" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="BB355" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="BC355" t="inlineStr"/>
+      <c r="BD355" t="inlineStr"/>
+      <c r="BE355" t="inlineStr"/>
+      <c r="BF355" t="inlineStr"/>
+      <c r="BG355" t="n">
+        <v>27</v>
+      </c>
+      <c r="BH355" t="n">
+        <v>184.4</v>
+      </c>
+      <c r="BI355" t="n">
+        <v>75</v>
+      </c>
+      <c r="BJ355" t="n">
+        <v>23000</v>
+      </c>
+      <c r="BK355" t="n">
+        <v>25.84210526315789</v>
+      </c>
+      <c r="BL355" t="n">
+        <v>178.5263157894737</v>
+      </c>
+      <c r="BM355" t="n">
+        <v>74.05263157894737</v>
+      </c>
+      <c r="BN355" t="inlineStr"/>
+      <c r="BO355" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="BP355" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="BQ355" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="BR355" t="n">
+        <v>20791.66666666667</v>
+      </c>
+      <c r="BS355" t="inlineStr"/>
+      <c r="BT355" t="inlineStr"/>
+      <c r="BU355" t="inlineStr"/>
+      <c r="BV355" t="inlineStr"/>
+      <c r="BW355" t="inlineStr"/>
+      <c r="BX355" t="inlineStr"/>
+      <c r="BY355" t="inlineStr"/>
+      <c r="BZ355" t="inlineStr"/>
+      <c r="CA355" t="inlineStr"/>
+      <c r="CB355" t="inlineStr"/>
+      <c r="CC355" t="inlineStr"/>
+      <c r="CD355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>8Ia7s2mS</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="n">
+        <v>45558.64583333334</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">muresan s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el alcoraz
+  huesca </t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F356" t="n">
+        <v>5899</v>
+      </c>
+      <c r="G356" t="n">
+        <v>4</v>
+      </c>
+      <c r="H356" t="n">
+        <v>1</v>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr"/>
+      <c r="M356" t="n">
+        <v>34</v>
+      </c>
+      <c r="N356" t="n">
+        <v>66</v>
+      </c>
+      <c r="O356" t="n">
+        <v>9</v>
+      </c>
+      <c r="P356" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>5</v>
+      </c>
+      <c r="R356" t="n">
+        <v>4</v>
+      </c>
+      <c r="S356" t="n">
+        <v>3</v>
+      </c>
+      <c r="T356" t="n">
+        <v>6</v>
+      </c>
+      <c r="U356" t="n">
+        <v>1</v>
+      </c>
+      <c r="V356" t="n">
+        <v>6</v>
+      </c>
+      <c r="W356" t="n">
+        <v>10</v>
+      </c>
+      <c r="X356" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y356" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z356" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA356" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB356" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC356" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD356" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE356" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF356" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG356" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH356" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI356" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ356" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK356" t="inlineStr"/>
+      <c r="AL356" t="inlineStr"/>
+      <c r="AM356" t="inlineStr"/>
+      <c r="AN356" t="inlineStr"/>
+      <c r="AO356" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="AP356" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="AQ356" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR356" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS356" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT356" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU356" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV356" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW356" t="inlineStr"/>
+      <c r="AX356" t="inlineStr"/>
+      <c r="AY356" t="inlineStr"/>
+      <c r="AZ356" t="inlineStr"/>
+      <c r="BA356" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="BB356" t="inlineStr"/>
+      <c r="BC356" t="inlineStr"/>
+      <c r="BD356" t="inlineStr"/>
+      <c r="BE356" t="inlineStr"/>
+      <c r="BF356" t="inlineStr"/>
+      <c r="BG356" t="inlineStr"/>
+      <c r="BH356" t="inlineStr"/>
+      <c r="BI356" t="inlineStr"/>
+      <c r="BJ356" t="inlineStr"/>
+      <c r="BK356" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="BL356" t="n">
+        <v>179.9333333333333</v>
+      </c>
+      <c r="BM356" t="n">
+        <v>65.66666666666667</v>
+      </c>
+      <c r="BN356" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BO356" t="inlineStr"/>
+      <c r="BP356" t="inlineStr"/>
+      <c r="BQ356" t="inlineStr"/>
+      <c r="BR356" t="inlineStr"/>
+      <c r="BS356" t="inlineStr"/>
+      <c r="BT356" t="inlineStr"/>
+      <c r="BU356" t="inlineStr"/>
+      <c r="BV356" t="inlineStr"/>
+      <c r="BW356" t="inlineStr"/>
+      <c r="BX356" t="inlineStr"/>
+      <c r="BY356" t="inlineStr"/>
+      <c r="BZ356" t="inlineStr"/>
+      <c r="CA356" t="inlineStr"/>
+      <c r="CB356" t="inlineStr"/>
+      <c r="CC356" t="inlineStr"/>
+      <c r="CD356" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD356"/>
+  <dimension ref="A1:CD366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83118,6 +83118,2140 @@
       <c r="CC356" t="inlineStr"/>
       <c r="CD356" t="inlineStr"/>
     </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>4vvdzeEs</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="n">
+        <v>45563.66666666666</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F357" t="n">
+        <v>22322</v>
+      </c>
+      <c r="G357" t="n">
+        <v>4</v>
+      </c>
+      <c r="H357" t="n">
+        <v>2</v>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="K357" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="L357" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M357" t="n">
+        <v>25</v>
+      </c>
+      <c r="N357" t="n">
+        <v>75</v>
+      </c>
+      <c r="O357" t="n">
+        <v>11</v>
+      </c>
+      <c r="P357" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>6</v>
+      </c>
+      <c r="R357" t="n">
+        <v>5</v>
+      </c>
+      <c r="S357" t="n">
+        <v>3</v>
+      </c>
+      <c r="T357" t="n">
+        <v>6</v>
+      </c>
+      <c r="U357" t="n">
+        <v>2</v>
+      </c>
+      <c r="V357" t="n">
+        <v>1</v>
+      </c>
+      <c r="W357" t="n">
+        <v>2</v>
+      </c>
+      <c r="X357" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y357" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z357" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA357" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB357" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC357" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD357" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE357" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF357" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG357" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH357" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI357" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ357" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK357" t="inlineStr"/>
+      <c r="AL357" t="inlineStr"/>
+      <c r="AM357" t="inlineStr"/>
+      <c r="AN357" t="inlineStr"/>
+      <c r="AO357" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="AP357" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="AQ357" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR357" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS357" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT357" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU357" t="inlineStr"/>
+      <c r="AV357" t="inlineStr"/>
+      <c r="AW357" t="inlineStr"/>
+      <c r="AX357" t="inlineStr"/>
+      <c r="AY357" t="inlineStr"/>
+      <c r="AZ357" t="inlineStr"/>
+      <c r="BA357" t="inlineStr"/>
+      <c r="BB357" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="BC357" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="BD357" t="n">
+        <v>183.125</v>
+      </c>
+      <c r="BE357" t="n">
+        <v>74.875</v>
+      </c>
+      <c r="BF357" t="n">
+        <v>19875</v>
+      </c>
+      <c r="BG357" t="inlineStr"/>
+      <c r="BH357" t="inlineStr"/>
+      <c r="BI357" t="inlineStr"/>
+      <c r="BJ357" t="inlineStr"/>
+      <c r="BK357" t="n">
+        <v>26.57142857142857</v>
+      </c>
+      <c r="BL357" t="n">
+        <v>177</v>
+      </c>
+      <c r="BM357" t="n">
+        <v>72.57142857142857</v>
+      </c>
+      <c r="BN357" t="n">
+        <v>19071.42857142857</v>
+      </c>
+      <c r="BO357" t="n">
+        <v>20.92857142857143</v>
+      </c>
+      <c r="BP357" t="n">
+        <v>178.8571428571429</v>
+      </c>
+      <c r="BQ357" t="n">
+        <v>70.78571428571429</v>
+      </c>
+      <c r="BR357" t="n">
+        <v>61142.85714285714</v>
+      </c>
+      <c r="BS357" t="inlineStr"/>
+      <c r="BT357" t="inlineStr"/>
+      <c r="BU357" t="inlineStr"/>
+      <c r="BV357" t="inlineStr"/>
+      <c r="BW357" t="inlineStr"/>
+      <c r="BX357" t="inlineStr"/>
+      <c r="BY357" t="inlineStr"/>
+      <c r="BZ357" t="inlineStr"/>
+      <c r="CA357" t="inlineStr"/>
+      <c r="CB357" t="inlineStr"/>
+      <c r="CC357" t="inlineStr"/>
+      <c r="CD357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F358" t="n">
+        <v>32332</v>
+      </c>
+      <c r="G358" t="n">
+        <v>3</v>
+      </c>
+      <c r="H358" t="n">
+        <v>0</v>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="K358" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="L358" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M358" t="n">
+        <v>61</v>
+      </c>
+      <c r="N358" t="n">
+        <v>39</v>
+      </c>
+      <c r="O358" t="n">
+        <v>11</v>
+      </c>
+      <c r="P358" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>6</v>
+      </c>
+      <c r="R358" t="n">
+        <v>4</v>
+      </c>
+      <c r="S358" t="n">
+        <v>3</v>
+      </c>
+      <c r="T358" t="n">
+        <v>3</v>
+      </c>
+      <c r="U358" t="n">
+        <v>2</v>
+      </c>
+      <c r="V358" t="n">
+        <v>2</v>
+      </c>
+      <c r="W358" t="n">
+        <v>15</v>
+      </c>
+      <c r="X358" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y358" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z358" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA358" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB358" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC358" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD358" t="n">
+        <v>33</v>
+      </c>
+      <c r="AE358" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF358" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG358" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH358" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI358" t="inlineStr"/>
+      <c r="AJ358" t="inlineStr"/>
+      <c r="AK358" t="inlineStr"/>
+      <c r="AL358" t="inlineStr"/>
+      <c r="AM358" t="inlineStr"/>
+      <c r="AN358" t="inlineStr"/>
+      <c r="AO358" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="AP358" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="AQ358" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR358" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS358" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT358" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU358" t="inlineStr"/>
+      <c r="AV358" t="inlineStr"/>
+      <c r="AW358" t="inlineStr"/>
+      <c r="AX358" t="inlineStr"/>
+      <c r="AY358" t="inlineStr"/>
+      <c r="AZ358" t="inlineStr"/>
+      <c r="BA358" t="inlineStr"/>
+      <c r="BB358" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="BC358" t="inlineStr"/>
+      <c r="BD358" t="inlineStr"/>
+      <c r="BE358" t="inlineStr"/>
+      <c r="BF358" t="inlineStr"/>
+      <c r="BG358" t="n">
+        <v>23.625</v>
+      </c>
+      <c r="BH358" t="n">
+        <v>181.875</v>
+      </c>
+      <c r="BI358" t="n">
+        <v>70.875</v>
+      </c>
+      <c r="BJ358" t="n">
+        <v>18875</v>
+      </c>
+      <c r="BK358" t="n">
+        <v>23.78947368421053</v>
+      </c>
+      <c r="BL358" t="n">
+        <v>180.7368421052632</v>
+      </c>
+      <c r="BM358" t="n">
+        <v>73.57894736842105</v>
+      </c>
+      <c r="BN358" t="n">
+        <v>24526.31578947368</v>
+      </c>
+      <c r="BO358" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="BP358" t="n">
+        <v>178.7</v>
+      </c>
+      <c r="BQ358" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="BR358" t="n">
+        <v>23200</v>
+      </c>
+      <c r="BS358" t="inlineStr"/>
+      <c r="BT358" t="inlineStr"/>
+      <c r="BU358" t="inlineStr"/>
+      <c r="BV358" t="inlineStr"/>
+      <c r="BW358" t="inlineStr"/>
+      <c r="BX358" t="inlineStr"/>
+      <c r="BY358" t="inlineStr"/>
+      <c r="BZ358" t="inlineStr"/>
+      <c r="CA358" t="inlineStr"/>
+      <c r="CB358" t="inlineStr"/>
+      <c r="CC358" t="inlineStr"/>
+      <c r="CD358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="n">
+        <v>45563.46875</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>14708</v>
+      </c>
+      <c r="F359" t="n">
+        <v>13186</v>
+      </c>
+      <c r="G359" t="n">
+        <v>1</v>
+      </c>
+      <c r="H359" t="n">
+        <v>1</v>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="K359" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L359" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M359" t="n">
+        <v>53</v>
+      </c>
+      <c r="N359" t="n">
+        <v>47</v>
+      </c>
+      <c r="O359" t="n">
+        <v>15</v>
+      </c>
+      <c r="P359" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>6</v>
+      </c>
+      <c r="R359" t="n">
+        <v>3</v>
+      </c>
+      <c r="S359" t="n">
+        <v>5</v>
+      </c>
+      <c r="T359" t="n">
+        <v>6</v>
+      </c>
+      <c r="U359" t="n">
+        <v>4</v>
+      </c>
+      <c r="V359" t="n">
+        <v>4</v>
+      </c>
+      <c r="W359" t="n">
+        <v>9</v>
+      </c>
+      <c r="X359" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y359" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z359" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA359" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB359" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC359" t="n">
+        <v>31</v>
+      </c>
+      <c r="AD359" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE359" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF359" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG359" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH359" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI359" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ359" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK359" t="inlineStr"/>
+      <c r="AL359" t="inlineStr"/>
+      <c r="AM359" t="inlineStr"/>
+      <c r="AN359" t="inlineStr"/>
+      <c r="AO359" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="AP359" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="AQ359" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR359" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS359" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT359" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU359" t="inlineStr"/>
+      <c r="AV359" t="inlineStr"/>
+      <c r="AW359" t="inlineStr"/>
+      <c r="AX359" t="inlineStr"/>
+      <c r="AY359" t="inlineStr"/>
+      <c r="AZ359" t="inlineStr"/>
+      <c r="BA359" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="BB359" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="BC359" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="BD359" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="BE359" t="n">
+        <v>74.875</v>
+      </c>
+      <c r="BF359" t="n">
+        <v>16750</v>
+      </c>
+      <c r="BG359" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="BH359" t="n">
+        <v>184</v>
+      </c>
+      <c r="BI359" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="BJ359" t="n">
+        <v>22700</v>
+      </c>
+      <c r="BK359" t="n">
+        <v>30.14285714285714</v>
+      </c>
+      <c r="BL359" t="n">
+        <v>175.9285714285714</v>
+      </c>
+      <c r="BM359" t="n">
+        <v>75.42857142857143</v>
+      </c>
+      <c r="BN359" t="n">
+        <v>19214.28571428571</v>
+      </c>
+      <c r="BO359" t="n">
+        <v>26</v>
+      </c>
+      <c r="BP359" t="n">
+        <v>180.1428571428571</v>
+      </c>
+      <c r="BQ359" t="n">
+        <v>70.14285714285714</v>
+      </c>
+      <c r="BR359" t="inlineStr"/>
+      <c r="BS359" t="inlineStr"/>
+      <c r="BT359" t="inlineStr"/>
+      <c r="BU359" t="inlineStr"/>
+      <c r="BV359" t="inlineStr"/>
+      <c r="BW359" t="inlineStr"/>
+      <c r="BX359" t="inlineStr"/>
+      <c r="BY359" t="inlineStr"/>
+      <c r="BZ359" t="inlineStr"/>
+      <c r="CA359" t="inlineStr"/>
+      <c r="CB359" t="inlineStr"/>
+      <c r="CC359" t="inlineStr"/>
+      <c r="CD359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="n">
+        <v>45563.375</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F360" t="n">
+        <v>10006</v>
+      </c>
+      <c r="G360" t="n">
+        <v>2</v>
+      </c>
+      <c r="H360" t="n">
+        <v>0</v>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="K360" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L360" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M360" t="n">
+        <v>45</v>
+      </c>
+      <c r="N360" t="n">
+        <v>55</v>
+      </c>
+      <c r="O360" t="n">
+        <v>14</v>
+      </c>
+      <c r="P360" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>8</v>
+      </c>
+      <c r="R360" t="n">
+        <v>1</v>
+      </c>
+      <c r="S360" t="n">
+        <v>3</v>
+      </c>
+      <c r="T360" t="n">
+        <v>5</v>
+      </c>
+      <c r="U360" t="n">
+        <v>3</v>
+      </c>
+      <c r="V360" t="n">
+        <v>3</v>
+      </c>
+      <c r="W360" t="n">
+        <v>28</v>
+      </c>
+      <c r="X360" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y360" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z360" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA360" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB360" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC360" t="n">
+        <v>35</v>
+      </c>
+      <c r="AD360" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE360" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF360" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG360" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH360" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI360" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ360" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK360" t="inlineStr"/>
+      <c r="AL360" t="inlineStr"/>
+      <c r="AM360" t="inlineStr"/>
+      <c r="AN360" t="inlineStr"/>
+      <c r="AO360" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="AP360" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="AQ360" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR360" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS360" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT360" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU360" t="inlineStr"/>
+      <c r="AV360" t="inlineStr"/>
+      <c r="AW360" t="inlineStr"/>
+      <c r="AX360" t="inlineStr"/>
+      <c r="AY360" t="inlineStr"/>
+      <c r="AZ360" t="inlineStr"/>
+      <c r="BA360" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="BB360" t="inlineStr"/>
+      <c r="BC360" t="n">
+        <v>27.11111111111111</v>
+      </c>
+      <c r="BD360" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="BE360" t="n">
+        <v>76.11111111111111</v>
+      </c>
+      <c r="BF360" t="n">
+        <v>23444.44444444445</v>
+      </c>
+      <c r="BG360" t="inlineStr"/>
+      <c r="BH360" t="inlineStr"/>
+      <c r="BI360" t="inlineStr"/>
+      <c r="BJ360" t="inlineStr"/>
+      <c r="BK360" t="n">
+        <v>23.81818181818182</v>
+      </c>
+      <c r="BL360" t="n">
+        <v>180.5454545454545</v>
+      </c>
+      <c r="BM360" t="n">
+        <v>70</v>
+      </c>
+      <c r="BN360" t="n">
+        <v>20727.27272727273</v>
+      </c>
+      <c r="BO360" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BP360" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BQ360" t="n">
+        <v>70.44444444444444</v>
+      </c>
+      <c r="BR360" t="n">
+        <v>12833.33333333333</v>
+      </c>
+      <c r="BS360" t="inlineStr"/>
+      <c r="BT360" t="inlineStr"/>
+      <c r="BU360" t="inlineStr"/>
+      <c r="BV360" t="inlineStr"/>
+      <c r="BW360" t="inlineStr"/>
+      <c r="BX360" t="inlineStr"/>
+      <c r="BY360" t="inlineStr"/>
+      <c r="BZ360" t="inlineStr"/>
+      <c r="CA360" t="inlineStr"/>
+      <c r="CB360" t="inlineStr"/>
+      <c r="CC360" t="inlineStr"/>
+      <c r="CD360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="n">
+        <v>45562.66666666666</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F361" t="n">
+        <v>20338</v>
+      </c>
+      <c r="G361" t="n">
+        <v>1</v>
+      </c>
+      <c r="H361" t="n">
+        <v>2</v>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="K361" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L361" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="M361" t="n">
+        <v>50</v>
+      </c>
+      <c r="N361" t="n">
+        <v>50</v>
+      </c>
+      <c r="O361" t="n">
+        <v>13</v>
+      </c>
+      <c r="P361" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>1</v>
+      </c>
+      <c r="R361" t="n">
+        <v>6</v>
+      </c>
+      <c r="S361" t="n">
+        <v>10</v>
+      </c>
+      <c r="T361" t="n">
+        <v>8</v>
+      </c>
+      <c r="U361" t="n">
+        <v>2</v>
+      </c>
+      <c r="V361" t="n">
+        <v>3</v>
+      </c>
+      <c r="W361" t="n">
+        <v>14</v>
+      </c>
+      <c r="X361" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y361" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z361" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA361" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB361" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC361" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD361" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE361" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF361" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG361" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH361" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI361" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ361" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK361" t="inlineStr"/>
+      <c r="AL361" t="inlineStr"/>
+      <c r="AM361" t="inlineStr"/>
+      <c r="AN361" t="inlineStr"/>
+      <c r="AO361" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="AP361" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="AQ361" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR361" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS361" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT361" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU361" t="inlineStr"/>
+      <c r="AV361" t="inlineStr"/>
+      <c r="AW361" t="inlineStr"/>
+      <c r="AX361" t="inlineStr"/>
+      <c r="AY361" t="inlineStr"/>
+      <c r="AZ361" t="inlineStr"/>
+      <c r="BA361" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="BB361" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="BC361" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="BD361" t="n">
+        <v>180</v>
+      </c>
+      <c r="BE361" t="n">
+        <v>71</v>
+      </c>
+      <c r="BF361" t="n">
+        <v>19500</v>
+      </c>
+      <c r="BG361" t="n">
+        <v>25.88888888888889</v>
+      </c>
+      <c r="BH361" t="n">
+        <v>182.5555555555555</v>
+      </c>
+      <c r="BI361" t="n">
+        <v>75.88888888888889</v>
+      </c>
+      <c r="BJ361" t="n">
+        <v>24111.11111111111</v>
+      </c>
+      <c r="BK361" t="n">
+        <v>26.53846153846154</v>
+      </c>
+      <c r="BL361" t="n">
+        <v>181.3076923076923</v>
+      </c>
+      <c r="BM361" t="n">
+        <v>70.69230769230769</v>
+      </c>
+      <c r="BN361" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BO361" t="n">
+        <v>26.29166666666667</v>
+      </c>
+      <c r="BP361" t="n">
+        <v>180.7083333333333</v>
+      </c>
+      <c r="BQ361" t="n">
+        <v>72.875</v>
+      </c>
+      <c r="BR361" t="n">
+        <v>20541.66666666667</v>
+      </c>
+      <c r="BS361" t="inlineStr"/>
+      <c r="BT361" t="inlineStr"/>
+      <c r="BU361" t="inlineStr"/>
+      <c r="BV361" t="inlineStr"/>
+      <c r="BW361" t="inlineStr"/>
+      <c r="BX361" t="inlineStr"/>
+      <c r="BY361" t="inlineStr"/>
+      <c r="BZ361" t="inlineStr"/>
+      <c r="CA361" t="inlineStr"/>
+      <c r="CB361" t="inlineStr"/>
+      <c r="CC361" t="inlineStr"/>
+      <c r="CD361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>n7g3az9D</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="n">
+        <v>45563.66666666666</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lax franco s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio la rosaleda
+  malaga </t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>30044</v>
+      </c>
+      <c r="F362" t="n">
+        <v>26377</v>
+      </c>
+      <c r="G362" t="n">
+        <v>0</v>
+      </c>
+      <c r="H362" t="n">
+        <v>3</v>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr"/>
+      <c r="M362" t="n">
+        <v>52</v>
+      </c>
+      <c r="N362" t="n">
+        <v>48</v>
+      </c>
+      <c r="O362" t="n">
+        <v>5</v>
+      </c>
+      <c r="P362" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>0</v>
+      </c>
+      <c r="R362" t="n">
+        <v>8</v>
+      </c>
+      <c r="S362" t="n">
+        <v>3</v>
+      </c>
+      <c r="T362" t="n">
+        <v>2</v>
+      </c>
+      <c r="U362" t="n">
+        <v>2</v>
+      </c>
+      <c r="V362" t="n">
+        <v>4</v>
+      </c>
+      <c r="W362" t="n">
+        <v>23</v>
+      </c>
+      <c r="X362" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y362" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z362" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA362" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB362" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC362" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD362" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE362" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF362" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG362" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH362" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI362" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ362" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK362" t="inlineStr"/>
+      <c r="AL362" t="inlineStr"/>
+      <c r="AM362" t="inlineStr"/>
+      <c r="AN362" t="inlineStr"/>
+      <c r="AO362" t="inlineStr">
+        <is>
+          <t>tjXr7SAp</t>
+        </is>
+      </c>
+      <c r="AP362" t="inlineStr">
+        <is>
+          <t>zT9gi7i9</t>
+        </is>
+      </c>
+      <c r="AQ362" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR362" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS362" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT362" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU362" t="inlineStr"/>
+      <c r="AV362" t="inlineStr"/>
+      <c r="AW362" t="inlineStr"/>
+      <c r="AX362" t="inlineStr"/>
+      <c r="AY362" t="inlineStr"/>
+      <c r="AZ362" t="inlineStr"/>
+      <c r="BA362" t="inlineStr"/>
+      <c r="BB362" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="BC362" t="inlineStr"/>
+      <c r="BD362" t="inlineStr"/>
+      <c r="BE362" t="inlineStr"/>
+      <c r="BF362" t="inlineStr"/>
+      <c r="BG362" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BH362" t="n">
+        <v>180</v>
+      </c>
+      <c r="BI362" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="BJ362" t="n">
+        <v>6000</v>
+      </c>
+      <c r="BK362" t="n">
+        <v>23.11111111111111</v>
+      </c>
+      <c r="BL362" t="n">
+        <v>182.7777777777778</v>
+      </c>
+      <c r="BM362" t="n">
+        <v>65.11111111111111</v>
+      </c>
+      <c r="BN362" t="n">
+        <v>4000</v>
+      </c>
+      <c r="BO362" t="n">
+        <v>26.94444444444444</v>
+      </c>
+      <c r="BP362" t="n">
+        <v>180.6111111111111</v>
+      </c>
+      <c r="BQ362" t="n">
+        <v>68.88888888888889</v>
+      </c>
+      <c r="BR362" t="inlineStr"/>
+      <c r="BS362" t="inlineStr"/>
+      <c r="BT362" t="inlineStr"/>
+      <c r="BU362" t="inlineStr"/>
+      <c r="BV362" t="inlineStr"/>
+      <c r="BW362" t="inlineStr"/>
+      <c r="BX362" t="inlineStr"/>
+      <c r="BY362" t="inlineStr"/>
+      <c r="BZ362" t="inlineStr"/>
+      <c r="CA362" t="inlineStr"/>
+      <c r="CB362" t="inlineStr"/>
+      <c r="CC362" t="inlineStr"/>
+      <c r="CD362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>SteFA0HE</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moreno a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el molinon
+  gijon </t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>29029</v>
+      </c>
+      <c r="F363" t="n">
+        <v>22426</v>
+      </c>
+      <c r="G363" t="n">
+        <v>1</v>
+      </c>
+      <c r="H363" t="n">
+        <v>0</v>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr"/>
+      <c r="L363" t="inlineStr"/>
+      <c r="M363" t="n">
+        <v>62</v>
+      </c>
+      <c r="N363" t="n">
+        <v>38</v>
+      </c>
+      <c r="O363" t="n">
+        <v>22</v>
+      </c>
+      <c r="P363" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>8</v>
+      </c>
+      <c r="R363" t="n">
+        <v>2</v>
+      </c>
+      <c r="S363" t="n">
+        <v>11</v>
+      </c>
+      <c r="T363" t="n">
+        <v>5</v>
+      </c>
+      <c r="U363" t="n">
+        <v>3</v>
+      </c>
+      <c r="V363" t="n">
+        <v>0</v>
+      </c>
+      <c r="W363" t="n">
+        <v>11</v>
+      </c>
+      <c r="X363" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y363" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z363" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA363" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB363" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC363" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD363" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE363" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF363" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG363" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH363" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI363" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ363" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK363" t="inlineStr"/>
+      <c r="AL363" t="inlineStr"/>
+      <c r="AM363" t="inlineStr"/>
+      <c r="AN363" t="inlineStr"/>
+      <c r="AO363" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="AP363" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="AQ363" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR363" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS363" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT363" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU363" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV363" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW363" t="inlineStr"/>
+      <c r="AX363" t="inlineStr"/>
+      <c r="AY363" t="inlineStr"/>
+      <c r="AZ363" t="inlineStr"/>
+      <c r="BA363" t="inlineStr"/>
+      <c r="BB363" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="BC363" t="n">
+        <v>26.125</v>
+      </c>
+      <c r="BD363" t="n">
+        <v>180.875</v>
+      </c>
+      <c r="BE363" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="BF363" t="n">
+        <v>8875</v>
+      </c>
+      <c r="BG363" t="inlineStr"/>
+      <c r="BH363" t="inlineStr"/>
+      <c r="BI363" t="inlineStr"/>
+      <c r="BJ363" t="inlineStr"/>
+      <c r="BK363" t="n">
+        <v>26.57142857142857</v>
+      </c>
+      <c r="BL363" t="n">
+        <v>179.7142857142857</v>
+      </c>
+      <c r="BM363" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BN363" t="n">
+        <v>7357.142857142857</v>
+      </c>
+      <c r="BO363" t="n">
+        <v>23.05263157894737</v>
+      </c>
+      <c r="BP363" t="n">
+        <v>177.4736842105263</v>
+      </c>
+      <c r="BQ363" t="n">
+        <v>68.21052631578948</v>
+      </c>
+      <c r="BR363" t="inlineStr"/>
+      <c r="BS363" t="inlineStr"/>
+      <c r="BT363" t="inlineStr"/>
+      <c r="BU363" t="inlineStr"/>
+      <c r="BV363" t="inlineStr"/>
+      <c r="BW363" t="inlineStr"/>
+      <c r="BX363" t="inlineStr"/>
+      <c r="BY363" t="inlineStr"/>
+      <c r="BZ363" t="inlineStr"/>
+      <c r="CA363" t="inlineStr"/>
+      <c r="CB363" t="inlineStr"/>
+      <c r="CC363" t="inlineStr"/>
+      <c r="CD363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>bB6CjuQr</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="n">
+        <v>45563.46875</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de la fuente ramos o 
+  esp </t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo mirandilla
+  cadiz </t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>20776</v>
+      </c>
+      <c r="F364" t="n">
+        <v>15315</v>
+      </c>
+      <c r="G364" t="n">
+        <v>1</v>
+      </c>
+      <c r="H364" t="n">
+        <v>2</v>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr"/>
+      <c r="L364" t="inlineStr"/>
+      <c r="M364" t="n">
+        <v>53</v>
+      </c>
+      <c r="N364" t="n">
+        <v>47</v>
+      </c>
+      <c r="O364" t="n">
+        <v>23</v>
+      </c>
+      <c r="P364" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>7</v>
+      </c>
+      <c r="R364" t="n">
+        <v>6</v>
+      </c>
+      <c r="S364" t="n">
+        <v>9</v>
+      </c>
+      <c r="T364" t="n">
+        <v>5</v>
+      </c>
+      <c r="U364" t="n">
+        <v>7</v>
+      </c>
+      <c r="V364" t="n">
+        <v>4</v>
+      </c>
+      <c r="W364" t="n">
+        <v>18</v>
+      </c>
+      <c r="X364" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y364" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z364" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA364" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB364" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC364" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD364" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE364" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF364" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG364" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH364" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI364" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ364" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK364" t="inlineStr"/>
+      <c r="AL364" t="inlineStr"/>
+      <c r="AM364" t="inlineStr"/>
+      <c r="AN364" t="inlineStr"/>
+      <c r="AO364" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="AP364" t="inlineStr">
+        <is>
+          <t>hh4xt2Df</t>
+        </is>
+      </c>
+      <c r="AQ364" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR364" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS364" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT364" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU364" t="inlineStr"/>
+      <c r="AV364" t="inlineStr"/>
+      <c r="AW364" t="inlineStr"/>
+      <c r="AX364" t="inlineStr"/>
+      <c r="AY364" t="inlineStr"/>
+      <c r="AZ364" t="inlineStr"/>
+      <c r="BA364" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="BB364" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="BC364" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD364" t="n">
+        <v>178.375</v>
+      </c>
+      <c r="BE364" t="n">
+        <v>72.875</v>
+      </c>
+      <c r="BF364" t="n">
+        <v>18750</v>
+      </c>
+      <c r="BG364" t="n">
+        <v>30.375</v>
+      </c>
+      <c r="BH364" t="n">
+        <v>182.625</v>
+      </c>
+      <c r="BI364" t="n">
+        <v>69</v>
+      </c>
+      <c r="BJ364" t="n">
+        <v>6000</v>
+      </c>
+      <c r="BK364" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BL364" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="BM364" t="n">
+        <v>70.625</v>
+      </c>
+      <c r="BN364" t="n">
+        <v>14187.5</v>
+      </c>
+      <c r="BO364" t="n">
+        <v>28.68421052631579</v>
+      </c>
+      <c r="BP364" t="n">
+        <v>182.1052631578947</v>
+      </c>
+      <c r="BQ364" t="n">
+        <v>66.84210526315789</v>
+      </c>
+      <c r="BR364" t="n">
+        <v>3473.684210526316</v>
+      </c>
+      <c r="BS364" t="inlineStr"/>
+      <c r="BT364" t="inlineStr"/>
+      <c r="BU364" t="inlineStr"/>
+      <c r="BV364" t="inlineStr"/>
+      <c r="BW364" t="inlineStr"/>
+      <c r="BX364" t="inlineStr"/>
+      <c r="BY364" t="inlineStr"/>
+      <c r="BZ364" t="inlineStr"/>
+      <c r="CA364" t="inlineStr"/>
+      <c r="CB364" t="inlineStr"/>
+      <c r="CC364" t="inlineStr"/>
+      <c r="CD364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>CnAE6iGt</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="n">
+        <v>45563.46875</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrera r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de anduva
+  miranda de ebro </t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>5759</v>
+      </c>
+      <c r="F365" t="n">
+        <v>3193</v>
+      </c>
+      <c r="G365" t="n">
+        <v>1</v>
+      </c>
+      <c r="H365" t="n">
+        <v>0</v>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr"/>
+      <c r="L365" t="inlineStr"/>
+      <c r="M365" t="n">
+        <v>44</v>
+      </c>
+      <c r="N365" t="n">
+        <v>56</v>
+      </c>
+      <c r="O365" t="n">
+        <v>16</v>
+      </c>
+      <c r="P365" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>2</v>
+      </c>
+      <c r="R365" t="n">
+        <v>1</v>
+      </c>
+      <c r="S365" t="n">
+        <v>7</v>
+      </c>
+      <c r="T365" t="n">
+        <v>3</v>
+      </c>
+      <c r="U365" t="n">
+        <v>7</v>
+      </c>
+      <c r="V365" t="n">
+        <v>2</v>
+      </c>
+      <c r="W365" t="n">
+        <v>15</v>
+      </c>
+      <c r="X365" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y365" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z365" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA365" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB365" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC365" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD365" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE365" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF365" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG365" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH365" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI365" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ365" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK365" t="inlineStr"/>
+      <c r="AL365" t="inlineStr"/>
+      <c r="AM365" t="inlineStr"/>
+      <c r="AN365" t="inlineStr"/>
+      <c r="AO365" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="AP365" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="AQ365" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR365" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS365" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT365" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU365" t="inlineStr"/>
+      <c r="AV365" t="inlineStr"/>
+      <c r="AW365" t="inlineStr"/>
+      <c r="AX365" t="inlineStr"/>
+      <c r="AY365" t="inlineStr"/>
+      <c r="AZ365" t="inlineStr"/>
+      <c r="BA365" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="BB365" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="BC365" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="BD365" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="BE365" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="BF365" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BG365" t="n">
+        <v>26.625</v>
+      </c>
+      <c r="BH365" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="BI365" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="BJ365" t="n">
+        <v>4500</v>
+      </c>
+      <c r="BK365" t="n">
+        <v>21.5625</v>
+      </c>
+      <c r="BL365" t="n">
+        <v>176.4375</v>
+      </c>
+      <c r="BM365" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="BN365" t="n">
+        <v>2437.5</v>
+      </c>
+      <c r="BO365" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="BP365" t="n">
+        <v>179.7272727272727</v>
+      </c>
+      <c r="BQ365" t="n">
+        <v>65.45454545454545</v>
+      </c>
+      <c r="BR365" t="n">
+        <v>3090.909090909091</v>
+      </c>
+      <c r="BS365" t="inlineStr"/>
+      <c r="BT365" t="inlineStr"/>
+      <c r="BU365" t="inlineStr"/>
+      <c r="BV365" t="inlineStr"/>
+      <c r="BW365" t="inlineStr"/>
+      <c r="BX365" t="inlineStr"/>
+      <c r="BY365" t="inlineStr"/>
+      <c r="BZ365" t="inlineStr"/>
+      <c r="CA365" t="inlineStr"/>
+      <c r="CB365" t="inlineStr"/>
+      <c r="CC365" t="inlineStr"/>
+      <c r="CD365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>6DRXcNX8</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="n">
+        <v>45562.64583333334</v>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guzman mansilla j  l 
+  esp </t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio carlos belmonte
+  albacete </t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>17524</v>
+      </c>
+      <c r="F366" t="n">
+        <v>11509</v>
+      </c>
+      <c r="G366" t="n">
+        <v>2</v>
+      </c>
+      <c r="H366" t="n">
+        <v>5</v>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr"/>
+      <c r="L366" t="inlineStr"/>
+      <c r="M366" t="n">
+        <v>57</v>
+      </c>
+      <c r="N366" t="n">
+        <v>43</v>
+      </c>
+      <c r="O366" t="n">
+        <v>20</v>
+      </c>
+      <c r="P366" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q366" t="n">
+        <v>7</v>
+      </c>
+      <c r="R366" t="n">
+        <v>7</v>
+      </c>
+      <c r="S366" t="n">
+        <v>9</v>
+      </c>
+      <c r="T366" t="n">
+        <v>4</v>
+      </c>
+      <c r="U366" t="n">
+        <v>4</v>
+      </c>
+      <c r="V366" t="n">
+        <v>3</v>
+      </c>
+      <c r="W366" t="n">
+        <v>11</v>
+      </c>
+      <c r="X366" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y366" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z366" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA366" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB366" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC366" t="n">
+        <v>31</v>
+      </c>
+      <c r="AD366" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE366" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF366" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG366" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH366" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI366" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ366" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK366" t="inlineStr"/>
+      <c r="AL366" t="inlineStr"/>
+      <c r="AM366" t="inlineStr"/>
+      <c r="AN366" t="inlineStr"/>
+      <c r="AO366" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="AP366" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="AQ366" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR366" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS366" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT366" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU366" t="inlineStr"/>
+      <c r="AV366" t="inlineStr"/>
+      <c r="AW366" t="inlineStr"/>
+      <c r="AX366" t="inlineStr"/>
+      <c r="AY366" t="inlineStr"/>
+      <c r="AZ366" t="inlineStr"/>
+      <c r="BA366" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="BB366" t="inlineStr"/>
+      <c r="BC366" t="inlineStr"/>
+      <c r="BD366" t="inlineStr"/>
+      <c r="BE366" t="inlineStr"/>
+      <c r="BF366" t="inlineStr"/>
+      <c r="BG366" t="inlineStr"/>
+      <c r="BH366" t="inlineStr"/>
+      <c r="BI366" t="inlineStr"/>
+      <c r="BJ366" t="inlineStr"/>
+      <c r="BK366" t="n">
+        <v>24.92307692307692</v>
+      </c>
+      <c r="BL366" t="n">
+        <v>180.6923076923077</v>
+      </c>
+      <c r="BM366" t="n">
+        <v>66.69230769230769</v>
+      </c>
+      <c r="BN366" t="n">
+        <v>5230.76923076923</v>
+      </c>
+      <c r="BO366" t="n">
+        <v>22</v>
+      </c>
+      <c r="BP366" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="BQ366" t="n">
+        <v>67.875</v>
+      </c>
+      <c r="BR366" t="n">
+        <v>11375</v>
+      </c>
+      <c r="BS366" t="inlineStr"/>
+      <c r="BT366" t="inlineStr"/>
+      <c r="BU366" t="inlineStr"/>
+      <c r="BV366" t="inlineStr"/>
+      <c r="BW366" t="inlineStr"/>
+      <c r="BX366" t="inlineStr"/>
+      <c r="BY366" t="inlineStr"/>
+      <c r="BZ366" t="inlineStr"/>
+      <c r="CA366" t="inlineStr"/>
+      <c r="CB366" t="inlineStr"/>
+      <c r="CC366" t="inlineStr"/>
+      <c r="CD366" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD366"/>
+  <dimension ref="A1:CD375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85252,6 +85252,1984 @@
       <c r="CC366" t="inlineStr"/>
       <c r="CD366" t="inlineStr"/>
     </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>n37VJZT0</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="n">
+        <v>45564.66666666666</v>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>70460</v>
+      </c>
+      <c r="F367" t="n">
+        <v>70112</v>
+      </c>
+      <c r="G367" t="n">
+        <v>1</v>
+      </c>
+      <c r="H367" t="n">
+        <v>1</v>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="K367" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L367" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M367" t="n">
+        <v>51</v>
+      </c>
+      <c r="N367" t="n">
+        <v>49</v>
+      </c>
+      <c r="O367" t="n">
+        <v>12</v>
+      </c>
+      <c r="P367" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q367" t="n">
+        <v>4</v>
+      </c>
+      <c r="R367" t="n">
+        <v>4</v>
+      </c>
+      <c r="S367" t="n">
+        <v>2</v>
+      </c>
+      <c r="T367" t="n">
+        <v>5</v>
+      </c>
+      <c r="U367" t="n">
+        <v>6</v>
+      </c>
+      <c r="V367" t="n">
+        <v>3</v>
+      </c>
+      <c r="W367" t="n">
+        <v>11</v>
+      </c>
+      <c r="X367" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y367" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z367" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA367" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB367" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC367" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD367" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE367" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF367" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG367" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH367" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI367" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ367" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK367" t="inlineStr"/>
+      <c r="AL367" t="inlineStr"/>
+      <c r="AM367" t="inlineStr"/>
+      <c r="AN367" t="inlineStr"/>
+      <c r="AO367" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="AP367" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="AQ367" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR367" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS367" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT367" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU367" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV367" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW367" t="inlineStr"/>
+      <c r="AX367" t="inlineStr"/>
+      <c r="AY367" t="inlineStr"/>
+      <c r="AZ367" t="inlineStr"/>
+      <c r="BA367" t="inlineStr"/>
+      <c r="BB367" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="BC367" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="BD367" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="BE367" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="BF367" t="n">
+        <v>82000</v>
+      </c>
+      <c r="BG367" t="n">
+        <v>26.63636363636364</v>
+      </c>
+      <c r="BH367" t="n">
+        <v>182.3636363636364</v>
+      </c>
+      <c r="BI367" t="n">
+        <v>86.09090909090909</v>
+      </c>
+      <c r="BJ367" t="n">
+        <v>215000</v>
+      </c>
+      <c r="BK367" t="n">
+        <v>25.69565217391304</v>
+      </c>
+      <c r="BL367" t="n">
+        <v>177.0434782608696</v>
+      </c>
+      <c r="BM367" t="n">
+        <v>79</v>
+      </c>
+      <c r="BN367" t="n">
+        <v>59086.95652173913</v>
+      </c>
+      <c r="BO367" t="n">
+        <v>23.18181818181818</v>
+      </c>
+      <c r="BP367" t="n">
+        <v>179.3636363636364</v>
+      </c>
+      <c r="BQ367" t="n">
+        <v>74.63636363636364</v>
+      </c>
+      <c r="BR367" t="n">
+        <v>95181.81818181818</v>
+      </c>
+      <c r="BS367" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BT367" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="BU367" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="BV367" t="n">
+        <v>41500</v>
+      </c>
+      <c r="BW367" t="n">
+        <v>2</v>
+      </c>
+      <c r="BX367" t="n">
+        <v>155</v>
+      </c>
+      <c r="BY367" t="n">
+        <v>26</v>
+      </c>
+      <c r="BZ367" t="n">
+        <v>177.75</v>
+      </c>
+      <c r="CA367" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="CB367" t="n">
+        <v>178750</v>
+      </c>
+      <c r="CC367" t="n">
+        <v>4</v>
+      </c>
+      <c r="CD367" t="n">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>4rQsoH7m</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="n">
+        <v>45564.5625</v>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F368" t="n">
+        <v>53065</v>
+      </c>
+      <c r="G368" t="n">
+        <v>1</v>
+      </c>
+      <c r="H368" t="n">
+        <v>0</v>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="K368" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L368" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M368" t="n">
+        <v>53</v>
+      </c>
+      <c r="N368" t="n">
+        <v>47</v>
+      </c>
+      <c r="O368" t="n">
+        <v>20</v>
+      </c>
+      <c r="P368" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q368" t="n">
+        <v>12</v>
+      </c>
+      <c r="R368" t="n">
+        <v>1</v>
+      </c>
+      <c r="S368" t="n">
+        <v>5</v>
+      </c>
+      <c r="T368" t="n">
+        <v>3</v>
+      </c>
+      <c r="U368" t="n">
+        <v>3</v>
+      </c>
+      <c r="V368" t="n">
+        <v>4</v>
+      </c>
+      <c r="W368" t="n">
+        <v>23</v>
+      </c>
+      <c r="X368" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y368" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z368" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA368" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB368" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC368" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD368" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE368" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF368" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG368" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH368" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI368" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ368" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK368" t="inlineStr"/>
+      <c r="AL368" t="inlineStr"/>
+      <c r="AM368" t="inlineStr"/>
+      <c r="AN368" t="inlineStr"/>
+      <c r="AO368" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="AP368" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="AQ368" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR368" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS368" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT368" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU368" t="inlineStr"/>
+      <c r="AV368" t="inlineStr"/>
+      <c r="AW368" t="inlineStr"/>
+      <c r="AX368" t="inlineStr"/>
+      <c r="AY368" t="inlineStr"/>
+      <c r="AZ368" t="inlineStr"/>
+      <c r="BA368" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="BB368" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="BC368" t="n">
+        <v>26.125</v>
+      </c>
+      <c r="BD368" t="n">
+        <v>182.625</v>
+      </c>
+      <c r="BE368" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="BF368" t="n">
+        <v>26625</v>
+      </c>
+      <c r="BG368" t="inlineStr"/>
+      <c r="BH368" t="inlineStr"/>
+      <c r="BI368" t="inlineStr"/>
+      <c r="BJ368" t="inlineStr"/>
+      <c r="BK368" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="BL368" t="n">
+        <v>180.9</v>
+      </c>
+      <c r="BM368" t="n">
+        <v>73</v>
+      </c>
+      <c r="BN368" t="inlineStr"/>
+      <c r="BO368" t="n">
+        <v>25</v>
+      </c>
+      <c r="BP368" t="n">
+        <v>181.0526315789474</v>
+      </c>
+      <c r="BQ368" t="n">
+        <v>71.94736842105263</v>
+      </c>
+      <c r="BR368" t="n">
+        <v>16578.94736842105</v>
+      </c>
+      <c r="BS368" t="n">
+        <v>31</v>
+      </c>
+      <c r="BT368" t="n">
+        <v>180</v>
+      </c>
+      <c r="BU368" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="BV368" t="n">
+        <v>27000</v>
+      </c>
+      <c r="BW368" t="n">
+        <v>4</v>
+      </c>
+      <c r="BX368" t="n">
+        <v>317</v>
+      </c>
+      <c r="BY368" t="n">
+        <v>29</v>
+      </c>
+      <c r="BZ368" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="CA368" t="n">
+        <v>73</v>
+      </c>
+      <c r="CB368" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CC368" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD368" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="n">
+        <v>45564.46875</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F369" t="n">
+        <v>48288</v>
+      </c>
+      <c r="G369" t="n">
+        <v>1</v>
+      </c>
+      <c r="H369" t="n">
+        <v>1</v>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="K369" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L369" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M369" t="n">
+        <v>39</v>
+      </c>
+      <c r="N369" t="n">
+        <v>61</v>
+      </c>
+      <c r="O369" t="n">
+        <v>13</v>
+      </c>
+      <c r="P369" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q369" t="n">
+        <v>5</v>
+      </c>
+      <c r="R369" t="n">
+        <v>3</v>
+      </c>
+      <c r="S369" t="n">
+        <v>6</v>
+      </c>
+      <c r="T369" t="n">
+        <v>7</v>
+      </c>
+      <c r="U369" t="n">
+        <v>2</v>
+      </c>
+      <c r="V369" t="n">
+        <v>3</v>
+      </c>
+      <c r="W369" t="n">
+        <v>10</v>
+      </c>
+      <c r="X369" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y369" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z369" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA369" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB369" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC369" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD369" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE369" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF369" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG369" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH369" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI369" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ369" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK369" t="inlineStr"/>
+      <c r="AL369" t="inlineStr"/>
+      <c r="AM369" t="inlineStr"/>
+      <c r="AN369" t="inlineStr"/>
+      <c r="AO369" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="AP369" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="AQ369" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR369" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS369" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT369" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU369" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV369" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW369" t="inlineStr"/>
+      <c r="AX369" t="inlineStr"/>
+      <c r="AY369" t="inlineStr"/>
+      <c r="AZ369" t="inlineStr"/>
+      <c r="BA369" t="inlineStr"/>
+      <c r="BB369" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="BC369" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD369" t="n">
+        <v>183.5555555555555</v>
+      </c>
+      <c r="BE369" t="n">
+        <v>76.22222222222223</v>
+      </c>
+      <c r="BF369" t="n">
+        <v>22888.88888888889</v>
+      </c>
+      <c r="BG369" t="n">
+        <v>24.625</v>
+      </c>
+      <c r="BH369" t="n">
+        <v>185.75</v>
+      </c>
+      <c r="BI369" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="BJ369" t="n">
+        <v>20875</v>
+      </c>
+      <c r="BK369" t="n">
+        <v>25.52631578947368</v>
+      </c>
+      <c r="BL369" t="n">
+        <v>182.7894736842105</v>
+      </c>
+      <c r="BM369" t="n">
+        <v>75.42105263157895</v>
+      </c>
+      <c r="BN369" t="n">
+        <v>23736.84210526316</v>
+      </c>
+      <c r="BO369" t="n">
+        <v>24.47058823529412</v>
+      </c>
+      <c r="BP369" t="n">
+        <v>178.4705882352941</v>
+      </c>
+      <c r="BQ369" t="n">
+        <v>73.05882352941177</v>
+      </c>
+      <c r="BR369" t="n">
+        <v>15941.17647058824</v>
+      </c>
+      <c r="BS369" t="n">
+        <v>26</v>
+      </c>
+      <c r="BT369" t="n">
+        <v>185</v>
+      </c>
+      <c r="BU369" t="n">
+        <v>80</v>
+      </c>
+      <c r="BV369" t="n">
+        <v>30750</v>
+      </c>
+      <c r="BW369" t="n">
+        <v>4</v>
+      </c>
+      <c r="BX369" t="n">
+        <v>320</v>
+      </c>
+      <c r="BY369" t="n">
+        <v>26</v>
+      </c>
+      <c r="BZ369" t="n">
+        <v>184</v>
+      </c>
+      <c r="CA369" t="n">
+        <v>77.75</v>
+      </c>
+      <c r="CB369" t="n">
+        <v>45750</v>
+      </c>
+      <c r="CC369" t="n">
+        <v>4</v>
+      </c>
+      <c r="CD369" t="n">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>h0AwIDbD</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="n">
+        <v>45564.375</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F370" t="n">
+        <v>21347</v>
+      </c>
+      <c r="G370" t="n">
+        <v>1</v>
+      </c>
+      <c r="H370" t="n">
+        <v>1</v>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="K370" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L370" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M370" t="n">
+        <v>48</v>
+      </c>
+      <c r="N370" t="n">
+        <v>52</v>
+      </c>
+      <c r="O370" t="n">
+        <v>12</v>
+      </c>
+      <c r="P370" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q370" t="n">
+        <v>2</v>
+      </c>
+      <c r="R370" t="n">
+        <v>4</v>
+      </c>
+      <c r="S370" t="n">
+        <v>5</v>
+      </c>
+      <c r="T370" t="n">
+        <v>2</v>
+      </c>
+      <c r="U370" t="n">
+        <v>5</v>
+      </c>
+      <c r="V370" t="n">
+        <v>3</v>
+      </c>
+      <c r="W370" t="n">
+        <v>18</v>
+      </c>
+      <c r="X370" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y370" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z370" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA370" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB370" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC370" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD370" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE370" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF370" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG370" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH370" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI370" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ370" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK370" t="inlineStr"/>
+      <c r="AL370" t="inlineStr"/>
+      <c r="AM370" t="inlineStr"/>
+      <c r="AN370" t="inlineStr"/>
+      <c r="AO370" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="AP370" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="AQ370" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR370" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS370" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT370" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU370" t="inlineStr"/>
+      <c r="AV370" t="inlineStr"/>
+      <c r="AW370" t="inlineStr"/>
+      <c r="AX370" t="inlineStr"/>
+      <c r="AY370" t="inlineStr"/>
+      <c r="AZ370" t="inlineStr"/>
+      <c r="BA370" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="BB370" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="BC370" t="inlineStr"/>
+      <c r="BD370" t="inlineStr"/>
+      <c r="BE370" t="inlineStr"/>
+      <c r="BF370" t="inlineStr"/>
+      <c r="BG370" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="BH370" t="n">
+        <v>182.375</v>
+      </c>
+      <c r="BI370" t="n">
+        <v>78.875</v>
+      </c>
+      <c r="BJ370" t="n">
+        <v>38000</v>
+      </c>
+      <c r="BK370" t="n">
+        <v>26.6875</v>
+      </c>
+      <c r="BL370" t="n">
+        <v>179.125</v>
+      </c>
+      <c r="BM370" t="n">
+        <v>74.875</v>
+      </c>
+      <c r="BN370" t="n">
+        <v>21437.5</v>
+      </c>
+      <c r="BO370" t="n">
+        <v>24.68181818181818</v>
+      </c>
+      <c r="BP370" t="n">
+        <v>182.1363636363636</v>
+      </c>
+      <c r="BQ370" t="n">
+        <v>74.45454545454545</v>
+      </c>
+      <c r="BR370" t="n">
+        <v>39363.63636363636</v>
+      </c>
+      <c r="BS370" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="BT370" t="n">
+        <v>177.6666666666667</v>
+      </c>
+      <c r="BU370" t="n">
+        <v>74.33333333333333</v>
+      </c>
+      <c r="BV370" t="n">
+        <v>19666.66666666667</v>
+      </c>
+      <c r="BW370" t="n">
+        <v>3</v>
+      </c>
+      <c r="BX370" t="n">
+        <v>223</v>
+      </c>
+      <c r="BY370" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BZ370" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="CA370" t="n">
+        <v>63</v>
+      </c>
+      <c r="CB370" t="n">
+        <v>3500</v>
+      </c>
+      <c r="CC370" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD370" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>noISncP7</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="n">
+        <v>45564.5625</v>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cid camacho g 
+  esp </t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo arcangel
+  cordoba </t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>21822</v>
+      </c>
+      <c r="F371" t="n">
+        <v>16130</v>
+      </c>
+      <c r="G371" t="n">
+        <v>3</v>
+      </c>
+      <c r="H371" t="n">
+        <v>1</v>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr"/>
+      <c r="L371" t="inlineStr"/>
+      <c r="M371" t="n">
+        <v>60</v>
+      </c>
+      <c r="N371" t="n">
+        <v>40</v>
+      </c>
+      <c r="O371" t="n">
+        <v>23</v>
+      </c>
+      <c r="P371" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q371" t="n">
+        <v>5</v>
+      </c>
+      <c r="R371" t="n">
+        <v>3</v>
+      </c>
+      <c r="S371" t="n">
+        <v>8</v>
+      </c>
+      <c r="T371" t="n">
+        <v>4</v>
+      </c>
+      <c r="U371" t="n">
+        <v>10</v>
+      </c>
+      <c r="V371" t="n">
+        <v>1</v>
+      </c>
+      <c r="W371" t="n">
+        <v>22</v>
+      </c>
+      <c r="X371" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y371" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z371" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA371" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB371" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC371" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD371" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE371" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF371" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG371" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH371" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI371" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ371" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK371" t="inlineStr"/>
+      <c r="AL371" t="inlineStr"/>
+      <c r="AM371" t="inlineStr"/>
+      <c r="AN371" t="inlineStr"/>
+      <c r="AO371" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="AP371" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="AQ371" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR371" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS371" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT371" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU371" t="inlineStr"/>
+      <c r="AV371" t="inlineStr"/>
+      <c r="AW371" t="inlineStr"/>
+      <c r="AX371" t="inlineStr"/>
+      <c r="AY371" t="inlineStr"/>
+      <c r="AZ371" t="inlineStr"/>
+      <c r="BA371" t="inlineStr"/>
+      <c r="BB371" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="BC371" t="inlineStr"/>
+      <c r="BD371" t="inlineStr"/>
+      <c r="BE371" t="inlineStr"/>
+      <c r="BF371" t="inlineStr"/>
+      <c r="BG371" t="n">
+        <v>28.625</v>
+      </c>
+      <c r="BH371" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="BI371" t="n">
+        <v>68</v>
+      </c>
+      <c r="BJ371" t="n">
+        <v>5500</v>
+      </c>
+      <c r="BK371" t="inlineStr"/>
+      <c r="BL371" t="inlineStr"/>
+      <c r="BM371" t="inlineStr"/>
+      <c r="BN371" t="inlineStr"/>
+      <c r="BO371" t="n">
+        <v>27.06666666666667</v>
+      </c>
+      <c r="BP371" t="n">
+        <v>178.3333333333333</v>
+      </c>
+      <c r="BQ371" t="n">
+        <v>68.26666666666667</v>
+      </c>
+      <c r="BR371" t="n">
+        <v>7733.333333333333</v>
+      </c>
+      <c r="BS371" t="inlineStr"/>
+      <c r="BT371" t="inlineStr"/>
+      <c r="BU371" t="inlineStr"/>
+      <c r="BV371" t="inlineStr"/>
+      <c r="BW371" t="inlineStr"/>
+      <c r="BX371" t="inlineStr"/>
+      <c r="BY371" t="inlineStr"/>
+      <c r="BZ371" t="inlineStr"/>
+      <c r="CA371" t="inlineStr"/>
+      <c r="CB371" t="inlineStr"/>
+      <c r="CC371" t="inlineStr"/>
+      <c r="CD371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>S4w21dv1</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="n">
+        <v>45564.5625</v>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez lopez r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo carlos tartiere
+  oviedo </t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>30500</v>
+      </c>
+      <c r="F372" t="n">
+        <v>19281</v>
+      </c>
+      <c r="G372" t="n">
+        <v>1</v>
+      </c>
+      <c r="H372" t="n">
+        <v>0</v>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr"/>
+      <c r="L372" t="inlineStr"/>
+      <c r="M372" t="n">
+        <v>43</v>
+      </c>
+      <c r="N372" t="n">
+        <v>57</v>
+      </c>
+      <c r="O372" t="n">
+        <v>19</v>
+      </c>
+      <c r="P372" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q372" t="n">
+        <v>5</v>
+      </c>
+      <c r="R372" t="n">
+        <v>2</v>
+      </c>
+      <c r="S372" t="n">
+        <v>8</v>
+      </c>
+      <c r="T372" t="n">
+        <v>3</v>
+      </c>
+      <c r="U372" t="n">
+        <v>6</v>
+      </c>
+      <c r="V372" t="n">
+        <v>3</v>
+      </c>
+      <c r="W372" t="n">
+        <v>15</v>
+      </c>
+      <c r="X372" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y372" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z372" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA372" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB372" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC372" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD372" t="n">
+        <v>33</v>
+      </c>
+      <c r="AE372" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF372" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG372" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH372" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI372" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ372" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK372" t="inlineStr"/>
+      <c r="AL372" t="inlineStr"/>
+      <c r="AM372" t="inlineStr"/>
+      <c r="AN372" t="inlineStr"/>
+      <c r="AO372" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="AP372" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="AQ372" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR372" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS372" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT372" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU372" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV372" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW372" t="inlineStr"/>
+      <c r="AX372" t="inlineStr"/>
+      <c r="AY372" t="inlineStr"/>
+      <c r="AZ372" t="inlineStr"/>
+      <c r="BA372" t="inlineStr"/>
+      <c r="BB372" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="BC372" t="inlineStr"/>
+      <c r="BD372" t="inlineStr"/>
+      <c r="BE372" t="inlineStr"/>
+      <c r="BF372" t="inlineStr"/>
+      <c r="BG372" t="inlineStr"/>
+      <c r="BH372" t="inlineStr"/>
+      <c r="BI372" t="inlineStr"/>
+      <c r="BJ372" t="inlineStr"/>
+      <c r="BK372" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="BL372" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="BM372" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="BN372" t="n">
+        <v>5400</v>
+      </c>
+      <c r="BO372" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BP372" t="n">
+        <v>180.9</v>
+      </c>
+      <c r="BQ372" t="n">
+        <v>67.15000000000001</v>
+      </c>
+      <c r="BR372" t="inlineStr"/>
+      <c r="BS372" t="inlineStr"/>
+      <c r="BT372" t="inlineStr"/>
+      <c r="BU372" t="inlineStr"/>
+      <c r="BV372" t="inlineStr"/>
+      <c r="BW372" t="inlineStr"/>
+      <c r="BX372" t="inlineStr"/>
+      <c r="BY372" t="inlineStr"/>
+      <c r="BZ372" t="inlineStr"/>
+      <c r="CA372" t="inlineStr"/>
+      <c r="CB372" t="inlineStr"/>
+      <c r="CC372" t="inlineStr"/>
+      <c r="CD372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2uLtd12L</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="n">
+        <v>45564.46875</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reig s  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el plantio
+  burgos </t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>12194</v>
+      </c>
+      <c r="F373" t="n">
+        <v>9890</v>
+      </c>
+      <c r="G373" t="n">
+        <v>2</v>
+      </c>
+      <c r="H373" t="n">
+        <v>2</v>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr"/>
+      <c r="L373" t="inlineStr"/>
+      <c r="M373" t="n">
+        <v>41</v>
+      </c>
+      <c r="N373" t="n">
+        <v>59</v>
+      </c>
+      <c r="O373" t="n">
+        <v>5</v>
+      </c>
+      <c r="P373" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q373" t="n">
+        <v>2</v>
+      </c>
+      <c r="R373" t="n">
+        <v>4</v>
+      </c>
+      <c r="S373" t="n">
+        <v>2</v>
+      </c>
+      <c r="T373" t="n">
+        <v>3</v>
+      </c>
+      <c r="U373" t="n">
+        <v>1</v>
+      </c>
+      <c r="V373" t="n">
+        <v>2</v>
+      </c>
+      <c r="W373" t="n">
+        <v>13</v>
+      </c>
+      <c r="X373" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y373" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z373" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA373" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB373" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC373" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD373" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE373" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF373" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG373" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH373" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI373" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ373" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK373" t="inlineStr"/>
+      <c r="AL373" t="inlineStr"/>
+      <c r="AM373" t="inlineStr"/>
+      <c r="AN373" t="inlineStr"/>
+      <c r="AO373" t="inlineStr">
+        <is>
+          <t>l6JQtDqc</t>
+        </is>
+      </c>
+      <c r="AP373" t="inlineStr">
+        <is>
+          <t>K0UZov8F</t>
+        </is>
+      </c>
+      <c r="AQ373" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR373" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS373" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT373" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU373" t="inlineStr"/>
+      <c r="AV373" t="inlineStr"/>
+      <c r="AW373" t="inlineStr"/>
+      <c r="AX373" t="inlineStr"/>
+      <c r="AY373" t="inlineStr"/>
+      <c r="AZ373" t="inlineStr"/>
+      <c r="BA373" t="inlineStr"/>
+      <c r="BB373" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="BC373" t="inlineStr"/>
+      <c r="BD373" t="inlineStr"/>
+      <c r="BE373" t="inlineStr"/>
+      <c r="BF373" t="inlineStr"/>
+      <c r="BG373" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="BH373" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="BI373" t="n">
+        <v>71</v>
+      </c>
+      <c r="BJ373" t="n">
+        <v>16444.44444444445</v>
+      </c>
+      <c r="BK373" t="n">
+        <v>24</v>
+      </c>
+      <c r="BL373" t="n">
+        <v>181.125</v>
+      </c>
+      <c r="BM373" t="n">
+        <v>69</v>
+      </c>
+      <c r="BN373" t="n">
+        <v>15750</v>
+      </c>
+      <c r="BO373" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="BP373" t="n">
+        <v>180.3</v>
+      </c>
+      <c r="BQ373" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="BR373" t="n">
+        <v>15350</v>
+      </c>
+      <c r="BS373" t="inlineStr"/>
+      <c r="BT373" t="inlineStr"/>
+      <c r="BU373" t="inlineStr"/>
+      <c r="BV373" t="inlineStr"/>
+      <c r="BW373" t="inlineStr"/>
+      <c r="BX373" t="inlineStr"/>
+      <c r="BY373" t="inlineStr"/>
+      <c r="BZ373" t="inlineStr"/>
+      <c r="CA373" t="inlineStr"/>
+      <c r="CB373" t="inlineStr"/>
+      <c r="CC373" t="inlineStr"/>
+      <c r="CD373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>fw0LlJfe</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="n">
+        <v>45564.46875</v>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mallo e 
+  esp </t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de castalia
+  castellon de la plana </t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>15500</v>
+      </c>
+      <c r="F374" t="n">
+        <v>11439</v>
+      </c>
+      <c r="G374" t="n">
+        <v>2</v>
+      </c>
+      <c r="H374" t="n">
+        <v>1</v>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr"/>
+      <c r="L374" t="inlineStr"/>
+      <c r="M374" t="n">
+        <v>49</v>
+      </c>
+      <c r="N374" t="n">
+        <v>51</v>
+      </c>
+      <c r="O374" t="n">
+        <v>19</v>
+      </c>
+      <c r="P374" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q374" t="n">
+        <v>8</v>
+      </c>
+      <c r="R374" t="n">
+        <v>6</v>
+      </c>
+      <c r="S374" t="n">
+        <v>4</v>
+      </c>
+      <c r="T374" t="n">
+        <v>5</v>
+      </c>
+      <c r="U374" t="n">
+        <v>7</v>
+      </c>
+      <c r="V374" t="n">
+        <v>5</v>
+      </c>
+      <c r="W374" t="n">
+        <v>19</v>
+      </c>
+      <c r="X374" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y374" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z374" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA374" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB374" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC374" t="n">
+        <v>36</v>
+      </c>
+      <c r="AD374" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE374" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF374" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG374" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH374" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI374" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ374" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK374" t="inlineStr"/>
+      <c r="AL374" t="inlineStr"/>
+      <c r="AM374" t="inlineStr"/>
+      <c r="AN374" t="inlineStr"/>
+      <c r="AO374" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="AP374" t="inlineStr">
+        <is>
+          <t>CYND5rZG</t>
+        </is>
+      </c>
+      <c r="AQ374" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR374" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS374" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT374" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU374" t="inlineStr"/>
+      <c r="AV374" t="inlineStr"/>
+      <c r="AW374" t="inlineStr"/>
+      <c r="AX374" t="inlineStr"/>
+      <c r="AY374" t="inlineStr"/>
+      <c r="AZ374" t="inlineStr"/>
+      <c r="BA374" t="inlineStr"/>
+      <c r="BB374" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="BC374" t="inlineStr"/>
+      <c r="BD374" t="inlineStr"/>
+      <c r="BE374" t="inlineStr"/>
+      <c r="BF374" t="inlineStr"/>
+      <c r="BG374" t="inlineStr"/>
+      <c r="BH374" t="inlineStr"/>
+      <c r="BI374" t="inlineStr"/>
+      <c r="BJ374" t="inlineStr"/>
+      <c r="BK374" t="inlineStr"/>
+      <c r="BL374" t="inlineStr"/>
+      <c r="BM374" t="inlineStr"/>
+      <c r="BN374" t="inlineStr"/>
+      <c r="BO374" t="n">
+        <v>28.16666666666667</v>
+      </c>
+      <c r="BP374" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="BQ374" t="n">
+        <v>69.16666666666667</v>
+      </c>
+      <c r="BR374" t="n">
+        <v>5833.333333333333</v>
+      </c>
+      <c r="BS374" t="inlineStr"/>
+      <c r="BT374" t="inlineStr"/>
+      <c r="BU374" t="inlineStr"/>
+      <c r="BV374" t="inlineStr"/>
+      <c r="BW374" t="inlineStr"/>
+      <c r="BX374" t="inlineStr"/>
+      <c r="BY374" t="inlineStr"/>
+      <c r="BZ374" t="inlineStr"/>
+      <c r="CA374" t="inlineStr"/>
+      <c r="CB374" t="inlineStr"/>
+      <c r="CC374" t="inlineStr"/>
+      <c r="CD374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>z7bN8vnR</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="n">
+        <v>45564.375</v>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzalez esteban j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi ciutat de valencia
+  valencia </t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>26354</v>
+      </c>
+      <c r="F375" t="n">
+        <v>14528</v>
+      </c>
+      <c r="G375" t="n">
+        <v>4</v>
+      </c>
+      <c r="H375" t="n">
+        <v>2</v>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr"/>
+      <c r="L375" t="inlineStr"/>
+      <c r="M375" t="n">
+        <v>46</v>
+      </c>
+      <c r="N375" t="n">
+        <v>54</v>
+      </c>
+      <c r="O375" t="n">
+        <v>13</v>
+      </c>
+      <c r="P375" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q375" t="n">
+        <v>8</v>
+      </c>
+      <c r="R375" t="n">
+        <v>4</v>
+      </c>
+      <c r="S375" t="n">
+        <v>5</v>
+      </c>
+      <c r="T375" t="n">
+        <v>9</v>
+      </c>
+      <c r="U375" t="n">
+        <v>0</v>
+      </c>
+      <c r="V375" t="n">
+        <v>4</v>
+      </c>
+      <c r="W375" t="n">
+        <v>10</v>
+      </c>
+      <c r="X375" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y375" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z375" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA375" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB375" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC375" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD375" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE375" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF375" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG375" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH375" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI375" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ375" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK375" t="inlineStr"/>
+      <c r="AL375" t="inlineStr"/>
+      <c r="AM375" t="inlineStr"/>
+      <c r="AN375" t="inlineStr"/>
+      <c r="AO375" t="inlineStr">
+        <is>
+          <t>fiZxGYJ3</t>
+        </is>
+      </c>
+      <c r="AP375" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="AQ375" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR375" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS375" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT375" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU375" t="inlineStr"/>
+      <c r="AV375" t="inlineStr"/>
+      <c r="AW375" t="inlineStr"/>
+      <c r="AX375" t="inlineStr"/>
+      <c r="AY375" t="inlineStr"/>
+      <c r="AZ375" t="inlineStr"/>
+      <c r="BA375" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="BB375" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="BC375" t="inlineStr"/>
+      <c r="BD375" t="inlineStr"/>
+      <c r="BE375" t="inlineStr"/>
+      <c r="BF375" t="inlineStr"/>
+      <c r="BG375" t="inlineStr"/>
+      <c r="BH375" t="inlineStr"/>
+      <c r="BI375" t="inlineStr"/>
+      <c r="BJ375" t="inlineStr"/>
+      <c r="BK375" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="BL375" t="n">
+        <v>177.6</v>
+      </c>
+      <c r="BM375" t="n">
+        <v>67</v>
+      </c>
+      <c r="BN375" t="inlineStr"/>
+      <c r="BO375" t="n">
+        <v>23.47368421052632</v>
+      </c>
+      <c r="BP375" t="n">
+        <v>182.8947368421053</v>
+      </c>
+      <c r="BQ375" t="n">
+        <v>69.63157894736842</v>
+      </c>
+      <c r="BR375" t="n">
+        <v>13421.05263157895</v>
+      </c>
+      <c r="BS375" t="inlineStr"/>
+      <c r="BT375" t="inlineStr"/>
+      <c r="BU375" t="inlineStr"/>
+      <c r="BV375" t="inlineStr"/>
+      <c r="BW375" t="inlineStr"/>
+      <c r="BX375" t="inlineStr"/>
+      <c r="BY375" t="inlineStr"/>
+      <c r="BZ375" t="inlineStr"/>
+      <c r="CA375" t="inlineStr"/>
+      <c r="CB375" t="inlineStr"/>
+      <c r="CC375" t="inlineStr"/>
+      <c r="CD375" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
